--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -134,7 +134,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -209,16 +209,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
@@ -259,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -294,7 +284,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -326,7 +316,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -371,25 +361,19 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -648,7 +632,7 @@
     </comment>
     <comment ref="Y7" authorId="0" shapeId="0">
       <text>
-        <t>用途：健康保険証・資格確認書の回収状況（資格喪失に伴う返却）。</t>
+        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
       </text>
     </comment>
     <comment ref="Z7" authorId="0" shapeId="0">
@@ -657,36 +641,6 @@
       </text>
     </comment>
     <comment ref="AA7" authorId="0" shapeId="0">
-      <text>
-        <t>用途：住民税の徴収方法（給与所得者異動届の区分）。</t>
-      </text>
-    </comment>
-    <comment ref="AB7" authorId="0" shapeId="0">
-      <text>
-        <t>用途：退職月からの住民税の取扱い目安。自動表示。</t>
-      </text>
-    </comment>
-    <comment ref="AC7" authorId="0" shapeId="0">
-      <text>
-        <t>用途：特別徴収を継続する場合の転職先（異動届で引継ぎ）。</t>
-      </text>
-    </comment>
-    <comment ref="AD7" authorId="0" shapeId="0">
-      <text>
-        <t>用途：給与所得者異動届の提出先市区町村（住民税の課税地）。</t>
-      </text>
-    </comment>
-    <comment ref="AE7" authorId="0" shapeId="0">
-      <text>
-        <t>用途：退職金の有無（退職所得の源泉・申告書要否の判断）。</t>
-      </text>
-    </comment>
-    <comment ref="AF7" authorId="0" shapeId="0">
-      <text>
-        <t>用途：退職所得の受給に関する申告書の受領（未提出は一律20.42%源泉）。</t>
-      </text>
-    </comment>
-    <comment ref="AG7" authorId="0" shapeId="0">
       <text>
         <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
       </text>
@@ -984,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1046,7 +1000,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>1.0（更新日 2026-09-10）</t>
+          <t>1.0（更新日 2026-09-11）</t>
         </is>
       </c>
     </row>
@@ -1058,10 +1012,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="53.5" customHeight="1">
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>退職される方の『雇用保険 資格喪失届・離職証明書』『健康保険・厚生年金 資格喪失届』『住民税の異動』の
+          <t>退職される方の『雇用保険 資格喪失届・離職証明書』『健康保険・厚生年金 資格喪失届』の
 手続きに必要な情報を回収します。このフォーム1本で手続きに着手できるよう、
 本人情報（氏名・生年月日・マイナンバー・各種番号・住所）もあわせてご記入ください。</t>
         </is>
@@ -1085,7 +1039,7 @@
     <row r="14" ht="20.5" customHeight="1">
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>2. 退職事由・雇用保険・社会保険・住民税の各項目を入力します。</t>
+          <t>2. 退職事由・雇用保険・社会保険の各項目を入力します。</t>
         </is>
       </c>
     </row>
@@ -1203,130 +1157,123 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="20.5" customHeight="1">
+    <row r="28" ht="37" customHeight="1">
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>保険証・資格確認書は本人/被扶養者分を回収のうえご返送ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="53.5" customHeight="1">
+          <t>資格確認書・高齢受給者証・限度額適用認定証などは本人/被扶養者分を回収のうえご返送ください（回収できないときは当方で回収不能届を出します）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="37" customHeight="1">
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>住民税は退職月で取扱いが変わります（1〜4月退職は原則一括徴収）。特別徴収を継続する場合は転職先情報もご記入ください。給与所得者異動届出書を、退職した翌月10日までに本人の課税市区町村へ提出します。</t>
+          <t>住民税の異動届（給与所得者異動届出書）と退職所得の受給に関する申告書は税務の手続きで、当事務所の受任範囲に含みません。貴社または顧問税理士でお手続きください。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="37" customHeight="1">
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>退職金がある場合は、本人から『退職所得の受給に関する申告書』を受領してください（未提出だと退職金に一律20.42%が源泉徴収されます）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="37" customHeight="1">
-      <c r="C31" s="5" t="inlineStr">
-        <is>
           <t>提出期限の目安：健康保険・厚生年金の資格喪失届は退職日の翌日から5日以内、雇用保険の資格喪失届・離職証明書は10日以内です。お早めにご返送ください。</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="24" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="31"/>
+    <row r="32" ht="24" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>本人情報の集め方</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="70" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
+    <row r="33" ht="70" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>本人情報は入社時と同じ内容をご記入ください。本人しか分からない項目（マイナンバー・基礎年金番号・雇用保険被保険者番号など）は、会社内で本人に確認のうえご記入ください。
 当事務所の書式「入社時 本人情報記入シート」（https://minano-sr.com/shoshiki/D-52.html）を印刷して本人に書いてもらう方法が簡単です。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20.5" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
+    <row r="34" ht="20.5" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>2名以上のとき</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>1行に1名ずつご記入ください（行を追加して複数名をまとめて送れます）。</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="35"/>
+    <row r="36" ht="24" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>マイナンバー等 機微情報の取扱い</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="53.5" customHeight="1">
+    <row r="37" ht="53.5" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>入力時</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>マイナンバー（12桁）は半角数字・ハイフン無しで入力します。会社所定の安全な経路で別提出する場合は、番号を入力せず『別経路提出』を選んでください。未回収の場合は『後日提出』を選択します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="37" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>入力時</t>
+          <t>基礎年金番号</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>マイナンバー（12桁）は半角数字・ハイフン無しで入力します。会社所定の安全な経路で別提出する場合は、番号を入力せず『別経路提出』を選んでください。未回収の場合は『後日提出』を選択します。</t>
+          <t>10桁（年金手帳・基礎年金番号通知書に記載）。不明なときはドロップダウンから『後日提出』を選べば未入力扱いになりません（分かり次第ご連絡ください）。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="37" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>基礎年金番号</t>
+          <t>雇用保険被保険者番号</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>10桁（年金手帳・基礎年金番号通知書に記載）。不明なときはドロップダウンから『後日提出』を選べば未入力扱いになりません（分かり次第ご連絡ください）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="37" customHeight="1">
+          <t>11桁（雇用保険被保険者証・離職票に記載）。前職が無い方は『なし』、番号が不明なときは『後日提出』を選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="53.5" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>雇用保険被保険者番号</t>
+          <t>返送方法</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>11桁（雇用保険被保険者証・離職票に記載）。前職が無い方は『なし』、番号が不明なときは『後日提出』を選択してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="53.5" customHeight="1">
+          <t>本ファイルはマイナンバー等の特定個人情報を含みます。メール添付で平文送付せず、①パスワード付きZIP（パスワードは別経路で連絡）、または ②当事務所が案内する安全な受け渡し方法 でご返送ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="37" customHeight="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>返送方法</t>
+          <t>社内保管</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>本ファイルはマイナンバー等の特定個人情報を含みます。メール添付で平文送付せず、①パスワード付きZIP（パスワードは別経路で連絡）、または ②当事務所が案内する安全な受け渡し方法 でご返送ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="37" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>社内保管</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>記入途中のファイルは関係者以外がアクセスできない場所に保管し、提出後は社内ルールに従って適切に削除・保管してください。</t>
         </is>
@@ -1335,8 +1282,8 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B1:C1"/>
@@ -1354,7 +1301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1588,7 +1535,7 @@
     <row r="21" ht="37" customHeight="1">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>健康保険証・資格確認書（本人・被扶養者分）</t>
+          <t>資格確認書・各認定証（本人・被扶養者分）</t>
         </is>
       </c>
       <c r="C21" s="16" t="n"/>
@@ -1598,42 +1545,16 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="37" customHeight="1">
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>住民税の異動に関する情報</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>特別徴収の継続／一括徴収／普通徴収の別。退職月により取扱いが変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="37" customHeight="1">
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>退職所得の受給に関する申告書</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>退職金がある場合のみ。未提出だと一律20.42%が源泉徴収されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="22"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>③ 当事務所への返送について</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="53.5" customHeight="1">
-      <c r="B26" s="23" t="inlineStr">
+    <row r="24" ht="53.5" customHeight="1">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>【ファイル名のつけ方】　YYYYMMDD_貴社名_対象者名_手続名_返送_v1.0.xlsx
 　例）20260710_ABC株式会社_山田太郎_退職時 受領フォーム_返送_v1.0.xlsx
@@ -1641,29 +1562,29 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="70" customHeight="1">
-      <c r="B27" s="14" t="inlineStr">
+    <row r="25" ht="70" customHeight="1">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>【ご返送方法】　マイナンバー等の重要情報を含みます。メール平文への添付は避け、当事務所の案件ページ（受任メールのリンク）からお送りください。メールに添付する場合はパスワード付きZIP（パスワードは別経路でご連絡）にしてください。マイナンバーを別経路で回収する運用の場合は、このフォームには入力せず、会社所定の安全な経路で提出してください。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20.5" customHeight="1">
-      <c r="B28" s="23" t="inlineStr">
+    <row r="26" ht="20.5" customHeight="1">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>【送付メール文（コピペ用）】　下の枠を選択してコピーし、件名・本文にお使いください。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="26" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>件名：【退職手続】退職連絡フォーム送付の件（〇〇株式会社）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="218.5" customHeight="1">
-      <c r="B30" s="27" t="inlineStr">
+    <row r="28" ht="218.5" customHeight="1">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>みなの社会保険労務士事務所
 ご担当者さま
@@ -1678,16 +1599,16 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32" ht="24" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="29"/>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>④ 入力の補足（情報が揃わないとき）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="53.5" customHeight="1">
-      <c r="B33" s="23" t="inlineStr">
+    <row r="31" ht="53.5" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>・『不明』『後日提出』を選べる欄は、空欄のままにせず状態を残してください。後で当事務所が確認・督促できます。
 ・該当しない欄は『該当なし』を選ぶか空欄で構いません（条件次第で対象外＝斜線になる欄もあります）。
@@ -1697,11 +1618,10 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B2:D2"/>
@@ -1709,6 +1629,7 @@
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B16:D16"/>
   </mergeCells>
   <conditionalFormatting sqref="C12">
@@ -1756,23 +1677,7 @@
       <formula>OR(C21="後日提出",C21="事務所で確認",C21="不明")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
-    <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
-      <formula>C22=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="13" dxfId="1" stopIfTrue="1">
-      <formula>OR(C22="後日提出",C22="事務所で確認",C22="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
-    <cfRule type="expression" priority="14" dxfId="2" stopIfTrue="1">
-      <formula>C23=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="1" stopIfTrue="1">
-      <formula>OR(C23="後日提出",C23="事務所で確認",C23="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="7">
+  <dataValidations count="5">
     <dataValidation sqref="C8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
@@ -1789,12 +1694,6 @@
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
       <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
     </dataValidation>
-    <dataValidation sqref="C22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1807,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI58"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1836,15 +1735,9 @@
     <col width="17" customWidth="1" min="24" max="24"/>
     <col width="18" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="26" customWidth="1" min="27" max="27"/>
-    <col width="34" customWidth="1" min="28" max="28"/>
-    <col width="26" customWidth="1" min="29" max="29"/>
-    <col width="24" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="36" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col width="36" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1853,9 +1746,9 @@
           <t>退職 情報</t>
         </is>
       </c>
-      <c r="Q1" s="28" t="inlineStr">
-        <is>
-          <t>※離職理由区分・住民税の取扱いは目安。最終判断は社労士。</t>
+      <c r="N1" s="28" t="inlineStr">
+        <is>
+          <t>※離職理由区分は目安。最終判断は社労士・ハローワークが行います。</t>
         </is>
       </c>
     </row>
@@ -1909,11 +1802,11 @@
         <v/>
       </c>
       <c r="C4" s="31">
-        <f>COUNTIF(AI9:AI58,0)</f>
+        <f>COUNTIF(AC9:AC58,0)</f>
         <v/>
       </c>
       <c r="E4" s="31">
-        <f>SUM(AI9:AI58)</f>
+        <f>SUM(AC9:AC58)</f>
         <v/>
       </c>
       <c r="G4" s="32">
@@ -1958,16 +1851,6 @@
       </c>
       <c r="AA6" s="38" t="inlineStr">
         <is>
-          <t>住民税</t>
-        </is>
-      </c>
-      <c r="AE6" s="39" t="inlineStr">
-        <is>
-          <t>退職金・税</t>
-        </is>
-      </c>
-      <c r="AG6" s="40" t="inlineStr">
-        <is>
           <t>その他</t>
         </is>
       </c>
@@ -2119,7 +2002,7 @@
       </c>
       <c r="Y7" s="6" t="inlineStr">
         <is>
-          <t>健康保険証の回収
+          <t>資格確認書等の回収
 【必】</t>
         </is>
       </c>
@@ -2129,199 +2012,138 @@
 【必】</t>
         </is>
       </c>
-      <c r="AA7" s="6" t="inlineStr">
-        <is>
-          <t>住民税の徴収方法（希望）
-【必】</t>
-        </is>
-      </c>
-      <c r="AB7" s="8" t="inlineStr">
-        <is>
-          <t>住民税の取扱い目安（自動）
-【自動】</t>
-        </is>
-      </c>
-      <c r="AC7" s="7" t="inlineStr">
-        <is>
-          <t>転職先（特別徴収を継続する場合）
-【任】</t>
-        </is>
-      </c>
-      <c r="AD7" s="7" t="inlineStr">
-        <is>
-          <t>課税市区町村（異動届の提出先）
-【任】</t>
-        </is>
-      </c>
-      <c r="AE7" s="7" t="inlineStr">
-        <is>
-          <t>退職金の支給予定
-【任】</t>
-        </is>
-      </c>
-      <c r="AF7" s="7" t="inlineStr">
-        <is>
-          <t>退職所得申告書の受領
-【任】</t>
-        </is>
-      </c>
-      <c r="AG7" s="7" t="inlineStr">
+      <c r="AA7" s="7" t="inlineStr">
         <is>
           <t>備考（連絡事項）
 【任】</t>
         </is>
       </c>
-      <c r="AH7" s="24" t="inlineStr">
+      <c r="AB7" s="24" t="inlineStr">
         <is>
           <t>行ステータス
 （CSV可否）</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="37" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>例</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>ヤマダ タロウ</t>
         </is>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="41" t="n">
         <v>32964</v>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>123456789012</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="F8" s="44" t="inlineStr">
+      <c r="F8" s="42" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="G8" s="44" t="inlineStr">
+      <c r="G8" s="42" t="inlineStr">
         <is>
           <t>930-0001</t>
         </is>
       </c>
-      <c r="H8" s="42" t="inlineStr">
+      <c r="H8" s="40" t="inlineStr">
         <is>
           <t>富山県</t>
         </is>
       </c>
-      <c r="I8" s="42" t="inlineStr">
+      <c r="I8" s="40" t="inlineStr">
         <is>
           <t>富山市〇〇1-2-3</t>
         </is>
       </c>
-      <c r="J8" s="42" t="inlineStr">
+      <c r="J8" s="40" t="inlineStr">
         <is>
           <t>〇〇マンション101</t>
         </is>
       </c>
-      <c r="K8" s="42" t="inlineStr">
+      <c r="K8" s="40" t="inlineStr">
         <is>
           <t>076-000-0000</t>
         </is>
       </c>
-      <c r="L8" s="43" t="n">
+      <c r="L8" s="41" t="n">
         <v>46234</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="41">
         <f>IF($L8="","",$L8+1)</f>
         <v/>
       </c>
-      <c r="N8" s="42" t="inlineStr">
+      <c r="N8" s="40" t="inlineStr">
         <is>
           <t>自己都合</t>
         </is>
       </c>
-      <c r="O8" s="42" t="inlineStr">
+      <c r="O8" s="40" t="inlineStr">
         <is>
           <t>一般（自己都合等）</t>
         </is>
       </c>
-      <c r="P8" s="42" t="inlineStr">
+      <c r="P8" s="40" t="inlineStr">
         <is>
           <t>転職のため（一身上の都合）。</t>
         </is>
       </c>
-      <c r="Q8" s="42" t="inlineStr">
+      <c r="Q8" s="40" t="inlineStr">
         <is>
           <t>該当なし（無期契約）</t>
         </is>
       </c>
-      <c r="R8" s="42" t="inlineStr">
+      <c r="R8" s="40" t="inlineStr">
         <is>
           <t>該当なし</t>
         </is>
       </c>
-      <c r="S8" s="42" t="inlineStr">
+      <c r="S8" s="40" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="T8" s="42" t="n"/>
-      <c r="U8" s="42" t="inlineStr">
+      <c r="T8" s="40" t="n"/>
+      <c r="U8" s="40" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="V8" s="42" t="inlineStr">
+      <c r="V8" s="40" t="inlineStr">
         <is>
           <t>毎月末日</t>
         </is>
       </c>
-      <c r="W8" s="45" t="n">
+      <c r="W8" s="43" t="n">
         <v>300000</v>
       </c>
-      <c r="X8" s="45" t="n">
+      <c r="X8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" s="42" t="inlineStr">
+      <c r="Y8" s="40" t="inlineStr">
         <is>
           <t>回収済</t>
         </is>
       </c>
-      <c r="Z8" s="42" t="inlineStr">
+      <c r="Z8" s="40" t="inlineStr">
         <is>
           <t>家族の扶養に入る</t>
         </is>
       </c>
-      <c r="AA8" s="42" t="inlineStr">
-        <is>
-          <t>普通徴収へ切替（自分で納付）</t>
-        </is>
-      </c>
-      <c r="AB8" s="42">
-        <f>IF($L8="","",IF(MONTH($L8)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L8)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="42" t="n"/>
-      <c r="AD8" s="42" t="inlineStr">
-        <is>
-          <t>千代田区</t>
-        </is>
-      </c>
-      <c r="AE8" s="42" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="AF8" s="42" t="inlineStr">
-        <is>
-          <t>該当なし</t>
-        </is>
-      </c>
-      <c r="AG8" s="42" t="inlineStr">
+      <c r="AA8" s="40" t="inlineStr">
         <is>
           <t>← この行は記入例です（編集不可）</t>
         </is>
@@ -2331,16 +2153,16 @@
       <c r="A9" s="16" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="18" t="n"/>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="46" t="n"/>
-      <c r="F9" s="46" t="n"/>
-      <c r="G9" s="46" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
       <c r="H9" s="16" t="n"/>
       <c r="I9" s="16" t="n"/>
       <c r="J9" s="16" t="n"/>
       <c r="K9" s="16" t="n"/>
       <c r="L9" s="18" t="n"/>
-      <c r="M9" s="47">
+      <c r="M9" s="45">
         <f>IF($L9="","",$L9+1)</f>
         <v/>
       </c>
@@ -2353,26 +2175,17 @@
       <c r="T9" s="16" t="n"/>
       <c r="U9" s="16" t="n"/>
       <c r="V9" s="16" t="n"/>
-      <c r="W9" s="48" t="n"/>
-      <c r="X9" s="48" t="n"/>
+      <c r="W9" s="46" t="n"/>
+      <c r="X9" s="46" t="n"/>
       <c r="Y9" s="16" t="n"/>
       <c r="Z9" s="16" t="n"/>
       <c r="AA9" s="16" t="n"/>
-      <c r="AB9" s="22">
-        <f>IF($L9="","",IF(MONTH($L9)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L9)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="16" t="n"/>
-      <c r="AD9" s="16" t="n"/>
-      <c r="AE9" s="16" t="n"/>
-      <c r="AF9" s="16" t="n"/>
-      <c r="AG9" s="16" t="n"/>
-      <c r="AH9" s="49">
-        <f>IF($A9="","",IF(AI9&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI9">
-        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($O9="",1,0)+IF($P9="",1,0)+IF($S9="",1,0)+IF($U9="",1,0)+IF($Y9="",1,0)+IF($Z9="",1,0)+IF($AA9="",1,0)+IF(AND($AA9="特別徴収を継続（転職先へ引継ぎ）",$AC9=""),1,0)+IF(AND($N9="契約期間満了",$Q9=""),1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0))</f>
+      <c r="AB9" s="47">
+        <f>IF($A9="","",IF(AC9&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($O9="",1,0)+IF($P9="",1,0)+IF($S9="",1,0)+IF($U9="",1,0)+IF($Y9="",1,0)+IF($Z9="",1,0)+IF(AND($N9="契約期間満了",$Q9=""),1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2380,16 +2193,16 @@
       <c r="A10" s="16" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="18" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="46" t="n"/>
-      <c r="F10" s="46" t="n"/>
-      <c r="G10" s="46" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
       <c r="H10" s="16" t="n"/>
       <c r="I10" s="16" t="n"/>
       <c r="J10" s="16" t="n"/>
       <c r="K10" s="16" t="n"/>
       <c r="L10" s="18" t="n"/>
-      <c r="M10" s="47">
+      <c r="M10" s="45">
         <f>IF($L10="","",$L10+1)</f>
         <v/>
       </c>
@@ -2402,26 +2215,17 @@
       <c r="T10" s="16" t="n"/>
       <c r="U10" s="16" t="n"/>
       <c r="V10" s="16" t="n"/>
-      <c r="W10" s="48" t="n"/>
-      <c r="X10" s="48" t="n"/>
+      <c r="W10" s="46" t="n"/>
+      <c r="X10" s="46" t="n"/>
       <c r="Y10" s="16" t="n"/>
       <c r="Z10" s="16" t="n"/>
       <c r="AA10" s="16" t="n"/>
-      <c r="AB10" s="22">
-        <f>IF($L10="","",IF(MONTH($L10)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L10)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC10" s="16" t="n"/>
-      <c r="AD10" s="16" t="n"/>
-      <c r="AE10" s="16" t="n"/>
-      <c r="AF10" s="16" t="n"/>
-      <c r="AG10" s="16" t="n"/>
-      <c r="AH10" s="49">
-        <f>IF($A10="","",IF(AI10&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI10">
-        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($O10="",1,0)+IF($P10="",1,0)+IF($S10="",1,0)+IF($U10="",1,0)+IF($Y10="",1,0)+IF($Z10="",1,0)+IF($AA10="",1,0)+IF(AND($AA10="特別徴収を継続（転職先へ引継ぎ）",$AC10=""),1,0)+IF(AND($N10="契約期間満了",$Q10=""),1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0))</f>
+      <c r="AB10" s="47">
+        <f>IF($A10="","",IF(AC10&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($O10="",1,0)+IF($P10="",1,0)+IF($S10="",1,0)+IF($U10="",1,0)+IF($Y10="",1,0)+IF($Z10="",1,0)+IF(AND($N10="契約期間満了",$Q10=""),1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2429,16 +2233,16 @@
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="18" t="n"/>
-      <c r="D11" s="46" t="n"/>
-      <c r="E11" s="46" t="n"/>
-      <c r="F11" s="46" t="n"/>
-      <c r="G11" s="46" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="44" t="n"/>
       <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="n"/>
       <c r="J11" s="16" t="n"/>
       <c r="K11" s="16" t="n"/>
       <c r="L11" s="18" t="n"/>
-      <c r="M11" s="47">
+      <c r="M11" s="45">
         <f>IF($L11="","",$L11+1)</f>
         <v/>
       </c>
@@ -2451,26 +2255,17 @@
       <c r="T11" s="16" t="n"/>
       <c r="U11" s="16" t="n"/>
       <c r="V11" s="16" t="n"/>
-      <c r="W11" s="48" t="n"/>
-      <c r="X11" s="48" t="n"/>
+      <c r="W11" s="46" t="n"/>
+      <c r="X11" s="46" t="n"/>
       <c r="Y11" s="16" t="n"/>
       <c r="Z11" s="16" t="n"/>
       <c r="AA11" s="16" t="n"/>
-      <c r="AB11" s="22">
-        <f>IF($L11="","",IF(MONTH($L11)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L11)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC11" s="16" t="n"/>
-      <c r="AD11" s="16" t="n"/>
-      <c r="AE11" s="16" t="n"/>
-      <c r="AF11" s="16" t="n"/>
-      <c r="AG11" s="16" t="n"/>
-      <c r="AH11" s="49">
-        <f>IF($A11="","",IF(AI11&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI11">
-        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($O11="",1,0)+IF($P11="",1,0)+IF($S11="",1,0)+IF($U11="",1,0)+IF($Y11="",1,0)+IF($Z11="",1,0)+IF($AA11="",1,0)+IF(AND($AA11="特別徴収を継続（転職先へ引継ぎ）",$AC11=""),1,0)+IF(AND($N11="契約期間満了",$Q11=""),1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0))</f>
+      <c r="AB11" s="47">
+        <f>IF($A11="","",IF(AC11&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($O11="",1,0)+IF($P11="",1,0)+IF($S11="",1,0)+IF($U11="",1,0)+IF($Y11="",1,0)+IF($Z11="",1,0)+IF(AND($N11="契約期間満了",$Q11=""),1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2478,16 +2273,16 @@
       <c r="A12" s="16" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="18" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="44" t="n"/>
       <c r="H12" s="16" t="n"/>
       <c r="I12" s="16" t="n"/>
       <c r="J12" s="16" t="n"/>
       <c r="K12" s="16" t="n"/>
       <c r="L12" s="18" t="n"/>
-      <c r="M12" s="47">
+      <c r="M12" s="45">
         <f>IF($L12="","",$L12+1)</f>
         <v/>
       </c>
@@ -2500,26 +2295,17 @@
       <c r="T12" s="16" t="n"/>
       <c r="U12" s="16" t="n"/>
       <c r="V12" s="16" t="n"/>
-      <c r="W12" s="48" t="n"/>
-      <c r="X12" s="48" t="n"/>
+      <c r="W12" s="46" t="n"/>
+      <c r="X12" s="46" t="n"/>
       <c r="Y12" s="16" t="n"/>
       <c r="Z12" s="16" t="n"/>
       <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="22">
-        <f>IF($L12="","",IF(MONTH($L12)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L12)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC12" s="16" t="n"/>
-      <c r="AD12" s="16" t="n"/>
-      <c r="AE12" s="16" t="n"/>
-      <c r="AF12" s="16" t="n"/>
-      <c r="AG12" s="16" t="n"/>
-      <c r="AH12" s="49">
-        <f>IF($A12="","",IF(AI12&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI12">
-        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($O12="",1,0)+IF($P12="",1,0)+IF($S12="",1,0)+IF($U12="",1,0)+IF($Y12="",1,0)+IF($Z12="",1,0)+IF($AA12="",1,0)+IF(AND($AA12="特別徴収を継続（転職先へ引継ぎ）",$AC12=""),1,0)+IF(AND($N12="契約期間満了",$Q12=""),1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0))</f>
+      <c r="AB12" s="47">
+        <f>IF($A12="","",IF(AC12&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($O12="",1,0)+IF($P12="",1,0)+IF($S12="",1,0)+IF($U12="",1,0)+IF($Y12="",1,0)+IF($Z12="",1,0)+IF(AND($N12="契約期間満了",$Q12=""),1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2527,16 +2313,16 @@
       <c r="A13" s="16" t="n"/>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="18" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
       <c r="H13" s="16" t="n"/>
       <c r="I13" s="16" t="n"/>
       <c r="J13" s="16" t="n"/>
       <c r="K13" s="16" t="n"/>
       <c r="L13" s="18" t="n"/>
-      <c r="M13" s="47">
+      <c r="M13" s="45">
         <f>IF($L13="","",$L13+1)</f>
         <v/>
       </c>
@@ -2549,26 +2335,17 @@
       <c r="T13" s="16" t="n"/>
       <c r="U13" s="16" t="n"/>
       <c r="V13" s="16" t="n"/>
-      <c r="W13" s="48" t="n"/>
-      <c r="X13" s="48" t="n"/>
+      <c r="W13" s="46" t="n"/>
+      <c r="X13" s="46" t="n"/>
       <c r="Y13" s="16" t="n"/>
       <c r="Z13" s="16" t="n"/>
       <c r="AA13" s="16" t="n"/>
-      <c r="AB13" s="22">
-        <f>IF($L13="","",IF(MONTH($L13)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L13)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC13" s="16" t="n"/>
-      <c r="AD13" s="16" t="n"/>
-      <c r="AE13" s="16" t="n"/>
-      <c r="AF13" s="16" t="n"/>
-      <c r="AG13" s="16" t="n"/>
-      <c r="AH13" s="49">
-        <f>IF($A13="","",IF(AI13&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI13">
-        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($O13="",1,0)+IF($P13="",1,0)+IF($S13="",1,0)+IF($U13="",1,0)+IF($Y13="",1,0)+IF($Z13="",1,0)+IF($AA13="",1,0)+IF(AND($AA13="特別徴収を継続（転職先へ引継ぎ）",$AC13=""),1,0)+IF(AND($N13="契約期間満了",$Q13=""),1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0))</f>
+      <c r="AB13" s="47">
+        <f>IF($A13="","",IF(AC13&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($O13="",1,0)+IF($P13="",1,0)+IF($S13="",1,0)+IF($U13="",1,0)+IF($Y13="",1,0)+IF($Z13="",1,0)+IF(AND($N13="契約期間満了",$Q13=""),1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2576,16 +2353,16 @@
       <c r="A14" s="16" t="n"/>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="18" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n"/>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="18" t="n"/>
-      <c r="M14" s="47">
+      <c r="M14" s="45">
         <f>IF($L14="","",$L14+1)</f>
         <v/>
       </c>
@@ -2598,26 +2375,17 @@
       <c r="T14" s="16" t="n"/>
       <c r="U14" s="16" t="n"/>
       <c r="V14" s="16" t="n"/>
-      <c r="W14" s="48" t="n"/>
-      <c r="X14" s="48" t="n"/>
+      <c r="W14" s="46" t="n"/>
+      <c r="X14" s="46" t="n"/>
       <c r="Y14" s="16" t="n"/>
       <c r="Z14" s="16" t="n"/>
       <c r="AA14" s="16" t="n"/>
-      <c r="AB14" s="22">
-        <f>IF($L14="","",IF(MONTH($L14)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L14)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC14" s="16" t="n"/>
-      <c r="AD14" s="16" t="n"/>
-      <c r="AE14" s="16" t="n"/>
-      <c r="AF14" s="16" t="n"/>
-      <c r="AG14" s="16" t="n"/>
-      <c r="AH14" s="49">
-        <f>IF($A14="","",IF(AI14&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI14">
-        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($O14="",1,0)+IF($P14="",1,0)+IF($S14="",1,0)+IF($U14="",1,0)+IF($Y14="",1,0)+IF($Z14="",1,0)+IF($AA14="",1,0)+IF(AND($AA14="特別徴収を継続（転職先へ引継ぎ）",$AC14=""),1,0)+IF(AND($N14="契約期間満了",$Q14=""),1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0))</f>
+      <c r="AB14" s="47">
+        <f>IF($A14="","",IF(AC14&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($O14="",1,0)+IF($P14="",1,0)+IF($S14="",1,0)+IF($U14="",1,0)+IF($Y14="",1,0)+IF($Z14="",1,0)+IF(AND($N14="契約期間満了",$Q14=""),1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2625,16 +2393,16 @@
       <c r="A15" s="16" t="n"/>
       <c r="B15" s="16" t="n"/>
       <c r="C15" s="18" t="n"/>
-      <c r="D15" s="46" t="n"/>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
       <c r="H15" s="16" t="n"/>
       <c r="I15" s="16" t="n"/>
       <c r="J15" s="16" t="n"/>
       <c r="K15" s="16" t="n"/>
       <c r="L15" s="18" t="n"/>
-      <c r="M15" s="47">
+      <c r="M15" s="45">
         <f>IF($L15="","",$L15+1)</f>
         <v/>
       </c>
@@ -2647,26 +2415,17 @@
       <c r="T15" s="16" t="n"/>
       <c r="U15" s="16" t="n"/>
       <c r="V15" s="16" t="n"/>
-      <c r="W15" s="48" t="n"/>
-      <c r="X15" s="48" t="n"/>
+      <c r="W15" s="46" t="n"/>
+      <c r="X15" s="46" t="n"/>
       <c r="Y15" s="16" t="n"/>
       <c r="Z15" s="16" t="n"/>
       <c r="AA15" s="16" t="n"/>
-      <c r="AB15" s="22">
-        <f>IF($L15="","",IF(MONTH($L15)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L15)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC15" s="16" t="n"/>
-      <c r="AD15" s="16" t="n"/>
-      <c r="AE15" s="16" t="n"/>
-      <c r="AF15" s="16" t="n"/>
-      <c r="AG15" s="16" t="n"/>
-      <c r="AH15" s="49">
-        <f>IF($A15="","",IF(AI15&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI15">
-        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($O15="",1,0)+IF($P15="",1,0)+IF($S15="",1,0)+IF($U15="",1,0)+IF($Y15="",1,0)+IF($Z15="",1,0)+IF($AA15="",1,0)+IF(AND($AA15="特別徴収を継続（転職先へ引継ぎ）",$AC15=""),1,0)+IF(AND($N15="契約期間満了",$Q15=""),1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0))</f>
+      <c r="AB15" s="47">
+        <f>IF($A15="","",IF(AC15&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($O15="",1,0)+IF($P15="",1,0)+IF($S15="",1,0)+IF($U15="",1,0)+IF($Y15="",1,0)+IF($Z15="",1,0)+IF(AND($N15="契約期間満了",$Q15=""),1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2674,16 +2433,16 @@
       <c r="A16" s="16" t="n"/>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="18" t="n"/>
-      <c r="D16" s="46" t="n"/>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="44" t="n"/>
       <c r="H16" s="16" t="n"/>
       <c r="I16" s="16" t="n"/>
       <c r="J16" s="16" t="n"/>
       <c r="K16" s="16" t="n"/>
       <c r="L16" s="18" t="n"/>
-      <c r="M16" s="47">
+      <c r="M16" s="45">
         <f>IF($L16="","",$L16+1)</f>
         <v/>
       </c>
@@ -2696,26 +2455,17 @@
       <c r="T16" s="16" t="n"/>
       <c r="U16" s="16" t="n"/>
       <c r="V16" s="16" t="n"/>
-      <c r="W16" s="48" t="n"/>
-      <c r="X16" s="48" t="n"/>
+      <c r="W16" s="46" t="n"/>
+      <c r="X16" s="46" t="n"/>
       <c r="Y16" s="16" t="n"/>
       <c r="Z16" s="16" t="n"/>
       <c r="AA16" s="16" t="n"/>
-      <c r="AB16" s="22">
-        <f>IF($L16="","",IF(MONTH($L16)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L16)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC16" s="16" t="n"/>
-      <c r="AD16" s="16" t="n"/>
-      <c r="AE16" s="16" t="n"/>
-      <c r="AF16" s="16" t="n"/>
-      <c r="AG16" s="16" t="n"/>
-      <c r="AH16" s="49">
-        <f>IF($A16="","",IF(AI16&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI16">
-        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($O16="",1,0)+IF($P16="",1,0)+IF($S16="",1,0)+IF($U16="",1,0)+IF($Y16="",1,0)+IF($Z16="",1,0)+IF($AA16="",1,0)+IF(AND($AA16="特別徴収を継続（転職先へ引継ぎ）",$AC16=""),1,0)+IF(AND($N16="契約期間満了",$Q16=""),1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0))</f>
+      <c r="AB16" s="47">
+        <f>IF($A16="","",IF(AC16&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($O16="",1,0)+IF($P16="",1,0)+IF($S16="",1,0)+IF($U16="",1,0)+IF($Y16="",1,0)+IF($Z16="",1,0)+IF(AND($N16="契約期間満了",$Q16=""),1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2723,16 +2473,16 @@
       <c r="A17" s="16" t="n"/>
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="18" t="n"/>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
       <c r="H17" s="16" t="n"/>
       <c r="I17" s="16" t="n"/>
       <c r="J17" s="16" t="n"/>
       <c r="K17" s="16" t="n"/>
       <c r="L17" s="18" t="n"/>
-      <c r="M17" s="47">
+      <c r="M17" s="45">
         <f>IF($L17="","",$L17+1)</f>
         <v/>
       </c>
@@ -2745,26 +2495,17 @@
       <c r="T17" s="16" t="n"/>
       <c r="U17" s="16" t="n"/>
       <c r="V17" s="16" t="n"/>
-      <c r="W17" s="48" t="n"/>
-      <c r="X17" s="48" t="n"/>
+      <c r="W17" s="46" t="n"/>
+      <c r="X17" s="46" t="n"/>
       <c r="Y17" s="16" t="n"/>
       <c r="Z17" s="16" t="n"/>
       <c r="AA17" s="16" t="n"/>
-      <c r="AB17" s="22">
-        <f>IF($L17="","",IF(MONTH($L17)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L17)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC17" s="16" t="n"/>
-      <c r="AD17" s="16" t="n"/>
-      <c r="AE17" s="16" t="n"/>
-      <c r="AF17" s="16" t="n"/>
-      <c r="AG17" s="16" t="n"/>
-      <c r="AH17" s="49">
-        <f>IF($A17="","",IF(AI17&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI17">
-        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($O17="",1,0)+IF($P17="",1,0)+IF($S17="",1,0)+IF($U17="",1,0)+IF($Y17="",1,0)+IF($Z17="",1,0)+IF($AA17="",1,0)+IF(AND($AA17="特別徴収を継続（転職先へ引継ぎ）",$AC17=""),1,0)+IF(AND($N17="契約期間満了",$Q17=""),1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0))</f>
+      <c r="AB17" s="47">
+        <f>IF($A17="","",IF(AC17&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($O17="",1,0)+IF($P17="",1,0)+IF($S17="",1,0)+IF($U17="",1,0)+IF($Y17="",1,0)+IF($Z17="",1,0)+IF(AND($N17="契約期間満了",$Q17=""),1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2772,16 +2513,16 @@
       <c r="A18" s="16" t="n"/>
       <c r="B18" s="16" t="n"/>
       <c r="C18" s="18" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
       <c r="H18" s="16" t="n"/>
       <c r="I18" s="16" t="n"/>
       <c r="J18" s="16" t="n"/>
       <c r="K18" s="16" t="n"/>
       <c r="L18" s="18" t="n"/>
-      <c r="M18" s="47">
+      <c r="M18" s="45">
         <f>IF($L18="","",$L18+1)</f>
         <v/>
       </c>
@@ -2794,26 +2535,17 @@
       <c r="T18" s="16" t="n"/>
       <c r="U18" s="16" t="n"/>
       <c r="V18" s="16" t="n"/>
-      <c r="W18" s="48" t="n"/>
-      <c r="X18" s="48" t="n"/>
+      <c r="W18" s="46" t="n"/>
+      <c r="X18" s="46" t="n"/>
       <c r="Y18" s="16" t="n"/>
       <c r="Z18" s="16" t="n"/>
       <c r="AA18" s="16" t="n"/>
-      <c r="AB18" s="22">
-        <f>IF($L18="","",IF(MONTH($L18)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L18)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC18" s="16" t="n"/>
-      <c r="AD18" s="16" t="n"/>
-      <c r="AE18" s="16" t="n"/>
-      <c r="AF18" s="16" t="n"/>
-      <c r="AG18" s="16" t="n"/>
-      <c r="AH18" s="49">
-        <f>IF($A18="","",IF(AI18&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI18">
-        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($O18="",1,0)+IF($P18="",1,0)+IF($S18="",1,0)+IF($U18="",1,0)+IF($Y18="",1,0)+IF($Z18="",1,0)+IF($AA18="",1,0)+IF(AND($AA18="特別徴収を継続（転職先へ引継ぎ）",$AC18=""),1,0)+IF(AND($N18="契約期間満了",$Q18=""),1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0))</f>
+      <c r="AB18" s="47">
+        <f>IF($A18="","",IF(AC18&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($O18="",1,0)+IF($P18="",1,0)+IF($S18="",1,0)+IF($U18="",1,0)+IF($Y18="",1,0)+IF($Z18="",1,0)+IF(AND($N18="契約期間満了",$Q18=""),1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2821,16 +2553,16 @@
       <c r="A19" s="16" t="n"/>
       <c r="B19" s="16" t="n"/>
       <c r="C19" s="18" t="n"/>
-      <c r="D19" s="46" t="n"/>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+      <c r="F19" s="44" t="n"/>
+      <c r="G19" s="44" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n"/>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="18" t="n"/>
-      <c r="M19" s="47">
+      <c r="M19" s="45">
         <f>IF($L19="","",$L19+1)</f>
         <v/>
       </c>
@@ -2843,26 +2575,17 @@
       <c r="T19" s="16" t="n"/>
       <c r="U19" s="16" t="n"/>
       <c r="V19" s="16" t="n"/>
-      <c r="W19" s="48" t="n"/>
-      <c r="X19" s="48" t="n"/>
+      <c r="W19" s="46" t="n"/>
+      <c r="X19" s="46" t="n"/>
       <c r="Y19" s="16" t="n"/>
       <c r="Z19" s="16" t="n"/>
       <c r="AA19" s="16" t="n"/>
-      <c r="AB19" s="22">
-        <f>IF($L19="","",IF(MONTH($L19)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L19)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC19" s="16" t="n"/>
-      <c r="AD19" s="16" t="n"/>
-      <c r="AE19" s="16" t="n"/>
-      <c r="AF19" s="16" t="n"/>
-      <c r="AG19" s="16" t="n"/>
-      <c r="AH19" s="49">
-        <f>IF($A19="","",IF(AI19&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI19">
-        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($O19="",1,0)+IF($P19="",1,0)+IF($S19="",1,0)+IF($U19="",1,0)+IF($Y19="",1,0)+IF($Z19="",1,0)+IF($AA19="",1,0)+IF(AND($AA19="特別徴収を継続（転職先へ引継ぎ）",$AC19=""),1,0)+IF(AND($N19="契約期間満了",$Q19=""),1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0))</f>
+      <c r="AB19" s="47">
+        <f>IF($A19="","",IF(AC19&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($O19="",1,0)+IF($P19="",1,0)+IF($S19="",1,0)+IF($U19="",1,0)+IF($Y19="",1,0)+IF($Z19="",1,0)+IF(AND($N19="契約期間満了",$Q19=""),1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2870,16 +2593,16 @@
       <c r="A20" s="16" t="n"/>
       <c r="B20" s="16" t="n"/>
       <c r="C20" s="18" t="n"/>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+      <c r="F20" s="44" t="n"/>
+      <c r="G20" s="44" t="n"/>
       <c r="H20" s="16" t="n"/>
       <c r="I20" s="16" t="n"/>
       <c r="J20" s="16" t="n"/>
       <c r="K20" s="16" t="n"/>
       <c r="L20" s="18" t="n"/>
-      <c r="M20" s="47">
+      <c r="M20" s="45">
         <f>IF($L20="","",$L20+1)</f>
         <v/>
       </c>
@@ -2892,26 +2615,17 @@
       <c r="T20" s="16" t="n"/>
       <c r="U20" s="16" t="n"/>
       <c r="V20" s="16" t="n"/>
-      <c r="W20" s="48" t="n"/>
-      <c r="X20" s="48" t="n"/>
+      <c r="W20" s="46" t="n"/>
+      <c r="X20" s="46" t="n"/>
       <c r="Y20" s="16" t="n"/>
       <c r="Z20" s="16" t="n"/>
       <c r="AA20" s="16" t="n"/>
-      <c r="AB20" s="22">
-        <f>IF($L20="","",IF(MONTH($L20)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L20)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC20" s="16" t="n"/>
-      <c r="AD20" s="16" t="n"/>
-      <c r="AE20" s="16" t="n"/>
-      <c r="AF20" s="16" t="n"/>
-      <c r="AG20" s="16" t="n"/>
-      <c r="AH20" s="49">
-        <f>IF($A20="","",IF(AI20&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI20">
-        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($O20="",1,0)+IF($P20="",1,0)+IF($S20="",1,0)+IF($U20="",1,0)+IF($Y20="",1,0)+IF($Z20="",1,0)+IF($AA20="",1,0)+IF(AND($AA20="特別徴収を継続（転職先へ引継ぎ）",$AC20=""),1,0)+IF(AND($N20="契約期間満了",$Q20=""),1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0))</f>
+      <c r="AB20" s="47">
+        <f>IF($A20="","",IF(AC20&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($O20="",1,0)+IF($P20="",1,0)+IF($S20="",1,0)+IF($U20="",1,0)+IF($Y20="",1,0)+IF($Z20="",1,0)+IF(AND($N20="契約期間満了",$Q20=""),1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2919,16 +2633,16 @@
       <c r="A21" s="16" t="n"/>
       <c r="B21" s="16" t="n"/>
       <c r="C21" s="18" t="n"/>
-      <c r="D21" s="46" t="n"/>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="44" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n"/>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="18" t="n"/>
-      <c r="M21" s="47">
+      <c r="M21" s="45">
         <f>IF($L21="","",$L21+1)</f>
         <v/>
       </c>
@@ -2941,26 +2655,17 @@
       <c r="T21" s="16" t="n"/>
       <c r="U21" s="16" t="n"/>
       <c r="V21" s="16" t="n"/>
-      <c r="W21" s="48" t="n"/>
-      <c r="X21" s="48" t="n"/>
+      <c r="W21" s="46" t="n"/>
+      <c r="X21" s="46" t="n"/>
       <c r="Y21" s="16" t="n"/>
       <c r="Z21" s="16" t="n"/>
       <c r="AA21" s="16" t="n"/>
-      <c r="AB21" s="22">
-        <f>IF($L21="","",IF(MONTH($L21)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L21)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC21" s="16" t="n"/>
-      <c r="AD21" s="16" t="n"/>
-      <c r="AE21" s="16" t="n"/>
-      <c r="AF21" s="16" t="n"/>
-      <c r="AG21" s="16" t="n"/>
-      <c r="AH21" s="49">
-        <f>IF($A21="","",IF(AI21&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI21">
-        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($O21="",1,0)+IF($P21="",1,0)+IF($S21="",1,0)+IF($U21="",1,0)+IF($Y21="",1,0)+IF($Z21="",1,0)+IF($AA21="",1,0)+IF(AND($AA21="特別徴収を継続（転職先へ引継ぎ）",$AC21=""),1,0)+IF(AND($N21="契約期間満了",$Q21=""),1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0))</f>
+      <c r="AB21" s="47">
+        <f>IF($A21="","",IF(AC21&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($O21="",1,0)+IF($P21="",1,0)+IF($S21="",1,0)+IF($U21="",1,0)+IF($Y21="",1,0)+IF($Z21="",1,0)+IF(AND($N21="契約期間満了",$Q21=""),1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2968,16 +2673,16 @@
       <c r="A22" s="16" t="n"/>
       <c r="B22" s="16" t="n"/>
       <c r="C22" s="18" t="n"/>
-      <c r="D22" s="46" t="n"/>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+      <c r="F22" s="44" t="n"/>
+      <c r="G22" s="44" t="n"/>
       <c r="H22" s="16" t="n"/>
       <c r="I22" s="16" t="n"/>
       <c r="J22" s="16" t="n"/>
       <c r="K22" s="16" t="n"/>
       <c r="L22" s="18" t="n"/>
-      <c r="M22" s="47">
+      <c r="M22" s="45">
         <f>IF($L22="","",$L22+1)</f>
         <v/>
       </c>
@@ -2990,26 +2695,17 @@
       <c r="T22" s="16" t="n"/>
       <c r="U22" s="16" t="n"/>
       <c r="V22" s="16" t="n"/>
-      <c r="W22" s="48" t="n"/>
-      <c r="X22" s="48" t="n"/>
+      <c r="W22" s="46" t="n"/>
+      <c r="X22" s="46" t="n"/>
       <c r="Y22" s="16" t="n"/>
       <c r="Z22" s="16" t="n"/>
       <c r="AA22" s="16" t="n"/>
-      <c r="AB22" s="22">
-        <f>IF($L22="","",IF(MONTH($L22)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L22)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC22" s="16" t="n"/>
-      <c r="AD22" s="16" t="n"/>
-      <c r="AE22" s="16" t="n"/>
-      <c r="AF22" s="16" t="n"/>
-      <c r="AG22" s="16" t="n"/>
-      <c r="AH22" s="49">
-        <f>IF($A22="","",IF(AI22&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI22">
-        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($O22="",1,0)+IF($P22="",1,0)+IF($S22="",1,0)+IF($U22="",1,0)+IF($Y22="",1,0)+IF($Z22="",1,0)+IF($AA22="",1,0)+IF(AND($AA22="特別徴収を継続（転職先へ引継ぎ）",$AC22=""),1,0)+IF(AND($N22="契約期間満了",$Q22=""),1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0))</f>
+      <c r="AB22" s="47">
+        <f>IF($A22="","",IF(AC22&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($O22="",1,0)+IF($P22="",1,0)+IF($S22="",1,0)+IF($U22="",1,0)+IF($Y22="",1,0)+IF($Z22="",1,0)+IF(AND($N22="契約期間満了",$Q22=""),1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3017,16 +2713,16 @@
       <c r="A23" s="16" t="n"/>
       <c r="B23" s="16" t="n"/>
       <c r="C23" s="18" t="n"/>
-      <c r="D23" s="46" t="n"/>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="44" t="n"/>
+      <c r="F23" s="44" t="n"/>
+      <c r="G23" s="44" t="n"/>
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="16" t="n"/>
       <c r="J23" s="16" t="n"/>
       <c r="K23" s="16" t="n"/>
       <c r="L23" s="18" t="n"/>
-      <c r="M23" s="47">
+      <c r="M23" s="45">
         <f>IF($L23="","",$L23+1)</f>
         <v/>
       </c>
@@ -3039,26 +2735,17 @@
       <c r="T23" s="16" t="n"/>
       <c r="U23" s="16" t="n"/>
       <c r="V23" s="16" t="n"/>
-      <c r="W23" s="48" t="n"/>
-      <c r="X23" s="48" t="n"/>
+      <c r="W23" s="46" t="n"/>
+      <c r="X23" s="46" t="n"/>
       <c r="Y23" s="16" t="n"/>
       <c r="Z23" s="16" t="n"/>
       <c r="AA23" s="16" t="n"/>
-      <c r="AB23" s="22">
-        <f>IF($L23="","",IF(MONTH($L23)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L23)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC23" s="16" t="n"/>
-      <c r="AD23" s="16" t="n"/>
-      <c r="AE23" s="16" t="n"/>
-      <c r="AF23" s="16" t="n"/>
-      <c r="AG23" s="16" t="n"/>
-      <c r="AH23" s="49">
-        <f>IF($A23="","",IF(AI23&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI23">
-        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($O23="",1,0)+IF($P23="",1,0)+IF($S23="",1,0)+IF($U23="",1,0)+IF($Y23="",1,0)+IF($Z23="",1,0)+IF($AA23="",1,0)+IF(AND($AA23="特別徴収を継続（転職先へ引継ぎ）",$AC23=""),1,0)+IF(AND($N23="契約期間満了",$Q23=""),1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0))</f>
+      <c r="AB23" s="47">
+        <f>IF($A23="","",IF(AC23&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($O23="",1,0)+IF($P23="",1,0)+IF($S23="",1,0)+IF($U23="",1,0)+IF($Y23="",1,0)+IF($Z23="",1,0)+IF(AND($N23="契約期間満了",$Q23=""),1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3066,16 +2753,16 @@
       <c r="A24" s="16" t="n"/>
       <c r="B24" s="16" t="n"/>
       <c r="C24" s="18" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n"/>
+      <c r="D24" s="44" t="n"/>
+      <c r="E24" s="44" t="n"/>
+      <c r="F24" s="44" t="n"/>
+      <c r="G24" s="44" t="n"/>
       <c r="H24" s="16" t="n"/>
       <c r="I24" s="16" t="n"/>
       <c r="J24" s="16" t="n"/>
       <c r="K24" s="16" t="n"/>
       <c r="L24" s="18" t="n"/>
-      <c r="M24" s="47">
+      <c r="M24" s="45">
         <f>IF($L24="","",$L24+1)</f>
         <v/>
       </c>
@@ -3088,26 +2775,17 @@
       <c r="T24" s="16" t="n"/>
       <c r="U24" s="16" t="n"/>
       <c r="V24" s="16" t="n"/>
-      <c r="W24" s="48" t="n"/>
-      <c r="X24" s="48" t="n"/>
+      <c r="W24" s="46" t="n"/>
+      <c r="X24" s="46" t="n"/>
       <c r="Y24" s="16" t="n"/>
       <c r="Z24" s="16" t="n"/>
       <c r="AA24" s="16" t="n"/>
-      <c r="AB24" s="22">
-        <f>IF($L24="","",IF(MONTH($L24)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L24)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC24" s="16" t="n"/>
-      <c r="AD24" s="16" t="n"/>
-      <c r="AE24" s="16" t="n"/>
-      <c r="AF24" s="16" t="n"/>
-      <c r="AG24" s="16" t="n"/>
-      <c r="AH24" s="49">
-        <f>IF($A24="","",IF(AI24&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI24">
-        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($O24="",1,0)+IF($P24="",1,0)+IF($S24="",1,0)+IF($U24="",1,0)+IF($Y24="",1,0)+IF($Z24="",1,0)+IF($AA24="",1,0)+IF(AND($AA24="特別徴収を継続（転職先へ引継ぎ）",$AC24=""),1,0)+IF(AND($N24="契約期間満了",$Q24=""),1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0))</f>
+      <c r="AB24" s="47">
+        <f>IF($A24="","",IF(AC24&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($O24="",1,0)+IF($P24="",1,0)+IF($S24="",1,0)+IF($U24="",1,0)+IF($Y24="",1,0)+IF($Z24="",1,0)+IF(AND($N24="契約期間満了",$Q24=""),1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3115,16 +2793,16 @@
       <c r="A25" s="16" t="n"/>
       <c r="B25" s="16" t="n"/>
       <c r="C25" s="18" t="n"/>
-      <c r="D25" s="46" t="n"/>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+      <c r="F25" s="44" t="n"/>
+      <c r="G25" s="44" t="n"/>
       <c r="H25" s="16" t="n"/>
       <c r="I25" s="16" t="n"/>
       <c r="J25" s="16" t="n"/>
       <c r="K25" s="16" t="n"/>
       <c r="L25" s="18" t="n"/>
-      <c r="M25" s="47">
+      <c r="M25" s="45">
         <f>IF($L25="","",$L25+1)</f>
         <v/>
       </c>
@@ -3137,26 +2815,17 @@
       <c r="T25" s="16" t="n"/>
       <c r="U25" s="16" t="n"/>
       <c r="V25" s="16" t="n"/>
-      <c r="W25" s="48" t="n"/>
-      <c r="X25" s="48" t="n"/>
+      <c r="W25" s="46" t="n"/>
+      <c r="X25" s="46" t="n"/>
       <c r="Y25" s="16" t="n"/>
       <c r="Z25" s="16" t="n"/>
       <c r="AA25" s="16" t="n"/>
-      <c r="AB25" s="22">
-        <f>IF($L25="","",IF(MONTH($L25)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L25)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC25" s="16" t="n"/>
-      <c r="AD25" s="16" t="n"/>
-      <c r="AE25" s="16" t="n"/>
-      <c r="AF25" s="16" t="n"/>
-      <c r="AG25" s="16" t="n"/>
-      <c r="AH25" s="49">
-        <f>IF($A25="","",IF(AI25&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI25">
-        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($O25="",1,0)+IF($P25="",1,0)+IF($S25="",1,0)+IF($U25="",1,0)+IF($Y25="",1,0)+IF($Z25="",1,0)+IF($AA25="",1,0)+IF(AND($AA25="特別徴収を継続（転職先へ引継ぎ）",$AC25=""),1,0)+IF(AND($N25="契約期間満了",$Q25=""),1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0))</f>
+      <c r="AB25" s="47">
+        <f>IF($A25="","",IF(AC25&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($O25="",1,0)+IF($P25="",1,0)+IF($S25="",1,0)+IF($U25="",1,0)+IF($Y25="",1,0)+IF($Z25="",1,0)+IF(AND($N25="契約期間満了",$Q25=""),1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3164,16 +2833,16 @@
       <c r="A26" s="16" t="n"/>
       <c r="B26" s="16" t="n"/>
       <c r="C26" s="18" t="n"/>
-      <c r="D26" s="46" t="n"/>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="46" t="n"/>
-      <c r="G26" s="46" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="44" t="n"/>
       <c r="H26" s="16" t="n"/>
       <c r="I26" s="16" t="n"/>
       <c r="J26" s="16" t="n"/>
       <c r="K26" s="16" t="n"/>
       <c r="L26" s="18" t="n"/>
-      <c r="M26" s="47">
+      <c r="M26" s="45">
         <f>IF($L26="","",$L26+1)</f>
         <v/>
       </c>
@@ -3186,26 +2855,17 @@
       <c r="T26" s="16" t="n"/>
       <c r="U26" s="16" t="n"/>
       <c r="V26" s="16" t="n"/>
-      <c r="W26" s="48" t="n"/>
-      <c r="X26" s="48" t="n"/>
+      <c r="W26" s="46" t="n"/>
+      <c r="X26" s="46" t="n"/>
       <c r="Y26" s="16" t="n"/>
       <c r="Z26" s="16" t="n"/>
       <c r="AA26" s="16" t="n"/>
-      <c r="AB26" s="22">
-        <f>IF($L26="","",IF(MONTH($L26)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L26)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC26" s="16" t="n"/>
-      <c r="AD26" s="16" t="n"/>
-      <c r="AE26" s="16" t="n"/>
-      <c r="AF26" s="16" t="n"/>
-      <c r="AG26" s="16" t="n"/>
-      <c r="AH26" s="49">
-        <f>IF($A26="","",IF(AI26&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI26">
-        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($O26="",1,0)+IF($P26="",1,0)+IF($S26="",1,0)+IF($U26="",1,0)+IF($Y26="",1,0)+IF($Z26="",1,0)+IF($AA26="",1,0)+IF(AND($AA26="特別徴収を継続（転職先へ引継ぎ）",$AC26=""),1,0)+IF(AND($N26="契約期間満了",$Q26=""),1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0))</f>
+      <c r="AB26" s="47">
+        <f>IF($A26="","",IF(AC26&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($O26="",1,0)+IF($P26="",1,0)+IF($S26="",1,0)+IF($U26="",1,0)+IF($Y26="",1,0)+IF($Z26="",1,0)+IF(AND($N26="契約期間満了",$Q26=""),1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3213,16 +2873,16 @@
       <c r="A27" s="16" t="n"/>
       <c r="B27" s="16" t="n"/>
       <c r="C27" s="18" t="n"/>
-      <c r="D27" s="46" t="n"/>
-      <c r="E27" s="46" t="n"/>
-      <c r="F27" s="46" t="n"/>
-      <c r="G27" s="46" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+      <c r="F27" s="44" t="n"/>
+      <c r="G27" s="44" t="n"/>
       <c r="H27" s="16" t="n"/>
       <c r="I27" s="16" t="n"/>
       <c r="J27" s="16" t="n"/>
       <c r="K27" s="16" t="n"/>
       <c r="L27" s="18" t="n"/>
-      <c r="M27" s="47">
+      <c r="M27" s="45">
         <f>IF($L27="","",$L27+1)</f>
         <v/>
       </c>
@@ -3235,26 +2895,17 @@
       <c r="T27" s="16" t="n"/>
       <c r="U27" s="16" t="n"/>
       <c r="V27" s="16" t="n"/>
-      <c r="W27" s="48" t="n"/>
-      <c r="X27" s="48" t="n"/>
+      <c r="W27" s="46" t="n"/>
+      <c r="X27" s="46" t="n"/>
       <c r="Y27" s="16" t="n"/>
       <c r="Z27" s="16" t="n"/>
       <c r="AA27" s="16" t="n"/>
-      <c r="AB27" s="22">
-        <f>IF($L27="","",IF(MONTH($L27)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L27)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC27" s="16" t="n"/>
-      <c r="AD27" s="16" t="n"/>
-      <c r="AE27" s="16" t="n"/>
-      <c r="AF27" s="16" t="n"/>
-      <c r="AG27" s="16" t="n"/>
-      <c r="AH27" s="49">
-        <f>IF($A27="","",IF(AI27&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI27">
-        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($O27="",1,0)+IF($P27="",1,0)+IF($S27="",1,0)+IF($U27="",1,0)+IF($Y27="",1,0)+IF($Z27="",1,0)+IF($AA27="",1,0)+IF(AND($AA27="特別徴収を継続（転職先へ引継ぎ）",$AC27=""),1,0)+IF(AND($N27="契約期間満了",$Q27=""),1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0))</f>
+      <c r="AB27" s="47">
+        <f>IF($A27="","",IF(AC27&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($O27="",1,0)+IF($P27="",1,0)+IF($S27="",1,0)+IF($U27="",1,0)+IF($Y27="",1,0)+IF($Z27="",1,0)+IF(AND($N27="契約期間満了",$Q27=""),1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3262,16 +2913,16 @@
       <c r="A28" s="16" t="n"/>
       <c r="B28" s="16" t="n"/>
       <c r="C28" s="18" t="n"/>
-      <c r="D28" s="46" t="n"/>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n"/>
-      <c r="G28" s="46" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="44" t="n"/>
+      <c r="G28" s="44" t="n"/>
       <c r="H28" s="16" t="n"/>
       <c r="I28" s="16" t="n"/>
       <c r="J28" s="16" t="n"/>
       <c r="K28" s="16" t="n"/>
       <c r="L28" s="18" t="n"/>
-      <c r="M28" s="47">
+      <c r="M28" s="45">
         <f>IF($L28="","",$L28+1)</f>
         <v/>
       </c>
@@ -3284,26 +2935,17 @@
       <c r="T28" s="16" t="n"/>
       <c r="U28" s="16" t="n"/>
       <c r="V28" s="16" t="n"/>
-      <c r="W28" s="48" t="n"/>
-      <c r="X28" s="48" t="n"/>
+      <c r="W28" s="46" t="n"/>
+      <c r="X28" s="46" t="n"/>
       <c r="Y28" s="16" t="n"/>
       <c r="Z28" s="16" t="n"/>
       <c r="AA28" s="16" t="n"/>
-      <c r="AB28" s="22">
-        <f>IF($L28="","",IF(MONTH($L28)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L28)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC28" s="16" t="n"/>
-      <c r="AD28" s="16" t="n"/>
-      <c r="AE28" s="16" t="n"/>
-      <c r="AF28" s="16" t="n"/>
-      <c r="AG28" s="16" t="n"/>
-      <c r="AH28" s="49">
-        <f>IF($A28="","",IF(AI28&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI28">
-        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($O28="",1,0)+IF($P28="",1,0)+IF($S28="",1,0)+IF($U28="",1,0)+IF($Y28="",1,0)+IF($Z28="",1,0)+IF($AA28="",1,0)+IF(AND($AA28="特別徴収を継続（転職先へ引継ぎ）",$AC28=""),1,0)+IF(AND($N28="契約期間満了",$Q28=""),1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0))</f>
+      <c r="AB28" s="47">
+        <f>IF($A28="","",IF(AC28&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($O28="",1,0)+IF($P28="",1,0)+IF($S28="",1,0)+IF($U28="",1,0)+IF($Y28="",1,0)+IF($Z28="",1,0)+IF(AND($N28="契約期間満了",$Q28=""),1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3311,16 +2953,16 @@
       <c r="A29" s="16" t="n"/>
       <c r="B29" s="16" t="n"/>
       <c r="C29" s="18" t="n"/>
-      <c r="D29" s="46" t="n"/>
-      <c r="E29" s="46" t="n"/>
-      <c r="F29" s="46" t="n"/>
-      <c r="G29" s="46" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+      <c r="F29" s="44" t="n"/>
+      <c r="G29" s="44" t="n"/>
       <c r="H29" s="16" t="n"/>
       <c r="I29" s="16" t="n"/>
       <c r="J29" s="16" t="n"/>
       <c r="K29" s="16" t="n"/>
       <c r="L29" s="18" t="n"/>
-      <c r="M29" s="47">
+      <c r="M29" s="45">
         <f>IF($L29="","",$L29+1)</f>
         <v/>
       </c>
@@ -3333,26 +2975,17 @@
       <c r="T29" s="16" t="n"/>
       <c r="U29" s="16" t="n"/>
       <c r="V29" s="16" t="n"/>
-      <c r="W29" s="48" t="n"/>
-      <c r="X29" s="48" t="n"/>
+      <c r="W29" s="46" t="n"/>
+      <c r="X29" s="46" t="n"/>
       <c r="Y29" s="16" t="n"/>
       <c r="Z29" s="16" t="n"/>
       <c r="AA29" s="16" t="n"/>
-      <c r="AB29" s="22">
-        <f>IF($L29="","",IF(MONTH($L29)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L29)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC29" s="16" t="n"/>
-      <c r="AD29" s="16" t="n"/>
-      <c r="AE29" s="16" t="n"/>
-      <c r="AF29" s="16" t="n"/>
-      <c r="AG29" s="16" t="n"/>
-      <c r="AH29" s="49">
-        <f>IF($A29="","",IF(AI29&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI29">
-        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($O29="",1,0)+IF($P29="",1,0)+IF($S29="",1,0)+IF($U29="",1,0)+IF($Y29="",1,0)+IF($Z29="",1,0)+IF($AA29="",1,0)+IF(AND($AA29="特別徴収を継続（転職先へ引継ぎ）",$AC29=""),1,0)+IF(AND($N29="契約期間満了",$Q29=""),1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0))</f>
+      <c r="AB29" s="47">
+        <f>IF($A29="","",IF(AC29&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($O29="",1,0)+IF($P29="",1,0)+IF($S29="",1,0)+IF($U29="",1,0)+IF($Y29="",1,0)+IF($Z29="",1,0)+IF(AND($N29="契約期間満了",$Q29=""),1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3360,16 +2993,16 @@
       <c r="A30" s="16" t="n"/>
       <c r="B30" s="16" t="n"/>
       <c r="C30" s="18" t="n"/>
-      <c r="D30" s="46" t="n"/>
-      <c r="E30" s="46" t="n"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="46" t="n"/>
+      <c r="D30" s="44" t="n"/>
+      <c r="E30" s="44" t="n"/>
+      <c r="F30" s="44" t="n"/>
+      <c r="G30" s="44" t="n"/>
       <c r="H30" s="16" t="n"/>
       <c r="I30" s="16" t="n"/>
       <c r="J30" s="16" t="n"/>
       <c r="K30" s="16" t="n"/>
       <c r="L30" s="18" t="n"/>
-      <c r="M30" s="47">
+      <c r="M30" s="45">
         <f>IF($L30="","",$L30+1)</f>
         <v/>
       </c>
@@ -3382,26 +3015,17 @@
       <c r="T30" s="16" t="n"/>
       <c r="U30" s="16" t="n"/>
       <c r="V30" s="16" t="n"/>
-      <c r="W30" s="48" t="n"/>
-      <c r="X30" s="48" t="n"/>
+      <c r="W30" s="46" t="n"/>
+      <c r="X30" s="46" t="n"/>
       <c r="Y30" s="16" t="n"/>
       <c r="Z30" s="16" t="n"/>
       <c r="AA30" s="16" t="n"/>
-      <c r="AB30" s="22">
-        <f>IF($L30="","",IF(MONTH($L30)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L30)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC30" s="16" t="n"/>
-      <c r="AD30" s="16" t="n"/>
-      <c r="AE30" s="16" t="n"/>
-      <c r="AF30" s="16" t="n"/>
-      <c r="AG30" s="16" t="n"/>
-      <c r="AH30" s="49">
-        <f>IF($A30="","",IF(AI30&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI30">
-        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($O30="",1,0)+IF($P30="",1,0)+IF($S30="",1,0)+IF($U30="",1,0)+IF($Y30="",1,0)+IF($Z30="",1,0)+IF($AA30="",1,0)+IF(AND($AA30="特別徴収を継続（転職先へ引継ぎ）",$AC30=""),1,0)+IF(AND($N30="契約期間満了",$Q30=""),1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0))</f>
+      <c r="AB30" s="47">
+        <f>IF($A30="","",IF(AC30&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($O30="",1,0)+IF($P30="",1,0)+IF($S30="",1,0)+IF($U30="",1,0)+IF($Y30="",1,0)+IF($Z30="",1,0)+IF(AND($N30="契約期間満了",$Q30=""),1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3409,16 +3033,16 @@
       <c r="A31" s="16" t="n"/>
       <c r="B31" s="16" t="n"/>
       <c r="C31" s="18" t="n"/>
-      <c r="D31" s="46" t="n"/>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="46" t="n"/>
-      <c r="G31" s="46" t="n"/>
+      <c r="D31" s="44" t="n"/>
+      <c r="E31" s="44" t="n"/>
+      <c r="F31" s="44" t="n"/>
+      <c r="G31" s="44" t="n"/>
       <c r="H31" s="16" t="n"/>
       <c r="I31" s="16" t="n"/>
       <c r="J31" s="16" t="n"/>
       <c r="K31" s="16" t="n"/>
       <c r="L31" s="18" t="n"/>
-      <c r="M31" s="47">
+      <c r="M31" s="45">
         <f>IF($L31="","",$L31+1)</f>
         <v/>
       </c>
@@ -3431,26 +3055,17 @@
       <c r="T31" s="16" t="n"/>
       <c r="U31" s="16" t="n"/>
       <c r="V31" s="16" t="n"/>
-      <c r="W31" s="48" t="n"/>
-      <c r="X31" s="48" t="n"/>
+      <c r="W31" s="46" t="n"/>
+      <c r="X31" s="46" t="n"/>
       <c r="Y31" s="16" t="n"/>
       <c r="Z31" s="16" t="n"/>
       <c r="AA31" s="16" t="n"/>
-      <c r="AB31" s="22">
-        <f>IF($L31="","",IF(MONTH($L31)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L31)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC31" s="16" t="n"/>
-      <c r="AD31" s="16" t="n"/>
-      <c r="AE31" s="16" t="n"/>
-      <c r="AF31" s="16" t="n"/>
-      <c r="AG31" s="16" t="n"/>
-      <c r="AH31" s="49">
-        <f>IF($A31="","",IF(AI31&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI31">
-        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($O31="",1,0)+IF($P31="",1,0)+IF($S31="",1,0)+IF($U31="",1,0)+IF($Y31="",1,0)+IF($Z31="",1,0)+IF($AA31="",1,0)+IF(AND($AA31="特別徴収を継続（転職先へ引継ぎ）",$AC31=""),1,0)+IF(AND($N31="契約期間満了",$Q31=""),1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0))</f>
+      <c r="AB31" s="47">
+        <f>IF($A31="","",IF(AC31&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($O31="",1,0)+IF($P31="",1,0)+IF($S31="",1,0)+IF($U31="",1,0)+IF($Y31="",1,0)+IF($Z31="",1,0)+IF(AND($N31="契約期間満了",$Q31=""),1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3458,16 +3073,16 @@
       <c r="A32" s="16" t="n"/>
       <c r="B32" s="16" t="n"/>
       <c r="C32" s="18" t="n"/>
-      <c r="D32" s="46" t="n"/>
-      <c r="E32" s="46" t="n"/>
-      <c r="F32" s="46" t="n"/>
-      <c r="G32" s="46" t="n"/>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="44" t="n"/>
+      <c r="F32" s="44" t="n"/>
+      <c r="G32" s="44" t="n"/>
       <c r="H32" s="16" t="n"/>
       <c r="I32" s="16" t="n"/>
       <c r="J32" s="16" t="n"/>
       <c r="K32" s="16" t="n"/>
       <c r="L32" s="18" t="n"/>
-      <c r="M32" s="47">
+      <c r="M32" s="45">
         <f>IF($L32="","",$L32+1)</f>
         <v/>
       </c>
@@ -3480,26 +3095,17 @@
       <c r="T32" s="16" t="n"/>
       <c r="U32" s="16" t="n"/>
       <c r="V32" s="16" t="n"/>
-      <c r="W32" s="48" t="n"/>
-      <c r="X32" s="48" t="n"/>
+      <c r="W32" s="46" t="n"/>
+      <c r="X32" s="46" t="n"/>
       <c r="Y32" s="16" t="n"/>
       <c r="Z32" s="16" t="n"/>
       <c r="AA32" s="16" t="n"/>
-      <c r="AB32" s="22">
-        <f>IF($L32="","",IF(MONTH($L32)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L32)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC32" s="16" t="n"/>
-      <c r="AD32" s="16" t="n"/>
-      <c r="AE32" s="16" t="n"/>
-      <c r="AF32" s="16" t="n"/>
-      <c r="AG32" s="16" t="n"/>
-      <c r="AH32" s="49">
-        <f>IF($A32="","",IF(AI32&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI32">
-        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($O32="",1,0)+IF($P32="",1,0)+IF($S32="",1,0)+IF($U32="",1,0)+IF($Y32="",1,0)+IF($Z32="",1,0)+IF($AA32="",1,0)+IF(AND($AA32="特別徴収を継続（転職先へ引継ぎ）",$AC32=""),1,0)+IF(AND($N32="契約期間満了",$Q32=""),1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0))</f>
+      <c r="AB32" s="47">
+        <f>IF($A32="","",IF(AC32&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($O32="",1,0)+IF($P32="",1,0)+IF($S32="",1,0)+IF($U32="",1,0)+IF($Y32="",1,0)+IF($Z32="",1,0)+IF(AND($N32="契約期間満了",$Q32=""),1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3507,16 +3113,16 @@
       <c r="A33" s="16" t="n"/>
       <c r="B33" s="16" t="n"/>
       <c r="C33" s="18" t="n"/>
-      <c r="D33" s="46" t="n"/>
-      <c r="E33" s="46" t="n"/>
-      <c r="F33" s="46" t="n"/>
-      <c r="G33" s="46" t="n"/>
+      <c r="D33" s="44" t="n"/>
+      <c r="E33" s="44" t="n"/>
+      <c r="F33" s="44" t="n"/>
+      <c r="G33" s="44" t="n"/>
       <c r="H33" s="16" t="n"/>
       <c r="I33" s="16" t="n"/>
       <c r="J33" s="16" t="n"/>
       <c r="K33" s="16" t="n"/>
       <c r="L33" s="18" t="n"/>
-      <c r="M33" s="47">
+      <c r="M33" s="45">
         <f>IF($L33="","",$L33+1)</f>
         <v/>
       </c>
@@ -3529,26 +3135,17 @@
       <c r="T33" s="16" t="n"/>
       <c r="U33" s="16" t="n"/>
       <c r="V33" s="16" t="n"/>
-      <c r="W33" s="48" t="n"/>
-      <c r="X33" s="48" t="n"/>
+      <c r="W33" s="46" t="n"/>
+      <c r="X33" s="46" t="n"/>
       <c r="Y33" s="16" t="n"/>
       <c r="Z33" s="16" t="n"/>
       <c r="AA33" s="16" t="n"/>
-      <c r="AB33" s="22">
-        <f>IF($L33="","",IF(MONTH($L33)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L33)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC33" s="16" t="n"/>
-      <c r="AD33" s="16" t="n"/>
-      <c r="AE33" s="16" t="n"/>
-      <c r="AF33" s="16" t="n"/>
-      <c r="AG33" s="16" t="n"/>
-      <c r="AH33" s="49">
-        <f>IF($A33="","",IF(AI33&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI33">
-        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($O33="",1,0)+IF($P33="",1,0)+IF($S33="",1,0)+IF($U33="",1,0)+IF($Y33="",1,0)+IF($Z33="",1,0)+IF($AA33="",1,0)+IF(AND($AA33="特別徴収を継続（転職先へ引継ぎ）",$AC33=""),1,0)+IF(AND($N33="契約期間満了",$Q33=""),1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0))</f>
+      <c r="AB33" s="47">
+        <f>IF($A33="","",IF(AC33&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($O33="",1,0)+IF($P33="",1,0)+IF($S33="",1,0)+IF($U33="",1,0)+IF($Y33="",1,0)+IF($Z33="",1,0)+IF(AND($N33="契約期間満了",$Q33=""),1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3556,16 +3153,16 @@
       <c r="A34" s="16" t="n"/>
       <c r="B34" s="16" t="n"/>
       <c r="C34" s="18" t="n"/>
-      <c r="D34" s="46" t="n"/>
-      <c r="E34" s="46" t="n"/>
-      <c r="F34" s="46" t="n"/>
-      <c r="G34" s="46" t="n"/>
+      <c r="D34" s="44" t="n"/>
+      <c r="E34" s="44" t="n"/>
+      <c r="F34" s="44" t="n"/>
+      <c r="G34" s="44" t="n"/>
       <c r="H34" s="16" t="n"/>
       <c r="I34" s="16" t="n"/>
       <c r="J34" s="16" t="n"/>
       <c r="K34" s="16" t="n"/>
       <c r="L34" s="18" t="n"/>
-      <c r="M34" s="47">
+      <c r="M34" s="45">
         <f>IF($L34="","",$L34+1)</f>
         <v/>
       </c>
@@ -3578,26 +3175,17 @@
       <c r="T34" s="16" t="n"/>
       <c r="U34" s="16" t="n"/>
       <c r="V34" s="16" t="n"/>
-      <c r="W34" s="48" t="n"/>
-      <c r="X34" s="48" t="n"/>
+      <c r="W34" s="46" t="n"/>
+      <c r="X34" s="46" t="n"/>
       <c r="Y34" s="16" t="n"/>
       <c r="Z34" s="16" t="n"/>
       <c r="AA34" s="16" t="n"/>
-      <c r="AB34" s="22">
-        <f>IF($L34="","",IF(MONTH($L34)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L34)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC34" s="16" t="n"/>
-      <c r="AD34" s="16" t="n"/>
-      <c r="AE34" s="16" t="n"/>
-      <c r="AF34" s="16" t="n"/>
-      <c r="AG34" s="16" t="n"/>
-      <c r="AH34" s="49">
-        <f>IF($A34="","",IF(AI34&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI34">
-        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($O34="",1,0)+IF($P34="",1,0)+IF($S34="",1,0)+IF($U34="",1,0)+IF($Y34="",1,0)+IF($Z34="",1,0)+IF($AA34="",1,0)+IF(AND($AA34="特別徴収を継続（転職先へ引継ぎ）",$AC34=""),1,0)+IF(AND($N34="契約期間満了",$Q34=""),1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0))</f>
+      <c r="AB34" s="47">
+        <f>IF($A34="","",IF(AC34&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($O34="",1,0)+IF($P34="",1,0)+IF($S34="",1,0)+IF($U34="",1,0)+IF($Y34="",1,0)+IF($Z34="",1,0)+IF(AND($N34="契約期間満了",$Q34=""),1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3605,16 +3193,16 @@
       <c r="A35" s="16" t="n"/>
       <c r="B35" s="16" t="n"/>
       <c r="C35" s="18" t="n"/>
-      <c r="D35" s="46" t="n"/>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="46" t="n"/>
+      <c r="D35" s="44" t="n"/>
+      <c r="E35" s="44" t="n"/>
+      <c r="F35" s="44" t="n"/>
+      <c r="G35" s="44" t="n"/>
       <c r="H35" s="16" t="n"/>
       <c r="I35" s="16" t="n"/>
       <c r="J35" s="16" t="n"/>
       <c r="K35" s="16" t="n"/>
       <c r="L35" s="18" t="n"/>
-      <c r="M35" s="47">
+      <c r="M35" s="45">
         <f>IF($L35="","",$L35+1)</f>
         <v/>
       </c>
@@ -3627,26 +3215,17 @@
       <c r="T35" s="16" t="n"/>
       <c r="U35" s="16" t="n"/>
       <c r="V35" s="16" t="n"/>
-      <c r="W35" s="48" t="n"/>
-      <c r="X35" s="48" t="n"/>
+      <c r="W35" s="46" t="n"/>
+      <c r="X35" s="46" t="n"/>
       <c r="Y35" s="16" t="n"/>
       <c r="Z35" s="16" t="n"/>
       <c r="AA35" s="16" t="n"/>
-      <c r="AB35" s="22">
-        <f>IF($L35="","",IF(MONTH($L35)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L35)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC35" s="16" t="n"/>
-      <c r="AD35" s="16" t="n"/>
-      <c r="AE35" s="16" t="n"/>
-      <c r="AF35" s="16" t="n"/>
-      <c r="AG35" s="16" t="n"/>
-      <c r="AH35" s="49">
-        <f>IF($A35="","",IF(AI35&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI35">
-        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($O35="",1,0)+IF($P35="",1,0)+IF($S35="",1,0)+IF($U35="",1,0)+IF($Y35="",1,0)+IF($Z35="",1,0)+IF($AA35="",1,0)+IF(AND($AA35="特別徴収を継続（転職先へ引継ぎ）",$AC35=""),1,0)+IF(AND($N35="契約期間満了",$Q35=""),1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0))</f>
+      <c r="AB35" s="47">
+        <f>IF($A35="","",IF(AC35&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($O35="",1,0)+IF($P35="",1,0)+IF($S35="",1,0)+IF($U35="",1,0)+IF($Y35="",1,0)+IF($Z35="",1,0)+IF(AND($N35="契約期間満了",$Q35=""),1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3654,16 +3233,16 @@
       <c r="A36" s="16" t="n"/>
       <c r="B36" s="16" t="n"/>
       <c r="C36" s="18" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
+      <c r="D36" s="44" t="n"/>
+      <c r="E36" s="44" t="n"/>
+      <c r="F36" s="44" t="n"/>
+      <c r="G36" s="44" t="n"/>
       <c r="H36" s="16" t="n"/>
       <c r="I36" s="16" t="n"/>
       <c r="J36" s="16" t="n"/>
       <c r="K36" s="16" t="n"/>
       <c r="L36" s="18" t="n"/>
-      <c r="M36" s="47">
+      <c r="M36" s="45">
         <f>IF($L36="","",$L36+1)</f>
         <v/>
       </c>
@@ -3676,26 +3255,17 @@
       <c r="T36" s="16" t="n"/>
       <c r="U36" s="16" t="n"/>
       <c r="V36" s="16" t="n"/>
-      <c r="W36" s="48" t="n"/>
-      <c r="X36" s="48" t="n"/>
+      <c r="W36" s="46" t="n"/>
+      <c r="X36" s="46" t="n"/>
       <c r="Y36" s="16" t="n"/>
       <c r="Z36" s="16" t="n"/>
       <c r="AA36" s="16" t="n"/>
-      <c r="AB36" s="22">
-        <f>IF($L36="","",IF(MONTH($L36)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L36)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC36" s="16" t="n"/>
-      <c r="AD36" s="16" t="n"/>
-      <c r="AE36" s="16" t="n"/>
-      <c r="AF36" s="16" t="n"/>
-      <c r="AG36" s="16" t="n"/>
-      <c r="AH36" s="49">
-        <f>IF($A36="","",IF(AI36&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI36">
-        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($O36="",1,0)+IF($P36="",1,0)+IF($S36="",1,0)+IF($U36="",1,0)+IF($Y36="",1,0)+IF($Z36="",1,0)+IF($AA36="",1,0)+IF(AND($AA36="特別徴収を継続（転職先へ引継ぎ）",$AC36=""),1,0)+IF(AND($N36="契約期間満了",$Q36=""),1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0))</f>
+      <c r="AB36" s="47">
+        <f>IF($A36="","",IF(AC36&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($O36="",1,0)+IF($P36="",1,0)+IF($S36="",1,0)+IF($U36="",1,0)+IF($Y36="",1,0)+IF($Z36="",1,0)+IF(AND($N36="契約期間満了",$Q36=""),1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3703,16 +3273,16 @@
       <c r="A37" s="16" t="n"/>
       <c r="B37" s="16" t="n"/>
       <c r="C37" s="18" t="n"/>
-      <c r="D37" s="46" t="n"/>
-      <c r="E37" s="46" t="n"/>
-      <c r="F37" s="46" t="n"/>
-      <c r="G37" s="46" t="n"/>
+      <c r="D37" s="44" t="n"/>
+      <c r="E37" s="44" t="n"/>
+      <c r="F37" s="44" t="n"/>
+      <c r="G37" s="44" t="n"/>
       <c r="H37" s="16" t="n"/>
       <c r="I37" s="16" t="n"/>
       <c r="J37" s="16" t="n"/>
       <c r="K37" s="16" t="n"/>
       <c r="L37" s="18" t="n"/>
-      <c r="M37" s="47">
+      <c r="M37" s="45">
         <f>IF($L37="","",$L37+1)</f>
         <v/>
       </c>
@@ -3725,26 +3295,17 @@
       <c r="T37" s="16" t="n"/>
       <c r="U37" s="16" t="n"/>
       <c r="V37" s="16" t="n"/>
-      <c r="W37" s="48" t="n"/>
-      <c r="X37" s="48" t="n"/>
+      <c r="W37" s="46" t="n"/>
+      <c r="X37" s="46" t="n"/>
       <c r="Y37" s="16" t="n"/>
       <c r="Z37" s="16" t="n"/>
       <c r="AA37" s="16" t="n"/>
-      <c r="AB37" s="22">
-        <f>IF($L37="","",IF(MONTH($L37)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L37)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC37" s="16" t="n"/>
-      <c r="AD37" s="16" t="n"/>
-      <c r="AE37" s="16" t="n"/>
-      <c r="AF37" s="16" t="n"/>
-      <c r="AG37" s="16" t="n"/>
-      <c r="AH37" s="49">
-        <f>IF($A37="","",IF(AI37&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI37">
-        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($O37="",1,0)+IF($P37="",1,0)+IF($S37="",1,0)+IF($U37="",1,0)+IF($Y37="",1,0)+IF($Z37="",1,0)+IF($AA37="",1,0)+IF(AND($AA37="特別徴収を継続（転職先へ引継ぎ）",$AC37=""),1,0)+IF(AND($N37="契約期間満了",$Q37=""),1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0))</f>
+      <c r="AB37" s="47">
+        <f>IF($A37="","",IF(AC37&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($O37="",1,0)+IF($P37="",1,0)+IF($S37="",1,0)+IF($U37="",1,0)+IF($Y37="",1,0)+IF($Z37="",1,0)+IF(AND($N37="契約期間満了",$Q37=""),1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3752,16 +3313,16 @@
       <c r="A38" s="16" t="n"/>
       <c r="B38" s="16" t="n"/>
       <c r="C38" s="18" t="n"/>
-      <c r="D38" s="46" t="n"/>
-      <c r="E38" s="46" t="n"/>
-      <c r="F38" s="46" t="n"/>
-      <c r="G38" s="46" t="n"/>
+      <c r="D38" s="44" t="n"/>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="44" t="n"/>
+      <c r="G38" s="44" t="n"/>
       <c r="H38" s="16" t="n"/>
       <c r="I38" s="16" t="n"/>
       <c r="J38" s="16" t="n"/>
       <c r="K38" s="16" t="n"/>
       <c r="L38" s="18" t="n"/>
-      <c r="M38" s="47">
+      <c r="M38" s="45">
         <f>IF($L38="","",$L38+1)</f>
         <v/>
       </c>
@@ -3774,26 +3335,17 @@
       <c r="T38" s="16" t="n"/>
       <c r="U38" s="16" t="n"/>
       <c r="V38" s="16" t="n"/>
-      <c r="W38" s="48" t="n"/>
-      <c r="X38" s="48" t="n"/>
+      <c r="W38" s="46" t="n"/>
+      <c r="X38" s="46" t="n"/>
       <c r="Y38" s="16" t="n"/>
       <c r="Z38" s="16" t="n"/>
       <c r="AA38" s="16" t="n"/>
-      <c r="AB38" s="22">
-        <f>IF($L38="","",IF(MONTH($L38)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L38)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC38" s="16" t="n"/>
-      <c r="AD38" s="16" t="n"/>
-      <c r="AE38" s="16" t="n"/>
-      <c r="AF38" s="16" t="n"/>
-      <c r="AG38" s="16" t="n"/>
-      <c r="AH38" s="49">
-        <f>IF($A38="","",IF(AI38&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI38">
-        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($O38="",1,0)+IF($P38="",1,0)+IF($S38="",1,0)+IF($U38="",1,0)+IF($Y38="",1,0)+IF($Z38="",1,0)+IF($AA38="",1,0)+IF(AND($AA38="特別徴収を継続（転職先へ引継ぎ）",$AC38=""),1,0)+IF(AND($N38="契約期間満了",$Q38=""),1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0))</f>
+      <c r="AB38" s="47">
+        <f>IF($A38="","",IF(AC38&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($O38="",1,0)+IF($P38="",1,0)+IF($S38="",1,0)+IF($U38="",1,0)+IF($Y38="",1,0)+IF($Z38="",1,0)+IF(AND($N38="契約期間満了",$Q38=""),1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3801,16 +3353,16 @@
       <c r="A39" s="16" t="n"/>
       <c r="B39" s="16" t="n"/>
       <c r="C39" s="18" t="n"/>
-      <c r="D39" s="46" t="n"/>
-      <c r="E39" s="46" t="n"/>
-      <c r="F39" s="46" t="n"/>
-      <c r="G39" s="46" t="n"/>
+      <c r="D39" s="44" t="n"/>
+      <c r="E39" s="44" t="n"/>
+      <c r="F39" s="44" t="n"/>
+      <c r="G39" s="44" t="n"/>
       <c r="H39" s="16" t="n"/>
       <c r="I39" s="16" t="n"/>
       <c r="J39" s="16" t="n"/>
       <c r="K39" s="16" t="n"/>
       <c r="L39" s="18" t="n"/>
-      <c r="M39" s="47">
+      <c r="M39" s="45">
         <f>IF($L39="","",$L39+1)</f>
         <v/>
       </c>
@@ -3823,26 +3375,17 @@
       <c r="T39" s="16" t="n"/>
       <c r="U39" s="16" t="n"/>
       <c r="V39" s="16" t="n"/>
-      <c r="W39" s="48" t="n"/>
-      <c r="X39" s="48" t="n"/>
+      <c r="W39" s="46" t="n"/>
+      <c r="X39" s="46" t="n"/>
       <c r="Y39" s="16" t="n"/>
       <c r="Z39" s="16" t="n"/>
       <c r="AA39" s="16" t="n"/>
-      <c r="AB39" s="22">
-        <f>IF($L39="","",IF(MONTH($L39)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L39)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC39" s="16" t="n"/>
-      <c r="AD39" s="16" t="n"/>
-      <c r="AE39" s="16" t="n"/>
-      <c r="AF39" s="16" t="n"/>
-      <c r="AG39" s="16" t="n"/>
-      <c r="AH39" s="49">
-        <f>IF($A39="","",IF(AI39&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI39">
-        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($O39="",1,0)+IF($P39="",1,0)+IF($S39="",1,0)+IF($U39="",1,0)+IF($Y39="",1,0)+IF($Z39="",1,0)+IF($AA39="",1,0)+IF(AND($AA39="特別徴収を継続（転職先へ引継ぎ）",$AC39=""),1,0)+IF(AND($N39="契約期間満了",$Q39=""),1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0))</f>
+      <c r="AB39" s="47">
+        <f>IF($A39="","",IF(AC39&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($O39="",1,0)+IF($P39="",1,0)+IF($S39="",1,0)+IF($U39="",1,0)+IF($Y39="",1,0)+IF($Z39="",1,0)+IF(AND($N39="契約期間満了",$Q39=""),1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3850,16 +3393,16 @@
       <c r="A40" s="16" t="n"/>
       <c r="B40" s="16" t="n"/>
       <c r="C40" s="18" t="n"/>
-      <c r="D40" s="46" t="n"/>
-      <c r="E40" s="46" t="n"/>
-      <c r="F40" s="46" t="n"/>
-      <c r="G40" s="46" t="n"/>
+      <c r="D40" s="44" t="n"/>
+      <c r="E40" s="44" t="n"/>
+      <c r="F40" s="44" t="n"/>
+      <c r="G40" s="44" t="n"/>
       <c r="H40" s="16" t="n"/>
       <c r="I40" s="16" t="n"/>
       <c r="J40" s="16" t="n"/>
       <c r="K40" s="16" t="n"/>
       <c r="L40" s="18" t="n"/>
-      <c r="M40" s="47">
+      <c r="M40" s="45">
         <f>IF($L40="","",$L40+1)</f>
         <v/>
       </c>
@@ -3872,26 +3415,17 @@
       <c r="T40" s="16" t="n"/>
       <c r="U40" s="16" t="n"/>
       <c r="V40" s="16" t="n"/>
-      <c r="W40" s="48" t="n"/>
-      <c r="X40" s="48" t="n"/>
+      <c r="W40" s="46" t="n"/>
+      <c r="X40" s="46" t="n"/>
       <c r="Y40" s="16" t="n"/>
       <c r="Z40" s="16" t="n"/>
       <c r="AA40" s="16" t="n"/>
-      <c r="AB40" s="22">
-        <f>IF($L40="","",IF(MONTH($L40)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L40)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC40" s="16" t="n"/>
-      <c r="AD40" s="16" t="n"/>
-      <c r="AE40" s="16" t="n"/>
-      <c r="AF40" s="16" t="n"/>
-      <c r="AG40" s="16" t="n"/>
-      <c r="AH40" s="49">
-        <f>IF($A40="","",IF(AI40&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI40">
-        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($O40="",1,0)+IF($P40="",1,0)+IF($S40="",1,0)+IF($U40="",1,0)+IF($Y40="",1,0)+IF($Z40="",1,0)+IF($AA40="",1,0)+IF(AND($AA40="特別徴収を継続（転職先へ引継ぎ）",$AC40=""),1,0)+IF(AND($N40="契約期間満了",$Q40=""),1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0))</f>
+      <c r="AB40" s="47">
+        <f>IF($A40="","",IF(AC40&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC40">
+        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($O40="",1,0)+IF($P40="",1,0)+IF($S40="",1,0)+IF($U40="",1,0)+IF($Y40="",1,0)+IF($Z40="",1,0)+IF(AND($N40="契約期間満了",$Q40=""),1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3899,16 +3433,16 @@
       <c r="A41" s="16" t="n"/>
       <c r="B41" s="16" t="n"/>
       <c r="C41" s="18" t="n"/>
-      <c r="D41" s="46" t="n"/>
-      <c r="E41" s="46" t="n"/>
-      <c r="F41" s="46" t="n"/>
-      <c r="G41" s="46" t="n"/>
+      <c r="D41" s="44" t="n"/>
+      <c r="E41" s="44" t="n"/>
+      <c r="F41" s="44" t="n"/>
+      <c r="G41" s="44" t="n"/>
       <c r="H41" s="16" t="n"/>
       <c r="I41" s="16" t="n"/>
       <c r="J41" s="16" t="n"/>
       <c r="K41" s="16" t="n"/>
       <c r="L41" s="18" t="n"/>
-      <c r="M41" s="47">
+      <c r="M41" s="45">
         <f>IF($L41="","",$L41+1)</f>
         <v/>
       </c>
@@ -3921,26 +3455,17 @@
       <c r="T41" s="16" t="n"/>
       <c r="U41" s="16" t="n"/>
       <c r="V41" s="16" t="n"/>
-      <c r="W41" s="48" t="n"/>
-      <c r="X41" s="48" t="n"/>
+      <c r="W41" s="46" t="n"/>
+      <c r="X41" s="46" t="n"/>
       <c r="Y41" s="16" t="n"/>
       <c r="Z41" s="16" t="n"/>
       <c r="AA41" s="16" t="n"/>
-      <c r="AB41" s="22">
-        <f>IF($L41="","",IF(MONTH($L41)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L41)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC41" s="16" t="n"/>
-      <c r="AD41" s="16" t="n"/>
-      <c r="AE41" s="16" t="n"/>
-      <c r="AF41" s="16" t="n"/>
-      <c r="AG41" s="16" t="n"/>
-      <c r="AH41" s="49">
-        <f>IF($A41="","",IF(AI41&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI41">
-        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($O41="",1,0)+IF($P41="",1,0)+IF($S41="",1,0)+IF($U41="",1,0)+IF($Y41="",1,0)+IF($Z41="",1,0)+IF($AA41="",1,0)+IF(AND($AA41="特別徴収を継続（転職先へ引継ぎ）",$AC41=""),1,0)+IF(AND($N41="契約期間満了",$Q41=""),1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0))</f>
+      <c r="AB41" s="47">
+        <f>IF($A41="","",IF(AC41&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($O41="",1,0)+IF($P41="",1,0)+IF($S41="",1,0)+IF($U41="",1,0)+IF($Y41="",1,0)+IF($Z41="",1,0)+IF(AND($N41="契約期間満了",$Q41=""),1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3948,16 +3473,16 @@
       <c r="A42" s="16" t="n"/>
       <c r="B42" s="16" t="n"/>
       <c r="C42" s="18" t="n"/>
-      <c r="D42" s="46" t="n"/>
-      <c r="E42" s="46" t="n"/>
-      <c r="F42" s="46" t="n"/>
-      <c r="G42" s="46" t="n"/>
+      <c r="D42" s="44" t="n"/>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+      <c r="G42" s="44" t="n"/>
       <c r="H42" s="16" t="n"/>
       <c r="I42" s="16" t="n"/>
       <c r="J42" s="16" t="n"/>
       <c r="K42" s="16" t="n"/>
       <c r="L42" s="18" t="n"/>
-      <c r="M42" s="47">
+      <c r="M42" s="45">
         <f>IF($L42="","",$L42+1)</f>
         <v/>
       </c>
@@ -3970,26 +3495,17 @@
       <c r="T42" s="16" t="n"/>
       <c r="U42" s="16" t="n"/>
       <c r="V42" s="16" t="n"/>
-      <c r="W42" s="48" t="n"/>
-      <c r="X42" s="48" t="n"/>
+      <c r="W42" s="46" t="n"/>
+      <c r="X42" s="46" t="n"/>
       <c r="Y42" s="16" t="n"/>
       <c r="Z42" s="16" t="n"/>
       <c r="AA42" s="16" t="n"/>
-      <c r="AB42" s="22">
-        <f>IF($L42="","",IF(MONTH($L42)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L42)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC42" s="16" t="n"/>
-      <c r="AD42" s="16" t="n"/>
-      <c r="AE42" s="16" t="n"/>
-      <c r="AF42" s="16" t="n"/>
-      <c r="AG42" s="16" t="n"/>
-      <c r="AH42" s="49">
-        <f>IF($A42="","",IF(AI42&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI42">
-        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($O42="",1,0)+IF($P42="",1,0)+IF($S42="",1,0)+IF($U42="",1,0)+IF($Y42="",1,0)+IF($Z42="",1,0)+IF($AA42="",1,0)+IF(AND($AA42="特別徴収を継続（転職先へ引継ぎ）",$AC42=""),1,0)+IF(AND($N42="契約期間満了",$Q42=""),1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0))</f>
+      <c r="AB42" s="47">
+        <f>IF($A42="","",IF(AC42&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($O42="",1,0)+IF($P42="",1,0)+IF($S42="",1,0)+IF($U42="",1,0)+IF($Y42="",1,0)+IF($Z42="",1,0)+IF(AND($N42="契約期間満了",$Q42=""),1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3997,16 +3513,16 @@
       <c r="A43" s="16" t="n"/>
       <c r="B43" s="16" t="n"/>
       <c r="C43" s="18" t="n"/>
-      <c r="D43" s="46" t="n"/>
-      <c r="E43" s="46" t="n"/>
-      <c r="F43" s="46" t="n"/>
-      <c r="G43" s="46" t="n"/>
+      <c r="D43" s="44" t="n"/>
+      <c r="E43" s="44" t="n"/>
+      <c r="F43" s="44" t="n"/>
+      <c r="G43" s="44" t="n"/>
       <c r="H43" s="16" t="n"/>
       <c r="I43" s="16" t="n"/>
       <c r="J43" s="16" t="n"/>
       <c r="K43" s="16" t="n"/>
       <c r="L43" s="18" t="n"/>
-      <c r="M43" s="47">
+      <c r="M43" s="45">
         <f>IF($L43="","",$L43+1)</f>
         <v/>
       </c>
@@ -4019,26 +3535,17 @@
       <c r="T43" s="16" t="n"/>
       <c r="U43" s="16" t="n"/>
       <c r="V43" s="16" t="n"/>
-      <c r="W43" s="48" t="n"/>
-      <c r="X43" s="48" t="n"/>
+      <c r="W43" s="46" t="n"/>
+      <c r="X43" s="46" t="n"/>
       <c r="Y43" s="16" t="n"/>
       <c r="Z43" s="16" t="n"/>
       <c r="AA43" s="16" t="n"/>
-      <c r="AB43" s="22">
-        <f>IF($L43="","",IF(MONTH($L43)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L43)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC43" s="16" t="n"/>
-      <c r="AD43" s="16" t="n"/>
-      <c r="AE43" s="16" t="n"/>
-      <c r="AF43" s="16" t="n"/>
-      <c r="AG43" s="16" t="n"/>
-      <c r="AH43" s="49">
-        <f>IF($A43="","",IF(AI43&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI43">
-        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($O43="",1,0)+IF($P43="",1,0)+IF($S43="",1,0)+IF($U43="",1,0)+IF($Y43="",1,0)+IF($Z43="",1,0)+IF($AA43="",1,0)+IF(AND($AA43="特別徴収を継続（転職先へ引継ぎ）",$AC43=""),1,0)+IF(AND($N43="契約期間満了",$Q43=""),1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0))</f>
+      <c r="AB43" s="47">
+        <f>IF($A43="","",IF(AC43&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($O43="",1,0)+IF($P43="",1,0)+IF($S43="",1,0)+IF($U43="",1,0)+IF($Y43="",1,0)+IF($Z43="",1,0)+IF(AND($N43="契約期間満了",$Q43=""),1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4046,16 +3553,16 @@
       <c r="A44" s="16" t="n"/>
       <c r="B44" s="16" t="n"/>
       <c r="C44" s="18" t="n"/>
-      <c r="D44" s="46" t="n"/>
-      <c r="E44" s="46" t="n"/>
-      <c r="F44" s="46" t="n"/>
-      <c r="G44" s="46" t="n"/>
+      <c r="D44" s="44" t="n"/>
+      <c r="E44" s="44" t="n"/>
+      <c r="F44" s="44" t="n"/>
+      <c r="G44" s="44" t="n"/>
       <c r="H44" s="16" t="n"/>
       <c r="I44" s="16" t="n"/>
       <c r="J44" s="16" t="n"/>
       <c r="K44" s="16" t="n"/>
       <c r="L44" s="18" t="n"/>
-      <c r="M44" s="47">
+      <c r="M44" s="45">
         <f>IF($L44="","",$L44+1)</f>
         <v/>
       </c>
@@ -4068,26 +3575,17 @@
       <c r="T44" s="16" t="n"/>
       <c r="U44" s="16" t="n"/>
       <c r="V44" s="16" t="n"/>
-      <c r="W44" s="48" t="n"/>
-      <c r="X44" s="48" t="n"/>
+      <c r="W44" s="46" t="n"/>
+      <c r="X44" s="46" t="n"/>
       <c r="Y44" s="16" t="n"/>
       <c r="Z44" s="16" t="n"/>
       <c r="AA44" s="16" t="n"/>
-      <c r="AB44" s="22">
-        <f>IF($L44="","",IF(MONTH($L44)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L44)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC44" s="16" t="n"/>
-      <c r="AD44" s="16" t="n"/>
-      <c r="AE44" s="16" t="n"/>
-      <c r="AF44" s="16" t="n"/>
-      <c r="AG44" s="16" t="n"/>
-      <c r="AH44" s="49">
-        <f>IF($A44="","",IF(AI44&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI44">
-        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($O44="",1,0)+IF($P44="",1,0)+IF($S44="",1,0)+IF($U44="",1,0)+IF($Y44="",1,0)+IF($Z44="",1,0)+IF($AA44="",1,0)+IF(AND($AA44="特別徴収を継続（転職先へ引継ぎ）",$AC44=""),1,0)+IF(AND($N44="契約期間満了",$Q44=""),1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0))</f>
+      <c r="AB44" s="47">
+        <f>IF($A44="","",IF(AC44&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($O44="",1,0)+IF($P44="",1,0)+IF($S44="",1,0)+IF($U44="",1,0)+IF($Y44="",1,0)+IF($Z44="",1,0)+IF(AND($N44="契約期間満了",$Q44=""),1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4095,16 +3593,16 @@
       <c r="A45" s="16" t="n"/>
       <c r="B45" s="16" t="n"/>
       <c r="C45" s="18" t="n"/>
-      <c r="D45" s="46" t="n"/>
-      <c r="E45" s="46" t="n"/>
-      <c r="F45" s="46" t="n"/>
-      <c r="G45" s="46" t="n"/>
+      <c r="D45" s="44" t="n"/>
+      <c r="E45" s="44" t="n"/>
+      <c r="F45" s="44" t="n"/>
+      <c r="G45" s="44" t="n"/>
       <c r="H45" s="16" t="n"/>
       <c r="I45" s="16" t="n"/>
       <c r="J45" s="16" t="n"/>
       <c r="K45" s="16" t="n"/>
       <c r="L45" s="18" t="n"/>
-      <c r="M45" s="47">
+      <c r="M45" s="45">
         <f>IF($L45="","",$L45+1)</f>
         <v/>
       </c>
@@ -4117,26 +3615,17 @@
       <c r="T45" s="16" t="n"/>
       <c r="U45" s="16" t="n"/>
       <c r="V45" s="16" t="n"/>
-      <c r="W45" s="48" t="n"/>
-      <c r="X45" s="48" t="n"/>
+      <c r="W45" s="46" t="n"/>
+      <c r="X45" s="46" t="n"/>
       <c r="Y45" s="16" t="n"/>
       <c r="Z45" s="16" t="n"/>
       <c r="AA45" s="16" t="n"/>
-      <c r="AB45" s="22">
-        <f>IF($L45="","",IF(MONTH($L45)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L45)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC45" s="16" t="n"/>
-      <c r="AD45" s="16" t="n"/>
-      <c r="AE45" s="16" t="n"/>
-      <c r="AF45" s="16" t="n"/>
-      <c r="AG45" s="16" t="n"/>
-      <c r="AH45" s="49">
-        <f>IF($A45="","",IF(AI45&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI45">
-        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($O45="",1,0)+IF($P45="",1,0)+IF($S45="",1,0)+IF($U45="",1,0)+IF($Y45="",1,0)+IF($Z45="",1,0)+IF($AA45="",1,0)+IF(AND($AA45="特別徴収を継続（転職先へ引継ぎ）",$AC45=""),1,0)+IF(AND($N45="契約期間満了",$Q45=""),1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0))</f>
+      <c r="AB45" s="47">
+        <f>IF($A45="","",IF(AC45&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($O45="",1,0)+IF($P45="",1,0)+IF($S45="",1,0)+IF($U45="",1,0)+IF($Y45="",1,0)+IF($Z45="",1,0)+IF(AND($N45="契約期間満了",$Q45=""),1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4144,16 +3633,16 @@
       <c r="A46" s="16" t="n"/>
       <c r="B46" s="16" t="n"/>
       <c r="C46" s="18" t="n"/>
-      <c r="D46" s="46" t="n"/>
-      <c r="E46" s="46" t="n"/>
-      <c r="F46" s="46" t="n"/>
-      <c r="G46" s="46" t="n"/>
+      <c r="D46" s="44" t="n"/>
+      <c r="E46" s="44" t="n"/>
+      <c r="F46" s="44" t="n"/>
+      <c r="G46" s="44" t="n"/>
       <c r="H46" s="16" t="n"/>
       <c r="I46" s="16" t="n"/>
       <c r="J46" s="16" t="n"/>
       <c r="K46" s="16" t="n"/>
       <c r="L46" s="18" t="n"/>
-      <c r="M46" s="47">
+      <c r="M46" s="45">
         <f>IF($L46="","",$L46+1)</f>
         <v/>
       </c>
@@ -4166,26 +3655,17 @@
       <c r="T46" s="16" t="n"/>
       <c r="U46" s="16" t="n"/>
       <c r="V46" s="16" t="n"/>
-      <c r="W46" s="48" t="n"/>
-      <c r="X46" s="48" t="n"/>
+      <c r="W46" s="46" t="n"/>
+      <c r="X46" s="46" t="n"/>
       <c r="Y46" s="16" t="n"/>
       <c r="Z46" s="16" t="n"/>
       <c r="AA46" s="16" t="n"/>
-      <c r="AB46" s="22">
-        <f>IF($L46="","",IF(MONTH($L46)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L46)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC46" s="16" t="n"/>
-      <c r="AD46" s="16" t="n"/>
-      <c r="AE46" s="16" t="n"/>
-      <c r="AF46" s="16" t="n"/>
-      <c r="AG46" s="16" t="n"/>
-      <c r="AH46" s="49">
-        <f>IF($A46="","",IF(AI46&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI46">
-        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($O46="",1,0)+IF($P46="",1,0)+IF($S46="",1,0)+IF($U46="",1,0)+IF($Y46="",1,0)+IF($Z46="",1,0)+IF($AA46="",1,0)+IF(AND($AA46="特別徴収を継続（転職先へ引継ぎ）",$AC46=""),1,0)+IF(AND($N46="契約期間満了",$Q46=""),1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0))</f>
+      <c r="AB46" s="47">
+        <f>IF($A46="","",IF(AC46&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($O46="",1,0)+IF($P46="",1,0)+IF($S46="",1,0)+IF($U46="",1,0)+IF($Y46="",1,0)+IF($Z46="",1,0)+IF(AND($N46="契約期間満了",$Q46=""),1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4193,16 +3673,16 @@
       <c r="A47" s="16" t="n"/>
       <c r="B47" s="16" t="n"/>
       <c r="C47" s="18" t="n"/>
-      <c r="D47" s="46" t="n"/>
-      <c r="E47" s="46" t="n"/>
-      <c r="F47" s="46" t="n"/>
-      <c r="G47" s="46" t="n"/>
+      <c r="D47" s="44" t="n"/>
+      <c r="E47" s="44" t="n"/>
+      <c r="F47" s="44" t="n"/>
+      <c r="G47" s="44" t="n"/>
       <c r="H47" s="16" t="n"/>
       <c r="I47" s="16" t="n"/>
       <c r="J47" s="16" t="n"/>
       <c r="K47" s="16" t="n"/>
       <c r="L47" s="18" t="n"/>
-      <c r="M47" s="47">
+      <c r="M47" s="45">
         <f>IF($L47="","",$L47+1)</f>
         <v/>
       </c>
@@ -4215,26 +3695,17 @@
       <c r="T47" s="16" t="n"/>
       <c r="U47" s="16" t="n"/>
       <c r="V47" s="16" t="n"/>
-      <c r="W47" s="48" t="n"/>
-      <c r="X47" s="48" t="n"/>
+      <c r="W47" s="46" t="n"/>
+      <c r="X47" s="46" t="n"/>
       <c r="Y47" s="16" t="n"/>
       <c r="Z47" s="16" t="n"/>
       <c r="AA47" s="16" t="n"/>
-      <c r="AB47" s="22">
-        <f>IF($L47="","",IF(MONTH($L47)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L47)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC47" s="16" t="n"/>
-      <c r="AD47" s="16" t="n"/>
-      <c r="AE47" s="16" t="n"/>
-      <c r="AF47" s="16" t="n"/>
-      <c r="AG47" s="16" t="n"/>
-      <c r="AH47" s="49">
-        <f>IF($A47="","",IF(AI47&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI47">
-        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($O47="",1,0)+IF($P47="",1,0)+IF($S47="",1,0)+IF($U47="",1,0)+IF($Y47="",1,0)+IF($Z47="",1,0)+IF($AA47="",1,0)+IF(AND($AA47="特別徴収を継続（転職先へ引継ぎ）",$AC47=""),1,0)+IF(AND($N47="契約期間満了",$Q47=""),1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0))</f>
+      <c r="AB47" s="47">
+        <f>IF($A47="","",IF(AC47&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($O47="",1,0)+IF($P47="",1,0)+IF($S47="",1,0)+IF($U47="",1,0)+IF($Y47="",1,0)+IF($Z47="",1,0)+IF(AND($N47="契約期間満了",$Q47=""),1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4242,16 +3713,16 @@
       <c r="A48" s="16" t="n"/>
       <c r="B48" s="16" t="n"/>
       <c r="C48" s="18" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
-      <c r="F48" s="46" t="n"/>
-      <c r="G48" s="46" t="n"/>
+      <c r="D48" s="44" t="n"/>
+      <c r="E48" s="44" t="n"/>
+      <c r="F48" s="44" t="n"/>
+      <c r="G48" s="44" t="n"/>
       <c r="H48" s="16" t="n"/>
       <c r="I48" s="16" t="n"/>
       <c r="J48" s="16" t="n"/>
       <c r="K48" s="16" t="n"/>
       <c r="L48" s="18" t="n"/>
-      <c r="M48" s="47">
+      <c r="M48" s="45">
         <f>IF($L48="","",$L48+1)</f>
         <v/>
       </c>
@@ -4264,26 +3735,17 @@
       <c r="T48" s="16" t="n"/>
       <c r="U48" s="16" t="n"/>
       <c r="V48" s="16" t="n"/>
-      <c r="W48" s="48" t="n"/>
-      <c r="X48" s="48" t="n"/>
+      <c r="W48" s="46" t="n"/>
+      <c r="X48" s="46" t="n"/>
       <c r="Y48" s="16" t="n"/>
       <c r="Z48" s="16" t="n"/>
       <c r="AA48" s="16" t="n"/>
-      <c r="AB48" s="22">
-        <f>IF($L48="","",IF(MONTH($L48)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L48)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC48" s="16" t="n"/>
-      <c r="AD48" s="16" t="n"/>
-      <c r="AE48" s="16" t="n"/>
-      <c r="AF48" s="16" t="n"/>
-      <c r="AG48" s="16" t="n"/>
-      <c r="AH48" s="49">
-        <f>IF($A48="","",IF(AI48&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI48">
-        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($O48="",1,0)+IF($P48="",1,0)+IF($S48="",1,0)+IF($U48="",1,0)+IF($Y48="",1,0)+IF($Z48="",1,0)+IF($AA48="",1,0)+IF(AND($AA48="特別徴収を継続（転職先へ引継ぎ）",$AC48=""),1,0)+IF(AND($N48="契約期間満了",$Q48=""),1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0))</f>
+      <c r="AB48" s="47">
+        <f>IF($A48="","",IF(AC48&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($O48="",1,0)+IF($P48="",1,0)+IF($S48="",1,0)+IF($U48="",1,0)+IF($Y48="",1,0)+IF($Z48="",1,0)+IF(AND($N48="契約期間満了",$Q48=""),1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4291,16 +3753,16 @@
       <c r="A49" s="16" t="n"/>
       <c r="B49" s="16" t="n"/>
       <c r="C49" s="18" t="n"/>
-      <c r="D49" s="46" t="n"/>
-      <c r="E49" s="46" t="n"/>
-      <c r="F49" s="46" t="n"/>
-      <c r="G49" s="46" t="n"/>
+      <c r="D49" s="44" t="n"/>
+      <c r="E49" s="44" t="n"/>
+      <c r="F49" s="44" t="n"/>
+      <c r="G49" s="44" t="n"/>
       <c r="H49" s="16" t="n"/>
       <c r="I49" s="16" t="n"/>
       <c r="J49" s="16" t="n"/>
       <c r="K49" s="16" t="n"/>
       <c r="L49" s="18" t="n"/>
-      <c r="M49" s="47">
+      <c r="M49" s="45">
         <f>IF($L49="","",$L49+1)</f>
         <v/>
       </c>
@@ -4313,26 +3775,17 @@
       <c r="T49" s="16" t="n"/>
       <c r="U49" s="16" t="n"/>
       <c r="V49" s="16" t="n"/>
-      <c r="W49" s="48" t="n"/>
-      <c r="X49" s="48" t="n"/>
+      <c r="W49" s="46" t="n"/>
+      <c r="X49" s="46" t="n"/>
       <c r="Y49" s="16" t="n"/>
       <c r="Z49" s="16" t="n"/>
       <c r="AA49" s="16" t="n"/>
-      <c r="AB49" s="22">
-        <f>IF($L49="","",IF(MONTH($L49)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L49)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC49" s="16" t="n"/>
-      <c r="AD49" s="16" t="n"/>
-      <c r="AE49" s="16" t="n"/>
-      <c r="AF49" s="16" t="n"/>
-      <c r="AG49" s="16" t="n"/>
-      <c r="AH49" s="49">
-        <f>IF($A49="","",IF(AI49&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI49">
-        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($O49="",1,0)+IF($P49="",1,0)+IF($S49="",1,0)+IF($U49="",1,0)+IF($Y49="",1,0)+IF($Z49="",1,0)+IF($AA49="",1,0)+IF(AND($AA49="特別徴収を継続（転職先へ引継ぎ）",$AC49=""),1,0)+IF(AND($N49="契約期間満了",$Q49=""),1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0))</f>
+      <c r="AB49" s="47">
+        <f>IF($A49="","",IF(AC49&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC49">
+        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($O49="",1,0)+IF($P49="",1,0)+IF($S49="",1,0)+IF($U49="",1,0)+IF($Y49="",1,0)+IF($Z49="",1,0)+IF(AND($N49="契約期間満了",$Q49=""),1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4340,16 +3793,16 @@
       <c r="A50" s="16" t="n"/>
       <c r="B50" s="16" t="n"/>
       <c r="C50" s="18" t="n"/>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="46" t="n"/>
-      <c r="F50" s="46" t="n"/>
-      <c r="G50" s="46" t="n"/>
+      <c r="D50" s="44" t="n"/>
+      <c r="E50" s="44" t="n"/>
+      <c r="F50" s="44" t="n"/>
+      <c r="G50" s="44" t="n"/>
       <c r="H50" s="16" t="n"/>
       <c r="I50" s="16" t="n"/>
       <c r="J50" s="16" t="n"/>
       <c r="K50" s="16" t="n"/>
       <c r="L50" s="18" t="n"/>
-      <c r="M50" s="47">
+      <c r="M50" s="45">
         <f>IF($L50="","",$L50+1)</f>
         <v/>
       </c>
@@ -4362,26 +3815,17 @@
       <c r="T50" s="16" t="n"/>
       <c r="U50" s="16" t="n"/>
       <c r="V50" s="16" t="n"/>
-      <c r="W50" s="48" t="n"/>
-      <c r="X50" s="48" t="n"/>
+      <c r="W50" s="46" t="n"/>
+      <c r="X50" s="46" t="n"/>
       <c r="Y50" s="16" t="n"/>
       <c r="Z50" s="16" t="n"/>
       <c r="AA50" s="16" t="n"/>
-      <c r="AB50" s="22">
-        <f>IF($L50="","",IF(MONTH($L50)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L50)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC50" s="16" t="n"/>
-      <c r="AD50" s="16" t="n"/>
-      <c r="AE50" s="16" t="n"/>
-      <c r="AF50" s="16" t="n"/>
-      <c r="AG50" s="16" t="n"/>
-      <c r="AH50" s="49">
-        <f>IF($A50="","",IF(AI50&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI50">
-        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($O50="",1,0)+IF($P50="",1,0)+IF($S50="",1,0)+IF($U50="",1,0)+IF($Y50="",1,0)+IF($Z50="",1,0)+IF($AA50="",1,0)+IF(AND($AA50="特別徴収を継続（転職先へ引継ぎ）",$AC50=""),1,0)+IF(AND($N50="契約期間満了",$Q50=""),1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0))</f>
+      <c r="AB50" s="47">
+        <f>IF($A50="","",IF(AC50&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($O50="",1,0)+IF($P50="",1,0)+IF($S50="",1,0)+IF($U50="",1,0)+IF($Y50="",1,0)+IF($Z50="",1,0)+IF(AND($N50="契約期間満了",$Q50=""),1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4389,16 +3833,16 @@
       <c r="A51" s="16" t="n"/>
       <c r="B51" s="16" t="n"/>
       <c r="C51" s="18" t="n"/>
-      <c r="D51" s="46" t="n"/>
-      <c r="E51" s="46" t="n"/>
-      <c r="F51" s="46" t="n"/>
-      <c r="G51" s="46" t="n"/>
+      <c r="D51" s="44" t="n"/>
+      <c r="E51" s="44" t="n"/>
+      <c r="F51" s="44" t="n"/>
+      <c r="G51" s="44" t="n"/>
       <c r="H51" s="16" t="n"/>
       <c r="I51" s="16" t="n"/>
       <c r="J51" s="16" t="n"/>
       <c r="K51" s="16" t="n"/>
       <c r="L51" s="18" t="n"/>
-      <c r="M51" s="47">
+      <c r="M51" s="45">
         <f>IF($L51="","",$L51+1)</f>
         <v/>
       </c>
@@ -4411,26 +3855,17 @@
       <c r="T51" s="16" t="n"/>
       <c r="U51" s="16" t="n"/>
       <c r="V51" s="16" t="n"/>
-      <c r="W51" s="48" t="n"/>
-      <c r="X51" s="48" t="n"/>
+      <c r="W51" s="46" t="n"/>
+      <c r="X51" s="46" t="n"/>
       <c r="Y51" s="16" t="n"/>
       <c r="Z51" s="16" t="n"/>
       <c r="AA51" s="16" t="n"/>
-      <c r="AB51" s="22">
-        <f>IF($L51="","",IF(MONTH($L51)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L51)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC51" s="16" t="n"/>
-      <c r="AD51" s="16" t="n"/>
-      <c r="AE51" s="16" t="n"/>
-      <c r="AF51" s="16" t="n"/>
-      <c r="AG51" s="16" t="n"/>
-      <c r="AH51" s="49">
-        <f>IF($A51="","",IF(AI51&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI51">
-        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($O51="",1,0)+IF($P51="",1,0)+IF($S51="",1,0)+IF($U51="",1,0)+IF($Y51="",1,0)+IF($Z51="",1,0)+IF($AA51="",1,0)+IF(AND($AA51="特別徴収を継続（転職先へ引継ぎ）",$AC51=""),1,0)+IF(AND($N51="契約期間満了",$Q51=""),1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0))</f>
+      <c r="AB51" s="47">
+        <f>IF($A51="","",IF(AC51&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($O51="",1,0)+IF($P51="",1,0)+IF($S51="",1,0)+IF($U51="",1,0)+IF($Y51="",1,0)+IF($Z51="",1,0)+IF(AND($N51="契約期間満了",$Q51=""),1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4438,16 +3873,16 @@
       <c r="A52" s="16" t="n"/>
       <c r="B52" s="16" t="n"/>
       <c r="C52" s="18" t="n"/>
-      <c r="D52" s="46" t="n"/>
-      <c r="E52" s="46" t="n"/>
-      <c r="F52" s="46" t="n"/>
-      <c r="G52" s="46" t="n"/>
+      <c r="D52" s="44" t="n"/>
+      <c r="E52" s="44" t="n"/>
+      <c r="F52" s="44" t="n"/>
+      <c r="G52" s="44" t="n"/>
       <c r="H52" s="16" t="n"/>
       <c r="I52" s="16" t="n"/>
       <c r="J52" s="16" t="n"/>
       <c r="K52" s="16" t="n"/>
       <c r="L52" s="18" t="n"/>
-      <c r="M52" s="47">
+      <c r="M52" s="45">
         <f>IF($L52="","",$L52+1)</f>
         <v/>
       </c>
@@ -4460,26 +3895,17 @@
       <c r="T52" s="16" t="n"/>
       <c r="U52" s="16" t="n"/>
       <c r="V52" s="16" t="n"/>
-      <c r="W52" s="48" t="n"/>
-      <c r="X52" s="48" t="n"/>
+      <c r="W52" s="46" t="n"/>
+      <c r="X52" s="46" t="n"/>
       <c r="Y52" s="16" t="n"/>
       <c r="Z52" s="16" t="n"/>
       <c r="AA52" s="16" t="n"/>
-      <c r="AB52" s="22">
-        <f>IF($L52="","",IF(MONTH($L52)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L52)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC52" s="16" t="n"/>
-      <c r="AD52" s="16" t="n"/>
-      <c r="AE52" s="16" t="n"/>
-      <c r="AF52" s="16" t="n"/>
-      <c r="AG52" s="16" t="n"/>
-      <c r="AH52" s="49">
-        <f>IF($A52="","",IF(AI52&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI52">
-        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($O52="",1,0)+IF($P52="",1,0)+IF($S52="",1,0)+IF($U52="",1,0)+IF($Y52="",1,0)+IF($Z52="",1,0)+IF($AA52="",1,0)+IF(AND($AA52="特別徴収を継続（転職先へ引継ぎ）",$AC52=""),1,0)+IF(AND($N52="契約期間満了",$Q52=""),1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0))</f>
+      <c r="AB52" s="47">
+        <f>IF($A52="","",IF(AC52&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($O52="",1,0)+IF($P52="",1,0)+IF($S52="",1,0)+IF($U52="",1,0)+IF($Y52="",1,0)+IF($Z52="",1,0)+IF(AND($N52="契約期間満了",$Q52=""),1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4487,16 +3913,16 @@
       <c r="A53" s="16" t="n"/>
       <c r="B53" s="16" t="n"/>
       <c r="C53" s="18" t="n"/>
-      <c r="D53" s="46" t="n"/>
-      <c r="E53" s="46" t="n"/>
-      <c r="F53" s="46" t="n"/>
-      <c r="G53" s="46" t="n"/>
+      <c r="D53" s="44" t="n"/>
+      <c r="E53" s="44" t="n"/>
+      <c r="F53" s="44" t="n"/>
+      <c r="G53" s="44" t="n"/>
       <c r="H53" s="16" t="n"/>
       <c r="I53" s="16" t="n"/>
       <c r="J53" s="16" t="n"/>
       <c r="K53" s="16" t="n"/>
       <c r="L53" s="18" t="n"/>
-      <c r="M53" s="47">
+      <c r="M53" s="45">
         <f>IF($L53="","",$L53+1)</f>
         <v/>
       </c>
@@ -4509,26 +3935,17 @@
       <c r="T53" s="16" t="n"/>
       <c r="U53" s="16" t="n"/>
       <c r="V53" s="16" t="n"/>
-      <c r="W53" s="48" t="n"/>
-      <c r="X53" s="48" t="n"/>
+      <c r="W53" s="46" t="n"/>
+      <c r="X53" s="46" t="n"/>
       <c r="Y53" s="16" t="n"/>
       <c r="Z53" s="16" t="n"/>
       <c r="AA53" s="16" t="n"/>
-      <c r="AB53" s="22">
-        <f>IF($L53="","",IF(MONTH($L53)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L53)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC53" s="16" t="n"/>
-      <c r="AD53" s="16" t="n"/>
-      <c r="AE53" s="16" t="n"/>
-      <c r="AF53" s="16" t="n"/>
-      <c r="AG53" s="16" t="n"/>
-      <c r="AH53" s="49">
-        <f>IF($A53="","",IF(AI53&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI53">
-        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($O53="",1,0)+IF($P53="",1,0)+IF($S53="",1,0)+IF($U53="",1,0)+IF($Y53="",1,0)+IF($Z53="",1,0)+IF($AA53="",1,0)+IF(AND($AA53="特別徴収を継続（転職先へ引継ぎ）",$AC53=""),1,0)+IF(AND($N53="契約期間満了",$Q53=""),1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0))</f>
+      <c r="AB53" s="47">
+        <f>IF($A53="","",IF(AC53&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC53">
+        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($O53="",1,0)+IF($P53="",1,0)+IF($S53="",1,0)+IF($U53="",1,0)+IF($Y53="",1,0)+IF($Z53="",1,0)+IF(AND($N53="契約期間満了",$Q53=""),1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4536,16 +3953,16 @@
       <c r="A54" s="16" t="n"/>
       <c r="B54" s="16" t="n"/>
       <c r="C54" s="18" t="n"/>
-      <c r="D54" s="46" t="n"/>
-      <c r="E54" s="46" t="n"/>
-      <c r="F54" s="46" t="n"/>
-      <c r="G54" s="46" t="n"/>
+      <c r="D54" s="44" t="n"/>
+      <c r="E54" s="44" t="n"/>
+      <c r="F54" s="44" t="n"/>
+      <c r="G54" s="44" t="n"/>
       <c r="H54" s="16" t="n"/>
       <c r="I54" s="16" t="n"/>
       <c r="J54" s="16" t="n"/>
       <c r="K54" s="16" t="n"/>
       <c r="L54" s="18" t="n"/>
-      <c r="M54" s="47">
+      <c r="M54" s="45">
         <f>IF($L54="","",$L54+1)</f>
         <v/>
       </c>
@@ -4558,26 +3975,17 @@
       <c r="T54" s="16" t="n"/>
       <c r="U54" s="16" t="n"/>
       <c r="V54" s="16" t="n"/>
-      <c r="W54" s="48" t="n"/>
-      <c r="X54" s="48" t="n"/>
+      <c r="W54" s="46" t="n"/>
+      <c r="X54" s="46" t="n"/>
       <c r="Y54" s="16" t="n"/>
       <c r="Z54" s="16" t="n"/>
       <c r="AA54" s="16" t="n"/>
-      <c r="AB54" s="22">
-        <f>IF($L54="","",IF(MONTH($L54)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L54)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC54" s="16" t="n"/>
-      <c r="AD54" s="16" t="n"/>
-      <c r="AE54" s="16" t="n"/>
-      <c r="AF54" s="16" t="n"/>
-      <c r="AG54" s="16" t="n"/>
-      <c r="AH54" s="49">
-        <f>IF($A54="","",IF(AI54&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI54">
-        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($O54="",1,0)+IF($P54="",1,0)+IF($S54="",1,0)+IF($U54="",1,0)+IF($Y54="",1,0)+IF($Z54="",1,0)+IF($AA54="",1,0)+IF(AND($AA54="特別徴収を継続（転職先へ引継ぎ）",$AC54=""),1,0)+IF(AND($N54="契約期間満了",$Q54=""),1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0))</f>
+      <c r="AB54" s="47">
+        <f>IF($A54="","",IF(AC54&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC54">
+        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($O54="",1,0)+IF($P54="",1,0)+IF($S54="",1,0)+IF($U54="",1,0)+IF($Y54="",1,0)+IF($Z54="",1,0)+IF(AND($N54="契約期間満了",$Q54=""),1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4585,16 +3993,16 @@
       <c r="A55" s="16" t="n"/>
       <c r="B55" s="16" t="n"/>
       <c r="C55" s="18" t="n"/>
-      <c r="D55" s="46" t="n"/>
-      <c r="E55" s="46" t="n"/>
-      <c r="F55" s="46" t="n"/>
-      <c r="G55" s="46" t="n"/>
+      <c r="D55" s="44" t="n"/>
+      <c r="E55" s="44" t="n"/>
+      <c r="F55" s="44" t="n"/>
+      <c r="G55" s="44" t="n"/>
       <c r="H55" s="16" t="n"/>
       <c r="I55" s="16" t="n"/>
       <c r="J55" s="16" t="n"/>
       <c r="K55" s="16" t="n"/>
       <c r="L55" s="18" t="n"/>
-      <c r="M55" s="47">
+      <c r="M55" s="45">
         <f>IF($L55="","",$L55+1)</f>
         <v/>
       </c>
@@ -4607,26 +4015,17 @@
       <c r="T55" s="16" t="n"/>
       <c r="U55" s="16" t="n"/>
       <c r="V55" s="16" t="n"/>
-      <c r="W55" s="48" t="n"/>
-      <c r="X55" s="48" t="n"/>
+      <c r="W55" s="46" t="n"/>
+      <c r="X55" s="46" t="n"/>
       <c r="Y55" s="16" t="n"/>
       <c r="Z55" s="16" t="n"/>
       <c r="AA55" s="16" t="n"/>
-      <c r="AB55" s="22">
-        <f>IF($L55="","",IF(MONTH($L55)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L55)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC55" s="16" t="n"/>
-      <c r="AD55" s="16" t="n"/>
-      <c r="AE55" s="16" t="n"/>
-      <c r="AF55" s="16" t="n"/>
-      <c r="AG55" s="16" t="n"/>
-      <c r="AH55" s="49">
-        <f>IF($A55="","",IF(AI55&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI55">
-        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($O55="",1,0)+IF($P55="",1,0)+IF($S55="",1,0)+IF($U55="",1,0)+IF($Y55="",1,0)+IF($Z55="",1,0)+IF($AA55="",1,0)+IF(AND($AA55="特別徴収を継続（転職先へ引継ぎ）",$AC55=""),1,0)+IF(AND($N55="契約期間満了",$Q55=""),1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0))</f>
+      <c r="AB55" s="47">
+        <f>IF($A55="","",IF(AC55&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC55">
+        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($O55="",1,0)+IF($P55="",1,0)+IF($S55="",1,0)+IF($U55="",1,0)+IF($Y55="",1,0)+IF($Z55="",1,0)+IF(AND($N55="契約期間満了",$Q55=""),1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4634,16 +4033,16 @@
       <c r="A56" s="16" t="n"/>
       <c r="B56" s="16" t="n"/>
       <c r="C56" s="18" t="n"/>
-      <c r="D56" s="46" t="n"/>
-      <c r="E56" s="46" t="n"/>
-      <c r="F56" s="46" t="n"/>
-      <c r="G56" s="46" t="n"/>
+      <c r="D56" s="44" t="n"/>
+      <c r="E56" s="44" t="n"/>
+      <c r="F56" s="44" t="n"/>
+      <c r="G56" s="44" t="n"/>
       <c r="H56" s="16" t="n"/>
       <c r="I56" s="16" t="n"/>
       <c r="J56" s="16" t="n"/>
       <c r="K56" s="16" t="n"/>
       <c r="L56" s="18" t="n"/>
-      <c r="M56" s="47">
+      <c r="M56" s="45">
         <f>IF($L56="","",$L56+1)</f>
         <v/>
       </c>
@@ -4656,26 +4055,17 @@
       <c r="T56" s="16" t="n"/>
       <c r="U56" s="16" t="n"/>
       <c r="V56" s="16" t="n"/>
-      <c r="W56" s="48" t="n"/>
-      <c r="X56" s="48" t="n"/>
+      <c r="W56" s="46" t="n"/>
+      <c r="X56" s="46" t="n"/>
       <c r="Y56" s="16" t="n"/>
       <c r="Z56" s="16" t="n"/>
       <c r="AA56" s="16" t="n"/>
-      <c r="AB56" s="22">
-        <f>IF($L56="","",IF(MONTH($L56)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L56)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC56" s="16" t="n"/>
-      <c r="AD56" s="16" t="n"/>
-      <c r="AE56" s="16" t="n"/>
-      <c r="AF56" s="16" t="n"/>
-      <c r="AG56" s="16" t="n"/>
-      <c r="AH56" s="49">
-        <f>IF($A56="","",IF(AI56&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI56">
-        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($O56="",1,0)+IF($P56="",1,0)+IF($S56="",1,0)+IF($U56="",1,0)+IF($Y56="",1,0)+IF($Z56="",1,0)+IF($AA56="",1,0)+IF(AND($AA56="特別徴収を継続（転職先へ引継ぎ）",$AC56=""),1,0)+IF(AND($N56="契約期間満了",$Q56=""),1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0))</f>
+      <c r="AB56" s="47">
+        <f>IF($A56="","",IF(AC56&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($O56="",1,0)+IF($P56="",1,0)+IF($S56="",1,0)+IF($U56="",1,0)+IF($Y56="",1,0)+IF($Z56="",1,0)+IF(AND($N56="契約期間満了",$Q56=""),1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4683,16 +4073,16 @@
       <c r="A57" s="16" t="n"/>
       <c r="B57" s="16" t="n"/>
       <c r="C57" s="18" t="n"/>
-      <c r="D57" s="46" t="n"/>
-      <c r="E57" s="46" t="n"/>
-      <c r="F57" s="46" t="n"/>
-      <c r="G57" s="46" t="n"/>
+      <c r="D57" s="44" t="n"/>
+      <c r="E57" s="44" t="n"/>
+      <c r="F57" s="44" t="n"/>
+      <c r="G57" s="44" t="n"/>
       <c r="H57" s="16" t="n"/>
       <c r="I57" s="16" t="n"/>
       <c r="J57" s="16" t="n"/>
       <c r="K57" s="16" t="n"/>
       <c r="L57" s="18" t="n"/>
-      <c r="M57" s="47">
+      <c r="M57" s="45">
         <f>IF($L57="","",$L57+1)</f>
         <v/>
       </c>
@@ -4705,26 +4095,17 @@
       <c r="T57" s="16" t="n"/>
       <c r="U57" s="16" t="n"/>
       <c r="V57" s="16" t="n"/>
-      <c r="W57" s="48" t="n"/>
-      <c r="X57" s="48" t="n"/>
+      <c r="W57" s="46" t="n"/>
+      <c r="X57" s="46" t="n"/>
       <c r="Y57" s="16" t="n"/>
       <c r="Z57" s="16" t="n"/>
       <c r="AA57" s="16" t="n"/>
-      <c r="AB57" s="22">
-        <f>IF($L57="","",IF(MONTH($L57)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L57)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC57" s="16" t="n"/>
-      <c r="AD57" s="16" t="n"/>
-      <c r="AE57" s="16" t="n"/>
-      <c r="AF57" s="16" t="n"/>
-      <c r="AG57" s="16" t="n"/>
-      <c r="AH57" s="49">
-        <f>IF($A57="","",IF(AI57&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI57">
-        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($O57="",1,0)+IF($P57="",1,0)+IF($S57="",1,0)+IF($U57="",1,0)+IF($Y57="",1,0)+IF($Z57="",1,0)+IF($AA57="",1,0)+IF(AND($AA57="特別徴収を継続（転職先へ引継ぎ）",$AC57=""),1,0)+IF(AND($N57="契約期間満了",$Q57=""),1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0))</f>
+      <c r="AB57" s="47">
+        <f>IF($A57="","",IF(AC57&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($O57="",1,0)+IF($P57="",1,0)+IF($S57="",1,0)+IF($U57="",1,0)+IF($Y57="",1,0)+IF($Z57="",1,0)+IF(AND($N57="契約期間満了",$Q57=""),1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4732,16 +4113,16 @@
       <c r="A58" s="16" t="n"/>
       <c r="B58" s="16" t="n"/>
       <c r="C58" s="18" t="n"/>
-      <c r="D58" s="46" t="n"/>
-      <c r="E58" s="46" t="n"/>
-      <c r="F58" s="46" t="n"/>
-      <c r="G58" s="46" t="n"/>
+      <c r="D58" s="44" t="n"/>
+      <c r="E58" s="44" t="n"/>
+      <c r="F58" s="44" t="n"/>
+      <c r="G58" s="44" t="n"/>
       <c r="H58" s="16" t="n"/>
       <c r="I58" s="16" t="n"/>
       <c r="J58" s="16" t="n"/>
       <c r="K58" s="16" t="n"/>
       <c r="L58" s="18" t="n"/>
-      <c r="M58" s="47">
+      <c r="M58" s="45">
         <f>IF($L58="","",$L58+1)</f>
         <v/>
       </c>
@@ -4754,43 +4135,32 @@
       <c r="T58" s="16" t="n"/>
       <c r="U58" s="16" t="n"/>
       <c r="V58" s="16" t="n"/>
-      <c r="W58" s="48" t="n"/>
-      <c r="X58" s="48" t="n"/>
+      <c r="W58" s="46" t="n"/>
+      <c r="X58" s="46" t="n"/>
       <c r="Y58" s="16" t="n"/>
       <c r="Z58" s="16" t="n"/>
       <c r="AA58" s="16" t="n"/>
-      <c r="AB58" s="22">
-        <f>IF($L58="","",IF(MONTH($L58)&lt;=4,"1〜4月退職：原則 一括徴収（5月分まで）",IF(MONTH($L58)=5,"5月退職：最終月（通常徴収で完了）","6〜12月退職：本人希望で一括／なければ普通徴収")))</f>
-        <v/>
-      </c>
-      <c r="AC58" s="16" t="n"/>
-      <c r="AD58" s="16" t="n"/>
-      <c r="AE58" s="16" t="n"/>
-      <c r="AF58" s="16" t="n"/>
-      <c r="AG58" s="16" t="n"/>
-      <c r="AH58" s="49">
-        <f>IF($A58="","",IF(AI58&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI58">
-        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($O58="",1,0)+IF($P58="",1,0)+IF($S58="",1,0)+IF($U58="",1,0)+IF($Y58="",1,0)+IF($Z58="",1,0)+IF($AA58="",1,0)+IF(AND($AA58="特別徴収を継続（転職先へ引継ぎ）",$AC58=""),1,0)+IF(AND($N58="契約期間満了",$Q58=""),1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0))</f>
+      <c r="AB58" s="47">
+        <f>IF($A58="","",IF(AC58&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AC58">
+        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($O58="",1,0)+IF($P58="",1,0)+IF($S58="",1,0)+IF($U58="",1,0)+IF($Y58="",1,0)+IF($Z58="",1,0)+IF(AND($N58="契約期間満了",$Q58=""),1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A6:K6"/>
+    <mergeCell ref="N1:AA1"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="S6:X6"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="AA6"/>
     <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AG6"/>
-    <mergeCell ref="Q1:AG1"/>
-    <mergeCell ref="AA6:AD6"/>
     <mergeCell ref="L6:R6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
@@ -4819,10 +4189,10 @@
     <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",B9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="31" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",LENB(B9)&lt;&gt;LEN(B9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",ISERROR(FIND("　",B9)),ISERROR(FIND(" ",B9)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4830,7 +4200,7 @@
     <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",C9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="33" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(C9),C9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4838,10 +4208,10 @@
     <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",D9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="25" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LEN(D9)&lt;&gt;12)</formula>
     </cfRule>
-    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LENB(D9)&lt;&gt;LEN(D9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4849,10 +4219,10 @@
     <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",E9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LEN(E9)&lt;&gt;10)</formula>
     </cfRule>
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LENB(E9)&lt;&gt;LEN(E9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4860,10 +4230,10 @@
     <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",F9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="27" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LEN(F9)&lt;&gt;11)</formula>
     </cfRule>
-    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LENB(F9)&lt;&gt;LEN(F9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4871,10 +4241,10 @@
     <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",G9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="28" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LEN(SUBSTITUTE(G9,"-",""))&lt;&gt;7)</formula>
     </cfRule>
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LENB(G9)&lt;&gt;LEN(G9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4887,7 +4257,7 @@
     <cfRule type="expression" priority="11" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",I9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>AND(I9&lt;&gt;"",LENB(I9)&lt;&gt;LEN(I9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4895,7 +4265,7 @@
     <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",L9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(L9),L9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4934,70 +4304,52 @@
       <formula>AND($A9&lt;&gt;"",Z9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA9:AA58">
+  <conditionalFormatting sqref="A9:A58">
     <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",AA9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A58">
-    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
       <formula>AND($A9="",OR($L9&lt;&gt;"",$N9&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="29" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",LENB(A9)&lt;&gt;LEN(A9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="33" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="30" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",ISERROR(FIND("　",A9)),ISERROR(FIND(" ",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC9:AC58">
-    <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
-      <formula>AND($AA9="特別徴収を継続（転職先へ引継ぎ）",AC9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="25" dxfId="3" stopIfTrue="1">
-      <formula>AND($AA9&lt;&gt;"",$AA9&lt;&gt;"特別徴収を継続（転職先へ引継ぎ）",AC9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Q9:Q58">
-    <cfRule type="expression" priority="23" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",Q9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="26" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="3" stopIfTrue="1">
       <formula>AND($N9&lt;&gt;"",$N9&lt;&gt;"契約期間満了",Q9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:R58">
-    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",R9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="27" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="24" dxfId="3" stopIfTrue="1">
       <formula>AND($N9&lt;&gt;"",$N9&lt;&gt;"契約期間満了",R9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J58">
-    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
       <formula>AND(J9&lt;&gt;"",LENB(J9)&lt;&gt;LEN(J9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K58">
-    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
       <formula>AND(K9&lt;&gt;"",LENB(K9)&lt;&gt;LEN(K9))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD9:AD58">
-    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
-      <formula>AND(AD9&lt;&gt;"",LENB(AD9)&lt;&gt;LEN(AD9)*2)</formula>
+  <conditionalFormatting sqref="AB9:AB58">
+    <cfRule type="expression" priority="42" dxfId="0" stopIfTrue="1">
+      <formula>AB9="CSV可"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
+      <formula>AB9="未入力"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH9:AH58">
-    <cfRule type="expression" priority="46" dxfId="0" stopIfTrue="1">
-      <formula>AH9="CSV可"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
-      <formula>AH9="未入力"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="20">
+  <dataValidations count="17">
     <dataValidation sqref="C8:C58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦の生年月日。例 1990/4/1。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
@@ -5048,20 +4400,11 @@
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の保険証/資格確認書の回収状況。" type="list" errorStyle="stop">
+    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
       <formula1>m_回収状況</formula1>
     </dataValidation>
     <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職後の医療保険の予定（任意継続・扶養・国保）。" type="list" errorStyle="stop">
       <formula1>m_退職後</formula1>
-    </dataValidation>
-    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職後の住民税の取扱い。&#10;特別徴収の継続（転職先へ引継ぎ）／一括徴収（最終給与・退職金から）／普通徴収へ切替（自分で納付）から選択。" type="list" errorStyle="stop">
-      <formula1>m_住民税</formula1>
-    </dataValidation>
-    <dataValidation sqref="AE8:AE58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職金（退職手当）の支給予定の有無。" type="list" errorStyle="stop">
-      <formula1>m_退職金</formula1>
-    </dataValidation>
-    <dataValidation sqref="AF8:AF58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職金がある場合、本人から『退職所得の受給に関する申告書』を受領。&#10;未提出だと退職金に一律20.42%が源泉徴収されます。" type="list" errorStyle="stop">
-      <formula1>m_退職所得申告</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5098,631 +4441,631 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.5" customHeight="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>性別</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="48" t="inlineStr">
         <is>
           <t>あり/なし</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="48" t="inlineStr">
         <is>
           <t>都道府県</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="48" t="inlineStr">
         <is>
           <t>番号提出状態</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="48" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="F1" s="50" t="inlineStr">
+      <c r="F1" s="48" t="inlineStr">
         <is>
           <t>雇保番号状態</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="48" t="inlineStr">
         <is>
           <t>退職理由</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="48" t="inlineStr">
         <is>
           <t>離職理由区分</t>
         </is>
       </c>
-      <c r="I1" s="50" t="inlineStr">
+      <c r="I1" s="48" t="inlineStr">
         <is>
           <t>契約更新条項</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="J1" s="48" t="inlineStr">
         <is>
           <t>更新希望</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
+      <c r="K1" s="48" t="inlineStr">
         <is>
           <t>回収状況</t>
         </is>
       </c>
-      <c r="L1" s="50" t="inlineStr">
+      <c r="L1" s="48" t="inlineStr">
         <is>
           <t>退職後</t>
         </is>
       </c>
-      <c r="M1" s="50" t="inlineStr">
+      <c r="M1" s="48" t="inlineStr">
         <is>
           <t>住民税徴収方法</t>
         </is>
       </c>
-      <c r="N1" s="50" t="inlineStr">
+      <c r="N1" s="48" t="inlineStr">
         <is>
           <t>退職金支給</t>
         </is>
       </c>
-      <c r="O1" s="50" t="inlineStr">
+      <c r="O1" s="48" t="inlineStr">
         <is>
           <t>退職所得申告書</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="B2" s="51" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C2" s="51" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="D2" s="51" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="E2" s="51" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="F2" s="51" t="inlineStr">
+      <c r="F2" s="49" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="G2" s="51" t="inlineStr">
+      <c r="G2" s="49" t="inlineStr">
         <is>
           <t>自己都合</t>
         </is>
       </c>
-      <c r="H2" s="51" t="inlineStr">
+      <c r="H2" s="49" t="inlineStr">
         <is>
           <t>一般（自己都合等）</t>
         </is>
       </c>
-      <c r="I2" s="51" t="inlineStr">
+      <c r="I2" s="49" t="inlineStr">
         <is>
           <t>該当なし（無期契約）</t>
         </is>
       </c>
-      <c r="J2" s="51" t="inlineStr">
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>該当なし</t>
         </is>
       </c>
-      <c r="K2" s="51" t="inlineStr">
+      <c r="K2" s="49" t="inlineStr">
         <is>
           <t>回収済</t>
         </is>
       </c>
-      <c r="L2" s="51" t="inlineStr">
+      <c r="L2" s="49" t="inlineStr">
         <is>
           <t>任意継続を希望</t>
         </is>
       </c>
-      <c r="M2" s="51" t="inlineStr">
+      <c r="M2" s="49" t="inlineStr">
         <is>
           <t>特別徴収を継続（転職先へ引継ぎ）</t>
         </is>
       </c>
-      <c r="N2" s="51" t="inlineStr">
+      <c r="N2" s="49" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="O2" s="51" t="inlineStr">
+      <c r="O2" s="49" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="B3" s="51" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C3" s="51" t="inlineStr">
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>青森県</t>
         </is>
       </c>
-      <c r="D3" s="51" t="inlineStr">
+      <c r="D3" s="49" t="inlineStr">
         <is>
           <t>別経路提出</t>
         </is>
       </c>
-      <c r="F3" s="51" t="inlineStr">
+      <c r="F3" s="49" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="G3" s="51" t="inlineStr">
+      <c r="G3" s="49" t="inlineStr">
         <is>
           <t>会社都合（解雇）</t>
         </is>
       </c>
-      <c r="H3" s="51" t="inlineStr">
+      <c r="H3" s="49" t="inlineStr">
         <is>
           <t>特定受給資格者（解雇・倒産等）</t>
         </is>
       </c>
-      <c r="I3" s="51" t="inlineStr">
+      <c r="I3" s="49" t="inlineStr">
         <is>
           <t>更新の明示なし</t>
         </is>
       </c>
-      <c r="J3" s="51" t="inlineStr">
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>更新を希望していた</t>
         </is>
       </c>
-      <c r="K3" s="51" t="inlineStr">
+      <c r="K3" s="49" t="inlineStr">
         <is>
           <t>未回収</t>
         </is>
       </c>
-      <c r="L3" s="51" t="inlineStr">
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>家族の扶養に入る</t>
         </is>
       </c>
-      <c r="M3" s="51" t="inlineStr">
+      <c r="M3" s="49" t="inlineStr">
         <is>
           <t>一括徴収（最終給与・退職金から）</t>
         </is>
       </c>
-      <c r="N3" s="51" t="inlineStr">
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="O3" s="51" t="inlineStr">
+      <c r="O3" s="49" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="51" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>岩手県</t>
         </is>
       </c>
-      <c r="G4" s="51" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>定年</t>
         </is>
       </c>
-      <c r="H4" s="51" t="inlineStr">
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>特定理由離職者（雇止め・正当な理由の自己都合）</t>
         </is>
       </c>
-      <c r="I4" s="51" t="inlineStr">
+      <c r="I4" s="49" t="inlineStr">
         <is>
           <t>更新する場合がある旨の明示あり</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>更新を希望しなかった</t>
         </is>
       </c>
-      <c r="K4" s="51" t="inlineStr">
+      <c r="K4" s="49" t="inlineStr">
         <is>
           <t>本人保管（資格確認書）</t>
         </is>
       </c>
-      <c r="L4" s="51" t="inlineStr">
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>国民健康保険へ</t>
         </is>
       </c>
-      <c r="M4" s="51" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>普通徴収へ切替（自分で納付）</t>
         </is>
       </c>
-      <c r="N4" s="51" t="inlineStr">
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="O4" s="51" t="inlineStr">
+      <c r="O4" s="49" t="inlineStr">
         <is>
           <t>該当なし</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>宮城県</t>
         </is>
       </c>
-      <c r="G5" s="51" t="inlineStr">
+      <c r="G5" s="49" t="inlineStr">
         <is>
           <t>契約期間満了</t>
         </is>
       </c>
-      <c r="H5" s="51" t="inlineStr">
+      <c r="H5" s="49" t="inlineStr">
         <is>
           <t>区分不明</t>
         </is>
       </c>
-      <c r="I5" s="51" t="inlineStr">
+      <c r="I5" s="49" t="inlineStr">
         <is>
           <t>更新する旨の明示あり（自動更新含む）</t>
         </is>
       </c>
-      <c r="K5" s="51" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="L5" s="51" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>未定・不明</t>
         </is>
       </c>
-      <c r="M5" s="51" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>不明・要相談</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="G6" s="51" t="inlineStr">
+      <c r="G6" s="49" t="inlineStr">
         <is>
           <t>役員退任</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="51" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>山形県</t>
         </is>
       </c>
-      <c r="G7" s="51" t="inlineStr">
+      <c r="G7" s="49" t="inlineStr">
         <is>
           <t>death（死亡）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="51" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="G8" s="51" t="inlineStr">
+      <c r="G8" s="49" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="51" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="51" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="51" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>群馬県</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="51" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>埼玉県</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="51" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>千葉県</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="51" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="51" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="51" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>新潟県</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="51" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>富山県</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="51" t="inlineStr">
+      <c r="C18" s="49" t="inlineStr">
         <is>
           <t>石川県</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="51" t="inlineStr">
+      <c r="C19" s="49" t="inlineStr">
         <is>
           <t>福井県</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="51" t="inlineStr">
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>山梨県</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="51" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>長野県</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="51" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>岐阜県</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="51" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>静岡県</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="51" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>愛知県</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="51" t="inlineStr">
+      <c r="C25" s="49" t="inlineStr">
         <is>
           <t>三重県</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="51" t="inlineStr">
+      <c r="C26" s="49" t="inlineStr">
         <is>
           <t>滋賀県</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="51" t="inlineStr">
+      <c r="C27" s="49" t="inlineStr">
         <is>
           <t>京都府</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="51" t="inlineStr">
+      <c r="C28" s="49" t="inlineStr">
         <is>
           <t>大阪府</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="51" t="inlineStr">
+      <c r="C29" s="49" t="inlineStr">
         <is>
           <t>兵庫県</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="51" t="inlineStr">
+      <c r="C30" s="49" t="inlineStr">
         <is>
           <t>奈良県</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="51" t="inlineStr">
+      <c r="C31" s="49" t="inlineStr">
         <is>
           <t>和歌山県</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="51" t="inlineStr">
+      <c r="C32" s="49" t="inlineStr">
         <is>
           <t>鳥取県</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="51" t="inlineStr">
+      <c r="C33" s="49" t="inlineStr">
         <is>
           <t>島根県</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="51" t="inlineStr">
+      <c r="C34" s="49" t="inlineStr">
         <is>
           <t>岡山県</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="51" t="inlineStr">
+      <c r="C35" s="49" t="inlineStr">
         <is>
           <t>広島県</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="51" t="inlineStr">
+      <c r="C36" s="49" t="inlineStr">
         <is>
           <t>山口県</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="51" t="inlineStr">
+      <c r="C37" s="49" t="inlineStr">
         <is>
           <t>徳島県</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="51" t="inlineStr">
+      <c r="C38" s="49" t="inlineStr">
         <is>
           <t>香川県</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="51" t="inlineStr">
+      <c r="C39" s="49" t="inlineStr">
         <is>
           <t>愛媛県</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="51" t="inlineStr">
+      <c r="C40" s="49" t="inlineStr">
         <is>
           <t>高知県</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="51" t="inlineStr">
+      <c r="C41" s="49" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="51" t="inlineStr">
+      <c r="C42" s="49" t="inlineStr">
         <is>
           <t>佐賀県</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="51" t="inlineStr">
+      <c r="C43" s="49" t="inlineStr">
         <is>
           <t>長崎県</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="51" t="inlineStr">
+      <c r="C44" s="49" t="inlineStr">
         <is>
           <t>熊本県</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="51" t="inlineStr">
+      <c r="C45" s="49" t="inlineStr">
         <is>
           <t>大分県</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="51" t="inlineStr">
+      <c r="C46" s="49" t="inlineStr">
         <is>
           <t>宮崎県</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="51" t="inlineStr">
+      <c r="C47" s="49" t="inlineStr">
         <is>
           <t>鹿児島県</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="51" t="inlineStr">
+      <c r="C48" s="49" t="inlineStr">
         <is>
           <t>沖縄県</t>
         </is>
@@ -5739,296 +5082,276 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>データシート</t>
         </is>
       </c>
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="49" t="inlineStr">
         <is>
           <t>退職 情報</t>
         </is>
       </c>
-      <c r="C1" s="51" t="n"/>
-      <c r="D1" s="51" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>開始行</t>
         </is>
       </c>
-      <c r="B2" s="51" t="n">
+      <c r="B2" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="51" t="n"/>
-      <c r="D2" s="51" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>終了行</t>
         </is>
       </c>
-      <c r="B3" s="51" t="n">
+      <c r="B3" s="49" t="n">
         <v>58</v>
       </c>
-      <c r="C3" s="51" t="n"/>
-      <c r="D3" s="51" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>見出し行</t>
         </is>
       </c>
-      <c r="B4" s="51" t="n">
+      <c r="B4" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="51" t="n"/>
+      <c r="C4" s="49" t="n"/>
+      <c r="D4" s="49" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>kanji</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>氏名（漢字）</t>
         </is>
       </c>
-      <c r="D5" s="51" t="n">
+      <c r="D5" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>kana</t>
         </is>
       </c>
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>氏名（フリガナ）</t>
         </is>
       </c>
-      <c r="D6" s="51" t="n">
+      <c r="D6" s="49" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C7" s="51" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
-      <c r="D7" s="51" t="n">
+      <c r="D7" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>num</t>
         </is>
       </c>
-      <c r="C8" s="51" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>マイナンバー(12桁)</t>
         </is>
       </c>
-      <c r="D8" s="51" t="n">
+      <c r="D8" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B9" s="51" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C9" s="51" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>基礎年金番号(10桁)</t>
         </is>
       </c>
-      <c r="D9" s="51" t="n">
+      <c r="D9" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B10" s="51" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C10" s="51" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>雇用保険被保険者番号(11桁)</t>
         </is>
       </c>
-      <c r="D10" s="51" t="n">
+      <c r="D10" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B11" s="51" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C11" s="51" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>郵便番号</t>
         </is>
       </c>
-      <c r="D11" s="51" t="n">
+      <c r="D11" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" s="51" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="C12" s="51" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>市区町村以下</t>
         </is>
       </c>
-      <c r="D12" s="51" t="n">
+      <c r="D12" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" s="51" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="C13" s="51" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>建物名・部屋番号</t>
         </is>
       </c>
-      <c r="D13" s="51" t="n">
+      <c r="D13" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" s="51" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C14" s="51" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>電話番号</t>
         </is>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" s="51" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C15" s="51" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>離職日（退職日）</t>
         </is>
       </c>
-      <c r="D15" s="51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="51" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B16" s="51" t="inlineStr">
-        <is>
-          <t>zen</t>
-        </is>
-      </c>
-      <c r="C16" s="51" t="inlineStr">
-        <is>
-          <t>課税市区町村（異動届の提出先）</t>
-        </is>
-      </c>
-      <c r="D16" s="51" t="n">
+      <c r="D15" s="49" t="n">
         <v>0</v>
       </c>
     </row>

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -517,7 +517,7 @@
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>用途：電子申請のフリガナ欄（全角カタカナ）。</t>
+        <t>用途：届出のフリガナ欄（全角カタカナ）。</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -29,6 +29,7 @@
     <definedName name="m_住民税">'_マスタ（非表示）'!$M$2:$M$5</definedName>
     <definedName name="m_退職金">'_マスタ（非表示）'!$N$2:$N$4</definedName>
     <definedName name="m_退職所得申告">'_マスタ（非表示）'!$O$2:$O$4</definedName>
+    <definedName name="m_国籍">'_マスタ（非表示）'!$P$2:$P$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'退職 情報'!$1:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,10 +38,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0&quot;件&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -134,7 +136,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -189,6 +191,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EAF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EAF1FB"/>
       </patternFill>
     </fill>
@@ -209,12 +216,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3FB"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -249,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -283,8 +290,14 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -316,40 +329,26 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -361,19 +360,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -383,12 +391,13 @@
     <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -512,7 +521,7 @@
   <commentList>
     <comment ref="A7" authorId="0" shapeId="0">
       <text>
-        <t>用途：各届出（資格喪失届・離職証明書・支給申請書 等）の被保険者氏名。</t>
+        <t>用途：雇用保険 資格喪失届・離職証明書、健保・厚年 資格喪失届の被保険者氏名。</t>
       </text>
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
@@ -582,7 +591,7 @@
     </comment>
     <comment ref="O7" authorId="0" shapeId="0">
       <text>
-        <t>用途：雇用保険の離職理由区分（給付制限・所定給付日数の判定に直結）。目安。</t>
+        <t>用途：雇用保険の離職理由区分。任意（当方で判定）。</t>
       </text>
     </comment>
     <comment ref="P7" authorId="0" shapeId="0">
@@ -602,47 +611,72 @@
     </comment>
     <comment ref="S7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職票の交付要否（本人が基本手当を申請するか）。</t>
+        <t>用途：雇用保険 資格喪失届の『被保険者となった年月日』。</t>
       </text>
     </comment>
     <comment ref="T7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職票の送付先（退職後に転居する場合）。</t>
+        <t>用途：雇用保険 資格喪失届の『1週間の所定労働時間』。</t>
       </text>
     </comment>
     <comment ref="U7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職証明書の賃金欄作成のための賃金台帳・出勤簿の添付確認。</t>
+        <t>用途：離職票の交付要否（本人が基本手当を申請するか）。</t>
       </text>
     </comment>
     <comment ref="V7" authorId="0" shapeId="0">
       <text>
-        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
+        <t>用途：離職票の送付先（退職後に転居する場合）。</t>
       </text>
     </comment>
     <comment ref="W7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
+        <t>用途：離職証明書の賃金欄作成のための賃金台帳・出勤簿の添付確認。</t>
       </text>
     </comment>
     <comment ref="X7" authorId="0" shapeId="0">
       <text>
-        <t>用途：直近賞与の参考値。</t>
+        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
       </text>
     </comment>
     <comment ref="Y7" authorId="0" shapeId="0">
       <text>
-        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
+        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
       </text>
     </comment>
     <comment ref="Z7" authorId="0" shapeId="0">
       <text>
-        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
+        <t>用途：直近賞与の参考値。</t>
       </text>
     </comment>
     <comment ref="AA7" authorId="0" shapeId="0">
       <text>
+        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
+      </text>
+    </comment>
+    <comment ref="AB7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
+      </text>
+    </comment>
+    <comment ref="AC7" authorId="0" shapeId="0">
+      <text>
         <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
+      </text>
+    </comment>
+    <comment ref="AD7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：外国人雇用状況の届出（資格取得届・喪失届と一体）の国籍欄。</t>
+      </text>
+    </comment>
+    <comment ref="AE7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：同 在留資格欄。外国籍の方のみ。</t>
+      </text>
+    </comment>
+    <comment ref="AF7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：同 在留期間欄。外国籍の方のみ。</t>
       </text>
     </comment>
   </commentList>
@@ -938,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1090,7 +1124,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>灰色。自動計算・編集不可。</t>
+          <t>灰色。自動で計算されます（上書きしないでください）。</t>
         </is>
       </c>
     </row>
@@ -1142,138 +1176,169 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="25" ht="37" customHeight="1">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>見出しの印</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>【必】必ず記入／【任】該当すれば記入／【条件により必須】選んだ区分によって必要になる欄（必要なときだけ薄赤に点灯し、不要なときは斜線になります）／【自動】自動計算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="37" customHeight="1">
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>記入例</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>水色・斜体の1行は記入例です。その下の行からご記入ください（記入例の行は消していただいても構いません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>ご注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20.5" customHeight="1">
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>離職理由区分は『目安』です。最終判断は社労士・ハローワークが行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="37" customHeight="1">
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>資格確認書・高齢受給者証・限度額適用認定証などは本人/被扶養者分を回収のうえご返送ください（回収できないときは当方で回収不能届を出します）。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="37" customHeight="1">
       <c r="C29" s="5" t="inlineStr">
         <is>
+          <t>水色・斜体の8行目は記入例です。9行目からご記入ください（記入例は消していただいても構いません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20.5" customHeight="1">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>離職理由区分は『目安』です。最終判断は社労士・ハローワークが行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="37" customHeight="1">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>資格確認書・高齢受給者証・限度額適用認定証などは本人/被扶養者分を回収のうえご返送ください（回収できないときは当方で回収不能届を出します）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="37" customHeight="1">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
           <t>住民税の異動届（給与所得者異動届出書）と退職所得の受給に関する申告書は税務の手続きで、当事務所の受任範囲に含みません。貴社または顧問税理士でお手続きください。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="37" customHeight="1">
-      <c r="C30" s="5" t="inlineStr">
+    <row r="33" ht="37" customHeight="1">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>提出期限の目安：健康保険・厚生年金の資格喪失届は退職日の翌日から5日以内、雇用保険の資格喪失届・離職証明書は10日以内です。お早めにご返送ください。</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32" ht="24" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="34"/>
+    <row r="35" ht="24" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>本人情報の集め方</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="70" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
+    <row r="36" ht="70" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>本人情報は入社時と同じ内容をご記入ください。本人しか分からない項目（マイナンバー・基礎年金番号・雇用保険被保険者番号など）は、会社内で本人に確認のうえご記入ください。
 当事務所の書式「入社時 本人情報記入シート」（https://minano-sr.com/shoshiki/D-52.html）を印刷して本人に書いてもらう方法が簡単です。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20.5" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
+    <row r="37" ht="20.5" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>2名以上のとき</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>1行に1名ずつご記入ください（行を追加して複数名をまとめて送れます）。</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36" ht="24" customHeight="1">
-      <c r="B36" s="3" t="inlineStr">
+    <row r="38"/>
+    <row r="39" ht="24" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>マイナンバー等 機微情報の取扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="53.5" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>入力時</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>マイナンバー（12桁）は半角数字・ハイフン無しで入力します。会社所定の安全な経路で別提出する場合は、番号を入力せず『別経路提出』を選んでください。未回収の場合は『後日提出』を選択します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="37" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>基礎年金番号</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>10桁（年金手帳・基礎年金番号通知書に記載）。不明なときはドロップダウンから『後日提出』を選べば未入力扱いになりません（分かり次第ご連絡ください）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="37" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>雇用保険被保険者番号</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>11桁（雇用保険被保険者証・離職票に記載）。前職が無い方は『なし』、番号が不明なときは『後日提出』を選択してください。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="53.5" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>返送方法</t>
+          <t>入力時</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>本ファイルはマイナンバー等の特定個人情報を含みます。メール添付で平文送付せず、①パスワード付きZIP（パスワードは別経路で連絡）、または ②当事務所が案内する安全な受け渡し方法 でご返送ください。</t>
+          <t>マイナンバー（12桁）は半角数字・ハイフン無しで入力します。会社所定の安全な経路で別提出する場合は、番号を入力せず『別経路提出』を選んでください。未回収の場合は『後日提出』を選択します。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="37" customHeight="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>基礎年金番号</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>10桁（年金手帳・基礎年金番号通知書に記載）。不明なときはドロップダウンから『後日提出』を選べば未入力扱いになりません（分かり次第ご連絡ください）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="37" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>雇用保険被保険者番号</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>11桁（雇用保険被保険者証・離職票に記載）。前職が無い方は『なし』、番号が不明なときは『後日提出』を選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="53.5" customHeight="1">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>返送方法</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>受任メールのリンクから案件ページを開き、記入したこのファイルをそのままお送りください。ZIPにする必要はありません。この経路は暗号化されており、メール添付より安全です。メールに直接添付して送るのは避けてください（マイナンバー等の特定個人情報を含みます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="37" customHeight="1">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
           <t>社内保管</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>記入途中のファイルは関係者以外がアクセスできない場所に保管し、提出後は社内ルールに従って適切に削除・保管してください。</t>
         </is>
@@ -1281,12 +1346,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B12:C12"/>
   </mergeCells>
@@ -1301,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1311,14 +1376,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>退職時 受領フォーム　提出チェック・添付・返送</t>
         </is>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1">
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>このシートは貴社（ご担当者さま）が、入力 → 提出前の確認 → 当事務所への返送まで迷わず進めるための案内です。本体シートをご記入のうえ、最後にここをご確認ください。</t>
         </is>
@@ -1333,129 +1398,129 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>貴社名</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>貴社名をご記入ください。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>ご入力担当者名</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>このフォームをご記入された方のお名前。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>ご担当者 連絡先</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>電話番号またはメールアドレス。確認時の連絡用。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>記入日</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>ご記入（最終確認）日。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>対象者数（自動）</t>
         </is>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="22">
         <f>'退職 情報'!A4</f>
         <v/>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>本体シートに入力された件数を自動表示します。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="37" customHeight="1">
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>必須の未入力 残（自動）</t>
         </is>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="22">
         <f>'退職 情報'!E4</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>未入力の必須項目の残数。0件になるまでご記入ください（本体の薄赤・行ステータス参照）。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>完了率（自動）</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="23">
         <f>'退職 情報'!G4</f>
         <v/>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>必須項目の充足率。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="37" customHeight="1">
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>提出可否（自動）</t>
         </is>
       </c>
-      <c r="C12" s="22">
-        <f>IF('退職 情報'!A4=0,"未入力（対象者なし）",IF('退職 情報'!E4=0,"提出可（必須の未入力なし）","未入力あり：本体シートの薄赤セル・行ステータスをご確認ください"))</f>
-        <v/>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="24">
+        <f>IF('退職 情報'!A4=0,"未入力（対象者なし）",IF(AND('退職 情報'!E4=0,'退職 情報'!C4&lt;&gt;'退職 情報'!A4),"確認が必要：式の入っていない行があります（行を挿入せず9〜58行にご記入ください）",IF('退職 情報'!E4=0,"提出可（必須の未入力なし）","未入力あり：本体シートの薄赤セル・行ステータスをご確認ください")))</f>
+        <v/>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>必須の未入力が無ければ『提出可』。残っていれば本体をご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>事務所への連絡事項</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>不明点・特記事項があればご記入ください（任意）。</t>
         </is>
@@ -1465,150 +1530,55 @@
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>② 添付資料チェック（この手続きで必要なもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20.5" customHeight="1">
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>「状態」を選び、未入手は『後日提出』『事務所で確認』等の状態を残してください（空欄のままにしない）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>資料・項目</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>補足（何のために使うか）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="37" customHeight="1">
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>賃金台帳（離職前6か月分）</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>離職証明書の賃金欄（基本手当の算定基礎）を作成するために使用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="37" customHeight="1">
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>出勤簿・タイムカード（離職前12か月分）</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>賃金支払基礎日数（11日以上の月）の確認に使用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="37" customHeight="1">
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>離職票の交付希望</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>本人が基本手当を申請するなら『あり』。本体シートにも入力欄あり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="37" customHeight="1">
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>資格確認書・各認定証（本人・被扶養者分）</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>資格喪失に伴う回収状況。回収済みであれば同封、未回収なら状態を記載。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+          <t>② 一緒に送っていただく書類</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="53.5" customHeight="1">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>書類の一覧と、いま何が届いているかは案件ページが正です。このシートには書類の状態を書かないでください（二重管理になります）。
+案件ページは受任メールのリンクから開けます。届いた書類はその場で受領済みに変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>この手続きで必要になるもの：
+　・賃金台帳（離職前1年分）
+　・出勤簿・タイムカード（賃金台帳と同じ期間）
+　・資格確認書・各認定証（本人・被扶養者分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>③ 当事務所への返送について</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="53.5" customHeight="1">
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>【ファイル名のつけ方】　YYYYMMDD_貴社名_対象者名_手続名_返送_v1.0.xlsx
-　例）20260710_ABC株式会社_山田太郎_退職時 受領フォーム_返送_v1.0.xlsx
-　複数名分をまとめる場合：20260710_ABC株式会社_複数名_各種手続_返送_v1.0.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="70" customHeight="1">
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>【ご返送方法】　マイナンバー等の重要情報を含みます。メール平文への添付は避け、当事務所の案件ページ（受任メールのリンク）からお送りください。メールに添付する場合はパスワード付きZIP（パスワードは別経路でご連絡）にしてください。マイナンバーを別経路で回収する運用の場合は、このフォームには入力せず、会社所定の安全な経路で提出してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20.5" customHeight="1">
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>【送付メール文（コピペ用）】　下の枠を選択してコピーし、件名・本文にお使いください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>件名：【退職手続】退職連絡フォーム送付の件（〇〇株式会社）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="218.5" customHeight="1">
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>みなの社会保険労務士事務所
-ご担当者さま
-いつもお世話になっております。
-退職連絡に関する入力フォームを送付いたします。
-　対象者数：　　名
-　添付資料：
-　未提出・後日提出の資料：
-　ご連絡事項：
-何卒よろしくお願いいたします。
-（貴社名・ご担当者名）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30" ht="24" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="20" ht="86.5" customHeight="1">
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>記入したこのファイルを、案件ページからそのままお送りください。ZIPにする必要はありません。ファイル名も変えなくて構いません。
+送り先は受任メールに載せた案件ページのリンクです。そのページの「受領フォーム」の欄から、このファイルを選ぶだけで届きます。
+メールに添付して送るのは避けてください（マイナンバー等を含みます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>④ 入力の補足（情報が揃わないとき）</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="53.5" customHeight="1">
-      <c r="B31" s="23" t="inlineStr">
+    <row r="23" ht="53.5" customHeight="1">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>・『不明』『後日提出』を選べる欄は、空欄のままにせず状態を残してください。後で当事務所が確認・督促できます。
 ・該当しない欄は『該当なし』を選ぶか空欄で構いません（条件次第で対象外＝斜線になる欄もあります）。
@@ -1617,20 +1587,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B31:D31"/>
+  <mergeCells count="10">
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <conditionalFormatting sqref="C12">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
@@ -1639,60 +1606,19 @@
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(SEARCH("未入力",C12)),ISERROR(SEARCH("提出可",C12)))</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("確認が必要",C12))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
       <formula>C10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
-    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
-      <formula>C18=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
-      <formula>OR(C18="後日提出",C18="事務所で確認",C18="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
-    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
-      <formula>C19=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="1" stopIfTrue="1">
-      <formula>OR(C19="後日提出",C19="事務所で確認",C19="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20">
-    <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
-      <formula>C20=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="1" stopIfTrue="1">
-      <formula>OR(C20="後日提出",C20="事務所で確認",C20="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21">
-    <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
-      <formula>C21=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
-      <formula>OR(C21="後日提出",C21="事務所で確認",C21="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="1">
     <dataValidation sqref="C8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation sqref="C18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1706,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1727,131 +1653,141 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="36" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="36" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>退職 情報</t>
         </is>
       </c>
-      <c r="N1" s="28" t="inlineStr">
+      <c r="Q1" s="26" t="inlineStr">
         <is>
           <t>※離職理由区分は目安。最終判断は社労士・ハローワークが行います。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="n"/>
-      <c r="B2" s="29" t="n"/>
-      <c r="C2" s="29" t="n"/>
-      <c r="D2" s="29" t="n"/>
-      <c r="E2" s="29" t="n"/>
-      <c r="F2" s="29" t="n"/>
-      <c r="G2" s="29" t="n"/>
-      <c r="H2" s="29" t="n"/>
-      <c r="I2" s="29" t="n"/>
-      <c r="J2" s="29" t="n"/>
-      <c r="K2" s="29" t="n"/>
-      <c r="L2" s="29" t="n"/>
-      <c r="M2" s="29" t="n"/>
-      <c r="N2" s="29" t="n"/>
+      <c r="A2" s="27" t="n"/>
+      <c r="B2" s="27" t="n"/>
+      <c r="C2" s="27" t="n"/>
+      <c r="D2" s="27" t="n"/>
+      <c r="E2" s="27" t="n"/>
+      <c r="F2" s="27" t="n"/>
+      <c r="G2" s="27" t="n"/>
+      <c r="H2" s="27" t="n"/>
+      <c r="I2" s="27" t="n"/>
+      <c r="J2" s="27" t="n"/>
+      <c r="K2" s="27" t="n"/>
+      <c r="L2" s="27" t="n"/>
+      <c r="M2" s="27" t="n"/>
+      <c r="N2" s="27" t="n"/>
     </row>
     <row r="3" ht="20.5" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>入力対象 件数</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>必須充足 件数</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>必須未入力 残</t>
         </is>
       </c>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>完了率</t>
         </is>
       </c>
-      <c r="I3" s="29" t="n"/>
-      <c r="J3" s="29" t="n"/>
-      <c r="K3" s="29" t="n"/>
-      <c r="L3" s="29" t="n"/>
-      <c r="M3" s="29" t="n"/>
-      <c r="N3" s="29" t="n"/>
+      <c r="I3" s="27" t="n"/>
+      <c r="J3" s="27" t="n"/>
+      <c r="K3" s="27" t="n"/>
+      <c r="L3" s="27" t="n"/>
+      <c r="M3" s="27" t="n"/>
+      <c r="N3" s="27" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="31">
+      <c r="A4" s="29">
         <f>COUNTA(A9:A58)</f>
         <v/>
       </c>
-      <c r="C4" s="31">
-        <f>COUNTIF(AC9:AC58,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="31">
-        <f>SUM(AC9:AC58)</f>
-        <v/>
-      </c>
-      <c r="G4" s="32">
+      <c r="C4" s="29">
+        <f>COUNTIF(AH9:AH58,0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="29">
+        <f>SUM(AH9:AH58)</f>
+        <v/>
+      </c>
+      <c r="G4" s="30">
         <f>IF(A4=0,0,C4/A4)</f>
         <v/>
       </c>
-      <c r="I4" s="29" t="n"/>
-      <c r="J4" s="29" t="n"/>
-      <c r="K4" s="29" t="n"/>
-      <c r="L4" s="29" t="n"/>
-      <c r="M4" s="29" t="n"/>
-      <c r="N4" s="29" t="n"/>
+      <c r="I4" s="27" t="n"/>
+      <c r="J4" s="27" t="n"/>
+      <c r="K4" s="27" t="n"/>
+      <c r="L4" s="27" t="n"/>
+      <c r="M4" s="27" t="n"/>
+      <c r="N4" s="27" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="33">
-        <f>IF(A4=0,"（このシートにはまだ入力がありません）",IF(E4=0,"✓ 必須の未入力はありません","⚠ 必須の未入力が "&amp;E4&amp;" 件あります：本体の赤いセル・右端の行ステータスをご確認ください"))</f>
-        <v/>
-      </c>
-      <c r="M5" s="29" t="n"/>
-      <c r="N5" s="29" t="n"/>
+      <c r="A5" s="31">
+        <f>IF(A4=0,"（まだ入力がありません。水色の記入例の下の行からご記入ください）",IF(AND(E4=0,C4&lt;&gt;A4),"⚠ 式の入っていない行があります：行を挿入せず 9〜58 行にご記入ください",IF(E4=0,"✓ 必須の未入力はありません","⚠ 必須の未入力が "&amp;E4&amp;" 件あります：本体の赤いセル・右端の行ステータスをご確認ください")))</f>
+        <v/>
+      </c>
+      <c r="M5" s="27" t="n"/>
+      <c r="N5" s="27" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>本人情報</t>
         </is>
       </c>
-      <c r="L6" s="35" t="inlineStr">
+      <c r="L6" s="33" t="inlineStr">
         <is>
           <t>退職事由</t>
         </is>
       </c>
-      <c r="S6" s="36" t="inlineStr">
+      <c r="S6" s="34" t="inlineStr">
         <is>
           <t>雇用保険</t>
         </is>
       </c>
-      <c r="Y6" s="37" t="inlineStr">
+      <c r="AA6" s="35" t="inlineStr">
         <is>
           <t>社会保険</t>
         </is>
       </c>
-      <c r="AA6" s="38" t="inlineStr">
+      <c r="AC6" s="36" t="inlineStr">
         <is>
           <t>その他</t>
+        </is>
+      </c>
+      <c r="AD6" s="37" t="inlineStr">
+        <is>
+          <t>外国籍のとき</t>
         </is>
       </c>
     </row>
@@ -1940,10 +1876,10 @@
 【必】</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>離職理由区分（目安）
-【必】</t>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>離職理由区分（分かる場合のみ・当方で判定します）
+【任】</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
@@ -1955,70 +1891,100 @@
       <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>契約更新条項（有期契約のみ）
-【任】</t>
+【条件により必須】</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
           <t>本人の更新希望（有期契約のみ）
-【任】</t>
+【条件により必須】</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>雇用保険 資格取得年月日
+【必】</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>1週間の所定労働時間(時間)
+【必】</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>離職票の交付希望
 【必】</t>
         </is>
       </c>
-      <c r="T7" s="7" t="inlineStr">
+      <c r="V7" s="7" t="inlineStr">
         <is>
           <t>離職票の送付先（転居する場合）
 【任】</t>
         </is>
       </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="W7" s="6" t="inlineStr">
         <is>
           <t>賃金台帳・出勤簿の添付
 【必】</t>
         </is>
       </c>
-      <c r="V7" s="7" t="inlineStr">
+      <c r="X7" s="7" t="inlineStr">
         <is>
           <t>賃金締切日
 【任】</t>
         </is>
       </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="Y7" s="7" t="inlineStr">
         <is>
           <t>離職前賃金（直近1か月・円）
 【任】</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
+      <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>直近の賞与（円）
 【任】</t>
         </is>
       </c>
-      <c r="Y7" s="6" t="inlineStr">
+      <c r="AA7" s="6" t="inlineStr">
         <is>
           <t>資格確認書等の回収
 【必】</t>
         </is>
       </c>
-      <c r="Z7" s="6" t="inlineStr">
+      <c r="AB7" s="6" t="inlineStr">
         <is>
           <t>退職後の希望
 【必】</t>
         </is>
       </c>
-      <c r="AA7" s="7" t="inlineStr">
+      <c r="AC7" s="7" t="inlineStr">
         <is>
           <t>備考（連絡事項）
 【任】</t>
         </is>
       </c>
-      <c r="AB7" s="24" t="inlineStr">
+      <c r="AD7" s="7" t="inlineStr">
+        <is>
+          <t>国籍・地域
+【任】</t>
+        </is>
+      </c>
+      <c r="AE7" s="7" t="inlineStr">
+        <is>
+          <t>在留資格【外国籍のとき必須】
+【条件により必須】</t>
+        </is>
+      </c>
+      <c r="AF7" s="7" t="inlineStr">
+        <is>
+          <t>在留期間の満了日【外国籍のとき必須】
+【条件により必須】</t>
+        </is>
+      </c>
+      <c r="AG7" s="38" t="inlineStr">
         <is>
           <t>行ステータス
 （CSV可否）</t>
@@ -2028,12 +1994,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="39" t="inlineStr">
         <is>
-          <t>例</t>
+          <t>山田　太郎</t>
         </is>
       </c>
       <c r="B8" s="40" t="inlineStr">
         <is>
-          <t>ヤマダ タロウ</t>
+          <t>ヤマダ　タロウ</t>
         </is>
       </c>
       <c r="C8" s="41" t="n">
@@ -2074,7 +2040,7 @@
           <t>〇〇マンション101</t>
         </is>
       </c>
-      <c r="K8" s="40" t="inlineStr">
+      <c r="K8" s="42" t="inlineStr">
         <is>
           <t>076-000-0000</t>
         </is>
@@ -2111,2056 +2077,2320 @@
           <t>該当なし</t>
         </is>
       </c>
-      <c r="S8" s="40" t="inlineStr">
+      <c r="S8" s="41" t="n">
+        <v>43922</v>
+      </c>
+      <c r="T8" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="U8" s="40" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="T8" s="40" t="n"/>
-      <c r="U8" s="40" t="inlineStr">
+      <c r="V8" s="40" t="n"/>
+      <c r="W8" s="40" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="V8" s="40" t="inlineStr">
+      <c r="X8" s="40" t="inlineStr">
         <is>
           <t>毎月末日</t>
         </is>
       </c>
-      <c r="W8" s="43" t="n">
+      <c r="Y8" s="44" t="n">
         <v>300000</v>
       </c>
-      <c r="X8" s="43" t="n">
+      <c r="Z8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" s="40" t="inlineStr">
+      <c r="AA8" s="40" t="inlineStr">
         <is>
           <t>回収済</t>
         </is>
       </c>
-      <c r="Z8" s="40" t="inlineStr">
+      <c r="AB8" s="40" t="inlineStr">
         <is>
           <t>家族の扶養に入る</t>
         </is>
       </c>
-      <c r="AA8" s="40" t="inlineStr">
-        <is>
-          <t>← この行は記入例です（編集不可）</t>
-        </is>
-      </c>
+      <c r="AC8" s="40" t="inlineStr">
+        <is>
+          <t>← この行は記入例です</t>
+        </is>
+      </c>
+      <c r="AD8" s="40" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="AE8" s="40" t="n"/>
+      <c r="AF8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="44" t="n"/>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="18" t="n"/>
-      <c r="M9" s="45">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
+      <c r="F9" s="45" t="n"/>
+      <c r="G9" s="45" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="45" t="n"/>
+      <c r="L9" s="20" t="n"/>
+      <c r="M9" s="46">
         <f>IF($L9="","",$L9+1)</f>
         <v/>
       </c>
-      <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="16" t="n"/>
-      <c r="R9" s="16" t="n"/>
-      <c r="S9" s="16" t="n"/>
-      <c r="T9" s="16" t="n"/>
-      <c r="U9" s="16" t="n"/>
-      <c r="V9" s="16" t="n"/>
-      <c r="W9" s="46" t="n"/>
-      <c r="X9" s="46" t="n"/>
-      <c r="Y9" s="16" t="n"/>
-      <c r="Z9" s="16" t="n"/>
-      <c r="AA9" s="16" t="n"/>
-      <c r="AB9" s="47">
-        <f>IF($A9="","",IF(AC9&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($O9="",1,0)+IF($P9="",1,0)+IF($S9="",1,0)+IF($U9="",1,0)+IF($Y9="",1,0)+IF($Z9="",1,0)+IF(AND($N9="契約期間満了",$Q9=""),1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0))</f>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="18" t="n"/>
+      <c r="P9" s="18" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="18" t="n"/>
+      <c r="S9" s="20" t="n"/>
+      <c r="T9" s="47" t="n"/>
+      <c r="U9" s="18" t="n"/>
+      <c r="V9" s="18" t="n"/>
+      <c r="W9" s="18" t="n"/>
+      <c r="X9" s="18" t="n"/>
+      <c r="Y9" s="48" t="n"/>
+      <c r="Z9" s="48" t="n"/>
+      <c r="AA9" s="18" t="n"/>
+      <c r="AB9" s="18" t="n"/>
+      <c r="AC9" s="18" t="n"/>
+      <c r="AD9" s="18" t="n"/>
+      <c r="AE9" s="18" t="n"/>
+      <c r="AF9" s="20" t="n"/>
+      <c r="AG9" s="13">
+        <f>IF($A9="","",IF(AH9&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH9">
+        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($P9="",1,0)+IF($S9="",1,0)+IF($T9="",1,0)+IF($U9="",1,0)+IF($W9="",1,0)+IF($AA9="",1,0)+IF($AB9="",1,0)+IF(AND($N9="契約期間満了",$Q9=""),1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0)+IF(AND($AD9="外国",$AE9=""),1,0)+IF(AND($AD9="外国",$AF9=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="44" t="n"/>
-      <c r="G10" s="44" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="18" t="n"/>
-      <c r="M10" s="45">
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="45" t="n"/>
+      <c r="G10" s="45" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="45" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="46">
         <f>IF($L10="","",$L10+1)</f>
         <v/>
       </c>
-      <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
-      <c r="R10" s="16" t="n"/>
-      <c r="S10" s="16" t="n"/>
-      <c r="T10" s="16" t="n"/>
-      <c r="U10" s="16" t="n"/>
-      <c r="V10" s="16" t="n"/>
-      <c r="W10" s="46" t="n"/>
-      <c r="X10" s="46" t="n"/>
-      <c r="Y10" s="16" t="n"/>
-      <c r="Z10" s="16" t="n"/>
-      <c r="AA10" s="16" t="n"/>
-      <c r="AB10" s="47">
-        <f>IF($A10="","",IF(AC10&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($O10="",1,0)+IF($P10="",1,0)+IF($S10="",1,0)+IF($U10="",1,0)+IF($Y10="",1,0)+IF($Z10="",1,0)+IF(AND($N10="契約期間満了",$Q10=""),1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0))</f>
+      <c r="N10" s="18" t="n"/>
+      <c r="O10" s="18" t="n"/>
+      <c r="P10" s="18" t="n"/>
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="18" t="n"/>
+      <c r="S10" s="20" t="n"/>
+      <c r="T10" s="47" t="n"/>
+      <c r="U10" s="18" t="n"/>
+      <c r="V10" s="18" t="n"/>
+      <c r="W10" s="18" t="n"/>
+      <c r="X10" s="18" t="n"/>
+      <c r="Y10" s="48" t="n"/>
+      <c r="Z10" s="48" t="n"/>
+      <c r="AA10" s="18" t="n"/>
+      <c r="AB10" s="18" t="n"/>
+      <c r="AC10" s="18" t="n"/>
+      <c r="AD10" s="18" t="n"/>
+      <c r="AE10" s="18" t="n"/>
+      <c r="AF10" s="20" t="n"/>
+      <c r="AG10" s="13">
+        <f>IF($A10="","",IF(AH10&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH10">
+        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($P10="",1,0)+IF($S10="",1,0)+IF($T10="",1,0)+IF($U10="",1,0)+IF($W10="",1,0)+IF($AA10="",1,0)+IF($AB10="",1,0)+IF(AND($N10="契約期間満了",$Q10=""),1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0)+IF(AND($AD10="外国",$AE10=""),1,0)+IF(AND($AD10="外国",$AF10=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
-      <c r="G11" s="44" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="45">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="45" t="n"/>
+      <c r="G11" s="45" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="45" t="n"/>
+      <c r="L11" s="20" t="n"/>
+      <c r="M11" s="46">
         <f>IF($L11="","",$L11+1)</f>
         <v/>
       </c>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
-      <c r="R11" s="16" t="n"/>
-      <c r="S11" s="16" t="n"/>
-      <c r="T11" s="16" t="n"/>
-      <c r="U11" s="16" t="n"/>
-      <c r="V11" s="16" t="n"/>
-      <c r="W11" s="46" t="n"/>
-      <c r="X11" s="46" t="n"/>
-      <c r="Y11" s="16" t="n"/>
-      <c r="Z11" s="16" t="n"/>
-      <c r="AA11" s="16" t="n"/>
-      <c r="AB11" s="47">
-        <f>IF($A11="","",IF(AC11&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($O11="",1,0)+IF($P11="",1,0)+IF($S11="",1,0)+IF($U11="",1,0)+IF($Y11="",1,0)+IF($Z11="",1,0)+IF(AND($N11="契約期間満了",$Q11=""),1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0))</f>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="18" t="n"/>
+      <c r="P11" s="18" t="n"/>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="18" t="n"/>
+      <c r="S11" s="20" t="n"/>
+      <c r="T11" s="47" t="n"/>
+      <c r="U11" s="18" t="n"/>
+      <c r="V11" s="18" t="n"/>
+      <c r="W11" s="18" t="n"/>
+      <c r="X11" s="18" t="n"/>
+      <c r="Y11" s="48" t="n"/>
+      <c r="Z11" s="48" t="n"/>
+      <c r="AA11" s="18" t="n"/>
+      <c r="AB11" s="18" t="n"/>
+      <c r="AC11" s="18" t="n"/>
+      <c r="AD11" s="18" t="n"/>
+      <c r="AE11" s="18" t="n"/>
+      <c r="AF11" s="20" t="n"/>
+      <c r="AG11" s="13">
+        <f>IF($A11="","",IF(AH11&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH11">
+        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($P11="",1,0)+IF($S11="",1,0)+IF($T11="",1,0)+IF($U11="",1,0)+IF($W11="",1,0)+IF($AA11="",1,0)+IF($AB11="",1,0)+IF(AND($N11="契約期間満了",$Q11=""),1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0)+IF(AND($AD11="外国",$AE11=""),1,0)+IF(AND($AD11="外国",$AF11=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="45">
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="45" t="n"/>
+      <c r="G12" s="45" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="46">
         <f>IF($L12="","",$L12+1)</f>
         <v/>
       </c>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="16" t="n"/>
-      <c r="S12" s="16" t="n"/>
-      <c r="T12" s="16" t="n"/>
-      <c r="U12" s="16" t="n"/>
-      <c r="V12" s="16" t="n"/>
-      <c r="W12" s="46" t="n"/>
-      <c r="X12" s="46" t="n"/>
-      <c r="Y12" s="16" t="n"/>
-      <c r="Z12" s="16" t="n"/>
-      <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="47">
-        <f>IF($A12="","",IF(AC12&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($O12="",1,0)+IF($P12="",1,0)+IF($S12="",1,0)+IF($U12="",1,0)+IF($Y12="",1,0)+IF($Z12="",1,0)+IF(AND($N12="契約期間満了",$Q12=""),1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0))</f>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="18" t="n"/>
+      <c r="P12" s="18" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="18" t="n"/>
+      <c r="S12" s="20" t="n"/>
+      <c r="T12" s="47" t="n"/>
+      <c r="U12" s="18" t="n"/>
+      <c r="V12" s="18" t="n"/>
+      <c r="W12" s="18" t="n"/>
+      <c r="X12" s="18" t="n"/>
+      <c r="Y12" s="48" t="n"/>
+      <c r="Z12" s="48" t="n"/>
+      <c r="AA12" s="18" t="n"/>
+      <c r="AB12" s="18" t="n"/>
+      <c r="AC12" s="18" t="n"/>
+      <c r="AD12" s="18" t="n"/>
+      <c r="AE12" s="18" t="n"/>
+      <c r="AF12" s="20" t="n"/>
+      <c r="AG12" s="13">
+        <f>IF($A12="","",IF(AH12&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH12">
+        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($P12="",1,0)+IF($S12="",1,0)+IF($T12="",1,0)+IF($U12="",1,0)+IF($W12="",1,0)+IF($AA12="",1,0)+IF($AB12="",1,0)+IF(AND($N12="契約期間満了",$Q12=""),1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0)+IF(AND($AD12="外国",$AE12=""),1,0)+IF(AND($AD12="外国",$AF12=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="18" t="n"/>
-      <c r="M13" s="45">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="45" t="n"/>
+      <c r="E13" s="45" t="n"/>
+      <c r="F13" s="45" t="n"/>
+      <c r="G13" s="45" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="45" t="n"/>
+      <c r="L13" s="20" t="n"/>
+      <c r="M13" s="46">
         <f>IF($L13="","",$L13+1)</f>
         <v/>
       </c>
-      <c r="N13" s="16" t="n"/>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
-      <c r="R13" s="16" t="n"/>
-      <c r="S13" s="16" t="n"/>
-      <c r="T13" s="16" t="n"/>
-      <c r="U13" s="16" t="n"/>
-      <c r="V13" s="16" t="n"/>
-      <c r="W13" s="46" t="n"/>
-      <c r="X13" s="46" t="n"/>
-      <c r="Y13" s="16" t="n"/>
-      <c r="Z13" s="16" t="n"/>
-      <c r="AA13" s="16" t="n"/>
-      <c r="AB13" s="47">
-        <f>IF($A13="","",IF(AC13&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($O13="",1,0)+IF($P13="",1,0)+IF($S13="",1,0)+IF($U13="",1,0)+IF($Y13="",1,0)+IF($Z13="",1,0)+IF(AND($N13="契約期間満了",$Q13=""),1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0))</f>
+      <c r="N13" s="18" t="n"/>
+      <c r="O13" s="18" t="n"/>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="18" t="n"/>
+      <c r="S13" s="20" t="n"/>
+      <c r="T13" s="47" t="n"/>
+      <c r="U13" s="18" t="n"/>
+      <c r="V13" s="18" t="n"/>
+      <c r="W13" s="18" t="n"/>
+      <c r="X13" s="18" t="n"/>
+      <c r="Y13" s="48" t="n"/>
+      <c r="Z13" s="48" t="n"/>
+      <c r="AA13" s="18" t="n"/>
+      <c r="AB13" s="18" t="n"/>
+      <c r="AC13" s="18" t="n"/>
+      <c r="AD13" s="18" t="n"/>
+      <c r="AE13" s="18" t="n"/>
+      <c r="AF13" s="20" t="n"/>
+      <c r="AG13" s="13">
+        <f>IF($A13="","",IF(AH13&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH13">
+        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($P13="",1,0)+IF($S13="",1,0)+IF($T13="",1,0)+IF($U13="",1,0)+IF($W13="",1,0)+IF($AA13="",1,0)+IF($AB13="",1,0)+IF(AND($N13="契約期間満了",$Q13=""),1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0)+IF(AND($AD13="外国",$AE13=""),1,0)+IF(AND($AD13="外国",$AF13=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="44" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="45">
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="45" t="n"/>
+      <c r="G14" s="45" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="45" t="n"/>
+      <c r="L14" s="20" t="n"/>
+      <c r="M14" s="46">
         <f>IF($L14="","",$L14+1)</f>
         <v/>
       </c>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="16" t="n"/>
-      <c r="S14" s="16" t="n"/>
-      <c r="T14" s="16" t="n"/>
-      <c r="U14" s="16" t="n"/>
-      <c r="V14" s="16" t="n"/>
-      <c r="W14" s="46" t="n"/>
-      <c r="X14" s="46" t="n"/>
-      <c r="Y14" s="16" t="n"/>
-      <c r="Z14" s="16" t="n"/>
-      <c r="AA14" s="16" t="n"/>
-      <c r="AB14" s="47">
-        <f>IF($A14="","",IF(AC14&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($O14="",1,0)+IF($P14="",1,0)+IF($S14="",1,0)+IF($U14="",1,0)+IF($Y14="",1,0)+IF($Z14="",1,0)+IF(AND($N14="契約期間満了",$Q14=""),1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0))</f>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="18" t="n"/>
+      <c r="P14" s="18" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="18" t="n"/>
+      <c r="S14" s="20" t="n"/>
+      <c r="T14" s="47" t="n"/>
+      <c r="U14" s="18" t="n"/>
+      <c r="V14" s="18" t="n"/>
+      <c r="W14" s="18" t="n"/>
+      <c r="X14" s="18" t="n"/>
+      <c r="Y14" s="48" t="n"/>
+      <c r="Z14" s="48" t="n"/>
+      <c r="AA14" s="18" t="n"/>
+      <c r="AB14" s="18" t="n"/>
+      <c r="AC14" s="18" t="n"/>
+      <c r="AD14" s="18" t="n"/>
+      <c r="AE14" s="18" t="n"/>
+      <c r="AF14" s="20" t="n"/>
+      <c r="AG14" s="13">
+        <f>IF($A14="","",IF(AH14&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH14">
+        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($P14="",1,0)+IF($S14="",1,0)+IF($T14="",1,0)+IF($U14="",1,0)+IF($W14="",1,0)+IF($AA14="",1,0)+IF($AB14="",1,0)+IF(AND($N14="契約期間満了",$Q14=""),1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0)+IF(AND($AD14="外国",$AE14=""),1,0)+IF(AND($AD14="外国",$AF14=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="44" t="n"/>
-      <c r="F15" s="44" t="n"/>
-      <c r="G15" s="44" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="45">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
+      <c r="F15" s="45" t="n"/>
+      <c r="G15" s="45" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="45" t="n"/>
+      <c r="L15" s="20" t="n"/>
+      <c r="M15" s="46">
         <f>IF($L15="","",$L15+1)</f>
         <v/>
       </c>
-      <c r="N15" s="16" t="n"/>
-      <c r="O15" s="16" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="16" t="n"/>
-      <c r="R15" s="16" t="n"/>
-      <c r="S15" s="16" t="n"/>
-      <c r="T15" s="16" t="n"/>
-      <c r="U15" s="16" t="n"/>
-      <c r="V15" s="16" t="n"/>
-      <c r="W15" s="46" t="n"/>
-      <c r="X15" s="46" t="n"/>
-      <c r="Y15" s="16" t="n"/>
-      <c r="Z15" s="16" t="n"/>
-      <c r="AA15" s="16" t="n"/>
-      <c r="AB15" s="47">
-        <f>IF($A15="","",IF(AC15&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($O15="",1,0)+IF($P15="",1,0)+IF($S15="",1,0)+IF($U15="",1,0)+IF($Y15="",1,0)+IF($Z15="",1,0)+IF(AND($N15="契約期間満了",$Q15=""),1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0))</f>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="18" t="n"/>
+      <c r="P15" s="18" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="18" t="n"/>
+      <c r="S15" s="20" t="n"/>
+      <c r="T15" s="47" t="n"/>
+      <c r="U15" s="18" t="n"/>
+      <c r="V15" s="18" t="n"/>
+      <c r="W15" s="18" t="n"/>
+      <c r="X15" s="18" t="n"/>
+      <c r="Y15" s="48" t="n"/>
+      <c r="Z15" s="48" t="n"/>
+      <c r="AA15" s="18" t="n"/>
+      <c r="AB15" s="18" t="n"/>
+      <c r="AC15" s="18" t="n"/>
+      <c r="AD15" s="18" t="n"/>
+      <c r="AE15" s="18" t="n"/>
+      <c r="AF15" s="20" t="n"/>
+      <c r="AG15" s="13">
+        <f>IF($A15="","",IF(AH15&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH15">
+        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($P15="",1,0)+IF($S15="",1,0)+IF($T15="",1,0)+IF($U15="",1,0)+IF($W15="",1,0)+IF($AA15="",1,0)+IF($AB15="",1,0)+IF(AND($N15="契約期間満了",$Q15=""),1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0)+IF(AND($AD15="外国",$AE15=""),1,0)+IF(AND($AD15="外国",$AF15=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="44" t="n"/>
-      <c r="F16" s="44" t="n"/>
-      <c r="G16" s="44" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="45">
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="45" t="n"/>
+      <c r="G16" s="45" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="45" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="46">
         <f>IF($L16="","",$L16+1)</f>
         <v/>
       </c>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-      <c r="R16" s="16" t="n"/>
-      <c r="S16" s="16" t="n"/>
-      <c r="T16" s="16" t="n"/>
-      <c r="U16" s="16" t="n"/>
-      <c r="V16" s="16" t="n"/>
-      <c r="W16" s="46" t="n"/>
-      <c r="X16" s="46" t="n"/>
-      <c r="Y16" s="16" t="n"/>
-      <c r="Z16" s="16" t="n"/>
-      <c r="AA16" s="16" t="n"/>
-      <c r="AB16" s="47">
-        <f>IF($A16="","",IF(AC16&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($O16="",1,0)+IF($P16="",1,0)+IF($S16="",1,0)+IF($U16="",1,0)+IF($Y16="",1,0)+IF($Z16="",1,0)+IF(AND($N16="契約期間満了",$Q16=""),1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0))</f>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="20" t="n"/>
+      <c r="T16" s="47" t="n"/>
+      <c r="U16" s="18" t="n"/>
+      <c r="V16" s="18" t="n"/>
+      <c r="W16" s="18" t="n"/>
+      <c r="X16" s="18" t="n"/>
+      <c r="Y16" s="48" t="n"/>
+      <c r="Z16" s="48" t="n"/>
+      <c r="AA16" s="18" t="n"/>
+      <c r="AB16" s="18" t="n"/>
+      <c r="AC16" s="18" t="n"/>
+      <c r="AD16" s="18" t="n"/>
+      <c r="AE16" s="18" t="n"/>
+      <c r="AF16" s="20" t="n"/>
+      <c r="AG16" s="13">
+        <f>IF($A16="","",IF(AH16&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH16">
+        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($P16="",1,0)+IF($S16="",1,0)+IF($T16="",1,0)+IF($U16="",1,0)+IF($W16="",1,0)+IF($AA16="",1,0)+IF($AB16="",1,0)+IF(AND($N16="契約期間満了",$Q16=""),1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0)+IF(AND($AD16="外国",$AE16=""),1,0)+IF(AND($AD16="外国",$AF16=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="44" t="n"/>
-      <c r="E17" s="44" t="n"/>
-      <c r="F17" s="44" t="n"/>
-      <c r="G17" s="44" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="45">
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="45" t="n"/>
+      <c r="F17" s="45" t="n"/>
+      <c r="G17" s="45" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="45" t="n"/>
+      <c r="L17" s="20" t="n"/>
+      <c r="M17" s="46">
         <f>IF($L17="","",$L17+1)</f>
         <v/>
       </c>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
-      <c r="R17" s="16" t="n"/>
-      <c r="S17" s="16" t="n"/>
-      <c r="T17" s="16" t="n"/>
-      <c r="U17" s="16" t="n"/>
-      <c r="V17" s="16" t="n"/>
-      <c r="W17" s="46" t="n"/>
-      <c r="X17" s="46" t="n"/>
-      <c r="Y17" s="16" t="n"/>
-      <c r="Z17" s="16" t="n"/>
-      <c r="AA17" s="16" t="n"/>
-      <c r="AB17" s="47">
-        <f>IF($A17="","",IF(AC17&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($O17="",1,0)+IF($P17="",1,0)+IF($S17="",1,0)+IF($U17="",1,0)+IF($Y17="",1,0)+IF($Z17="",1,0)+IF(AND($N17="契約期間満了",$Q17=""),1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0))</f>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="18" t="n"/>
+      <c r="P17" s="18" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="18" t="n"/>
+      <c r="S17" s="20" t="n"/>
+      <c r="T17" s="47" t="n"/>
+      <c r="U17" s="18" t="n"/>
+      <c r="V17" s="18" t="n"/>
+      <c r="W17" s="18" t="n"/>
+      <c r="X17" s="18" t="n"/>
+      <c r="Y17" s="48" t="n"/>
+      <c r="Z17" s="48" t="n"/>
+      <c r="AA17" s="18" t="n"/>
+      <c r="AB17" s="18" t="n"/>
+      <c r="AC17" s="18" t="n"/>
+      <c r="AD17" s="18" t="n"/>
+      <c r="AE17" s="18" t="n"/>
+      <c r="AF17" s="20" t="n"/>
+      <c r="AG17" s="13">
+        <f>IF($A17="","",IF(AH17&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH17">
+        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($P17="",1,0)+IF($S17="",1,0)+IF($T17="",1,0)+IF($U17="",1,0)+IF($W17="",1,0)+IF($AA17="",1,0)+IF($AB17="",1,0)+IF(AND($N17="契約期間満了",$Q17=""),1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0)+IF(AND($AD17="外国",$AE17=""),1,0)+IF(AND($AD17="外国",$AF17=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="44" t="n"/>
-      <c r="F18" s="44" t="n"/>
-      <c r="G18" s="44" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="18" t="n"/>
-      <c r="M18" s="45">
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="45" t="n"/>
+      <c r="L18" s="20" t="n"/>
+      <c r="M18" s="46">
         <f>IF($L18="","",$L18+1)</f>
         <v/>
       </c>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="16" t="n"/>
-      <c r="R18" s="16" t="n"/>
-      <c r="S18" s="16" t="n"/>
-      <c r="T18" s="16" t="n"/>
-      <c r="U18" s="16" t="n"/>
-      <c r="V18" s="16" t="n"/>
-      <c r="W18" s="46" t="n"/>
-      <c r="X18" s="46" t="n"/>
-      <c r="Y18" s="16" t="n"/>
-      <c r="Z18" s="16" t="n"/>
-      <c r="AA18" s="16" t="n"/>
-      <c r="AB18" s="47">
-        <f>IF($A18="","",IF(AC18&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($O18="",1,0)+IF($P18="",1,0)+IF($S18="",1,0)+IF($U18="",1,0)+IF($Y18="",1,0)+IF($Z18="",1,0)+IF(AND($N18="契約期間満了",$Q18=""),1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0))</f>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="18" t="n"/>
+      <c r="P18" s="18" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="18" t="n"/>
+      <c r="S18" s="20" t="n"/>
+      <c r="T18" s="47" t="n"/>
+      <c r="U18" s="18" t="n"/>
+      <c r="V18" s="18" t="n"/>
+      <c r="W18" s="18" t="n"/>
+      <c r="X18" s="18" t="n"/>
+      <c r="Y18" s="48" t="n"/>
+      <c r="Z18" s="48" t="n"/>
+      <c r="AA18" s="18" t="n"/>
+      <c r="AB18" s="18" t="n"/>
+      <c r="AC18" s="18" t="n"/>
+      <c r="AD18" s="18" t="n"/>
+      <c r="AE18" s="18" t="n"/>
+      <c r="AF18" s="20" t="n"/>
+      <c r="AG18" s="13">
+        <f>IF($A18="","",IF(AH18&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH18">
+        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($P18="",1,0)+IF($S18="",1,0)+IF($T18="",1,0)+IF($U18="",1,0)+IF($W18="",1,0)+IF($AA18="",1,0)+IF($AB18="",1,0)+IF(AND($N18="契約期間満了",$Q18=""),1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0)+IF(AND($AD18="外国",$AE18=""),1,0)+IF(AND($AD18="外国",$AF18=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="44" t="n"/>
-      <c r="E19" s="44" t="n"/>
-      <c r="F19" s="44" t="n"/>
-      <c r="G19" s="44" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="16" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="18" t="n"/>
-      <c r="M19" s="45">
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="45" t="n"/>
+      <c r="E19" s="45" t="n"/>
+      <c r="F19" s="45" t="n"/>
+      <c r="G19" s="45" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="20" t="n"/>
+      <c r="M19" s="46">
         <f>IF($L19="","",$L19+1)</f>
         <v/>
       </c>
-      <c r="N19" s="16" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
-      <c r="R19" s="16" t="n"/>
-      <c r="S19" s="16" t="n"/>
-      <c r="T19" s="16" t="n"/>
-      <c r="U19" s="16" t="n"/>
-      <c r="V19" s="16" t="n"/>
-      <c r="W19" s="46" t="n"/>
-      <c r="X19" s="46" t="n"/>
-      <c r="Y19" s="16" t="n"/>
-      <c r="Z19" s="16" t="n"/>
-      <c r="AA19" s="16" t="n"/>
-      <c r="AB19" s="47">
-        <f>IF($A19="","",IF(AC19&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($O19="",1,0)+IF($P19="",1,0)+IF($S19="",1,0)+IF($U19="",1,0)+IF($Y19="",1,0)+IF($Z19="",1,0)+IF(AND($N19="契約期間満了",$Q19=""),1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0))</f>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="18" t="n"/>
+      <c r="P19" s="18" t="n"/>
+      <c r="Q19" s="18" t="n"/>
+      <c r="R19" s="18" t="n"/>
+      <c r="S19" s="20" t="n"/>
+      <c r="T19" s="47" t="n"/>
+      <c r="U19" s="18" t="n"/>
+      <c r="V19" s="18" t="n"/>
+      <c r="W19" s="18" t="n"/>
+      <c r="X19" s="18" t="n"/>
+      <c r="Y19" s="48" t="n"/>
+      <c r="Z19" s="48" t="n"/>
+      <c r="AA19" s="18" t="n"/>
+      <c r="AB19" s="18" t="n"/>
+      <c r="AC19" s="18" t="n"/>
+      <c r="AD19" s="18" t="n"/>
+      <c r="AE19" s="18" t="n"/>
+      <c r="AF19" s="20" t="n"/>
+      <c r="AG19" s="13">
+        <f>IF($A19="","",IF(AH19&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH19">
+        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($P19="",1,0)+IF($S19="",1,0)+IF($T19="",1,0)+IF($U19="",1,0)+IF($W19="",1,0)+IF($AA19="",1,0)+IF($AB19="",1,0)+IF(AND($N19="契約期間満了",$Q19=""),1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0)+IF(AND($AD19="外国",$AE19=""),1,0)+IF(AND($AD19="外国",$AF19=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="44" t="n"/>
-      <c r="F20" s="44" t="n"/>
-      <c r="G20" s="44" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="45">
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="45" t="n"/>
+      <c r="E20" s="45" t="n"/>
+      <c r="F20" s="45" t="n"/>
+      <c r="G20" s="45" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="20" t="n"/>
+      <c r="M20" s="46">
         <f>IF($L20="","",$L20+1)</f>
         <v/>
       </c>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="16" t="n"/>
-      <c r="R20" s="16" t="n"/>
-      <c r="S20" s="16" t="n"/>
-      <c r="T20" s="16" t="n"/>
-      <c r="U20" s="16" t="n"/>
-      <c r="V20" s="16" t="n"/>
-      <c r="W20" s="46" t="n"/>
-      <c r="X20" s="46" t="n"/>
-      <c r="Y20" s="16" t="n"/>
-      <c r="Z20" s="16" t="n"/>
-      <c r="AA20" s="16" t="n"/>
-      <c r="AB20" s="47">
-        <f>IF($A20="","",IF(AC20&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($O20="",1,0)+IF($P20="",1,0)+IF($S20="",1,0)+IF($U20="",1,0)+IF($Y20="",1,0)+IF($Z20="",1,0)+IF(AND($N20="契約期間満了",$Q20=""),1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0))</f>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="18" t="n"/>
+      <c r="P20" s="18" t="n"/>
+      <c r="Q20" s="18" t="n"/>
+      <c r="R20" s="18" t="n"/>
+      <c r="S20" s="20" t="n"/>
+      <c r="T20" s="47" t="n"/>
+      <c r="U20" s="18" t="n"/>
+      <c r="V20" s="18" t="n"/>
+      <c r="W20" s="18" t="n"/>
+      <c r="X20" s="18" t="n"/>
+      <c r="Y20" s="48" t="n"/>
+      <c r="Z20" s="48" t="n"/>
+      <c r="AA20" s="18" t="n"/>
+      <c r="AB20" s="18" t="n"/>
+      <c r="AC20" s="18" t="n"/>
+      <c r="AD20" s="18" t="n"/>
+      <c r="AE20" s="18" t="n"/>
+      <c r="AF20" s="20" t="n"/>
+      <c r="AG20" s="13">
+        <f>IF($A20="","",IF(AH20&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH20">
+        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($P20="",1,0)+IF($S20="",1,0)+IF($T20="",1,0)+IF($U20="",1,0)+IF($W20="",1,0)+IF($AA20="",1,0)+IF($AB20="",1,0)+IF(AND($N20="契約期間満了",$Q20=""),1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0)+IF(AND($AD20="外国",$AE20=""),1,0)+IF(AND($AD20="外国",$AF20=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="44" t="n"/>
-      <c r="E21" s="44" t="n"/>
-      <c r="F21" s="44" t="n"/>
-      <c r="G21" s="44" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="45">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="45" t="n"/>
+      <c r="E21" s="45" t="n"/>
+      <c r="F21" s="45" t="n"/>
+      <c r="G21" s="45" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="45" t="n"/>
+      <c r="L21" s="20" t="n"/>
+      <c r="M21" s="46">
         <f>IF($L21="","",$L21+1)</f>
         <v/>
       </c>
-      <c r="N21" s="16" t="n"/>
-      <c r="O21" s="16" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="16" t="n"/>
-      <c r="R21" s="16" t="n"/>
-      <c r="S21" s="16" t="n"/>
-      <c r="T21" s="16" t="n"/>
-      <c r="U21" s="16" t="n"/>
-      <c r="V21" s="16" t="n"/>
-      <c r="W21" s="46" t="n"/>
-      <c r="X21" s="46" t="n"/>
-      <c r="Y21" s="16" t="n"/>
-      <c r="Z21" s="16" t="n"/>
-      <c r="AA21" s="16" t="n"/>
-      <c r="AB21" s="47">
-        <f>IF($A21="","",IF(AC21&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($O21="",1,0)+IF($P21="",1,0)+IF($S21="",1,0)+IF($U21="",1,0)+IF($Y21="",1,0)+IF($Z21="",1,0)+IF(AND($N21="契約期間満了",$Q21=""),1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0))</f>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="18" t="n"/>
+      <c r="P21" s="18" t="n"/>
+      <c r="Q21" s="18" t="n"/>
+      <c r="R21" s="18" t="n"/>
+      <c r="S21" s="20" t="n"/>
+      <c r="T21" s="47" t="n"/>
+      <c r="U21" s="18" t="n"/>
+      <c r="V21" s="18" t="n"/>
+      <c r="W21" s="18" t="n"/>
+      <c r="X21" s="18" t="n"/>
+      <c r="Y21" s="48" t="n"/>
+      <c r="Z21" s="48" t="n"/>
+      <c r="AA21" s="18" t="n"/>
+      <c r="AB21" s="18" t="n"/>
+      <c r="AC21" s="18" t="n"/>
+      <c r="AD21" s="18" t="n"/>
+      <c r="AE21" s="18" t="n"/>
+      <c r="AF21" s="20" t="n"/>
+      <c r="AG21" s="13">
+        <f>IF($A21="","",IF(AH21&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH21">
+        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($P21="",1,0)+IF($S21="",1,0)+IF($T21="",1,0)+IF($U21="",1,0)+IF($W21="",1,0)+IF($AA21="",1,0)+IF($AB21="",1,0)+IF(AND($N21="契約期間満了",$Q21=""),1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0)+IF(AND($AD21="外国",$AE21=""),1,0)+IF(AND($AD21="外国",$AF21=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="44" t="n"/>
-      <c r="E22" s="44" t="n"/>
-      <c r="F22" s="44" t="n"/>
-      <c r="G22" s="44" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="45">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="45" t="n"/>
+      <c r="G22" s="45" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="45" t="n"/>
+      <c r="L22" s="20" t="n"/>
+      <c r="M22" s="46">
         <f>IF($L22="","",$L22+1)</f>
         <v/>
       </c>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="16" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="16" t="n"/>
-      <c r="R22" s="16" t="n"/>
-      <c r="S22" s="16" t="n"/>
-      <c r="T22" s="16" t="n"/>
-      <c r="U22" s="16" t="n"/>
-      <c r="V22" s="16" t="n"/>
-      <c r="W22" s="46" t="n"/>
-      <c r="X22" s="46" t="n"/>
-      <c r="Y22" s="16" t="n"/>
-      <c r="Z22" s="16" t="n"/>
-      <c r="AA22" s="16" t="n"/>
-      <c r="AB22" s="47">
-        <f>IF($A22="","",IF(AC22&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($O22="",1,0)+IF($P22="",1,0)+IF($S22="",1,0)+IF($U22="",1,0)+IF($Y22="",1,0)+IF($Z22="",1,0)+IF(AND($N22="契約期間満了",$Q22=""),1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0))</f>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="18" t="n"/>
+      <c r="P22" s="18" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="R22" s="18" t="n"/>
+      <c r="S22" s="20" t="n"/>
+      <c r="T22" s="47" t="n"/>
+      <c r="U22" s="18" t="n"/>
+      <c r="V22" s="18" t="n"/>
+      <c r="W22" s="18" t="n"/>
+      <c r="X22" s="18" t="n"/>
+      <c r="Y22" s="48" t="n"/>
+      <c r="Z22" s="48" t="n"/>
+      <c r="AA22" s="18" t="n"/>
+      <c r="AB22" s="18" t="n"/>
+      <c r="AC22" s="18" t="n"/>
+      <c r="AD22" s="18" t="n"/>
+      <c r="AE22" s="18" t="n"/>
+      <c r="AF22" s="20" t="n"/>
+      <c r="AG22" s="13">
+        <f>IF($A22="","",IF(AH22&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH22">
+        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($P22="",1,0)+IF($S22="",1,0)+IF($T22="",1,0)+IF($U22="",1,0)+IF($W22="",1,0)+IF($AA22="",1,0)+IF($AB22="",1,0)+IF(AND($N22="契約期間満了",$Q22=""),1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0)+IF(AND($AD22="外国",$AE22=""),1,0)+IF(AND($AD22="外国",$AF22=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="44" t="n"/>
-      <c r="E23" s="44" t="n"/>
-      <c r="F23" s="44" t="n"/>
-      <c r="G23" s="44" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="16" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="45">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="45" t="n"/>
+      <c r="E23" s="45" t="n"/>
+      <c r="F23" s="45" t="n"/>
+      <c r="G23" s="45" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="45" t="n"/>
+      <c r="L23" s="20" t="n"/>
+      <c r="M23" s="46">
         <f>IF($L23="","",$L23+1)</f>
         <v/>
       </c>
-      <c r="N23" s="16" t="n"/>
-      <c r="O23" s="16" t="n"/>
-      <c r="P23" s="16" t="n"/>
-      <c r="Q23" s="16" t="n"/>
-      <c r="R23" s="16" t="n"/>
-      <c r="S23" s="16" t="n"/>
-      <c r="T23" s="16" t="n"/>
-      <c r="U23" s="16" t="n"/>
-      <c r="V23" s="16" t="n"/>
-      <c r="W23" s="46" t="n"/>
-      <c r="X23" s="46" t="n"/>
-      <c r="Y23" s="16" t="n"/>
-      <c r="Z23" s="16" t="n"/>
-      <c r="AA23" s="16" t="n"/>
-      <c r="AB23" s="47">
-        <f>IF($A23="","",IF(AC23&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($O23="",1,0)+IF($P23="",1,0)+IF($S23="",1,0)+IF($U23="",1,0)+IF($Y23="",1,0)+IF($Z23="",1,0)+IF(AND($N23="契約期間満了",$Q23=""),1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0))</f>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="18" t="n"/>
+      <c r="P23" s="18" t="n"/>
+      <c r="Q23" s="18" t="n"/>
+      <c r="R23" s="18" t="n"/>
+      <c r="S23" s="20" t="n"/>
+      <c r="T23" s="47" t="n"/>
+      <c r="U23" s="18" t="n"/>
+      <c r="V23" s="18" t="n"/>
+      <c r="W23" s="18" t="n"/>
+      <c r="X23" s="18" t="n"/>
+      <c r="Y23" s="48" t="n"/>
+      <c r="Z23" s="48" t="n"/>
+      <c r="AA23" s="18" t="n"/>
+      <c r="AB23" s="18" t="n"/>
+      <c r="AC23" s="18" t="n"/>
+      <c r="AD23" s="18" t="n"/>
+      <c r="AE23" s="18" t="n"/>
+      <c r="AF23" s="20" t="n"/>
+      <c r="AG23" s="13">
+        <f>IF($A23="","",IF(AH23&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH23">
+        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($P23="",1,0)+IF($S23="",1,0)+IF($T23="",1,0)+IF($U23="",1,0)+IF($W23="",1,0)+IF($AA23="",1,0)+IF($AB23="",1,0)+IF(AND($N23="契約期間満了",$Q23=""),1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0)+IF(AND($AD23="外国",$AE23=""),1,0)+IF(AND($AD23="外国",$AF23=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="44" t="n"/>
-      <c r="E24" s="44" t="n"/>
-      <c r="F24" s="44" t="n"/>
-      <c r="G24" s="44" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="16" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="45">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="45" t="n"/>
+      <c r="G24" s="45" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="45" t="n"/>
+      <c r="L24" s="20" t="n"/>
+      <c r="M24" s="46">
         <f>IF($L24="","",$L24+1)</f>
         <v/>
       </c>
-      <c r="N24" s="16" t="n"/>
-      <c r="O24" s="16" t="n"/>
-      <c r="P24" s="16" t="n"/>
-      <c r="Q24" s="16" t="n"/>
-      <c r="R24" s="16" t="n"/>
-      <c r="S24" s="16" t="n"/>
-      <c r="T24" s="16" t="n"/>
-      <c r="U24" s="16" t="n"/>
-      <c r="V24" s="16" t="n"/>
-      <c r="W24" s="46" t="n"/>
-      <c r="X24" s="46" t="n"/>
-      <c r="Y24" s="16" t="n"/>
-      <c r="Z24" s="16" t="n"/>
-      <c r="AA24" s="16" t="n"/>
-      <c r="AB24" s="47">
-        <f>IF($A24="","",IF(AC24&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($O24="",1,0)+IF($P24="",1,0)+IF($S24="",1,0)+IF($U24="",1,0)+IF($Y24="",1,0)+IF($Z24="",1,0)+IF(AND($N24="契約期間満了",$Q24=""),1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0))</f>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
+      <c r="P24" s="18" t="n"/>
+      <c r="Q24" s="18" t="n"/>
+      <c r="R24" s="18" t="n"/>
+      <c r="S24" s="20" t="n"/>
+      <c r="T24" s="47" t="n"/>
+      <c r="U24" s="18" t="n"/>
+      <c r="V24" s="18" t="n"/>
+      <c r="W24" s="18" t="n"/>
+      <c r="X24" s="18" t="n"/>
+      <c r="Y24" s="48" t="n"/>
+      <c r="Z24" s="48" t="n"/>
+      <c r="AA24" s="18" t="n"/>
+      <c r="AB24" s="18" t="n"/>
+      <c r="AC24" s="18" t="n"/>
+      <c r="AD24" s="18" t="n"/>
+      <c r="AE24" s="18" t="n"/>
+      <c r="AF24" s="20" t="n"/>
+      <c r="AG24" s="13">
+        <f>IF($A24="","",IF(AH24&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH24">
+        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($P24="",1,0)+IF($S24="",1,0)+IF($T24="",1,0)+IF($U24="",1,0)+IF($W24="",1,0)+IF($AA24="",1,0)+IF($AB24="",1,0)+IF(AND($N24="契約期間満了",$Q24=""),1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0)+IF(AND($AD24="外国",$AE24=""),1,0)+IF(AND($AD24="外国",$AF24=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="44" t="n"/>
-      <c r="E25" s="44" t="n"/>
-      <c r="F25" s="44" t="n"/>
-      <c r="G25" s="44" t="n"/>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="45">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="45" t="n"/>
+      <c r="F25" s="45" t="n"/>
+      <c r="G25" s="45" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="45" t="n"/>
+      <c r="L25" s="20" t="n"/>
+      <c r="M25" s="46">
         <f>IF($L25="","",$L25+1)</f>
         <v/>
       </c>
-      <c r="N25" s="16" t="n"/>
-      <c r="O25" s="16" t="n"/>
-      <c r="P25" s="16" t="n"/>
-      <c r="Q25" s="16" t="n"/>
-      <c r="R25" s="16" t="n"/>
-      <c r="S25" s="16" t="n"/>
-      <c r="T25" s="16" t="n"/>
-      <c r="U25" s="16" t="n"/>
-      <c r="V25" s="16" t="n"/>
-      <c r="W25" s="46" t="n"/>
-      <c r="X25" s="46" t="n"/>
-      <c r="Y25" s="16" t="n"/>
-      <c r="Z25" s="16" t="n"/>
-      <c r="AA25" s="16" t="n"/>
-      <c r="AB25" s="47">
-        <f>IF($A25="","",IF(AC25&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($O25="",1,0)+IF($P25="",1,0)+IF($S25="",1,0)+IF($U25="",1,0)+IF($Y25="",1,0)+IF($Z25="",1,0)+IF(AND($N25="契約期間満了",$Q25=""),1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0))</f>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="18" t="n"/>
+      <c r="R25" s="18" t="n"/>
+      <c r="S25" s="20" t="n"/>
+      <c r="T25" s="47" t="n"/>
+      <c r="U25" s="18" t="n"/>
+      <c r="V25" s="18" t="n"/>
+      <c r="W25" s="18" t="n"/>
+      <c r="X25" s="18" t="n"/>
+      <c r="Y25" s="48" t="n"/>
+      <c r="Z25" s="48" t="n"/>
+      <c r="AA25" s="18" t="n"/>
+      <c r="AB25" s="18" t="n"/>
+      <c r="AC25" s="18" t="n"/>
+      <c r="AD25" s="18" t="n"/>
+      <c r="AE25" s="18" t="n"/>
+      <c r="AF25" s="20" t="n"/>
+      <c r="AG25" s="13">
+        <f>IF($A25="","",IF(AH25&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH25">
+        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($P25="",1,0)+IF($S25="",1,0)+IF($T25="",1,0)+IF($U25="",1,0)+IF($W25="",1,0)+IF($AA25="",1,0)+IF($AB25="",1,0)+IF(AND($N25="契約期間満了",$Q25=""),1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0)+IF(AND($AD25="外国",$AE25=""),1,0)+IF(AND($AD25="外国",$AF25=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="44" t="n"/>
-      <c r="E26" s="44" t="n"/>
-      <c r="F26" s="44" t="n"/>
-      <c r="G26" s="44" t="n"/>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="45">
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="45" t="n"/>
+      <c r="G26" s="45" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="45" t="n"/>
+      <c r="L26" s="20" t="n"/>
+      <c r="M26" s="46">
         <f>IF($L26="","",$L26+1)</f>
         <v/>
       </c>
-      <c r="N26" s="16" t="n"/>
-      <c r="O26" s="16" t="n"/>
-      <c r="P26" s="16" t="n"/>
-      <c r="Q26" s="16" t="n"/>
-      <c r="R26" s="16" t="n"/>
-      <c r="S26" s="16" t="n"/>
-      <c r="T26" s="16" t="n"/>
-      <c r="U26" s="16" t="n"/>
-      <c r="V26" s="16" t="n"/>
-      <c r="W26" s="46" t="n"/>
-      <c r="X26" s="46" t="n"/>
-      <c r="Y26" s="16" t="n"/>
-      <c r="Z26" s="16" t="n"/>
-      <c r="AA26" s="16" t="n"/>
-      <c r="AB26" s="47">
-        <f>IF($A26="","",IF(AC26&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($O26="",1,0)+IF($P26="",1,0)+IF($S26="",1,0)+IF($U26="",1,0)+IF($Y26="",1,0)+IF($Z26="",1,0)+IF(AND($N26="契約期間満了",$Q26=""),1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0))</f>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="18" t="n"/>
+      <c r="P26" s="18" t="n"/>
+      <c r="Q26" s="18" t="n"/>
+      <c r="R26" s="18" t="n"/>
+      <c r="S26" s="20" t="n"/>
+      <c r="T26" s="47" t="n"/>
+      <c r="U26" s="18" t="n"/>
+      <c r="V26" s="18" t="n"/>
+      <c r="W26" s="18" t="n"/>
+      <c r="X26" s="18" t="n"/>
+      <c r="Y26" s="48" t="n"/>
+      <c r="Z26" s="48" t="n"/>
+      <c r="AA26" s="18" t="n"/>
+      <c r="AB26" s="18" t="n"/>
+      <c r="AC26" s="18" t="n"/>
+      <c r="AD26" s="18" t="n"/>
+      <c r="AE26" s="18" t="n"/>
+      <c r="AF26" s="20" t="n"/>
+      <c r="AG26" s="13">
+        <f>IF($A26="","",IF(AH26&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH26">
+        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($P26="",1,0)+IF($S26="",1,0)+IF($T26="",1,0)+IF($U26="",1,0)+IF($W26="",1,0)+IF($AA26="",1,0)+IF($AB26="",1,0)+IF(AND($N26="契約期間満了",$Q26=""),1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0)+IF(AND($AD26="外国",$AE26=""),1,0)+IF(AND($AD26="外国",$AF26=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="44" t="n"/>
-      <c r="E27" s="44" t="n"/>
-      <c r="F27" s="44" t="n"/>
-      <c r="G27" s="44" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="45">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="45" t="n"/>
+      <c r="E27" s="45" t="n"/>
+      <c r="F27" s="45" t="n"/>
+      <c r="G27" s="45" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="45" t="n"/>
+      <c r="L27" s="20" t="n"/>
+      <c r="M27" s="46">
         <f>IF($L27="","",$L27+1)</f>
         <v/>
       </c>
-      <c r="N27" s="16" t="n"/>
-      <c r="O27" s="16" t="n"/>
-      <c r="P27" s="16" t="n"/>
-      <c r="Q27" s="16" t="n"/>
-      <c r="R27" s="16" t="n"/>
-      <c r="S27" s="16" t="n"/>
-      <c r="T27" s="16" t="n"/>
-      <c r="U27" s="16" t="n"/>
-      <c r="V27" s="16" t="n"/>
-      <c r="W27" s="46" t="n"/>
-      <c r="X27" s="46" t="n"/>
-      <c r="Y27" s="16" t="n"/>
-      <c r="Z27" s="16" t="n"/>
-      <c r="AA27" s="16" t="n"/>
-      <c r="AB27" s="47">
-        <f>IF($A27="","",IF(AC27&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($O27="",1,0)+IF($P27="",1,0)+IF($S27="",1,0)+IF($U27="",1,0)+IF($Y27="",1,0)+IF($Z27="",1,0)+IF(AND($N27="契約期間満了",$Q27=""),1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0))</f>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="18" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="18" t="n"/>
+      <c r="R27" s="18" t="n"/>
+      <c r="S27" s="20" t="n"/>
+      <c r="T27" s="47" t="n"/>
+      <c r="U27" s="18" t="n"/>
+      <c r="V27" s="18" t="n"/>
+      <c r="W27" s="18" t="n"/>
+      <c r="X27" s="18" t="n"/>
+      <c r="Y27" s="48" t="n"/>
+      <c r="Z27" s="48" t="n"/>
+      <c r="AA27" s="18" t="n"/>
+      <c r="AB27" s="18" t="n"/>
+      <c r="AC27" s="18" t="n"/>
+      <c r="AD27" s="18" t="n"/>
+      <c r="AE27" s="18" t="n"/>
+      <c r="AF27" s="20" t="n"/>
+      <c r="AG27" s="13">
+        <f>IF($A27="","",IF(AH27&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH27">
+        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($P27="",1,0)+IF($S27="",1,0)+IF($T27="",1,0)+IF($U27="",1,0)+IF($W27="",1,0)+IF($AA27="",1,0)+IF($AB27="",1,0)+IF(AND($N27="契約期間満了",$Q27=""),1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0)+IF(AND($AD27="外国",$AE27=""),1,0)+IF(AND($AD27="外国",$AF27=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="44" t="n"/>
-      <c r="E28" s="44" t="n"/>
-      <c r="F28" s="44" t="n"/>
-      <c r="G28" s="44" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="45">
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="45" t="n"/>
+      <c r="F28" s="45" t="n"/>
+      <c r="G28" s="45" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="45" t="n"/>
+      <c r="L28" s="20" t="n"/>
+      <c r="M28" s="46">
         <f>IF($L28="","",$L28+1)</f>
         <v/>
       </c>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16" t="n"/>
-      <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="16" t="n"/>
-      <c r="R28" s="16" t="n"/>
-      <c r="S28" s="16" t="n"/>
-      <c r="T28" s="16" t="n"/>
-      <c r="U28" s="16" t="n"/>
-      <c r="V28" s="16" t="n"/>
-      <c r="W28" s="46" t="n"/>
-      <c r="X28" s="46" t="n"/>
-      <c r="Y28" s="16" t="n"/>
-      <c r="Z28" s="16" t="n"/>
-      <c r="AA28" s="16" t="n"/>
-      <c r="AB28" s="47">
-        <f>IF($A28="","",IF(AC28&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($O28="",1,0)+IF($P28="",1,0)+IF($S28="",1,0)+IF($U28="",1,0)+IF($Y28="",1,0)+IF($Z28="",1,0)+IF(AND($N28="契約期間満了",$Q28=""),1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0))</f>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
+      <c r="P28" s="18" t="n"/>
+      <c r="Q28" s="18" t="n"/>
+      <c r="R28" s="18" t="n"/>
+      <c r="S28" s="20" t="n"/>
+      <c r="T28" s="47" t="n"/>
+      <c r="U28" s="18" t="n"/>
+      <c r="V28" s="18" t="n"/>
+      <c r="W28" s="18" t="n"/>
+      <c r="X28" s="18" t="n"/>
+      <c r="Y28" s="48" t="n"/>
+      <c r="Z28" s="48" t="n"/>
+      <c r="AA28" s="18" t="n"/>
+      <c r="AB28" s="18" t="n"/>
+      <c r="AC28" s="18" t="n"/>
+      <c r="AD28" s="18" t="n"/>
+      <c r="AE28" s="18" t="n"/>
+      <c r="AF28" s="20" t="n"/>
+      <c r="AG28" s="13">
+        <f>IF($A28="","",IF(AH28&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH28">
+        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($P28="",1,0)+IF($S28="",1,0)+IF($T28="",1,0)+IF($U28="",1,0)+IF($W28="",1,0)+IF($AA28="",1,0)+IF($AB28="",1,0)+IF(AND($N28="契約期間満了",$Q28=""),1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0)+IF(AND($AD28="外国",$AE28=""),1,0)+IF(AND($AD28="外国",$AF28=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="44" t="n"/>
-      <c r="E29" s="44" t="n"/>
-      <c r="F29" s="44" t="n"/>
-      <c r="G29" s="44" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="18" t="n"/>
-      <c r="M29" s="45">
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="45" t="n"/>
+      <c r="E29" s="45" t="n"/>
+      <c r="F29" s="45" t="n"/>
+      <c r="G29" s="45" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="45" t="n"/>
+      <c r="L29" s="20" t="n"/>
+      <c r="M29" s="46">
         <f>IF($L29="","",$L29+1)</f>
         <v/>
       </c>
-      <c r="N29" s="16" t="n"/>
-      <c r="O29" s="16" t="n"/>
-      <c r="P29" s="16" t="n"/>
-      <c r="Q29" s="16" t="n"/>
-      <c r="R29" s="16" t="n"/>
-      <c r="S29" s="16" t="n"/>
-      <c r="T29" s="16" t="n"/>
-      <c r="U29" s="16" t="n"/>
-      <c r="V29" s="16" t="n"/>
-      <c r="W29" s="46" t="n"/>
-      <c r="X29" s="46" t="n"/>
-      <c r="Y29" s="16" t="n"/>
-      <c r="Z29" s="16" t="n"/>
-      <c r="AA29" s="16" t="n"/>
-      <c r="AB29" s="47">
-        <f>IF($A29="","",IF(AC29&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($O29="",1,0)+IF($P29="",1,0)+IF($S29="",1,0)+IF($U29="",1,0)+IF($Y29="",1,0)+IF($Z29="",1,0)+IF(AND($N29="契約期間満了",$Q29=""),1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0))</f>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="18" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="18" t="n"/>
+      <c r="R29" s="18" t="n"/>
+      <c r="S29" s="20" t="n"/>
+      <c r="T29" s="47" t="n"/>
+      <c r="U29" s="18" t="n"/>
+      <c r="V29" s="18" t="n"/>
+      <c r="W29" s="18" t="n"/>
+      <c r="X29" s="18" t="n"/>
+      <c r="Y29" s="48" t="n"/>
+      <c r="Z29" s="48" t="n"/>
+      <c r="AA29" s="18" t="n"/>
+      <c r="AB29" s="18" t="n"/>
+      <c r="AC29" s="18" t="n"/>
+      <c r="AD29" s="18" t="n"/>
+      <c r="AE29" s="18" t="n"/>
+      <c r="AF29" s="20" t="n"/>
+      <c r="AG29" s="13">
+        <f>IF($A29="","",IF(AH29&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH29">
+        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($P29="",1,0)+IF($S29="",1,0)+IF($T29="",1,0)+IF($U29="",1,0)+IF($W29="",1,0)+IF($AA29="",1,0)+IF($AB29="",1,0)+IF(AND($N29="契約期間満了",$Q29=""),1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0)+IF(AND($AD29="外国",$AE29=""),1,0)+IF(AND($AD29="外国",$AF29=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="44" t="n"/>
-      <c r="E30" s="44" t="n"/>
-      <c r="F30" s="44" t="n"/>
-      <c r="G30" s="44" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="18" t="n"/>
-      <c r="M30" s="45">
+      <c r="A30" s="18" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="45" t="n"/>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="45" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="20" t="n"/>
+      <c r="M30" s="46">
         <f>IF($L30="","",$L30+1)</f>
         <v/>
       </c>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="16" t="n"/>
-      <c r="P30" s="16" t="n"/>
-      <c r="Q30" s="16" t="n"/>
-      <c r="R30" s="16" t="n"/>
-      <c r="S30" s="16" t="n"/>
-      <c r="T30" s="16" t="n"/>
-      <c r="U30" s="16" t="n"/>
-      <c r="V30" s="16" t="n"/>
-      <c r="W30" s="46" t="n"/>
-      <c r="X30" s="46" t="n"/>
-      <c r="Y30" s="16" t="n"/>
-      <c r="Z30" s="16" t="n"/>
-      <c r="AA30" s="16" t="n"/>
-      <c r="AB30" s="47">
-        <f>IF($A30="","",IF(AC30&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($O30="",1,0)+IF($P30="",1,0)+IF($S30="",1,0)+IF($U30="",1,0)+IF($Y30="",1,0)+IF($Z30="",1,0)+IF(AND($N30="契約期間満了",$Q30=""),1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0))</f>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="18" t="n"/>
+      <c r="P30" s="18" t="n"/>
+      <c r="Q30" s="18" t="n"/>
+      <c r="R30" s="18" t="n"/>
+      <c r="S30" s="20" t="n"/>
+      <c r="T30" s="47" t="n"/>
+      <c r="U30" s="18" t="n"/>
+      <c r="V30" s="18" t="n"/>
+      <c r="W30" s="18" t="n"/>
+      <c r="X30" s="18" t="n"/>
+      <c r="Y30" s="48" t="n"/>
+      <c r="Z30" s="48" t="n"/>
+      <c r="AA30" s="18" t="n"/>
+      <c r="AB30" s="18" t="n"/>
+      <c r="AC30" s="18" t="n"/>
+      <c r="AD30" s="18" t="n"/>
+      <c r="AE30" s="18" t="n"/>
+      <c r="AF30" s="20" t="n"/>
+      <c r="AG30" s="13">
+        <f>IF($A30="","",IF(AH30&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH30">
+        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($P30="",1,0)+IF($S30="",1,0)+IF($T30="",1,0)+IF($U30="",1,0)+IF($W30="",1,0)+IF($AA30="",1,0)+IF($AB30="",1,0)+IF(AND($N30="契約期間満了",$Q30=""),1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0)+IF(AND($AD30="外国",$AE30=""),1,0)+IF(AND($AD30="外国",$AF30=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="44" t="n"/>
-      <c r="E31" s="44" t="n"/>
-      <c r="F31" s="44" t="n"/>
-      <c r="G31" s="44" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="45">
+      <c r="A31" s="18" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="45" t="n"/>
+      <c r="E31" s="45" t="n"/>
+      <c r="F31" s="45" t="n"/>
+      <c r="G31" s="45" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="45" t="n"/>
+      <c r="L31" s="20" t="n"/>
+      <c r="M31" s="46">
         <f>IF($L31="","",$L31+1)</f>
         <v/>
       </c>
-      <c r="N31" s="16" t="n"/>
-      <c r="O31" s="16" t="n"/>
-      <c r="P31" s="16" t="n"/>
-      <c r="Q31" s="16" t="n"/>
-      <c r="R31" s="16" t="n"/>
-      <c r="S31" s="16" t="n"/>
-      <c r="T31" s="16" t="n"/>
-      <c r="U31" s="16" t="n"/>
-      <c r="V31" s="16" t="n"/>
-      <c r="W31" s="46" t="n"/>
-      <c r="X31" s="46" t="n"/>
-      <c r="Y31" s="16" t="n"/>
-      <c r="Z31" s="16" t="n"/>
-      <c r="AA31" s="16" t="n"/>
-      <c r="AB31" s="47">
-        <f>IF($A31="","",IF(AC31&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($O31="",1,0)+IF($P31="",1,0)+IF($S31="",1,0)+IF($U31="",1,0)+IF($Y31="",1,0)+IF($Z31="",1,0)+IF(AND($N31="契約期間満了",$Q31=""),1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0))</f>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="18" t="n"/>
+      <c r="R31" s="18" t="n"/>
+      <c r="S31" s="20" t="n"/>
+      <c r="T31" s="47" t="n"/>
+      <c r="U31" s="18" t="n"/>
+      <c r="V31" s="18" t="n"/>
+      <c r="W31" s="18" t="n"/>
+      <c r="X31" s="18" t="n"/>
+      <c r="Y31" s="48" t="n"/>
+      <c r="Z31" s="48" t="n"/>
+      <c r="AA31" s="18" t="n"/>
+      <c r="AB31" s="18" t="n"/>
+      <c r="AC31" s="18" t="n"/>
+      <c r="AD31" s="18" t="n"/>
+      <c r="AE31" s="18" t="n"/>
+      <c r="AF31" s="20" t="n"/>
+      <c r="AG31" s="13">
+        <f>IF($A31="","",IF(AH31&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH31">
+        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($P31="",1,0)+IF($S31="",1,0)+IF($T31="",1,0)+IF($U31="",1,0)+IF($W31="",1,0)+IF($AA31="",1,0)+IF($AB31="",1,0)+IF(AND($N31="契約期間満了",$Q31=""),1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0)+IF(AND($AD31="外国",$AE31=""),1,0)+IF(AND($AD31="外国",$AF31=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="44" t="n"/>
-      <c r="E32" s="44" t="n"/>
-      <c r="F32" s="44" t="n"/>
-      <c r="G32" s="44" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="45">
+      <c r="A32" s="18" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="45" t="n"/>
+      <c r="E32" s="45" t="n"/>
+      <c r="F32" s="45" t="n"/>
+      <c r="G32" s="45" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="45" t="n"/>
+      <c r="L32" s="20" t="n"/>
+      <c r="M32" s="46">
         <f>IF($L32="","",$L32+1)</f>
         <v/>
       </c>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="16" t="n"/>
-      <c r="P32" s="16" t="n"/>
-      <c r="Q32" s="16" t="n"/>
-      <c r="R32" s="16" t="n"/>
-      <c r="S32" s="16" t="n"/>
-      <c r="T32" s="16" t="n"/>
-      <c r="U32" s="16" t="n"/>
-      <c r="V32" s="16" t="n"/>
-      <c r="W32" s="46" t="n"/>
-      <c r="X32" s="46" t="n"/>
-      <c r="Y32" s="16" t="n"/>
-      <c r="Z32" s="16" t="n"/>
-      <c r="AA32" s="16" t="n"/>
-      <c r="AB32" s="47">
-        <f>IF($A32="","",IF(AC32&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($O32="",1,0)+IF($P32="",1,0)+IF($S32="",1,0)+IF($U32="",1,0)+IF($Y32="",1,0)+IF($Z32="",1,0)+IF(AND($N32="契約期間満了",$Q32=""),1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0))</f>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="18" t="n"/>
+      <c r="P32" s="18" t="n"/>
+      <c r="Q32" s="18" t="n"/>
+      <c r="R32" s="18" t="n"/>
+      <c r="S32" s="20" t="n"/>
+      <c r="T32" s="47" t="n"/>
+      <c r="U32" s="18" t="n"/>
+      <c r="V32" s="18" t="n"/>
+      <c r="W32" s="18" t="n"/>
+      <c r="X32" s="18" t="n"/>
+      <c r="Y32" s="48" t="n"/>
+      <c r="Z32" s="48" t="n"/>
+      <c r="AA32" s="18" t="n"/>
+      <c r="AB32" s="18" t="n"/>
+      <c r="AC32" s="18" t="n"/>
+      <c r="AD32" s="18" t="n"/>
+      <c r="AE32" s="18" t="n"/>
+      <c r="AF32" s="20" t="n"/>
+      <c r="AG32" s="13">
+        <f>IF($A32="","",IF(AH32&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH32">
+        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($P32="",1,0)+IF($S32="",1,0)+IF($T32="",1,0)+IF($U32="",1,0)+IF($W32="",1,0)+IF($AA32="",1,0)+IF($AB32="",1,0)+IF(AND($N32="契約期間満了",$Q32=""),1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0)+IF(AND($AD32="外国",$AE32=""),1,0)+IF(AND($AD32="外国",$AF32=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="44" t="n"/>
-      <c r="E33" s="44" t="n"/>
-      <c r="F33" s="44" t="n"/>
-      <c r="G33" s="44" t="n"/>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="45">
+      <c r="A33" s="18" t="n"/>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="E33" s="45" t="n"/>
+      <c r="F33" s="45" t="n"/>
+      <c r="G33" s="45" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="45" t="n"/>
+      <c r="L33" s="20" t="n"/>
+      <c r="M33" s="46">
         <f>IF($L33="","",$L33+1)</f>
         <v/>
       </c>
-      <c r="N33" s="16" t="n"/>
-      <c r="O33" s="16" t="n"/>
-      <c r="P33" s="16" t="n"/>
-      <c r="Q33" s="16" t="n"/>
-      <c r="R33" s="16" t="n"/>
-      <c r="S33" s="16" t="n"/>
-      <c r="T33" s="16" t="n"/>
-      <c r="U33" s="16" t="n"/>
-      <c r="V33" s="16" t="n"/>
-      <c r="W33" s="46" t="n"/>
-      <c r="X33" s="46" t="n"/>
-      <c r="Y33" s="16" t="n"/>
-      <c r="Z33" s="16" t="n"/>
-      <c r="AA33" s="16" t="n"/>
-      <c r="AB33" s="47">
-        <f>IF($A33="","",IF(AC33&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($O33="",1,0)+IF($P33="",1,0)+IF($S33="",1,0)+IF($U33="",1,0)+IF($Y33="",1,0)+IF($Z33="",1,0)+IF(AND($N33="契約期間満了",$Q33=""),1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0))</f>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
+      <c r="P33" s="18" t="n"/>
+      <c r="Q33" s="18" t="n"/>
+      <c r="R33" s="18" t="n"/>
+      <c r="S33" s="20" t="n"/>
+      <c r="T33" s="47" t="n"/>
+      <c r="U33" s="18" t="n"/>
+      <c r="V33" s="18" t="n"/>
+      <c r="W33" s="18" t="n"/>
+      <c r="X33" s="18" t="n"/>
+      <c r="Y33" s="48" t="n"/>
+      <c r="Z33" s="48" t="n"/>
+      <c r="AA33" s="18" t="n"/>
+      <c r="AB33" s="18" t="n"/>
+      <c r="AC33" s="18" t="n"/>
+      <c r="AD33" s="18" t="n"/>
+      <c r="AE33" s="18" t="n"/>
+      <c r="AF33" s="20" t="n"/>
+      <c r="AG33" s="13">
+        <f>IF($A33="","",IF(AH33&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH33">
+        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($P33="",1,0)+IF($S33="",1,0)+IF($T33="",1,0)+IF($U33="",1,0)+IF($W33="",1,0)+IF($AA33="",1,0)+IF($AB33="",1,0)+IF(AND($N33="契約期間満了",$Q33=""),1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0)+IF(AND($AD33="外国",$AE33=""),1,0)+IF(AND($AD33="外国",$AF33=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="44" t="n"/>
-      <c r="E34" s="44" t="n"/>
-      <c r="F34" s="44" t="n"/>
-      <c r="G34" s="44" t="n"/>
-      <c r="H34" s="16" t="n"/>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="18" t="n"/>
-      <c r="M34" s="45">
+      <c r="A34" s="18" t="n"/>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="45" t="n"/>
+      <c r="E34" s="45" t="n"/>
+      <c r="F34" s="45" t="n"/>
+      <c r="G34" s="45" t="n"/>
+      <c r="H34" s="18" t="n"/>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="20" t="n"/>
+      <c r="M34" s="46">
         <f>IF($L34="","",$L34+1)</f>
         <v/>
       </c>
-      <c r="N34" s="16" t="n"/>
-      <c r="O34" s="16" t="n"/>
-      <c r="P34" s="16" t="n"/>
-      <c r="Q34" s="16" t="n"/>
-      <c r="R34" s="16" t="n"/>
-      <c r="S34" s="16" t="n"/>
-      <c r="T34" s="16" t="n"/>
-      <c r="U34" s="16" t="n"/>
-      <c r="V34" s="16" t="n"/>
-      <c r="W34" s="46" t="n"/>
-      <c r="X34" s="46" t="n"/>
-      <c r="Y34" s="16" t="n"/>
-      <c r="Z34" s="16" t="n"/>
-      <c r="AA34" s="16" t="n"/>
-      <c r="AB34" s="47">
-        <f>IF($A34="","",IF(AC34&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($O34="",1,0)+IF($P34="",1,0)+IF($S34="",1,0)+IF($U34="",1,0)+IF($Y34="",1,0)+IF($Z34="",1,0)+IF(AND($N34="契約期間満了",$Q34=""),1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0))</f>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="18" t="n"/>
+      <c r="P34" s="18" t="n"/>
+      <c r="Q34" s="18" t="n"/>
+      <c r="R34" s="18" t="n"/>
+      <c r="S34" s="20" t="n"/>
+      <c r="T34" s="47" t="n"/>
+      <c r="U34" s="18" t="n"/>
+      <c r="V34" s="18" t="n"/>
+      <c r="W34" s="18" t="n"/>
+      <c r="X34" s="18" t="n"/>
+      <c r="Y34" s="48" t="n"/>
+      <c r="Z34" s="48" t="n"/>
+      <c r="AA34" s="18" t="n"/>
+      <c r="AB34" s="18" t="n"/>
+      <c r="AC34" s="18" t="n"/>
+      <c r="AD34" s="18" t="n"/>
+      <c r="AE34" s="18" t="n"/>
+      <c r="AF34" s="20" t="n"/>
+      <c r="AG34" s="13">
+        <f>IF($A34="","",IF(AH34&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH34">
+        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($P34="",1,0)+IF($S34="",1,0)+IF($T34="",1,0)+IF($U34="",1,0)+IF($W34="",1,0)+IF($AA34="",1,0)+IF($AB34="",1,0)+IF(AND($N34="契約期間満了",$Q34=""),1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0)+IF(AND($AD34="外国",$AE34=""),1,0)+IF(AND($AD34="外国",$AF34=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="44" t="n"/>
-      <c r="E35" s="44" t="n"/>
-      <c r="F35" s="44" t="n"/>
-      <c r="G35" s="44" t="n"/>
-      <c r="H35" s="16" t="n"/>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="45">
+      <c r="A35" s="18" t="n"/>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="45" t="n"/>
+      <c r="E35" s="45" t="n"/>
+      <c r="F35" s="45" t="n"/>
+      <c r="G35" s="45" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="20" t="n"/>
+      <c r="M35" s="46">
         <f>IF($L35="","",$L35+1)</f>
         <v/>
       </c>
-      <c r="N35" s="16" t="n"/>
-      <c r="O35" s="16" t="n"/>
-      <c r="P35" s="16" t="n"/>
-      <c r="Q35" s="16" t="n"/>
-      <c r="R35" s="16" t="n"/>
-      <c r="S35" s="16" t="n"/>
-      <c r="T35" s="16" t="n"/>
-      <c r="U35" s="16" t="n"/>
-      <c r="V35" s="16" t="n"/>
-      <c r="W35" s="46" t="n"/>
-      <c r="X35" s="46" t="n"/>
-      <c r="Y35" s="16" t="n"/>
-      <c r="Z35" s="16" t="n"/>
-      <c r="AA35" s="16" t="n"/>
-      <c r="AB35" s="47">
-        <f>IF($A35="","",IF(AC35&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($O35="",1,0)+IF($P35="",1,0)+IF($S35="",1,0)+IF($U35="",1,0)+IF($Y35="",1,0)+IF($Z35="",1,0)+IF(AND($N35="契約期間満了",$Q35=""),1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0))</f>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="18" t="n"/>
+      <c r="R35" s="18" t="n"/>
+      <c r="S35" s="20" t="n"/>
+      <c r="T35" s="47" t="n"/>
+      <c r="U35" s="18" t="n"/>
+      <c r="V35" s="18" t="n"/>
+      <c r="W35" s="18" t="n"/>
+      <c r="X35" s="18" t="n"/>
+      <c r="Y35" s="48" t="n"/>
+      <c r="Z35" s="48" t="n"/>
+      <c r="AA35" s="18" t="n"/>
+      <c r="AB35" s="18" t="n"/>
+      <c r="AC35" s="18" t="n"/>
+      <c r="AD35" s="18" t="n"/>
+      <c r="AE35" s="18" t="n"/>
+      <c r="AF35" s="20" t="n"/>
+      <c r="AG35" s="13">
+        <f>IF($A35="","",IF(AH35&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH35">
+        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($P35="",1,0)+IF($S35="",1,0)+IF($T35="",1,0)+IF($U35="",1,0)+IF($W35="",1,0)+IF($AA35="",1,0)+IF($AB35="",1,0)+IF(AND($N35="契約期間満了",$Q35=""),1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0)+IF(AND($AD35="外国",$AE35=""),1,0)+IF(AND($AD35="外国",$AF35=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="18" t="n"/>
-      <c r="D36" s="44" t="n"/>
-      <c r="E36" s="44" t="n"/>
-      <c r="F36" s="44" t="n"/>
-      <c r="G36" s="44" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="18" t="n"/>
-      <c r="M36" s="45">
+      <c r="A36" s="18" t="n"/>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="45" t="n"/>
+      <c r="L36" s="20" t="n"/>
+      <c r="M36" s="46">
         <f>IF($L36="","",$L36+1)</f>
         <v/>
       </c>
-      <c r="N36" s="16" t="n"/>
-      <c r="O36" s="16" t="n"/>
-      <c r="P36" s="16" t="n"/>
-      <c r="Q36" s="16" t="n"/>
-      <c r="R36" s="16" t="n"/>
-      <c r="S36" s="16" t="n"/>
-      <c r="T36" s="16" t="n"/>
-      <c r="U36" s="16" t="n"/>
-      <c r="V36" s="16" t="n"/>
-      <c r="W36" s="46" t="n"/>
-      <c r="X36" s="46" t="n"/>
-      <c r="Y36" s="16" t="n"/>
-      <c r="Z36" s="16" t="n"/>
-      <c r="AA36" s="16" t="n"/>
-      <c r="AB36" s="47">
-        <f>IF($A36="","",IF(AC36&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($O36="",1,0)+IF($P36="",1,0)+IF($S36="",1,0)+IF($U36="",1,0)+IF($Y36="",1,0)+IF($Z36="",1,0)+IF(AND($N36="契約期間満了",$Q36=""),1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0))</f>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="18" t="n"/>
+      <c r="P36" s="18" t="n"/>
+      <c r="Q36" s="18" t="n"/>
+      <c r="R36" s="18" t="n"/>
+      <c r="S36" s="20" t="n"/>
+      <c r="T36" s="47" t="n"/>
+      <c r="U36" s="18" t="n"/>
+      <c r="V36" s="18" t="n"/>
+      <c r="W36" s="18" t="n"/>
+      <c r="X36" s="18" t="n"/>
+      <c r="Y36" s="48" t="n"/>
+      <c r="Z36" s="48" t="n"/>
+      <c r="AA36" s="18" t="n"/>
+      <c r="AB36" s="18" t="n"/>
+      <c r="AC36" s="18" t="n"/>
+      <c r="AD36" s="18" t="n"/>
+      <c r="AE36" s="18" t="n"/>
+      <c r="AF36" s="20" t="n"/>
+      <c r="AG36" s="13">
+        <f>IF($A36="","",IF(AH36&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH36">
+        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($P36="",1,0)+IF($S36="",1,0)+IF($T36="",1,0)+IF($U36="",1,0)+IF($W36="",1,0)+IF($AA36="",1,0)+IF($AB36="",1,0)+IF(AND($N36="契約期間満了",$Q36=""),1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0)+IF(AND($AD36="外国",$AE36=""),1,0)+IF(AND($AD36="外国",$AF36=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="44" t="n"/>
-      <c r="E37" s="44" t="n"/>
-      <c r="F37" s="44" t="n"/>
-      <c r="G37" s="44" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="18" t="n"/>
-      <c r="M37" s="45">
+      <c r="A37" s="18" t="n"/>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="45" t="n"/>
+      <c r="E37" s="45" t="n"/>
+      <c r="F37" s="45" t="n"/>
+      <c r="G37" s="45" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="45" t="n"/>
+      <c r="L37" s="20" t="n"/>
+      <c r="M37" s="46">
         <f>IF($L37="","",$L37+1)</f>
         <v/>
       </c>
-      <c r="N37" s="16" t="n"/>
-      <c r="O37" s="16" t="n"/>
-      <c r="P37" s="16" t="n"/>
-      <c r="Q37" s="16" t="n"/>
-      <c r="R37" s="16" t="n"/>
-      <c r="S37" s="16" t="n"/>
-      <c r="T37" s="16" t="n"/>
-      <c r="U37" s="16" t="n"/>
-      <c r="V37" s="16" t="n"/>
-      <c r="W37" s="46" t="n"/>
-      <c r="X37" s="46" t="n"/>
-      <c r="Y37" s="16" t="n"/>
-      <c r="Z37" s="16" t="n"/>
-      <c r="AA37" s="16" t="n"/>
-      <c r="AB37" s="47">
-        <f>IF($A37="","",IF(AC37&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($O37="",1,0)+IF($P37="",1,0)+IF($S37="",1,0)+IF($U37="",1,0)+IF($Y37="",1,0)+IF($Z37="",1,0)+IF(AND($N37="契約期間満了",$Q37=""),1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0))</f>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="P37" s="18" t="n"/>
+      <c r="Q37" s="18" t="n"/>
+      <c r="R37" s="18" t="n"/>
+      <c r="S37" s="20" t="n"/>
+      <c r="T37" s="47" t="n"/>
+      <c r="U37" s="18" t="n"/>
+      <c r="V37" s="18" t="n"/>
+      <c r="W37" s="18" t="n"/>
+      <c r="X37" s="18" t="n"/>
+      <c r="Y37" s="48" t="n"/>
+      <c r="Z37" s="48" t="n"/>
+      <c r="AA37" s="18" t="n"/>
+      <c r="AB37" s="18" t="n"/>
+      <c r="AC37" s="18" t="n"/>
+      <c r="AD37" s="18" t="n"/>
+      <c r="AE37" s="18" t="n"/>
+      <c r="AF37" s="20" t="n"/>
+      <c r="AG37" s="13">
+        <f>IF($A37="","",IF(AH37&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH37">
+        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($P37="",1,0)+IF($S37="",1,0)+IF($T37="",1,0)+IF($U37="",1,0)+IF($W37="",1,0)+IF($AA37="",1,0)+IF($AB37="",1,0)+IF(AND($N37="契約期間満了",$Q37=""),1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0)+IF(AND($AD37="外国",$AE37=""),1,0)+IF(AND($AD37="外国",$AF37=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="44" t="n"/>
-      <c r="E38" s="44" t="n"/>
-      <c r="F38" s="44" t="n"/>
-      <c r="G38" s="44" t="n"/>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="18" t="n"/>
-      <c r="M38" s="45">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="45" t="n"/>
+      <c r="G38" s="45" t="n"/>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="45" t="n"/>
+      <c r="L38" s="20" t="n"/>
+      <c r="M38" s="46">
         <f>IF($L38="","",$L38+1)</f>
         <v/>
       </c>
-      <c r="N38" s="16" t="n"/>
-      <c r="O38" s="16" t="n"/>
-      <c r="P38" s="16" t="n"/>
-      <c r="Q38" s="16" t="n"/>
-      <c r="R38" s="16" t="n"/>
-      <c r="S38" s="16" t="n"/>
-      <c r="T38" s="16" t="n"/>
-      <c r="U38" s="16" t="n"/>
-      <c r="V38" s="16" t="n"/>
-      <c r="W38" s="46" t="n"/>
-      <c r="X38" s="46" t="n"/>
-      <c r="Y38" s="16" t="n"/>
-      <c r="Z38" s="16" t="n"/>
-      <c r="AA38" s="16" t="n"/>
-      <c r="AB38" s="47">
-        <f>IF($A38="","",IF(AC38&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($O38="",1,0)+IF($P38="",1,0)+IF($S38="",1,0)+IF($U38="",1,0)+IF($Y38="",1,0)+IF($Z38="",1,0)+IF(AND($N38="契約期間満了",$Q38=""),1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0))</f>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+      <c r="P38" s="18" t="n"/>
+      <c r="Q38" s="18" t="n"/>
+      <c r="R38" s="18" t="n"/>
+      <c r="S38" s="20" t="n"/>
+      <c r="T38" s="47" t="n"/>
+      <c r="U38" s="18" t="n"/>
+      <c r="V38" s="18" t="n"/>
+      <c r="W38" s="18" t="n"/>
+      <c r="X38" s="18" t="n"/>
+      <c r="Y38" s="48" t="n"/>
+      <c r="Z38" s="48" t="n"/>
+      <c r="AA38" s="18" t="n"/>
+      <c r="AB38" s="18" t="n"/>
+      <c r="AC38" s="18" t="n"/>
+      <c r="AD38" s="18" t="n"/>
+      <c r="AE38" s="18" t="n"/>
+      <c r="AF38" s="20" t="n"/>
+      <c r="AG38" s="13">
+        <f>IF($A38="","",IF(AH38&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH38">
+        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($P38="",1,0)+IF($S38="",1,0)+IF($T38="",1,0)+IF($U38="",1,0)+IF($W38="",1,0)+IF($AA38="",1,0)+IF($AB38="",1,0)+IF(AND($N38="契約期間満了",$Q38=""),1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0)+IF(AND($AD38="外国",$AE38=""),1,0)+IF(AND($AD38="外国",$AF38=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="44" t="n"/>
-      <c r="E39" s="44" t="n"/>
-      <c r="F39" s="44" t="n"/>
-      <c r="G39" s="44" t="n"/>
-      <c r="H39" s="16" t="n"/>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="18" t="n"/>
-      <c r="M39" s="45">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="45" t="n"/>
+      <c r="E39" s="45" t="n"/>
+      <c r="F39" s="45" t="n"/>
+      <c r="G39" s="45" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="45" t="n"/>
+      <c r="L39" s="20" t="n"/>
+      <c r="M39" s="46">
         <f>IF($L39="","",$L39+1)</f>
         <v/>
       </c>
-      <c r="N39" s="16" t="n"/>
-      <c r="O39" s="16" t="n"/>
-      <c r="P39" s="16" t="n"/>
-      <c r="Q39" s="16" t="n"/>
-      <c r="R39" s="16" t="n"/>
-      <c r="S39" s="16" t="n"/>
-      <c r="T39" s="16" t="n"/>
-      <c r="U39" s="16" t="n"/>
-      <c r="V39" s="16" t="n"/>
-      <c r="W39" s="46" t="n"/>
-      <c r="X39" s="46" t="n"/>
-      <c r="Y39" s="16" t="n"/>
-      <c r="Z39" s="16" t="n"/>
-      <c r="AA39" s="16" t="n"/>
-      <c r="AB39" s="47">
-        <f>IF($A39="","",IF(AC39&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($O39="",1,0)+IF($P39="",1,0)+IF($S39="",1,0)+IF($U39="",1,0)+IF($Y39="",1,0)+IF($Z39="",1,0)+IF(AND($N39="契約期間満了",$Q39=""),1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0))</f>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="18" t="n"/>
+      <c r="P39" s="18" t="n"/>
+      <c r="Q39" s="18" t="n"/>
+      <c r="R39" s="18" t="n"/>
+      <c r="S39" s="20" t="n"/>
+      <c r="T39" s="47" t="n"/>
+      <c r="U39" s="18" t="n"/>
+      <c r="V39" s="18" t="n"/>
+      <c r="W39" s="18" t="n"/>
+      <c r="X39" s="18" t="n"/>
+      <c r="Y39" s="48" t="n"/>
+      <c r="Z39" s="48" t="n"/>
+      <c r="AA39" s="18" t="n"/>
+      <c r="AB39" s="18" t="n"/>
+      <c r="AC39" s="18" t="n"/>
+      <c r="AD39" s="18" t="n"/>
+      <c r="AE39" s="18" t="n"/>
+      <c r="AF39" s="20" t="n"/>
+      <c r="AG39" s="13">
+        <f>IF($A39="","",IF(AH39&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH39">
+        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($P39="",1,0)+IF($S39="",1,0)+IF($T39="",1,0)+IF($U39="",1,0)+IF($W39="",1,0)+IF($AA39="",1,0)+IF($AB39="",1,0)+IF(AND($N39="契約期間満了",$Q39=""),1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0)+IF(AND($AD39="外国",$AE39=""),1,0)+IF(AND($AD39="外国",$AF39=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="18" t="n"/>
-      <c r="D40" s="44" t="n"/>
-      <c r="E40" s="44" t="n"/>
-      <c r="F40" s="44" t="n"/>
-      <c r="G40" s="44" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="18" t="n"/>
-      <c r="M40" s="45">
+      <c r="A40" s="18" t="n"/>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="45" t="n"/>
+      <c r="E40" s="45" t="n"/>
+      <c r="F40" s="45" t="n"/>
+      <c r="G40" s="45" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="45" t="n"/>
+      <c r="L40" s="20" t="n"/>
+      <c r="M40" s="46">
         <f>IF($L40="","",$L40+1)</f>
         <v/>
       </c>
-      <c r="N40" s="16" t="n"/>
-      <c r="O40" s="16" t="n"/>
-      <c r="P40" s="16" t="n"/>
-      <c r="Q40" s="16" t="n"/>
-      <c r="R40" s="16" t="n"/>
-      <c r="S40" s="16" t="n"/>
-      <c r="T40" s="16" t="n"/>
-      <c r="U40" s="16" t="n"/>
-      <c r="V40" s="16" t="n"/>
-      <c r="W40" s="46" t="n"/>
-      <c r="X40" s="46" t="n"/>
-      <c r="Y40" s="16" t="n"/>
-      <c r="Z40" s="16" t="n"/>
-      <c r="AA40" s="16" t="n"/>
-      <c r="AB40" s="47">
-        <f>IF($A40="","",IF(AC40&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($O40="",1,0)+IF($P40="",1,0)+IF($S40="",1,0)+IF($U40="",1,0)+IF($Y40="",1,0)+IF($Z40="",1,0)+IF(AND($N40="契約期間満了",$Q40=""),1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0))</f>
+      <c r="N40" s="18" t="n"/>
+      <c r="O40" s="18" t="n"/>
+      <c r="P40" s="18" t="n"/>
+      <c r="Q40" s="18" t="n"/>
+      <c r="R40" s="18" t="n"/>
+      <c r="S40" s="20" t="n"/>
+      <c r="T40" s="47" t="n"/>
+      <c r="U40" s="18" t="n"/>
+      <c r="V40" s="18" t="n"/>
+      <c r="W40" s="18" t="n"/>
+      <c r="X40" s="18" t="n"/>
+      <c r="Y40" s="48" t="n"/>
+      <c r="Z40" s="48" t="n"/>
+      <c r="AA40" s="18" t="n"/>
+      <c r="AB40" s="18" t="n"/>
+      <c r="AC40" s="18" t="n"/>
+      <c r="AD40" s="18" t="n"/>
+      <c r="AE40" s="18" t="n"/>
+      <c r="AF40" s="20" t="n"/>
+      <c r="AG40" s="13">
+        <f>IF($A40="","",IF(AH40&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH40">
+        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($P40="",1,0)+IF($S40="",1,0)+IF($T40="",1,0)+IF($U40="",1,0)+IF($W40="",1,0)+IF($AA40="",1,0)+IF($AB40="",1,0)+IF(AND($N40="契約期間満了",$Q40=""),1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0)+IF(AND($AD40="外国",$AE40=""),1,0)+IF(AND($AD40="外国",$AF40=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="44" t="n"/>
-      <c r="E41" s="44" t="n"/>
-      <c r="F41" s="44" t="n"/>
-      <c r="G41" s="44" t="n"/>
-      <c r="H41" s="16" t="n"/>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="18" t="n"/>
-      <c r="M41" s="45">
+      <c r="A41" s="18" t="n"/>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="45" t="n"/>
+      <c r="E41" s="45" t="n"/>
+      <c r="F41" s="45" t="n"/>
+      <c r="G41" s="45" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="45" t="n"/>
+      <c r="L41" s="20" t="n"/>
+      <c r="M41" s="46">
         <f>IF($L41="","",$L41+1)</f>
         <v/>
       </c>
-      <c r="N41" s="16" t="n"/>
-      <c r="O41" s="16" t="n"/>
-      <c r="P41" s="16" t="n"/>
-      <c r="Q41" s="16" t="n"/>
-      <c r="R41" s="16" t="n"/>
-      <c r="S41" s="16" t="n"/>
-      <c r="T41" s="16" t="n"/>
-      <c r="U41" s="16" t="n"/>
-      <c r="V41" s="16" t="n"/>
-      <c r="W41" s="46" t="n"/>
-      <c r="X41" s="46" t="n"/>
-      <c r="Y41" s="16" t="n"/>
-      <c r="Z41" s="16" t="n"/>
-      <c r="AA41" s="16" t="n"/>
-      <c r="AB41" s="47">
-        <f>IF($A41="","",IF(AC41&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC41">
-        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($O41="",1,0)+IF($P41="",1,0)+IF($S41="",1,0)+IF($U41="",1,0)+IF($Y41="",1,0)+IF($Z41="",1,0)+IF(AND($N41="契約期間満了",$Q41=""),1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0))</f>
+      <c r="N41" s="18" t="n"/>
+      <c r="O41" s="18" t="n"/>
+      <c r="P41" s="18" t="n"/>
+      <c r="Q41" s="18" t="n"/>
+      <c r="R41" s="18" t="n"/>
+      <c r="S41" s="20" t="n"/>
+      <c r="T41" s="47" t="n"/>
+      <c r="U41" s="18" t="n"/>
+      <c r="V41" s="18" t="n"/>
+      <c r="W41" s="18" t="n"/>
+      <c r="X41" s="18" t="n"/>
+      <c r="Y41" s="48" t="n"/>
+      <c r="Z41" s="48" t="n"/>
+      <c r="AA41" s="18" t="n"/>
+      <c r="AB41" s="18" t="n"/>
+      <c r="AC41" s="18" t="n"/>
+      <c r="AD41" s="18" t="n"/>
+      <c r="AE41" s="18" t="n"/>
+      <c r="AF41" s="20" t="n"/>
+      <c r="AG41" s="13">
+        <f>IF($A41="","",IF(AH41&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH41">
+        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($P41="",1,0)+IF($S41="",1,0)+IF($T41="",1,0)+IF($U41="",1,0)+IF($W41="",1,0)+IF($AA41="",1,0)+IF($AB41="",1,0)+IF(AND($N41="契約期間満了",$Q41=""),1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0)+IF(AND($AD41="外国",$AE41=""),1,0)+IF(AND($AD41="外国",$AF41=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="44" t="n"/>
-      <c r="F42" s="44" t="n"/>
-      <c r="G42" s="44" t="n"/>
-      <c r="H42" s="16" t="n"/>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="18" t="n"/>
-      <c r="M42" s="45">
+      <c r="A42" s="18" t="n"/>
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="45" t="n"/>
+      <c r="E42" s="45" t="n"/>
+      <c r="F42" s="45" t="n"/>
+      <c r="G42" s="45" t="n"/>
+      <c r="H42" s="18" t="n"/>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="45" t="n"/>
+      <c r="L42" s="20" t="n"/>
+      <c r="M42" s="46">
         <f>IF($L42="","",$L42+1)</f>
         <v/>
       </c>
-      <c r="N42" s="16" t="n"/>
-      <c r="O42" s="16" t="n"/>
-      <c r="P42" s="16" t="n"/>
-      <c r="Q42" s="16" t="n"/>
-      <c r="R42" s="16" t="n"/>
-      <c r="S42" s="16" t="n"/>
-      <c r="T42" s="16" t="n"/>
-      <c r="U42" s="16" t="n"/>
-      <c r="V42" s="16" t="n"/>
-      <c r="W42" s="46" t="n"/>
-      <c r="X42" s="46" t="n"/>
-      <c r="Y42" s="16" t="n"/>
-      <c r="Z42" s="16" t="n"/>
-      <c r="AA42" s="16" t="n"/>
-      <c r="AB42" s="47">
-        <f>IF($A42="","",IF(AC42&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($O42="",1,0)+IF($P42="",1,0)+IF($S42="",1,0)+IF($U42="",1,0)+IF($Y42="",1,0)+IF($Z42="",1,0)+IF(AND($N42="契約期間満了",$Q42=""),1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0))</f>
+      <c r="N42" s="18" t="n"/>
+      <c r="O42" s="18" t="n"/>
+      <c r="P42" s="18" t="n"/>
+      <c r="Q42" s="18" t="n"/>
+      <c r="R42" s="18" t="n"/>
+      <c r="S42" s="20" t="n"/>
+      <c r="T42" s="47" t="n"/>
+      <c r="U42" s="18" t="n"/>
+      <c r="V42" s="18" t="n"/>
+      <c r="W42" s="18" t="n"/>
+      <c r="X42" s="18" t="n"/>
+      <c r="Y42" s="48" t="n"/>
+      <c r="Z42" s="48" t="n"/>
+      <c r="AA42" s="18" t="n"/>
+      <c r="AB42" s="18" t="n"/>
+      <c r="AC42" s="18" t="n"/>
+      <c r="AD42" s="18" t="n"/>
+      <c r="AE42" s="18" t="n"/>
+      <c r="AF42" s="20" t="n"/>
+      <c r="AG42" s="13">
+        <f>IF($A42="","",IF(AH42&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH42">
+        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($P42="",1,0)+IF($S42="",1,0)+IF($T42="",1,0)+IF($U42="",1,0)+IF($W42="",1,0)+IF($AA42="",1,0)+IF($AB42="",1,0)+IF(AND($N42="契約期間満了",$Q42=""),1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0)+IF(AND($AD42="外国",$AE42=""),1,0)+IF(AND($AD42="外国",$AF42=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="44" t="n"/>
-      <c r="E43" s="44" t="n"/>
-      <c r="F43" s="44" t="n"/>
-      <c r="G43" s="44" t="n"/>
-      <c r="H43" s="16" t="n"/>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="18" t="n"/>
-      <c r="M43" s="45">
+      <c r="A43" s="18" t="n"/>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="45" t="n"/>
+      <c r="E43" s="45" t="n"/>
+      <c r="F43" s="45" t="n"/>
+      <c r="G43" s="45" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="18" t="n"/>
+      <c r="K43" s="45" t="n"/>
+      <c r="L43" s="20" t="n"/>
+      <c r="M43" s="46">
         <f>IF($L43="","",$L43+1)</f>
         <v/>
       </c>
-      <c r="N43" s="16" t="n"/>
-      <c r="O43" s="16" t="n"/>
-      <c r="P43" s="16" t="n"/>
-      <c r="Q43" s="16" t="n"/>
-      <c r="R43" s="16" t="n"/>
-      <c r="S43" s="16" t="n"/>
-      <c r="T43" s="16" t="n"/>
-      <c r="U43" s="16" t="n"/>
-      <c r="V43" s="16" t="n"/>
-      <c r="W43" s="46" t="n"/>
-      <c r="X43" s="46" t="n"/>
-      <c r="Y43" s="16" t="n"/>
-      <c r="Z43" s="16" t="n"/>
-      <c r="AA43" s="16" t="n"/>
-      <c r="AB43" s="47">
-        <f>IF($A43="","",IF(AC43&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC43">
-        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($O43="",1,0)+IF($P43="",1,0)+IF($S43="",1,0)+IF($U43="",1,0)+IF($Y43="",1,0)+IF($Z43="",1,0)+IF(AND($N43="契約期間満了",$Q43=""),1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0))</f>
+      <c r="N43" s="18" t="n"/>
+      <c r="O43" s="18" t="n"/>
+      <c r="P43" s="18" t="n"/>
+      <c r="Q43" s="18" t="n"/>
+      <c r="R43" s="18" t="n"/>
+      <c r="S43" s="20" t="n"/>
+      <c r="T43" s="47" t="n"/>
+      <c r="U43" s="18" t="n"/>
+      <c r="V43" s="18" t="n"/>
+      <c r="W43" s="18" t="n"/>
+      <c r="X43" s="18" t="n"/>
+      <c r="Y43" s="48" t="n"/>
+      <c r="Z43" s="48" t="n"/>
+      <c r="AA43" s="18" t="n"/>
+      <c r="AB43" s="18" t="n"/>
+      <c r="AC43" s="18" t="n"/>
+      <c r="AD43" s="18" t="n"/>
+      <c r="AE43" s="18" t="n"/>
+      <c r="AF43" s="20" t="n"/>
+      <c r="AG43" s="13">
+        <f>IF($A43="","",IF(AH43&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH43">
+        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($P43="",1,0)+IF($S43="",1,0)+IF($T43="",1,0)+IF($U43="",1,0)+IF($W43="",1,0)+IF($AA43="",1,0)+IF($AB43="",1,0)+IF(AND($N43="契約期間満了",$Q43=""),1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0)+IF(AND($AD43="外国",$AE43=""),1,0)+IF(AND($AD43="外国",$AF43=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="44" t="n"/>
-      <c r="E44" s="44" t="n"/>
-      <c r="F44" s="44" t="n"/>
-      <c r="G44" s="44" t="n"/>
-      <c r="H44" s="16" t="n"/>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="18" t="n"/>
-      <c r="M44" s="45">
+      <c r="A44" s="18" t="n"/>
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="45" t="n"/>
+      <c r="E44" s="45" t="n"/>
+      <c r="F44" s="45" t="n"/>
+      <c r="G44" s="45" t="n"/>
+      <c r="H44" s="18" t="n"/>
+      <c r="I44" s="18" t="n"/>
+      <c r="J44" s="18" t="n"/>
+      <c r="K44" s="45" t="n"/>
+      <c r="L44" s="20" t="n"/>
+      <c r="M44" s="46">
         <f>IF($L44="","",$L44+1)</f>
         <v/>
       </c>
-      <c r="N44" s="16" t="n"/>
-      <c r="O44" s="16" t="n"/>
-      <c r="P44" s="16" t="n"/>
-      <c r="Q44" s="16" t="n"/>
-      <c r="R44" s="16" t="n"/>
-      <c r="S44" s="16" t="n"/>
-      <c r="T44" s="16" t="n"/>
-      <c r="U44" s="16" t="n"/>
-      <c r="V44" s="16" t="n"/>
-      <c r="W44" s="46" t="n"/>
-      <c r="X44" s="46" t="n"/>
-      <c r="Y44" s="16" t="n"/>
-      <c r="Z44" s="16" t="n"/>
-      <c r="AA44" s="16" t="n"/>
-      <c r="AB44" s="47">
-        <f>IF($A44="","",IF(AC44&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($O44="",1,0)+IF($P44="",1,0)+IF($S44="",1,0)+IF($U44="",1,0)+IF($Y44="",1,0)+IF($Z44="",1,0)+IF(AND($N44="契約期間満了",$Q44=""),1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0))</f>
+      <c r="N44" s="18" t="n"/>
+      <c r="O44" s="18" t="n"/>
+      <c r="P44" s="18" t="n"/>
+      <c r="Q44" s="18" t="n"/>
+      <c r="R44" s="18" t="n"/>
+      <c r="S44" s="20" t="n"/>
+      <c r="T44" s="47" t="n"/>
+      <c r="U44" s="18" t="n"/>
+      <c r="V44" s="18" t="n"/>
+      <c r="W44" s="18" t="n"/>
+      <c r="X44" s="18" t="n"/>
+      <c r="Y44" s="48" t="n"/>
+      <c r="Z44" s="48" t="n"/>
+      <c r="AA44" s="18" t="n"/>
+      <c r="AB44" s="18" t="n"/>
+      <c r="AC44" s="18" t="n"/>
+      <c r="AD44" s="18" t="n"/>
+      <c r="AE44" s="18" t="n"/>
+      <c r="AF44" s="20" t="n"/>
+      <c r="AG44" s="13">
+        <f>IF($A44="","",IF(AH44&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH44">
+        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($P44="",1,0)+IF($S44="",1,0)+IF($T44="",1,0)+IF($U44="",1,0)+IF($W44="",1,0)+IF($AA44="",1,0)+IF($AB44="",1,0)+IF(AND($N44="契約期間満了",$Q44=""),1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0)+IF(AND($AD44="外国",$AE44=""),1,0)+IF(AND($AD44="外国",$AF44=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="44" t="n"/>
-      <c r="E45" s="44" t="n"/>
-      <c r="F45" s="44" t="n"/>
-      <c r="G45" s="44" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="16" t="n"/>
-      <c r="J45" s="16" t="n"/>
-      <c r="K45" s="16" t="n"/>
-      <c r="L45" s="18" t="n"/>
-      <c r="M45" s="45">
+      <c r="A45" s="18" t="n"/>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="45" t="n"/>
+      <c r="E45" s="45" t="n"/>
+      <c r="F45" s="45" t="n"/>
+      <c r="G45" s="45" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="18" t="n"/>
+      <c r="K45" s="45" t="n"/>
+      <c r="L45" s="20" t="n"/>
+      <c r="M45" s="46">
         <f>IF($L45="","",$L45+1)</f>
         <v/>
       </c>
-      <c r="N45" s="16" t="n"/>
-      <c r="O45" s="16" t="n"/>
-      <c r="P45" s="16" t="n"/>
-      <c r="Q45" s="16" t="n"/>
-      <c r="R45" s="16" t="n"/>
-      <c r="S45" s="16" t="n"/>
-      <c r="T45" s="16" t="n"/>
-      <c r="U45" s="16" t="n"/>
-      <c r="V45" s="16" t="n"/>
-      <c r="W45" s="46" t="n"/>
-      <c r="X45" s="46" t="n"/>
-      <c r="Y45" s="16" t="n"/>
-      <c r="Z45" s="16" t="n"/>
-      <c r="AA45" s="16" t="n"/>
-      <c r="AB45" s="47">
-        <f>IF($A45="","",IF(AC45&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($O45="",1,0)+IF($P45="",1,0)+IF($S45="",1,0)+IF($U45="",1,0)+IF($Y45="",1,0)+IF($Z45="",1,0)+IF(AND($N45="契約期間満了",$Q45=""),1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0))</f>
+      <c r="N45" s="18" t="n"/>
+      <c r="O45" s="18" t="n"/>
+      <c r="P45" s="18" t="n"/>
+      <c r="Q45" s="18" t="n"/>
+      <c r="R45" s="18" t="n"/>
+      <c r="S45" s="20" t="n"/>
+      <c r="T45" s="47" t="n"/>
+      <c r="U45" s="18" t="n"/>
+      <c r="V45" s="18" t="n"/>
+      <c r="W45" s="18" t="n"/>
+      <c r="X45" s="18" t="n"/>
+      <c r="Y45" s="48" t="n"/>
+      <c r="Z45" s="48" t="n"/>
+      <c r="AA45" s="18" t="n"/>
+      <c r="AB45" s="18" t="n"/>
+      <c r="AC45" s="18" t="n"/>
+      <c r="AD45" s="18" t="n"/>
+      <c r="AE45" s="18" t="n"/>
+      <c r="AF45" s="20" t="n"/>
+      <c r="AG45" s="13">
+        <f>IF($A45="","",IF(AH45&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH45">
+        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($P45="",1,0)+IF($S45="",1,0)+IF($T45="",1,0)+IF($U45="",1,0)+IF($W45="",1,0)+IF($AA45="",1,0)+IF($AB45="",1,0)+IF(AND($N45="契約期間満了",$Q45=""),1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0)+IF(AND($AD45="外国",$AE45=""),1,0)+IF(AND($AD45="外国",$AF45=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="18" t="n"/>
-      <c r="D46" s="44" t="n"/>
-      <c r="E46" s="44" t="n"/>
-      <c r="F46" s="44" t="n"/>
-      <c r="G46" s="44" t="n"/>
-      <c r="H46" s="16" t="n"/>
-      <c r="I46" s="16" t="n"/>
-      <c r="J46" s="16" t="n"/>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="18" t="n"/>
-      <c r="M46" s="45">
+      <c r="A46" s="18" t="n"/>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="45" t="n"/>
+      <c r="E46" s="45" t="n"/>
+      <c r="F46" s="45" t="n"/>
+      <c r="G46" s="45" t="n"/>
+      <c r="H46" s="18" t="n"/>
+      <c r="I46" s="18" t="n"/>
+      <c r="J46" s="18" t="n"/>
+      <c r="K46" s="45" t="n"/>
+      <c r="L46" s="20" t="n"/>
+      <c r="M46" s="46">
         <f>IF($L46="","",$L46+1)</f>
         <v/>
       </c>
-      <c r="N46" s="16" t="n"/>
-      <c r="O46" s="16" t="n"/>
-      <c r="P46" s="16" t="n"/>
-      <c r="Q46" s="16" t="n"/>
-      <c r="R46" s="16" t="n"/>
-      <c r="S46" s="16" t="n"/>
-      <c r="T46" s="16" t="n"/>
-      <c r="U46" s="16" t="n"/>
-      <c r="V46" s="16" t="n"/>
-      <c r="W46" s="46" t="n"/>
-      <c r="X46" s="46" t="n"/>
-      <c r="Y46" s="16" t="n"/>
-      <c r="Z46" s="16" t="n"/>
-      <c r="AA46" s="16" t="n"/>
-      <c r="AB46" s="47">
-        <f>IF($A46="","",IF(AC46&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($O46="",1,0)+IF($P46="",1,0)+IF($S46="",1,0)+IF($U46="",1,0)+IF($Y46="",1,0)+IF($Z46="",1,0)+IF(AND($N46="契約期間満了",$Q46=""),1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0))</f>
+      <c r="N46" s="18" t="n"/>
+      <c r="O46" s="18" t="n"/>
+      <c r="P46" s="18" t="n"/>
+      <c r="Q46" s="18" t="n"/>
+      <c r="R46" s="18" t="n"/>
+      <c r="S46" s="20" t="n"/>
+      <c r="T46" s="47" t="n"/>
+      <c r="U46" s="18" t="n"/>
+      <c r="V46" s="18" t="n"/>
+      <c r="W46" s="18" t="n"/>
+      <c r="X46" s="18" t="n"/>
+      <c r="Y46" s="48" t="n"/>
+      <c r="Z46" s="48" t="n"/>
+      <c r="AA46" s="18" t="n"/>
+      <c r="AB46" s="18" t="n"/>
+      <c r="AC46" s="18" t="n"/>
+      <c r="AD46" s="18" t="n"/>
+      <c r="AE46" s="18" t="n"/>
+      <c r="AF46" s="20" t="n"/>
+      <c r="AG46" s="13">
+        <f>IF($A46="","",IF(AH46&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH46">
+        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($P46="",1,0)+IF($S46="",1,0)+IF($T46="",1,0)+IF($U46="",1,0)+IF($W46="",1,0)+IF($AA46="",1,0)+IF($AB46="",1,0)+IF(AND($N46="契約期間満了",$Q46=""),1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0)+IF(AND($AD46="外国",$AE46=""),1,0)+IF(AND($AD46="外国",$AF46=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="44" t="n"/>
-      <c r="E47" s="44" t="n"/>
-      <c r="F47" s="44" t="n"/>
-      <c r="G47" s="44" t="n"/>
-      <c r="H47" s="16" t="n"/>
-      <c r="I47" s="16" t="n"/>
-      <c r="J47" s="16" t="n"/>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="18" t="n"/>
-      <c r="M47" s="45">
+      <c r="A47" s="18" t="n"/>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="45" t="n"/>
+      <c r="E47" s="45" t="n"/>
+      <c r="F47" s="45" t="n"/>
+      <c r="G47" s="45" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="45" t="n"/>
+      <c r="L47" s="20" t="n"/>
+      <c r="M47" s="46">
         <f>IF($L47="","",$L47+1)</f>
         <v/>
       </c>
-      <c r="N47" s="16" t="n"/>
-      <c r="O47" s="16" t="n"/>
-      <c r="P47" s="16" t="n"/>
-      <c r="Q47" s="16" t="n"/>
-      <c r="R47" s="16" t="n"/>
-      <c r="S47" s="16" t="n"/>
-      <c r="T47" s="16" t="n"/>
-      <c r="U47" s="16" t="n"/>
-      <c r="V47" s="16" t="n"/>
-      <c r="W47" s="46" t="n"/>
-      <c r="X47" s="46" t="n"/>
-      <c r="Y47" s="16" t="n"/>
-      <c r="Z47" s="16" t="n"/>
-      <c r="AA47" s="16" t="n"/>
-      <c r="AB47" s="47">
-        <f>IF($A47="","",IF(AC47&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($O47="",1,0)+IF($P47="",1,0)+IF($S47="",1,0)+IF($U47="",1,0)+IF($Y47="",1,0)+IF($Z47="",1,0)+IF(AND($N47="契約期間満了",$Q47=""),1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0))</f>
+      <c r="N47" s="18" t="n"/>
+      <c r="O47" s="18" t="n"/>
+      <c r="P47" s="18" t="n"/>
+      <c r="Q47" s="18" t="n"/>
+      <c r="R47" s="18" t="n"/>
+      <c r="S47" s="20" t="n"/>
+      <c r="T47" s="47" t="n"/>
+      <c r="U47" s="18" t="n"/>
+      <c r="V47" s="18" t="n"/>
+      <c r="W47" s="18" t="n"/>
+      <c r="X47" s="18" t="n"/>
+      <c r="Y47" s="48" t="n"/>
+      <c r="Z47" s="48" t="n"/>
+      <c r="AA47" s="18" t="n"/>
+      <c r="AB47" s="18" t="n"/>
+      <c r="AC47" s="18" t="n"/>
+      <c r="AD47" s="18" t="n"/>
+      <c r="AE47" s="18" t="n"/>
+      <c r="AF47" s="20" t="n"/>
+      <c r="AG47" s="13">
+        <f>IF($A47="","",IF(AH47&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH47">
+        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($P47="",1,0)+IF($S47="",1,0)+IF($T47="",1,0)+IF($U47="",1,0)+IF($W47="",1,0)+IF($AA47="",1,0)+IF($AB47="",1,0)+IF(AND($N47="契約期間満了",$Q47=""),1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0)+IF(AND($AD47="外国",$AE47=""),1,0)+IF(AND($AD47="外国",$AF47=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="18" t="n"/>
-      <c r="D48" s="44" t="n"/>
-      <c r="E48" s="44" t="n"/>
-      <c r="F48" s="44" t="n"/>
-      <c r="G48" s="44" t="n"/>
-      <c r="H48" s="16" t="n"/>
-      <c r="I48" s="16" t="n"/>
-      <c r="J48" s="16" t="n"/>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="18" t="n"/>
-      <c r="M48" s="45">
+      <c r="A48" s="18" t="n"/>
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="45" t="n"/>
+      <c r="E48" s="45" t="n"/>
+      <c r="F48" s="45" t="n"/>
+      <c r="G48" s="45" t="n"/>
+      <c r="H48" s="18" t="n"/>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="45" t="n"/>
+      <c r="L48" s="20" t="n"/>
+      <c r="M48" s="46">
         <f>IF($L48="","",$L48+1)</f>
         <v/>
       </c>
-      <c r="N48" s="16" t="n"/>
-      <c r="O48" s="16" t="n"/>
-      <c r="P48" s="16" t="n"/>
-      <c r="Q48" s="16" t="n"/>
-      <c r="R48" s="16" t="n"/>
-      <c r="S48" s="16" t="n"/>
-      <c r="T48" s="16" t="n"/>
-      <c r="U48" s="16" t="n"/>
-      <c r="V48" s="16" t="n"/>
-      <c r="W48" s="46" t="n"/>
-      <c r="X48" s="46" t="n"/>
-      <c r="Y48" s="16" t="n"/>
-      <c r="Z48" s="16" t="n"/>
-      <c r="AA48" s="16" t="n"/>
-      <c r="AB48" s="47">
-        <f>IF($A48="","",IF(AC48&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($O48="",1,0)+IF($P48="",1,0)+IF($S48="",1,0)+IF($U48="",1,0)+IF($Y48="",1,0)+IF($Z48="",1,0)+IF(AND($N48="契約期間満了",$Q48=""),1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0))</f>
+      <c r="N48" s="18" t="n"/>
+      <c r="O48" s="18" t="n"/>
+      <c r="P48" s="18" t="n"/>
+      <c r="Q48" s="18" t="n"/>
+      <c r="R48" s="18" t="n"/>
+      <c r="S48" s="20" t="n"/>
+      <c r="T48" s="47" t="n"/>
+      <c r="U48" s="18" t="n"/>
+      <c r="V48" s="18" t="n"/>
+      <c r="W48" s="18" t="n"/>
+      <c r="X48" s="18" t="n"/>
+      <c r="Y48" s="48" t="n"/>
+      <c r="Z48" s="48" t="n"/>
+      <c r="AA48" s="18" t="n"/>
+      <c r="AB48" s="18" t="n"/>
+      <c r="AC48" s="18" t="n"/>
+      <c r="AD48" s="18" t="n"/>
+      <c r="AE48" s="18" t="n"/>
+      <c r="AF48" s="20" t="n"/>
+      <c r="AG48" s="13">
+        <f>IF($A48="","",IF(AH48&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH48">
+        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($P48="",1,0)+IF($S48="",1,0)+IF($T48="",1,0)+IF($U48="",1,0)+IF($W48="",1,0)+IF($AA48="",1,0)+IF($AB48="",1,0)+IF(AND($N48="契約期間満了",$Q48=""),1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0)+IF(AND($AD48="外国",$AE48=""),1,0)+IF(AND($AD48="外国",$AF48=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="18" t="n"/>
-      <c r="D49" s="44" t="n"/>
-      <c r="E49" s="44" t="n"/>
-      <c r="F49" s="44" t="n"/>
-      <c r="G49" s="44" t="n"/>
-      <c r="H49" s="16" t="n"/>
-      <c r="I49" s="16" t="n"/>
-      <c r="J49" s="16" t="n"/>
-      <c r="K49" s="16" t="n"/>
-      <c r="L49" s="18" t="n"/>
-      <c r="M49" s="45">
+      <c r="A49" s="18" t="n"/>
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="45" t="n"/>
+      <c r="E49" s="45" t="n"/>
+      <c r="F49" s="45" t="n"/>
+      <c r="G49" s="45" t="n"/>
+      <c r="H49" s="18" t="n"/>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="45" t="n"/>
+      <c r="L49" s="20" t="n"/>
+      <c r="M49" s="46">
         <f>IF($L49="","",$L49+1)</f>
         <v/>
       </c>
-      <c r="N49" s="16" t="n"/>
-      <c r="O49" s="16" t="n"/>
-      <c r="P49" s="16" t="n"/>
-      <c r="Q49" s="16" t="n"/>
-      <c r="R49" s="16" t="n"/>
-      <c r="S49" s="16" t="n"/>
-      <c r="T49" s="16" t="n"/>
-      <c r="U49" s="16" t="n"/>
-      <c r="V49" s="16" t="n"/>
-      <c r="W49" s="46" t="n"/>
-      <c r="X49" s="46" t="n"/>
-      <c r="Y49" s="16" t="n"/>
-      <c r="Z49" s="16" t="n"/>
-      <c r="AA49" s="16" t="n"/>
-      <c r="AB49" s="47">
-        <f>IF($A49="","",IF(AC49&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC49">
-        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($O49="",1,0)+IF($P49="",1,0)+IF($S49="",1,0)+IF($U49="",1,0)+IF($Y49="",1,0)+IF($Z49="",1,0)+IF(AND($N49="契約期間満了",$Q49=""),1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0))</f>
+      <c r="N49" s="18" t="n"/>
+      <c r="O49" s="18" t="n"/>
+      <c r="P49" s="18" t="n"/>
+      <c r="Q49" s="18" t="n"/>
+      <c r="R49" s="18" t="n"/>
+      <c r="S49" s="20" t="n"/>
+      <c r="T49" s="47" t="n"/>
+      <c r="U49" s="18" t="n"/>
+      <c r="V49" s="18" t="n"/>
+      <c r="W49" s="18" t="n"/>
+      <c r="X49" s="18" t="n"/>
+      <c r="Y49" s="48" t="n"/>
+      <c r="Z49" s="48" t="n"/>
+      <c r="AA49" s="18" t="n"/>
+      <c r="AB49" s="18" t="n"/>
+      <c r="AC49" s="18" t="n"/>
+      <c r="AD49" s="18" t="n"/>
+      <c r="AE49" s="18" t="n"/>
+      <c r="AF49" s="20" t="n"/>
+      <c r="AG49" s="13">
+        <f>IF($A49="","",IF(AH49&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH49">
+        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($P49="",1,0)+IF($S49="",1,0)+IF($T49="",1,0)+IF($U49="",1,0)+IF($W49="",1,0)+IF($AA49="",1,0)+IF($AB49="",1,0)+IF(AND($N49="契約期間満了",$Q49=""),1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0)+IF(AND($AD49="外国",$AE49=""),1,0)+IF(AND($AD49="外国",$AF49=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="44" t="n"/>
-      <c r="E50" s="44" t="n"/>
-      <c r="F50" s="44" t="n"/>
-      <c r="G50" s="44" t="n"/>
-      <c r="H50" s="16" t="n"/>
-      <c r="I50" s="16" t="n"/>
-      <c r="J50" s="16" t="n"/>
-      <c r="K50" s="16" t="n"/>
-      <c r="L50" s="18" t="n"/>
-      <c r="M50" s="45">
+      <c r="A50" s="18" t="n"/>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="20" t="n"/>
+      <c r="D50" s="45" t="n"/>
+      <c r="E50" s="45" t="n"/>
+      <c r="F50" s="45" t="n"/>
+      <c r="G50" s="45" t="n"/>
+      <c r="H50" s="18" t="n"/>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="18" t="n"/>
+      <c r="K50" s="45" t="n"/>
+      <c r="L50" s="20" t="n"/>
+      <c r="M50" s="46">
         <f>IF($L50="","",$L50+1)</f>
         <v/>
       </c>
-      <c r="N50" s="16" t="n"/>
-      <c r="O50" s="16" t="n"/>
-      <c r="P50" s="16" t="n"/>
-      <c r="Q50" s="16" t="n"/>
-      <c r="R50" s="16" t="n"/>
-      <c r="S50" s="16" t="n"/>
-      <c r="T50" s="16" t="n"/>
-      <c r="U50" s="16" t="n"/>
-      <c r="V50" s="16" t="n"/>
-      <c r="W50" s="46" t="n"/>
-      <c r="X50" s="46" t="n"/>
-      <c r="Y50" s="16" t="n"/>
-      <c r="Z50" s="16" t="n"/>
-      <c r="AA50" s="16" t="n"/>
-      <c r="AB50" s="47">
-        <f>IF($A50="","",IF(AC50&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC50">
-        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($O50="",1,0)+IF($P50="",1,0)+IF($S50="",1,0)+IF($U50="",1,0)+IF($Y50="",1,0)+IF($Z50="",1,0)+IF(AND($N50="契約期間満了",$Q50=""),1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0))</f>
+      <c r="N50" s="18" t="n"/>
+      <c r="O50" s="18" t="n"/>
+      <c r="P50" s="18" t="n"/>
+      <c r="Q50" s="18" t="n"/>
+      <c r="R50" s="18" t="n"/>
+      <c r="S50" s="20" t="n"/>
+      <c r="T50" s="47" t="n"/>
+      <c r="U50" s="18" t="n"/>
+      <c r="V50" s="18" t="n"/>
+      <c r="W50" s="18" t="n"/>
+      <c r="X50" s="18" t="n"/>
+      <c r="Y50" s="48" t="n"/>
+      <c r="Z50" s="48" t="n"/>
+      <c r="AA50" s="18" t="n"/>
+      <c r="AB50" s="18" t="n"/>
+      <c r="AC50" s="18" t="n"/>
+      <c r="AD50" s="18" t="n"/>
+      <c r="AE50" s="18" t="n"/>
+      <c r="AF50" s="20" t="n"/>
+      <c r="AG50" s="13">
+        <f>IF($A50="","",IF(AH50&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH50">
+        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($P50="",1,0)+IF($S50="",1,0)+IF($T50="",1,0)+IF($U50="",1,0)+IF($W50="",1,0)+IF($AA50="",1,0)+IF($AB50="",1,0)+IF(AND($N50="契約期間満了",$Q50=""),1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0)+IF(AND($AD50="外国",$AE50=""),1,0)+IF(AND($AD50="外国",$AF50=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="18" t="n"/>
-      <c r="D51" s="44" t="n"/>
-      <c r="E51" s="44" t="n"/>
-      <c r="F51" s="44" t="n"/>
-      <c r="G51" s="44" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="16" t="n"/>
-      <c r="J51" s="16" t="n"/>
-      <c r="K51" s="16" t="n"/>
-      <c r="L51" s="18" t="n"/>
-      <c r="M51" s="45">
+      <c r="A51" s="18" t="n"/>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="45" t="n"/>
+      <c r="E51" s="45" t="n"/>
+      <c r="F51" s="45" t="n"/>
+      <c r="G51" s="45" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="45" t="n"/>
+      <c r="L51" s="20" t="n"/>
+      <c r="M51" s="46">
         <f>IF($L51="","",$L51+1)</f>
         <v/>
       </c>
-      <c r="N51" s="16" t="n"/>
-      <c r="O51" s="16" t="n"/>
-      <c r="P51" s="16" t="n"/>
-      <c r="Q51" s="16" t="n"/>
-      <c r="R51" s="16" t="n"/>
-      <c r="S51" s="16" t="n"/>
-      <c r="T51" s="16" t="n"/>
-      <c r="U51" s="16" t="n"/>
-      <c r="V51" s="16" t="n"/>
-      <c r="W51" s="46" t="n"/>
-      <c r="X51" s="46" t="n"/>
-      <c r="Y51" s="16" t="n"/>
-      <c r="Z51" s="16" t="n"/>
-      <c r="AA51" s="16" t="n"/>
-      <c r="AB51" s="47">
-        <f>IF($A51="","",IF(AC51&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($O51="",1,0)+IF($P51="",1,0)+IF($S51="",1,0)+IF($U51="",1,0)+IF($Y51="",1,0)+IF($Z51="",1,0)+IF(AND($N51="契約期間満了",$Q51=""),1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0))</f>
+      <c r="N51" s="18" t="n"/>
+      <c r="O51" s="18" t="n"/>
+      <c r="P51" s="18" t="n"/>
+      <c r="Q51" s="18" t="n"/>
+      <c r="R51" s="18" t="n"/>
+      <c r="S51" s="20" t="n"/>
+      <c r="T51" s="47" t="n"/>
+      <c r="U51" s="18" t="n"/>
+      <c r="V51" s="18" t="n"/>
+      <c r="W51" s="18" t="n"/>
+      <c r="X51" s="18" t="n"/>
+      <c r="Y51" s="48" t="n"/>
+      <c r="Z51" s="48" t="n"/>
+      <c r="AA51" s="18" t="n"/>
+      <c r="AB51" s="18" t="n"/>
+      <c r="AC51" s="18" t="n"/>
+      <c r="AD51" s="18" t="n"/>
+      <c r="AE51" s="18" t="n"/>
+      <c r="AF51" s="20" t="n"/>
+      <c r="AG51" s="13">
+        <f>IF($A51="","",IF(AH51&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH51">
+        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($P51="",1,0)+IF($S51="",1,0)+IF($T51="",1,0)+IF($U51="",1,0)+IF($W51="",1,0)+IF($AA51="",1,0)+IF($AB51="",1,0)+IF(AND($N51="契約期間満了",$Q51=""),1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0)+IF(AND($AD51="外国",$AE51=""),1,0)+IF(AND($AD51="外国",$AF51=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="18" t="n"/>
-      <c r="D52" s="44" t="n"/>
-      <c r="E52" s="44" t="n"/>
-      <c r="F52" s="44" t="n"/>
-      <c r="G52" s="44" t="n"/>
-      <c r="H52" s="16" t="n"/>
-      <c r="I52" s="16" t="n"/>
-      <c r="J52" s="16" t="n"/>
-      <c r="K52" s="16" t="n"/>
-      <c r="L52" s="18" t="n"/>
-      <c r="M52" s="45">
+      <c r="A52" s="18" t="n"/>
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="45" t="n"/>
+      <c r="E52" s="45" t="n"/>
+      <c r="F52" s="45" t="n"/>
+      <c r="G52" s="45" t="n"/>
+      <c r="H52" s="18" t="n"/>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="45" t="n"/>
+      <c r="L52" s="20" t="n"/>
+      <c r="M52" s="46">
         <f>IF($L52="","",$L52+1)</f>
         <v/>
       </c>
-      <c r="N52" s="16" t="n"/>
-      <c r="O52" s="16" t="n"/>
-      <c r="P52" s="16" t="n"/>
-      <c r="Q52" s="16" t="n"/>
-      <c r="R52" s="16" t="n"/>
-      <c r="S52" s="16" t="n"/>
-      <c r="T52" s="16" t="n"/>
-      <c r="U52" s="16" t="n"/>
-      <c r="V52" s="16" t="n"/>
-      <c r="W52" s="46" t="n"/>
-      <c r="X52" s="46" t="n"/>
-      <c r="Y52" s="16" t="n"/>
-      <c r="Z52" s="16" t="n"/>
-      <c r="AA52" s="16" t="n"/>
-      <c r="AB52" s="47">
-        <f>IF($A52="","",IF(AC52&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC52">
-        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($O52="",1,0)+IF($P52="",1,0)+IF($S52="",1,0)+IF($U52="",1,0)+IF($Y52="",1,0)+IF($Z52="",1,0)+IF(AND($N52="契約期間満了",$Q52=""),1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0))</f>
+      <c r="N52" s="18" t="n"/>
+      <c r="O52" s="18" t="n"/>
+      <c r="P52" s="18" t="n"/>
+      <c r="Q52" s="18" t="n"/>
+      <c r="R52" s="18" t="n"/>
+      <c r="S52" s="20" t="n"/>
+      <c r="T52" s="47" t="n"/>
+      <c r="U52" s="18" t="n"/>
+      <c r="V52" s="18" t="n"/>
+      <c r="W52" s="18" t="n"/>
+      <c r="X52" s="18" t="n"/>
+      <c r="Y52" s="48" t="n"/>
+      <c r="Z52" s="48" t="n"/>
+      <c r="AA52" s="18" t="n"/>
+      <c r="AB52" s="18" t="n"/>
+      <c r="AC52" s="18" t="n"/>
+      <c r="AD52" s="18" t="n"/>
+      <c r="AE52" s="18" t="n"/>
+      <c r="AF52" s="20" t="n"/>
+      <c r="AG52" s="13">
+        <f>IF($A52="","",IF(AH52&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH52">
+        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($P52="",1,0)+IF($S52="",1,0)+IF($T52="",1,0)+IF($U52="",1,0)+IF($W52="",1,0)+IF($AA52="",1,0)+IF($AB52="",1,0)+IF(AND($N52="契約期間満了",$Q52=""),1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0)+IF(AND($AD52="外国",$AE52=""),1,0)+IF(AND($AD52="外国",$AF52=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="18" t="n"/>
-      <c r="D53" s="44" t="n"/>
-      <c r="E53" s="44" t="n"/>
-      <c r="F53" s="44" t="n"/>
-      <c r="G53" s="44" t="n"/>
-      <c r="H53" s="16" t="n"/>
-      <c r="I53" s="16" t="n"/>
-      <c r="J53" s="16" t="n"/>
-      <c r="K53" s="16" t="n"/>
-      <c r="L53" s="18" t="n"/>
-      <c r="M53" s="45">
+      <c r="A53" s="18" t="n"/>
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="45" t="n"/>
+      <c r="E53" s="45" t="n"/>
+      <c r="F53" s="45" t="n"/>
+      <c r="G53" s="45" t="n"/>
+      <c r="H53" s="18" t="n"/>
+      <c r="I53" s="18" t="n"/>
+      <c r="J53" s="18" t="n"/>
+      <c r="K53" s="45" t="n"/>
+      <c r="L53" s="20" t="n"/>
+      <c r="M53" s="46">
         <f>IF($L53="","",$L53+1)</f>
         <v/>
       </c>
-      <c r="N53" s="16" t="n"/>
-      <c r="O53" s="16" t="n"/>
-      <c r="P53" s="16" t="n"/>
-      <c r="Q53" s="16" t="n"/>
-      <c r="R53" s="16" t="n"/>
-      <c r="S53" s="16" t="n"/>
-      <c r="T53" s="16" t="n"/>
-      <c r="U53" s="16" t="n"/>
-      <c r="V53" s="16" t="n"/>
-      <c r="W53" s="46" t="n"/>
-      <c r="X53" s="46" t="n"/>
-      <c r="Y53" s="16" t="n"/>
-      <c r="Z53" s="16" t="n"/>
-      <c r="AA53" s="16" t="n"/>
-      <c r="AB53" s="47">
-        <f>IF($A53="","",IF(AC53&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC53">
-        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($O53="",1,0)+IF($P53="",1,0)+IF($S53="",1,0)+IF($U53="",1,0)+IF($Y53="",1,0)+IF($Z53="",1,0)+IF(AND($N53="契約期間満了",$Q53=""),1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0))</f>
+      <c r="N53" s="18" t="n"/>
+      <c r="O53" s="18" t="n"/>
+      <c r="P53" s="18" t="n"/>
+      <c r="Q53" s="18" t="n"/>
+      <c r="R53" s="18" t="n"/>
+      <c r="S53" s="20" t="n"/>
+      <c r="T53" s="47" t="n"/>
+      <c r="U53" s="18" t="n"/>
+      <c r="V53" s="18" t="n"/>
+      <c r="W53" s="18" t="n"/>
+      <c r="X53" s="18" t="n"/>
+      <c r="Y53" s="48" t="n"/>
+      <c r="Z53" s="48" t="n"/>
+      <c r="AA53" s="18" t="n"/>
+      <c r="AB53" s="18" t="n"/>
+      <c r="AC53" s="18" t="n"/>
+      <c r="AD53" s="18" t="n"/>
+      <c r="AE53" s="18" t="n"/>
+      <c r="AF53" s="20" t="n"/>
+      <c r="AG53" s="13">
+        <f>IF($A53="","",IF(AH53&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH53">
+        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($P53="",1,0)+IF($S53="",1,0)+IF($T53="",1,0)+IF($U53="",1,0)+IF($W53="",1,0)+IF($AA53="",1,0)+IF($AB53="",1,0)+IF(AND($N53="契約期間満了",$Q53=""),1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0)+IF(AND($AD53="外国",$AE53=""),1,0)+IF(AND($AD53="外国",$AF53=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="44" t="n"/>
-      <c r="E54" s="44" t="n"/>
-      <c r="F54" s="44" t="n"/>
-      <c r="G54" s="44" t="n"/>
-      <c r="H54" s="16" t="n"/>
-      <c r="I54" s="16" t="n"/>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="18" t="n"/>
-      <c r="M54" s="45">
+      <c r="A54" s="18" t="n"/>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="45" t="n"/>
+      <c r="E54" s="45" t="n"/>
+      <c r="F54" s="45" t="n"/>
+      <c r="G54" s="45" t="n"/>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+      <c r="J54" s="18" t="n"/>
+      <c r="K54" s="45" t="n"/>
+      <c r="L54" s="20" t="n"/>
+      <c r="M54" s="46">
         <f>IF($L54="","",$L54+1)</f>
         <v/>
       </c>
-      <c r="N54" s="16" t="n"/>
-      <c r="O54" s="16" t="n"/>
-      <c r="P54" s="16" t="n"/>
-      <c r="Q54" s="16" t="n"/>
-      <c r="R54" s="16" t="n"/>
-      <c r="S54" s="16" t="n"/>
-      <c r="T54" s="16" t="n"/>
-      <c r="U54" s="16" t="n"/>
-      <c r="V54" s="16" t="n"/>
-      <c r="W54" s="46" t="n"/>
-      <c r="X54" s="46" t="n"/>
-      <c r="Y54" s="16" t="n"/>
-      <c r="Z54" s="16" t="n"/>
-      <c r="AA54" s="16" t="n"/>
-      <c r="AB54" s="47">
-        <f>IF($A54="","",IF(AC54&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC54">
-        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($O54="",1,0)+IF($P54="",1,0)+IF($S54="",1,0)+IF($U54="",1,0)+IF($Y54="",1,0)+IF($Z54="",1,0)+IF(AND($N54="契約期間満了",$Q54=""),1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0))</f>
+      <c r="N54" s="18" t="n"/>
+      <c r="O54" s="18" t="n"/>
+      <c r="P54" s="18" t="n"/>
+      <c r="Q54" s="18" t="n"/>
+      <c r="R54" s="18" t="n"/>
+      <c r="S54" s="20" t="n"/>
+      <c r="T54" s="47" t="n"/>
+      <c r="U54" s="18" t="n"/>
+      <c r="V54" s="18" t="n"/>
+      <c r="W54" s="18" t="n"/>
+      <c r="X54" s="18" t="n"/>
+      <c r="Y54" s="48" t="n"/>
+      <c r="Z54" s="48" t="n"/>
+      <c r="AA54" s="18" t="n"/>
+      <c r="AB54" s="18" t="n"/>
+      <c r="AC54" s="18" t="n"/>
+      <c r="AD54" s="18" t="n"/>
+      <c r="AE54" s="18" t="n"/>
+      <c r="AF54" s="20" t="n"/>
+      <c r="AG54" s="13">
+        <f>IF($A54="","",IF(AH54&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH54">
+        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($P54="",1,0)+IF($S54="",1,0)+IF($T54="",1,0)+IF($U54="",1,0)+IF($W54="",1,0)+IF($AA54="",1,0)+IF($AB54="",1,0)+IF(AND($N54="契約期間満了",$Q54=""),1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0)+IF(AND($AD54="外国",$AE54=""),1,0)+IF(AND($AD54="外国",$AF54=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="44" t="n"/>
-      <c r="E55" s="44" t="n"/>
-      <c r="F55" s="44" t="n"/>
-      <c r="G55" s="44" t="n"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="18" t="n"/>
-      <c r="M55" s="45">
+      <c r="A55" s="18" t="n"/>
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="45" t="n"/>
+      <c r="E55" s="45" t="n"/>
+      <c r="F55" s="45" t="n"/>
+      <c r="G55" s="45" t="n"/>
+      <c r="H55" s="18" t="n"/>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="18" t="n"/>
+      <c r="K55" s="45" t="n"/>
+      <c r="L55" s="20" t="n"/>
+      <c r="M55" s="46">
         <f>IF($L55="","",$L55+1)</f>
         <v/>
       </c>
-      <c r="N55" s="16" t="n"/>
-      <c r="O55" s="16" t="n"/>
-      <c r="P55" s="16" t="n"/>
-      <c r="Q55" s="16" t="n"/>
-      <c r="R55" s="16" t="n"/>
-      <c r="S55" s="16" t="n"/>
-      <c r="T55" s="16" t="n"/>
-      <c r="U55" s="16" t="n"/>
-      <c r="V55" s="16" t="n"/>
-      <c r="W55" s="46" t="n"/>
-      <c r="X55" s="46" t="n"/>
-      <c r="Y55" s="16" t="n"/>
-      <c r="Z55" s="16" t="n"/>
-      <c r="AA55" s="16" t="n"/>
-      <c r="AB55" s="47">
-        <f>IF($A55="","",IF(AC55&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC55">
-        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($O55="",1,0)+IF($P55="",1,0)+IF($S55="",1,0)+IF($U55="",1,0)+IF($Y55="",1,0)+IF($Z55="",1,0)+IF(AND($N55="契約期間満了",$Q55=""),1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0))</f>
+      <c r="N55" s="18" t="n"/>
+      <c r="O55" s="18" t="n"/>
+      <c r="P55" s="18" t="n"/>
+      <c r="Q55" s="18" t="n"/>
+      <c r="R55" s="18" t="n"/>
+      <c r="S55" s="20" t="n"/>
+      <c r="T55" s="47" t="n"/>
+      <c r="U55" s="18" t="n"/>
+      <c r="V55" s="18" t="n"/>
+      <c r="W55" s="18" t="n"/>
+      <c r="X55" s="18" t="n"/>
+      <c r="Y55" s="48" t="n"/>
+      <c r="Z55" s="48" t="n"/>
+      <c r="AA55" s="18" t="n"/>
+      <c r="AB55" s="18" t="n"/>
+      <c r="AC55" s="18" t="n"/>
+      <c r="AD55" s="18" t="n"/>
+      <c r="AE55" s="18" t="n"/>
+      <c r="AF55" s="20" t="n"/>
+      <c r="AG55" s="13">
+        <f>IF($A55="","",IF(AH55&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH55">
+        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($P55="",1,0)+IF($S55="",1,0)+IF($T55="",1,0)+IF($U55="",1,0)+IF($W55="",1,0)+IF($AA55="",1,0)+IF($AB55="",1,0)+IF(AND($N55="契約期間満了",$Q55=""),1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0)+IF(AND($AD55="外国",$AE55=""),1,0)+IF(AND($AD55="外国",$AF55=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="44" t="n"/>
-      <c r="E56" s="44" t="n"/>
-      <c r="F56" s="44" t="n"/>
-      <c r="G56" s="44" t="n"/>
-      <c r="H56" s="16" t="n"/>
-      <c r="I56" s="16" t="n"/>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="18" t="n"/>
-      <c r="M56" s="45">
+      <c r="A56" s="18" t="n"/>
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="45" t="n"/>
+      <c r="E56" s="45" t="n"/>
+      <c r="F56" s="45" t="n"/>
+      <c r="G56" s="45" t="n"/>
+      <c r="H56" s="18" t="n"/>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="45" t="n"/>
+      <c r="L56" s="20" t="n"/>
+      <c r="M56" s="46">
         <f>IF($L56="","",$L56+1)</f>
         <v/>
       </c>
-      <c r="N56" s="16" t="n"/>
-      <c r="O56" s="16" t="n"/>
-      <c r="P56" s="16" t="n"/>
-      <c r="Q56" s="16" t="n"/>
-      <c r="R56" s="16" t="n"/>
-      <c r="S56" s="16" t="n"/>
-      <c r="T56" s="16" t="n"/>
-      <c r="U56" s="16" t="n"/>
-      <c r="V56" s="16" t="n"/>
-      <c r="W56" s="46" t="n"/>
-      <c r="X56" s="46" t="n"/>
-      <c r="Y56" s="16" t="n"/>
-      <c r="Z56" s="16" t="n"/>
-      <c r="AA56" s="16" t="n"/>
-      <c r="AB56" s="47">
-        <f>IF($A56="","",IF(AC56&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC56">
-        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($O56="",1,0)+IF($P56="",1,0)+IF($S56="",1,0)+IF($U56="",1,0)+IF($Y56="",1,0)+IF($Z56="",1,0)+IF(AND($N56="契約期間満了",$Q56=""),1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0))</f>
+      <c r="N56" s="18" t="n"/>
+      <c r="O56" s="18" t="n"/>
+      <c r="P56" s="18" t="n"/>
+      <c r="Q56" s="18" t="n"/>
+      <c r="R56" s="18" t="n"/>
+      <c r="S56" s="20" t="n"/>
+      <c r="T56" s="47" t="n"/>
+      <c r="U56" s="18" t="n"/>
+      <c r="V56" s="18" t="n"/>
+      <c r="W56" s="18" t="n"/>
+      <c r="X56" s="18" t="n"/>
+      <c r="Y56" s="48" t="n"/>
+      <c r="Z56" s="48" t="n"/>
+      <c r="AA56" s="18" t="n"/>
+      <c r="AB56" s="18" t="n"/>
+      <c r="AC56" s="18" t="n"/>
+      <c r="AD56" s="18" t="n"/>
+      <c r="AE56" s="18" t="n"/>
+      <c r="AF56" s="20" t="n"/>
+      <c r="AG56" s="13">
+        <f>IF($A56="","",IF(AH56&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH56">
+        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($P56="",1,0)+IF($S56="",1,0)+IF($T56="",1,0)+IF($U56="",1,0)+IF($W56="",1,0)+IF($AA56="",1,0)+IF($AB56="",1,0)+IF(AND($N56="契約期間満了",$Q56=""),1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0)+IF(AND($AD56="外国",$AE56=""),1,0)+IF(AND($AD56="外国",$AF56=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
-      <c r="B57" s="16" t="n"/>
-      <c r="C57" s="18" t="n"/>
-      <c r="D57" s="44" t="n"/>
-      <c r="E57" s="44" t="n"/>
-      <c r="F57" s="44" t="n"/>
-      <c r="G57" s="44" t="n"/>
-      <c r="H57" s="16" t="n"/>
-      <c r="I57" s="16" t="n"/>
-      <c r="J57" s="16" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="18" t="n"/>
-      <c r="M57" s="45">
+      <c r="A57" s="18" t="n"/>
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="45" t="n"/>
+      <c r="E57" s="45" t="n"/>
+      <c r="F57" s="45" t="n"/>
+      <c r="G57" s="45" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="45" t="n"/>
+      <c r="L57" s="20" t="n"/>
+      <c r="M57" s="46">
         <f>IF($L57="","",$L57+1)</f>
         <v/>
       </c>
-      <c r="N57" s="16" t="n"/>
-      <c r="O57" s="16" t="n"/>
-      <c r="P57" s="16" t="n"/>
-      <c r="Q57" s="16" t="n"/>
-      <c r="R57" s="16" t="n"/>
-      <c r="S57" s="16" t="n"/>
-      <c r="T57" s="16" t="n"/>
-      <c r="U57" s="16" t="n"/>
-      <c r="V57" s="16" t="n"/>
-      <c r="W57" s="46" t="n"/>
-      <c r="X57" s="46" t="n"/>
-      <c r="Y57" s="16" t="n"/>
-      <c r="Z57" s="16" t="n"/>
-      <c r="AA57" s="16" t="n"/>
-      <c r="AB57" s="47">
-        <f>IF($A57="","",IF(AC57&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($O57="",1,0)+IF($P57="",1,0)+IF($S57="",1,0)+IF($U57="",1,0)+IF($Y57="",1,0)+IF($Z57="",1,0)+IF(AND($N57="契約期間満了",$Q57=""),1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0))</f>
+      <c r="N57" s="18" t="n"/>
+      <c r="O57" s="18" t="n"/>
+      <c r="P57" s="18" t="n"/>
+      <c r="Q57" s="18" t="n"/>
+      <c r="R57" s="18" t="n"/>
+      <c r="S57" s="20" t="n"/>
+      <c r="T57" s="47" t="n"/>
+      <c r="U57" s="18" t="n"/>
+      <c r="V57" s="18" t="n"/>
+      <c r="W57" s="18" t="n"/>
+      <c r="X57" s="18" t="n"/>
+      <c r="Y57" s="48" t="n"/>
+      <c r="Z57" s="48" t="n"/>
+      <c r="AA57" s="18" t="n"/>
+      <c r="AB57" s="18" t="n"/>
+      <c r="AC57" s="18" t="n"/>
+      <c r="AD57" s="18" t="n"/>
+      <c r="AE57" s="18" t="n"/>
+      <c r="AF57" s="20" t="n"/>
+      <c r="AG57" s="13">
+        <f>IF($A57="","",IF(AH57&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH57">
+        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($P57="",1,0)+IF($S57="",1,0)+IF($T57="",1,0)+IF($U57="",1,0)+IF($W57="",1,0)+IF($AA57="",1,0)+IF($AB57="",1,0)+IF(AND($N57="契約期間満了",$Q57=""),1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0)+IF(AND($AD57="外国",$AE57=""),1,0)+IF(AND($AD57="外国",$AF57=""),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="18" t="n"/>
-      <c r="D58" s="44" t="n"/>
-      <c r="E58" s="44" t="n"/>
-      <c r="F58" s="44" t="n"/>
-      <c r="G58" s="44" t="n"/>
-      <c r="H58" s="16" t="n"/>
-      <c r="I58" s="16" t="n"/>
-      <c r="J58" s="16" t="n"/>
-      <c r="K58" s="16" t="n"/>
-      <c r="L58" s="18" t="n"/>
-      <c r="M58" s="45">
+      <c r="A58" s="18" t="n"/>
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="45" t="n"/>
+      <c r="E58" s="45" t="n"/>
+      <c r="F58" s="45" t="n"/>
+      <c r="G58" s="45" t="n"/>
+      <c r="H58" s="18" t="n"/>
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="45" t="n"/>
+      <c r="L58" s="20" t="n"/>
+      <c r="M58" s="46">
         <f>IF($L58="","",$L58+1)</f>
         <v/>
       </c>
-      <c r="N58" s="16" t="n"/>
-      <c r="O58" s="16" t="n"/>
-      <c r="P58" s="16" t="n"/>
-      <c r="Q58" s="16" t="n"/>
-      <c r="R58" s="16" t="n"/>
-      <c r="S58" s="16" t="n"/>
-      <c r="T58" s="16" t="n"/>
-      <c r="U58" s="16" t="n"/>
-      <c r="V58" s="16" t="n"/>
-      <c r="W58" s="46" t="n"/>
-      <c r="X58" s="46" t="n"/>
-      <c r="Y58" s="16" t="n"/>
-      <c r="Z58" s="16" t="n"/>
-      <c r="AA58" s="16" t="n"/>
-      <c r="AB58" s="47">
-        <f>IF($A58="","",IF(AC58&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AC58">
-        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($O58="",1,0)+IF($P58="",1,0)+IF($S58="",1,0)+IF($U58="",1,0)+IF($Y58="",1,0)+IF($Z58="",1,0)+IF(AND($N58="契約期間満了",$Q58=""),1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0))</f>
+      <c r="N58" s="18" t="n"/>
+      <c r="O58" s="18" t="n"/>
+      <c r="P58" s="18" t="n"/>
+      <c r="Q58" s="18" t="n"/>
+      <c r="R58" s="18" t="n"/>
+      <c r="S58" s="20" t="n"/>
+      <c r="T58" s="47" t="n"/>
+      <c r="U58" s="18" t="n"/>
+      <c r="V58" s="18" t="n"/>
+      <c r="W58" s="18" t="n"/>
+      <c r="X58" s="18" t="n"/>
+      <c r="Y58" s="48" t="n"/>
+      <c r="Z58" s="48" t="n"/>
+      <c r="AA58" s="18" t="n"/>
+      <c r="AB58" s="18" t="n"/>
+      <c r="AC58" s="18" t="n"/>
+      <c r="AD58" s="18" t="n"/>
+      <c r="AE58" s="18" t="n"/>
+      <c r="AF58" s="20" t="n"/>
+      <c r="AG58" s="13">
+        <f>IF($A58="","",IF(AH58&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AH58">
+        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($P58="",1,0)+IF($S58="",1,0)+IF($T58="",1,0)+IF($U58="",1,0)+IF($W58="",1,0)+IF($AA58="",1,0)+IF($AB58="",1,0)+IF(AND($N58="契約期間満了",$Q58=""),1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0)+IF(AND($AD58="外国",$AE58=""),1,0)+IF(AND($AD58="外国",$AF58=""),1,0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="N1:AA1"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="S6:X6"/>
+    <mergeCell ref="AD6:AF6"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="A1:P1"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="AA6"/>
-    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AC6"/>
+    <mergeCell ref="S6:Z6"/>
+    <mergeCell ref="Q1:AF1"/>
     <mergeCell ref="L6:R6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
@@ -4184,99 +4414,97 @@
     <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("未入力が",A5))</formula>
     </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("式の入っていない",A5))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:B58">
-    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",B9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",LENB(B9)&lt;&gt;LEN(B9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",ISERROR(FIND("　",B9)),ISERROR(FIND(" ",B9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C58">
-    <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",C9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="33" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(C9),C9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D58">
-    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",D9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="31" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LEN(D9)&lt;&gt;12)</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LENB(D9)&lt;&gt;LEN(D9))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E58">
-    <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",E9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LEN(E9)&lt;&gt;10)</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LENB(E9)&lt;&gt;LEN(E9))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F58">
-    <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",F9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="27" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="33" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LEN(F9)&lt;&gt;11)</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LENB(F9)&lt;&gt;LEN(F9))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G58">
-    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",G9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LEN(SUBSTITUTE(G9,"-",""))&lt;&gt;7)</formula>
     </cfRule>
-    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LENB(G9)&lt;&gt;LEN(G9))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H58">
-    <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="11" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",H9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I58">
-    <cfRule type="expression" priority="11" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",I9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
       <formula>AND(I9&lt;&gt;"",LENB(I9)&lt;&gt;LEN(I9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:L58">
-    <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="13" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",L9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(L9),L9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9:N58">
-    <cfRule type="expression" priority="13" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="14" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",N9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O9:O58">
-    <cfRule type="expression" priority="14" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",O9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P58">
@@ -4288,68 +4516,100 @@
     <cfRule type="expression" priority="16" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",S9="")</formula>
     </cfRule>
+    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(S9),S9&gt;80000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T9:T58">
+    <cfRule type="expression" priority="17" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",T9="")</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9:U58">
-    <cfRule type="expression" priority="17" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",U9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y9:Y58">
-    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",Y9="")</formula>
+  <conditionalFormatting sqref="W9:W58">
+    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",W9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z9:Z58">
-    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",Z9="")</formula>
+  <conditionalFormatting sqref="AA9:AA58">
+    <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",AA9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB9:AB58">
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",AB9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A58">
-    <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
       <formula>AND($A9="",OR($L9&lt;&gt;"",$N9&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",LENB(A9)&lt;&gt;LEN(A9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",ISERROR(FIND("　",A9)),ISERROR(FIND(" ",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q9:Q58">
-    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",Q9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" dxfId="3" stopIfTrue="1">
-      <formula>AND($N9&lt;&gt;"",$N9&lt;&gt;"契約期間満了",Q9="")</formula>
+    <cfRule type="expression" priority="27" dxfId="3" stopIfTrue="1">
+      <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),Q9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:R58">
-    <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",R9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" dxfId="3" stopIfTrue="1">
-      <formula>AND($N9&lt;&gt;"",$N9&lt;&gt;"契約期間満了",R9="")</formula>
+    <cfRule type="expression" priority="28" dxfId="3" stopIfTrue="1">
+      <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),R9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AE58">
+    <cfRule type="expression" priority="25" dxfId="2" stopIfTrue="1">
+      <formula>AND($AD9="外国",AE9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" dxfId="3" stopIfTrue="1">
+      <formula>AND($AD9&lt;&gt;"",NOT($AD9="外国"),AE9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF9:AF58">
+    <cfRule type="expression" priority="26" dxfId="2" stopIfTrue="1">
+      <formula>AND($AD9="外国",AF9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="3" stopIfTrue="1">
+      <formula>AND($AD9&lt;&gt;"",NOT($AD9="外国"),AF9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="49" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AF9),AF9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J58">
-    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
       <formula>AND(J9&lt;&gt;"",LENB(J9)&lt;&gt;LEN(J9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K58">
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
       <formula>AND(K9&lt;&gt;"",LENB(K9)&lt;&gt;LEN(K9))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB9:AB58">
-    <cfRule type="expression" priority="42" dxfId="0" stopIfTrue="1">
-      <formula>AB9="CSV可"</formula>
+  <conditionalFormatting sqref="AG9:AG58">
+    <cfRule type="expression" priority="50" dxfId="0" stopIfTrue="1">
+      <formula>AG9="CSV可"</formula>
     </cfRule>
-    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
-      <formula>AB9="未入力"</formula>
+    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
+      <formula>AG9="未入力"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="17">
+  <dataValidations count="21">
     <dataValidation sqref="C8:C58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦の生年月日。例 1990/4/1。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
@@ -4377,7 +4637,7 @@
     <dataValidation sqref="N8:N58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="実際の退職事由を選択。" type="list" errorStyle="stop">
       <formula1>m_退職理由</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="雇用保険の離職理由区分の目安。最終判断は社労士・ハローワーク。" type="list" errorStyle="stop">
+    <dataValidation sqref="O8:O58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="分かる場合のみ選択。空欄で構いません。最終判断は当事務所とハローワークが行います。" type="list" errorStyle="stop">
       <formula1>m_離職理由区分</formula1>
     </dataValidation>
     <dataValidation sqref="Q8:Q58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="有期契約（退職理由＝契約期間満了）のとき必須。&#10;契約書に更新の定めがあったか。離職理由区分・給付制限・所定給付日数の判定に直結します。" type="list" errorStyle="stop">
@@ -4386,25 +4646,40 @@
     <dataValidation sqref="R8:R58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="有期契約（退職理由＝契約期間満了）のとき必須。&#10;本人が契約更新を希望していたか。雇止めの離職理由区分の判定に使用します。" type="list" errorStyle="stop">
       <formula1>m_更新希望</formula1>
     </dataValidation>
-    <dataValidation sqref="S8:S58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人が離職票（基本手当の申請）を希望するか。" type="list" errorStyle="stop">
+    <dataValidation sqref="S8:S58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="この会社で雇用保険に入った日。雇用保険被保険者証・資格取得等確認通知書に載っています。" type="whole" errorStyle="warning" operator="between">
+      <formula1>1</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation sqref="T8:T58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="契約上の1週間の所定労働時間。実労働時間ではありません（例 40、29.5）。" type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>80</formula2>
+    </dataValidation>
+    <dataValidation sqref="U8:U58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人が離職票（基本手当の申請）を希望するか。" type="list" errorStyle="stop">
       <formula1>m_ありなし</formula1>
     </dataValidation>
-    <dataValidation sqref="U8:U58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="離職証明書の賃金欄作成のため、離職前6か月（賃金）・12か月（基礎日数）の台帳添付があるか。" type="list" errorStyle="stop">
+    <dataValidation sqref="W8:W58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="離職証明書の賃金欄と被保険者期間の確認のため、離職前1年分の賃金台帳・出勤簿があるか。賃金支払基礎日数11日以上の月が12か月に満たないときは2年分。" type="list" errorStyle="stop">
       <formula1>m_ありなし</formula1>
     </dataValidation>
-    <dataValidation sqref="W8:W58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="X8:X58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
+    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
       <formula1>m_回収状況</formula1>
     </dataValidation>
-    <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職後の医療保険の予定（任意継続・扶養・国保）。" type="list" errorStyle="stop">
+    <dataValidation sqref="AB8:AB58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職後の医療保険の予定（任意継続・扶養・国保）。" type="list" errorStyle="stop">
       <formula1>m_退職後</formula1>
+    </dataValidation>
+    <dataValidation sqref="AD8:AD58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="日本国籍の方は『日本』。外国籍の方は『外国』を選び、右の2欄もご記入ください。" type="list" errorStyle="stop">
+      <formula1>m_国籍</formula1>
+    </dataValidation>
+    <dataValidation sqref="AF8:AF58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="在留カードの『在留期間（満了日）』。西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
+      <formula1>1</formula1>
+      <formula2>99999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4420,7 +4695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4438,634 +4713,650 @@
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.5" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>性別</t>
         </is>
       </c>
-      <c r="B1" s="48" t="inlineStr">
+      <c r="B1" s="49" t="inlineStr">
         <is>
           <t>あり/なし</t>
         </is>
       </c>
-      <c r="C1" s="48" t="inlineStr">
+      <c r="C1" s="49" t="inlineStr">
         <is>
           <t>都道府県</t>
         </is>
       </c>
-      <c r="D1" s="48" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>番号提出状態</t>
         </is>
       </c>
-      <c r="E1" s="48" t="inlineStr">
+      <c r="E1" s="49" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="F1" s="48" t="inlineStr">
+      <c r="F1" s="49" t="inlineStr">
         <is>
           <t>雇保番号状態</t>
         </is>
       </c>
-      <c r="G1" s="48" t="inlineStr">
+      <c r="G1" s="49" t="inlineStr">
         <is>
           <t>退職理由</t>
         </is>
       </c>
-      <c r="H1" s="48" t="inlineStr">
+      <c r="H1" s="49" t="inlineStr">
         <is>
           <t>離職理由区分</t>
         </is>
       </c>
-      <c r="I1" s="48" t="inlineStr">
+      <c r="I1" s="49" t="inlineStr">
         <is>
           <t>契約更新条項</t>
         </is>
       </c>
-      <c r="J1" s="48" t="inlineStr">
+      <c r="J1" s="49" t="inlineStr">
         <is>
           <t>更新希望</t>
         </is>
       </c>
-      <c r="K1" s="48" t="inlineStr">
+      <c r="K1" s="49" t="inlineStr">
         <is>
           <t>回収状況</t>
         </is>
       </c>
-      <c r="L1" s="48" t="inlineStr">
+      <c r="L1" s="49" t="inlineStr">
         <is>
           <t>退職後</t>
         </is>
       </c>
-      <c r="M1" s="48" t="inlineStr">
+      <c r="M1" s="49" t="inlineStr">
         <is>
           <t>住民税徴収方法</t>
         </is>
       </c>
-      <c r="N1" s="48" t="inlineStr">
+      <c r="N1" s="49" t="inlineStr">
         <is>
           <t>退職金支給</t>
         </is>
       </c>
-      <c r="O1" s="48" t="inlineStr">
+      <c r="O1" s="49" t="inlineStr">
         <is>
           <t>退職所得申告書</t>
         </is>
       </c>
+      <c r="P1" s="49" t="inlineStr">
+        <is>
+          <t>国籍</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="50" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="C2" s="50" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="50" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="E2" s="49" t="inlineStr">
+      <c r="E2" s="50" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="50" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="G2" s="49" t="inlineStr">
+      <c r="G2" s="50" t="inlineStr">
         <is>
           <t>自己都合</t>
         </is>
       </c>
-      <c r="H2" s="49" t="inlineStr">
+      <c r="H2" s="50" t="inlineStr">
         <is>
           <t>一般（自己都合等）</t>
         </is>
       </c>
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="50" t="inlineStr">
         <is>
           <t>該当なし（無期契約）</t>
         </is>
       </c>
-      <c r="J2" s="49" t="inlineStr">
+      <c r="J2" s="50" t="inlineStr">
         <is>
           <t>該当なし</t>
         </is>
       </c>
-      <c r="K2" s="49" t="inlineStr">
+      <c r="K2" s="50" t="inlineStr">
         <is>
           <t>回収済</t>
         </is>
       </c>
-      <c r="L2" s="49" t="inlineStr">
+      <c r="L2" s="50" t="inlineStr">
         <is>
           <t>任意継続を希望</t>
         </is>
       </c>
-      <c r="M2" s="49" t="inlineStr">
+      <c r="M2" s="50" t="inlineStr">
         <is>
           <t>特別徴収を継続（転職先へ引継ぎ）</t>
         </is>
       </c>
-      <c r="N2" s="49" t="inlineStr">
+      <c r="N2" s="50" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="O2" s="49" t="inlineStr">
+      <c r="O2" s="50" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
+      <c r="P2" s="50" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="B3" s="49" t="inlineStr">
+      <c r="B3" s="50" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="C3" s="50" t="inlineStr">
         <is>
           <t>青森県</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
         <is>
           <t>別経路提出</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
+      <c r="F3" s="50" t="inlineStr">
         <is>
           <t>後日提出</t>
         </is>
       </c>
-      <c r="G3" s="49" t="inlineStr">
+      <c r="G3" s="50" t="inlineStr">
         <is>
           <t>会社都合（解雇）</t>
         </is>
       </c>
-      <c r="H3" s="49" t="inlineStr">
+      <c r="H3" s="50" t="inlineStr">
         <is>
           <t>特定受給資格者（解雇・倒産等）</t>
         </is>
       </c>
-      <c r="I3" s="49" t="inlineStr">
+      <c r="I3" s="50" t="inlineStr">
         <is>
           <t>更新の明示なし</t>
         </is>
       </c>
-      <c r="J3" s="49" t="inlineStr">
+      <c r="J3" s="50" t="inlineStr">
         <is>
           <t>更新を希望していた</t>
         </is>
       </c>
-      <c r="K3" s="49" t="inlineStr">
+      <c r="K3" s="50" t="inlineStr">
         <is>
           <t>未回収</t>
         </is>
       </c>
-      <c r="L3" s="49" t="inlineStr">
+      <c r="L3" s="50" t="inlineStr">
         <is>
           <t>家族の扶養に入る</t>
         </is>
       </c>
-      <c r="M3" s="49" t="inlineStr">
+      <c r="M3" s="50" t="inlineStr">
         <is>
           <t>一括徴収（最終給与・退職金から）</t>
         </is>
       </c>
-      <c r="N3" s="49" t="inlineStr">
+      <c r="N3" s="50" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="O3" s="49" t="inlineStr">
+      <c r="O3" s="50" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
+      <c r="P3" s="50" t="inlineStr">
+        <is>
+          <t>外国</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>岩手県</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="50" t="inlineStr">
         <is>
           <t>定年</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="50" t="inlineStr">
         <is>
           <t>特定理由離職者（雇止め・正当な理由の自己都合）</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="50" t="inlineStr">
         <is>
           <t>更新する場合がある旨の明示あり</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="50" t="inlineStr">
         <is>
           <t>更新を希望しなかった</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="50" t="inlineStr">
         <is>
           <t>本人保管（資格確認書）</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="50" t="inlineStr">
         <is>
           <t>国民健康保険へ</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="50" t="inlineStr">
         <is>
           <t>普通徴収へ切替（自分で納付）</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="50" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="50" t="inlineStr">
         <is>
           <t>該当なし</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>宮城県</t>
         </is>
       </c>
-      <c r="G5" s="49" t="inlineStr">
+      <c r="G5" s="50" t="inlineStr">
         <is>
           <t>契約期間満了</t>
         </is>
       </c>
-      <c r="H5" s="49" t="inlineStr">
+      <c r="H5" s="50" t="inlineStr">
         <is>
           <t>区分不明</t>
         </is>
       </c>
-      <c r="I5" s="49" t="inlineStr">
+      <c r="I5" s="50" t="inlineStr">
         <is>
           <t>更新する旨の明示あり（自動更新含む）</t>
         </is>
       </c>
-      <c r="K5" s="49" t="inlineStr">
+      <c r="K5" s="50" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="L5" s="49" t="inlineStr">
+      <c r="L5" s="50" t="inlineStr">
         <is>
           <t>未定・不明</t>
         </is>
       </c>
-      <c r="M5" s="49" t="inlineStr">
+      <c r="M5" s="50" t="inlineStr">
         <is>
           <t>不明・要相談</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="G6" s="49" t="inlineStr">
+      <c r="G6" s="50" t="inlineStr">
         <is>
           <t>役員退任</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>山形県</t>
         </is>
       </c>
-      <c r="G7" s="49" t="inlineStr">
-        <is>
-          <t>death（死亡）</t>
+      <c r="G7" s="50" t="inlineStr">
+        <is>
+          <t>死亡</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="G8" s="49" t="inlineStr">
+      <c r="G8" s="50" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>群馬県</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>埼玉県</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>千葉県</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>新潟県</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>富山県</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>石川県</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="49" t="inlineStr">
+      <c r="C19" s="50" t="inlineStr">
         <is>
           <t>福井県</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="49" t="inlineStr">
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>山梨県</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="50" t="inlineStr">
         <is>
           <t>長野県</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="49" t="inlineStr">
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>岐阜県</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="50" t="inlineStr">
         <is>
           <t>静岡県</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="49" t="inlineStr">
+      <c r="C24" s="50" t="inlineStr">
         <is>
           <t>愛知県</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>三重県</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="49" t="inlineStr">
+      <c r="C26" s="50" t="inlineStr">
         <is>
           <t>滋賀県</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="49" t="inlineStr">
+      <c r="C27" s="50" t="inlineStr">
         <is>
           <t>京都府</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="49" t="inlineStr">
+      <c r="C28" s="50" t="inlineStr">
         <is>
           <t>大阪府</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="49" t="inlineStr">
+      <c r="C29" s="50" t="inlineStr">
         <is>
           <t>兵庫県</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="49" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
         <is>
           <t>奈良県</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="49" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <t>和歌山県</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="49" t="inlineStr">
+      <c r="C32" s="50" t="inlineStr">
         <is>
           <t>鳥取県</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="49" t="inlineStr">
+      <c r="C33" s="50" t="inlineStr">
         <is>
           <t>島根県</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="49" t="inlineStr">
+      <c r="C34" s="50" t="inlineStr">
         <is>
           <t>岡山県</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="49" t="inlineStr">
+      <c r="C35" s="50" t="inlineStr">
         <is>
           <t>広島県</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="49" t="inlineStr">
+      <c r="C36" s="50" t="inlineStr">
         <is>
           <t>山口県</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="49" t="inlineStr">
+      <c r="C37" s="50" t="inlineStr">
         <is>
           <t>徳島県</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="49" t="inlineStr">
+      <c r="C38" s="50" t="inlineStr">
         <is>
           <t>香川県</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="49" t="inlineStr">
+      <c r="C39" s="50" t="inlineStr">
         <is>
           <t>愛媛県</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="49" t="inlineStr">
+      <c r="C40" s="50" t="inlineStr">
         <is>
           <t>高知県</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="49" t="inlineStr">
+      <c r="C41" s="50" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="49" t="inlineStr">
+      <c r="C42" s="50" t="inlineStr">
         <is>
           <t>佐賀県</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="49" t="inlineStr">
+      <c r="C43" s="50" t="inlineStr">
         <is>
           <t>長崎県</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="49" t="inlineStr">
+      <c r="C44" s="50" t="inlineStr">
         <is>
           <t>熊本県</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="49" t="inlineStr">
+      <c r="C45" s="50" t="inlineStr">
         <is>
           <t>大分県</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="49" t="inlineStr">
+      <c r="C46" s="50" t="inlineStr">
         <is>
           <t>宮崎県</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="49" t="inlineStr">
+      <c r="C47" s="50" t="inlineStr">
         <is>
           <t>鹿児島県</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="49" t="inlineStr">
+      <c r="C48" s="50" t="inlineStr">
         <is>
           <t>沖縄県</t>
         </is>
@@ -5082,276 +5373,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>データシート</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>退職 情報</t>
         </is>
       </c>
-      <c r="C1" s="49" t="n"/>
-      <c r="D1" s="49" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>開始行</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n">
+      <c r="B2" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>終了行</t>
         </is>
       </c>
-      <c r="B3" s="49" t="n">
+      <c r="B3" s="50" t="n">
         <v>58</v>
       </c>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>見出し行</t>
         </is>
       </c>
-      <c r="B4" s="49" t="n">
+      <c r="B4" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
+      <c r="C4" s="50" t="n"/>
+      <c r="D4" s="50" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>kanji</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>氏名（漢字）</t>
         </is>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>kana</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>氏名（フリガナ）</t>
         </is>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="50" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>num</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>マイナンバー(12桁)</t>
         </is>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>基礎年金番号(10桁)</t>
         </is>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>雇用保険被保険者番号(11桁)</t>
         </is>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>郵便番号</t>
         </is>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>市区町村以下</t>
         </is>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="50" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>建物名・部屋番号</t>
         </is>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>numh</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>電話番号</t>
         </is>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="50" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>離職日（退職日）</t>
         </is>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B16" s="50" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C16" s="50" t="inlineStr">
+        <is>
+          <t>雇用保険 資格取得年月日</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
+      <c r="B17" s="50" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C17" s="50" t="inlineStr">
+        <is>
+          <t>在留期間の満了日【外国籍のとき必須】</t>
+        </is>
+      </c>
+      <c r="D17" s="50" t="n">
         <v>0</v>
       </c>
     </row>

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -596,85 +596,95 @@
     </comment>
     <comment ref="P7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職証明書『具体的事情記載欄』への転記用。</t>
+        <t>用途：離職理由区分の裏付け（いつ話が出たか）。</t>
       </text>
     </comment>
     <comment ref="Q7" authorId="0" shapeId="0">
       <text>
-        <t>用途：有期契約の雇止め判定（離職理由区分）。</t>
+        <t>用途：離職証明書『具体的事情記載欄』への転記用。</t>
       </text>
     </comment>
     <comment ref="R7" authorId="0" shapeId="0">
       <text>
-        <t>用途：雇止め時の本人の更新希望（離職理由区分の判定）。</t>
+        <t>用途：有期契約の雇止め判定（離職理由区分）。</t>
       </text>
     </comment>
     <comment ref="S7" authorId="0" shapeId="0">
       <text>
-        <t>用途：雇用保険 資格喪失届の『被保険者となった年月日』。</t>
+        <t>用途：雇止め時の本人の更新希望（離職理由区分の判定）。</t>
       </text>
     </comment>
     <comment ref="T7" authorId="0" shapeId="0">
       <text>
-        <t>用途：雇用保険 資格喪失届の『1週間の所定労働時間』。</t>
+        <t>用途：雇用保険 資格喪失届の『被保険者となった年月日』。</t>
       </text>
     </comment>
     <comment ref="U7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職票の交付要否（本人が基本手当を申請するか）。</t>
+        <t>用途：雇用保険 資格喪失届の『1週間の所定労働時間』。</t>
       </text>
     </comment>
     <comment ref="V7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職票の送付先（退職後に転居する場合）。</t>
+        <t>用途：離職票の交付要否（本人が基本手当を申請するか）。</t>
       </text>
     </comment>
     <comment ref="W7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職証明書の賃金欄作成のための賃金台帳・出勤簿の添付確認。</t>
+        <t>用途：離職票の送付先（退職後に転居する場合）。</t>
       </text>
     </comment>
     <comment ref="X7" authorId="0" shapeId="0">
       <text>
-        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
+        <t>用途：離職証明書の賃金欄作成のための賃金台帳・出勤簿の添付確認。</t>
       </text>
     </comment>
     <comment ref="Y7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
+        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
       </text>
     </comment>
     <comment ref="Z7" authorId="0" shapeId="0">
       <text>
-        <t>用途：直近賞与の参考値。</t>
+        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
       </text>
     </comment>
     <comment ref="AA7" authorId="0" shapeId="0">
       <text>
-        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
+        <t>用途：直近賞与の参考値。</t>
       </text>
     </comment>
     <comment ref="AB7" authorId="0" shapeId="0">
       <text>
-        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
+        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
       </text>
     </comment>
     <comment ref="AC7" authorId="0" shapeId="0">
       <text>
-        <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
+        <t>用途：健康保険被保険者証等回収不能届に書く品目。</t>
       </text>
     </comment>
     <comment ref="AD7" authorId="0" shapeId="0">
       <text>
-        <t>用途：外国人雇用状況の届出（資格取得届・喪失届と一体）の国籍欄。</t>
+        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
       </text>
     </comment>
     <comment ref="AE7" authorId="0" shapeId="0">
       <text>
+        <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
+      </text>
+    </comment>
+    <comment ref="AF7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：外国人雇用状況の届出（資格取得届・喪失届と一体）の国籍欄。</t>
+      </text>
+    </comment>
+    <comment ref="AG7" authorId="0" shapeId="0">
+      <text>
         <t>用途：同 在留資格欄。外国籍の方のみ。</t>
       </text>
     </comment>
-    <comment ref="AF7" authorId="0" shapeId="0">
+    <comment ref="AH7" authorId="0" shapeId="0">
       <text>
         <t>用途：同 在留期間欄。外国籍の方のみ。</t>
       </text>
@@ -1366,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1449,101 +1459,140 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="21" t="inlineStr">
+    <row r="9" ht="53.5" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>健康保険・厚生年金の事業所整理記号</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>毎月20日ごろ年金事務所から届く『保険料納入告知額・領収済額通知書』に載っています。口座振替の会社は別名の紙で届きます。例）12-アイウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>同 事業所番号</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>同じ紙の整理記号の隣にある番号です。5桁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="37" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>雇用保険の事業所番号</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>『雇用保険適用事業所設置届 事業主控』または資格取得等確認通知書に載っています。4桁-6桁-1桁。例）1610-123456-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>対象者数（自動）</t>
         </is>
       </c>
-      <c r="C9" s="22">
+      <c r="C12" s="22">
         <f>'退職 情報'!A4</f>
         <v/>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>本体シートに入力された件数を自動表示します。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="37" customHeight="1">
-      <c r="B10" s="21" t="inlineStr">
+    <row r="13" ht="37" customHeight="1">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>必須の未入力 残（自動）</t>
         </is>
       </c>
-      <c r="C10" s="22">
+      <c r="C13" s="22">
         <f>'退職 情報'!E4</f>
         <v/>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>未入力の必須項目の残数。0件になるまでご記入ください（本体の薄赤・行ステータス参照）。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="21" t="inlineStr">
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>完了率（自動）</t>
         </is>
       </c>
-      <c r="C11" s="23">
+      <c r="C14" s="23">
         <f>'退職 情報'!G4</f>
         <v/>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>必須項目の充足率。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="37" customHeight="1">
-      <c r="B12" s="21" t="inlineStr">
+    <row r="15" ht="37" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>提出可否（自動）</t>
         </is>
       </c>
-      <c r="C12" s="24">
+      <c r="C15" s="24">
         <f>IF('退職 情報'!A4=0,"未入力（対象者なし）",IF(AND('退職 情報'!E4=0,'退職 情報'!C4&lt;&gt;'退職 情報'!A4),"確認が必要：式の入っていない行があります（行を挿入せず9〜58行にご記入ください）",IF('退職 情報'!E4=0,"提出可（必須の未入力なし）","未入力あり：本体シートの薄赤セル・行ステータスをご確認ください")))</f>
         <v/>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>必須の未入力が無ければ『提出可』。残っていれば本体をご確認ください。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>事務所への連絡事項</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>不明点・特記事項があればご記入ください（任意）。</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="17"/>
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>② 一緒に送っていただく書類</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="53.5" customHeight="1">
-      <c r="B16" s="16" t="inlineStr">
+    <row r="19" ht="53.5" customHeight="1">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>書類の一覧と、いま何が届いているかは案件ページが正です。このシートには書類の状態を書かないでください（二重管理になります）。
 案件ページは受任メールのリンクから開けます。届いた書類はその場で受領済みに変わります。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="B17" s="25" t="inlineStr">
+    <row r="20" ht="70" customHeight="1">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>この手続きで必要になるもの：
 　・賃金台帳（離職前1年分）
@@ -1552,16 +1601,16 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="21"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>③ 当事務所への返送について</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="86.5" customHeight="1">
-      <c r="B20" s="16" t="inlineStr">
+    <row r="23" ht="86.5" customHeight="1">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>記入したこのファイルを、案件ページからそのままお送りください。ZIPにする必要はありません。ファイル名も変えなくて構いません。
 送り先は受任メールに載せた案件ページのリンクです。そのページの「受領フォーム」の欄から、このファイルを選ぶだけで届きます。
@@ -1569,16 +1618,16 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="24"/>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>④ 入力の補足（情報が揃わないとき）</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="53.5" customHeight="1">
-      <c r="B23" s="25" t="inlineStr">
+    <row r="26" ht="53.5" customHeight="1">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>・『不明』『後日提出』を選べる欄は、空欄のままにせず状態を残してください。後で当事務所が確認・督促できます。
 ・該当しない欄は『該当なし』を選ぶか空欄で構いません（条件次第で対象外＝斜線になる欄もあります）。
@@ -1593,26 +1642,26 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B20:D20"/>
   </mergeCells>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C15">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("提出可",C12))</formula>
+      <formula>ISNUMBER(SEARCH("提出可",C15))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(SEARCH("未入力",C12)),ISERROR(SEARCH("提出可",C12)))</formula>
+      <formula>AND(ISNUMBER(SEARCH("未入力",C15)),ISERROR(SEARCH("提出可",C15)))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("確認が必要",C12))</formula>
+      <formula>ISNUMBER(SEARCH("確認が必要",C15))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="C13">
     <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
-      <formula>C10&gt;0</formula>
+      <formula>C13&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -1632,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1650,25 +1699,27 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="17" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="36" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="32" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="36" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1677,7 +1728,7 @@
           <t>退職 情報</t>
         </is>
       </c>
-      <c r="Q1" s="26" t="inlineStr">
+      <c r="R1" s="26" t="inlineStr">
         <is>
           <t>※離職理由区分は目安。最終判断は社労士・ハローワークが行います。</t>
         </is>
@@ -1733,11 +1784,11 @@
         <v/>
       </c>
       <c r="C4" s="29">
-        <f>COUNTIF(AH9:AH58,0)</f>
+        <f>COUNTIF(AJ9:AJ58,0)</f>
         <v/>
       </c>
       <c r="E4" s="29">
-        <f>SUM(AH9:AH58)</f>
+        <f>SUM(AJ9:AJ58)</f>
         <v/>
       </c>
       <c r="G4" s="30">
@@ -1770,22 +1821,22 @@
           <t>退職事由</t>
         </is>
       </c>
-      <c r="S6" s="34" t="inlineStr">
+      <c r="T6" s="34" t="inlineStr">
         <is>
           <t>雇用保険</t>
         </is>
       </c>
-      <c r="AA6" s="35" t="inlineStr">
+      <c r="AB6" s="35" t="inlineStr">
         <is>
           <t>社会保険</t>
         </is>
       </c>
-      <c r="AC6" s="36" t="inlineStr">
+      <c r="AE6" s="36" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AD6" s="37" t="inlineStr">
+      <c r="AF6" s="37" t="inlineStr">
         <is>
           <t>外国籍のとき</t>
         </is>
@@ -1882,109 +1933,121 @@
 【任】</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>退職の話が出た日
+【任】</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>離職理由の具体的事情
 【必】</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>契約更新条項（有期契約のみ）
 【条件により必須】</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>本人の更新希望（有期契約のみ）
 【条件により必須】</t>
         </is>
       </c>
-      <c r="S7" s="6" t="inlineStr">
+      <c r="T7" s="6" t="inlineStr">
         <is>
           <t>雇用保険 資格取得年月日
 【必】</t>
         </is>
       </c>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>1週間の所定労働時間(時間)
 【必】</t>
         </is>
       </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="V7" s="6" t="inlineStr">
         <is>
           <t>離職票の交付希望
 【必】</t>
         </is>
       </c>
-      <c r="V7" s="7" t="inlineStr">
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>離職票の送付先（転居する場合）
 【任】</t>
         </is>
       </c>
-      <c r="W7" s="6" t="inlineStr">
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>賃金台帳・出勤簿の添付
 【必】</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
+      <c r="Y7" s="7" t="inlineStr">
         <is>
           <t>賃金締切日
 【任】</t>
         </is>
       </c>
-      <c r="Y7" s="7" t="inlineStr">
+      <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>離職前賃金（直近1か月・円）
 【任】</t>
         </is>
       </c>
-      <c r="Z7" s="7" t="inlineStr">
+      <c r="AA7" s="7" t="inlineStr">
         <is>
           <t>直近の賞与（円）
 【任】</t>
         </is>
       </c>
-      <c r="AA7" s="6" t="inlineStr">
+      <c r="AB7" s="6" t="inlineStr">
         <is>
           <t>資格確認書等の回収
 【必】</t>
         </is>
       </c>
-      <c r="AB7" s="6" t="inlineStr">
+      <c r="AC7" s="7" t="inlineStr">
+        <is>
+          <t>回収できなかったもの
+【条件により必須】</t>
+        </is>
+      </c>
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>退職後の希望
 【必】</t>
         </is>
       </c>
-      <c r="AC7" s="7" t="inlineStr">
+      <c r="AE7" s="7" t="inlineStr">
         <is>
           <t>備考（連絡事項）
 【任】</t>
         </is>
       </c>
-      <c r="AD7" s="7" t="inlineStr">
+      <c r="AF7" s="7" t="inlineStr">
         <is>
           <t>国籍・地域
 【任】</t>
         </is>
       </c>
-      <c r="AE7" s="7" t="inlineStr">
+      <c r="AG7" s="7" t="inlineStr">
         <is>
           <t>在留資格【外国籍のとき必須】
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AF7" s="7" t="inlineStr">
+      <c r="AH7" s="7" t="inlineStr">
         <is>
           <t>在留期間の満了日【外国籍のとき必須】
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AG7" s="38" t="inlineStr">
+      <c r="AI7" s="38" t="inlineStr">
         <is>
           <t>行ステータス
 （CSV可否）</t>
@@ -2062,71 +2125,75 @@
           <t>一般（自己都合等）</t>
         </is>
       </c>
-      <c r="P8" s="40" t="inlineStr">
+      <c r="P8" s="41" t="n">
+        <v>46203</v>
+      </c>
+      <c r="Q8" s="40" t="inlineStr">
         <is>
           <t>転職のため（一身上の都合）。</t>
         </is>
       </c>
-      <c r="Q8" s="40" t="inlineStr">
+      <c r="R8" s="40" t="inlineStr">
         <is>
           <t>該当なし（無期契約）</t>
         </is>
       </c>
-      <c r="R8" s="40" t="inlineStr">
+      <c r="S8" s="40" t="inlineStr">
         <is>
           <t>該当なし</t>
         </is>
       </c>
-      <c r="S8" s="41" t="n">
+      <c r="T8" s="41" t="n">
         <v>43922</v>
       </c>
-      <c r="T8" s="43" t="n">
+      <c r="U8" s="43" t="n">
         <v>40</v>
       </c>
-      <c r="U8" s="40" t="inlineStr">
+      <c r="V8" s="40" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="V8" s="40" t="n"/>
-      <c r="W8" s="40" t="inlineStr">
+      <c r="W8" s="40" t="n"/>
+      <c r="X8" s="40" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="X8" s="40" t="inlineStr">
+      <c r="Y8" s="40" t="inlineStr">
         <is>
           <t>毎月末日</t>
         </is>
       </c>
-      <c r="Y8" s="44" t="n">
+      <c r="Z8" s="44" t="n">
         <v>300000</v>
       </c>
-      <c r="Z8" s="44" t="n">
+      <c r="AA8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" s="40" t="inlineStr">
+      <c r="AB8" s="40" t="inlineStr">
         <is>
           <t>回収済</t>
         </is>
       </c>
-      <c r="AB8" s="40" t="inlineStr">
+      <c r="AC8" s="40" t="inlineStr"/>
+      <c r="AD8" s="40" t="inlineStr">
         <is>
           <t>家族の扶養に入る</t>
         </is>
       </c>
-      <c r="AC8" s="40" t="inlineStr">
+      <c r="AE8" s="40" t="inlineStr">
         <is>
           <t>← この行は記入例です</t>
         </is>
       </c>
-      <c r="AD8" s="40" t="inlineStr">
+      <c r="AF8" s="40" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="AE8" s="40" t="n"/>
-      <c r="AF8" s="41" t="n"/>
+      <c r="AG8" s="40" t="n"/>
+      <c r="AH8" s="41" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
@@ -2147,29 +2214,31 @@
       </c>
       <c r="N9" s="18" t="n"/>
       <c r="O9" s="18" t="n"/>
-      <c r="P9" s="18" t="n"/>
+      <c r="P9" s="20" t="n"/>
       <c r="Q9" s="18" t="n"/>
       <c r="R9" s="18" t="n"/>
-      <c r="S9" s="20" t="n"/>
-      <c r="T9" s="47" t="n"/>
-      <c r="U9" s="18" t="n"/>
+      <c r="S9" s="18" t="n"/>
+      <c r="T9" s="20" t="n"/>
+      <c r="U9" s="47" t="n"/>
       <c r="V9" s="18" t="n"/>
       <c r="W9" s="18" t="n"/>
       <c r="X9" s="18" t="n"/>
-      <c r="Y9" s="48" t="n"/>
+      <c r="Y9" s="18" t="n"/>
       <c r="Z9" s="48" t="n"/>
-      <c r="AA9" s="18" t="n"/>
+      <c r="AA9" s="48" t="n"/>
       <c r="AB9" s="18" t="n"/>
       <c r="AC9" s="18" t="n"/>
       <c r="AD9" s="18" t="n"/>
       <c r="AE9" s="18" t="n"/>
-      <c r="AF9" s="20" t="n"/>
-      <c r="AG9" s="13">
-        <f>IF($A9="","",IF(AH9&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH9">
-        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($P9="",1,0)+IF($S9="",1,0)+IF($T9="",1,0)+IF($U9="",1,0)+IF($W9="",1,0)+IF($AA9="",1,0)+IF($AB9="",1,0)+IF(AND($N9="契約期間満了",$Q9=""),1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0)+IF(AND($AD9="外国",$AE9=""),1,0)+IF(AND($AD9="外国",$AF9=""),1,0))</f>
+      <c r="AF9" s="18" t="n"/>
+      <c r="AG9" s="18" t="n"/>
+      <c r="AH9" s="20" t="n"/>
+      <c r="AI9" s="13">
+        <f>IF($A9="","",IF(AJ9&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ9">
+        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($Q9="",1,0)+IF($T9="",1,0)+IF($U9="",1,0)+IF($V9="",1,0)+IF($X9="",1,0)+IF($AB9="",1,0)+IF($AD9="",1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0)+IF(AND($N9="契約期間満了",$S9=""),1,0)+IF(AND($AF9="外国",$AG9=""),1,0)+IF(AND($AF9="外国",$AH9=""),1,0)+IF(AND($AB9="未回収",$AC9=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2192,29 +2261,31 @@
       </c>
       <c r="N10" s="18" t="n"/>
       <c r="O10" s="18" t="n"/>
-      <c r="P10" s="18" t="n"/>
+      <c r="P10" s="20" t="n"/>
       <c r="Q10" s="18" t="n"/>
       <c r="R10" s="18" t="n"/>
-      <c r="S10" s="20" t="n"/>
-      <c r="T10" s="47" t="n"/>
-      <c r="U10" s="18" t="n"/>
+      <c r="S10" s="18" t="n"/>
+      <c r="T10" s="20" t="n"/>
+      <c r="U10" s="47" t="n"/>
       <c r="V10" s="18" t="n"/>
       <c r="W10" s="18" t="n"/>
       <c r="X10" s="18" t="n"/>
-      <c r="Y10" s="48" t="n"/>
+      <c r="Y10" s="18" t="n"/>
       <c r="Z10" s="48" t="n"/>
-      <c r="AA10" s="18" t="n"/>
+      <c r="AA10" s="48" t="n"/>
       <c r="AB10" s="18" t="n"/>
       <c r="AC10" s="18" t="n"/>
       <c r="AD10" s="18" t="n"/>
       <c r="AE10" s="18" t="n"/>
-      <c r="AF10" s="20" t="n"/>
-      <c r="AG10" s="13">
-        <f>IF($A10="","",IF(AH10&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH10">
-        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($P10="",1,0)+IF($S10="",1,0)+IF($T10="",1,0)+IF($U10="",1,0)+IF($W10="",1,0)+IF($AA10="",1,0)+IF($AB10="",1,0)+IF(AND($N10="契約期間満了",$Q10=""),1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0)+IF(AND($AD10="外国",$AE10=""),1,0)+IF(AND($AD10="外国",$AF10=""),1,0))</f>
+      <c r="AF10" s="18" t="n"/>
+      <c r="AG10" s="18" t="n"/>
+      <c r="AH10" s="20" t="n"/>
+      <c r="AI10" s="13">
+        <f>IF($A10="","",IF(AJ10&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ10">
+        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($Q10="",1,0)+IF($T10="",1,0)+IF($U10="",1,0)+IF($V10="",1,0)+IF($X10="",1,0)+IF($AB10="",1,0)+IF($AD10="",1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0)+IF(AND($N10="契約期間満了",$S10=""),1,0)+IF(AND($AF10="外国",$AG10=""),1,0)+IF(AND($AF10="外国",$AH10=""),1,0)+IF(AND($AB10="未回収",$AC10=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2237,29 +2308,31 @@
       </c>
       <c r="N11" s="18" t="n"/>
       <c r="O11" s="18" t="n"/>
-      <c r="P11" s="18" t="n"/>
+      <c r="P11" s="20" t="n"/>
       <c r="Q11" s="18" t="n"/>
       <c r="R11" s="18" t="n"/>
-      <c r="S11" s="20" t="n"/>
-      <c r="T11" s="47" t="n"/>
-      <c r="U11" s="18" t="n"/>
+      <c r="S11" s="18" t="n"/>
+      <c r="T11" s="20" t="n"/>
+      <c r="U11" s="47" t="n"/>
       <c r="V11" s="18" t="n"/>
       <c r="W11" s="18" t="n"/>
       <c r="X11" s="18" t="n"/>
-      <c r="Y11" s="48" t="n"/>
+      <c r="Y11" s="18" t="n"/>
       <c r="Z11" s="48" t="n"/>
-      <c r="AA11" s="18" t="n"/>
+      <c r="AA11" s="48" t="n"/>
       <c r="AB11" s="18" t="n"/>
       <c r="AC11" s="18" t="n"/>
       <c r="AD11" s="18" t="n"/>
       <c r="AE11" s="18" t="n"/>
-      <c r="AF11" s="20" t="n"/>
-      <c r="AG11" s="13">
-        <f>IF($A11="","",IF(AH11&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH11">
-        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($P11="",1,0)+IF($S11="",1,0)+IF($T11="",1,0)+IF($U11="",1,0)+IF($W11="",1,0)+IF($AA11="",1,0)+IF($AB11="",1,0)+IF(AND($N11="契約期間満了",$Q11=""),1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0)+IF(AND($AD11="外国",$AE11=""),1,0)+IF(AND($AD11="外国",$AF11=""),1,0))</f>
+      <c r="AF11" s="18" t="n"/>
+      <c r="AG11" s="18" t="n"/>
+      <c r="AH11" s="20" t="n"/>
+      <c r="AI11" s="13">
+        <f>IF($A11="","",IF(AJ11&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ11">
+        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($Q11="",1,0)+IF($T11="",1,0)+IF($U11="",1,0)+IF($V11="",1,0)+IF($X11="",1,0)+IF($AB11="",1,0)+IF($AD11="",1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0)+IF(AND($N11="契約期間満了",$S11=""),1,0)+IF(AND($AF11="外国",$AG11=""),1,0)+IF(AND($AF11="外国",$AH11=""),1,0)+IF(AND($AB11="未回収",$AC11=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2282,29 +2355,31 @@
       </c>
       <c r="N12" s="18" t="n"/>
       <c r="O12" s="18" t="n"/>
-      <c r="P12" s="18" t="n"/>
+      <c r="P12" s="20" t="n"/>
       <c r="Q12" s="18" t="n"/>
       <c r="R12" s="18" t="n"/>
-      <c r="S12" s="20" t="n"/>
-      <c r="T12" s="47" t="n"/>
-      <c r="U12" s="18" t="n"/>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" s="20" t="n"/>
+      <c r="U12" s="47" t="n"/>
       <c r="V12" s="18" t="n"/>
       <c r="W12" s="18" t="n"/>
       <c r="X12" s="18" t="n"/>
-      <c r="Y12" s="48" t="n"/>
+      <c r="Y12" s="18" t="n"/>
       <c r="Z12" s="48" t="n"/>
-      <c r="AA12" s="18" t="n"/>
+      <c r="AA12" s="48" t="n"/>
       <c r="AB12" s="18" t="n"/>
       <c r="AC12" s="18" t="n"/>
       <c r="AD12" s="18" t="n"/>
       <c r="AE12" s="18" t="n"/>
-      <c r="AF12" s="20" t="n"/>
-      <c r="AG12" s="13">
-        <f>IF($A12="","",IF(AH12&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH12">
-        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($P12="",1,0)+IF($S12="",1,0)+IF($T12="",1,0)+IF($U12="",1,0)+IF($W12="",1,0)+IF($AA12="",1,0)+IF($AB12="",1,0)+IF(AND($N12="契約期間満了",$Q12=""),1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0)+IF(AND($AD12="外国",$AE12=""),1,0)+IF(AND($AD12="外国",$AF12=""),1,0))</f>
+      <c r="AF12" s="18" t="n"/>
+      <c r="AG12" s="18" t="n"/>
+      <c r="AH12" s="20" t="n"/>
+      <c r="AI12" s="13">
+        <f>IF($A12="","",IF(AJ12&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ12">
+        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($Q12="",1,0)+IF($T12="",1,0)+IF($U12="",1,0)+IF($V12="",1,0)+IF($X12="",1,0)+IF($AB12="",1,0)+IF($AD12="",1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0)+IF(AND($N12="契約期間満了",$S12=""),1,0)+IF(AND($AF12="外国",$AG12=""),1,0)+IF(AND($AF12="外国",$AH12=""),1,0)+IF(AND($AB12="未回収",$AC12=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2327,29 +2402,31 @@
       </c>
       <c r="N13" s="18" t="n"/>
       <c r="O13" s="18" t="n"/>
-      <c r="P13" s="18" t="n"/>
+      <c r="P13" s="20" t="n"/>
       <c r="Q13" s="18" t="n"/>
       <c r="R13" s="18" t="n"/>
-      <c r="S13" s="20" t="n"/>
-      <c r="T13" s="47" t="n"/>
-      <c r="U13" s="18" t="n"/>
+      <c r="S13" s="18" t="n"/>
+      <c r="T13" s="20" t="n"/>
+      <c r="U13" s="47" t="n"/>
       <c r="V13" s="18" t="n"/>
       <c r="W13" s="18" t="n"/>
       <c r="X13" s="18" t="n"/>
-      <c r="Y13" s="48" t="n"/>
+      <c r="Y13" s="18" t="n"/>
       <c r="Z13" s="48" t="n"/>
-      <c r="AA13" s="18" t="n"/>
+      <c r="AA13" s="48" t="n"/>
       <c r="AB13" s="18" t="n"/>
       <c r="AC13" s="18" t="n"/>
       <c r="AD13" s="18" t="n"/>
       <c r="AE13" s="18" t="n"/>
-      <c r="AF13" s="20" t="n"/>
-      <c r="AG13" s="13">
-        <f>IF($A13="","",IF(AH13&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH13">
-        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($P13="",1,0)+IF($S13="",1,0)+IF($T13="",1,0)+IF($U13="",1,0)+IF($W13="",1,0)+IF($AA13="",1,0)+IF($AB13="",1,0)+IF(AND($N13="契約期間満了",$Q13=""),1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0)+IF(AND($AD13="外国",$AE13=""),1,0)+IF(AND($AD13="外国",$AF13=""),1,0))</f>
+      <c r="AF13" s="18" t="n"/>
+      <c r="AG13" s="18" t="n"/>
+      <c r="AH13" s="20" t="n"/>
+      <c r="AI13" s="13">
+        <f>IF($A13="","",IF(AJ13&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ13">
+        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($Q13="",1,0)+IF($T13="",1,0)+IF($U13="",1,0)+IF($V13="",1,0)+IF($X13="",1,0)+IF($AB13="",1,0)+IF($AD13="",1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0)+IF(AND($N13="契約期間満了",$S13=""),1,0)+IF(AND($AF13="外国",$AG13=""),1,0)+IF(AND($AF13="外国",$AH13=""),1,0)+IF(AND($AB13="未回収",$AC13=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2372,29 +2449,31 @@
       </c>
       <c r="N14" s="18" t="n"/>
       <c r="O14" s="18" t="n"/>
-      <c r="P14" s="18" t="n"/>
+      <c r="P14" s="20" t="n"/>
       <c r="Q14" s="18" t="n"/>
       <c r="R14" s="18" t="n"/>
-      <c r="S14" s="20" t="n"/>
-      <c r="T14" s="47" t="n"/>
-      <c r="U14" s="18" t="n"/>
+      <c r="S14" s="18" t="n"/>
+      <c r="T14" s="20" t="n"/>
+      <c r="U14" s="47" t="n"/>
       <c r="V14" s="18" t="n"/>
       <c r="W14" s="18" t="n"/>
       <c r="X14" s="18" t="n"/>
-      <c r="Y14" s="48" t="n"/>
+      <c r="Y14" s="18" t="n"/>
       <c r="Z14" s="48" t="n"/>
-      <c r="AA14" s="18" t="n"/>
+      <c r="AA14" s="48" t="n"/>
       <c r="AB14" s="18" t="n"/>
       <c r="AC14" s="18" t="n"/>
       <c r="AD14" s="18" t="n"/>
       <c r="AE14" s="18" t="n"/>
-      <c r="AF14" s="20" t="n"/>
-      <c r="AG14" s="13">
-        <f>IF($A14="","",IF(AH14&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH14">
-        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($P14="",1,0)+IF($S14="",1,0)+IF($T14="",1,0)+IF($U14="",1,0)+IF($W14="",1,0)+IF($AA14="",1,0)+IF($AB14="",1,0)+IF(AND($N14="契約期間満了",$Q14=""),1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0)+IF(AND($AD14="外国",$AE14=""),1,0)+IF(AND($AD14="外国",$AF14=""),1,0))</f>
+      <c r="AF14" s="18" t="n"/>
+      <c r="AG14" s="18" t="n"/>
+      <c r="AH14" s="20" t="n"/>
+      <c r="AI14" s="13">
+        <f>IF($A14="","",IF(AJ14&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ14">
+        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($Q14="",1,0)+IF($T14="",1,0)+IF($U14="",1,0)+IF($V14="",1,0)+IF($X14="",1,0)+IF($AB14="",1,0)+IF($AD14="",1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0)+IF(AND($N14="契約期間満了",$S14=""),1,0)+IF(AND($AF14="外国",$AG14=""),1,0)+IF(AND($AF14="外国",$AH14=""),1,0)+IF(AND($AB14="未回収",$AC14=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2417,29 +2496,31 @@
       </c>
       <c r="N15" s="18" t="n"/>
       <c r="O15" s="18" t="n"/>
-      <c r="P15" s="18" t="n"/>
+      <c r="P15" s="20" t="n"/>
       <c r="Q15" s="18" t="n"/>
       <c r="R15" s="18" t="n"/>
-      <c r="S15" s="20" t="n"/>
-      <c r="T15" s="47" t="n"/>
-      <c r="U15" s="18" t="n"/>
+      <c r="S15" s="18" t="n"/>
+      <c r="T15" s="20" t="n"/>
+      <c r="U15" s="47" t="n"/>
       <c r="V15" s="18" t="n"/>
       <c r="W15" s="18" t="n"/>
       <c r="X15" s="18" t="n"/>
-      <c r="Y15" s="48" t="n"/>
+      <c r="Y15" s="18" t="n"/>
       <c r="Z15" s="48" t="n"/>
-      <c r="AA15" s="18" t="n"/>
+      <c r="AA15" s="48" t="n"/>
       <c r="AB15" s="18" t="n"/>
       <c r="AC15" s="18" t="n"/>
       <c r="AD15" s="18" t="n"/>
       <c r="AE15" s="18" t="n"/>
-      <c r="AF15" s="20" t="n"/>
-      <c r="AG15" s="13">
-        <f>IF($A15="","",IF(AH15&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH15">
-        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($P15="",1,0)+IF($S15="",1,0)+IF($T15="",1,0)+IF($U15="",1,0)+IF($W15="",1,0)+IF($AA15="",1,0)+IF($AB15="",1,0)+IF(AND($N15="契約期間満了",$Q15=""),1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0)+IF(AND($AD15="外国",$AE15=""),1,0)+IF(AND($AD15="外国",$AF15=""),1,0))</f>
+      <c r="AF15" s="18" t="n"/>
+      <c r="AG15" s="18" t="n"/>
+      <c r="AH15" s="20" t="n"/>
+      <c r="AI15" s="13">
+        <f>IF($A15="","",IF(AJ15&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ15">
+        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($Q15="",1,0)+IF($T15="",1,0)+IF($U15="",1,0)+IF($V15="",1,0)+IF($X15="",1,0)+IF($AB15="",1,0)+IF($AD15="",1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0)+IF(AND($N15="契約期間満了",$S15=""),1,0)+IF(AND($AF15="外国",$AG15=""),1,0)+IF(AND($AF15="外国",$AH15=""),1,0)+IF(AND($AB15="未回収",$AC15=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2462,29 +2543,31 @@
       </c>
       <c r="N16" s="18" t="n"/>
       <c r="O16" s="18" t="n"/>
-      <c r="P16" s="18" t="n"/>
+      <c r="P16" s="20" t="n"/>
       <c r="Q16" s="18" t="n"/>
       <c r="R16" s="18" t="n"/>
-      <c r="S16" s="20" t="n"/>
-      <c r="T16" s="47" t="n"/>
-      <c r="U16" s="18" t="n"/>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="20" t="n"/>
+      <c r="U16" s="47" t="n"/>
       <c r="V16" s="18" t="n"/>
       <c r="W16" s="18" t="n"/>
       <c r="X16" s="18" t="n"/>
-      <c r="Y16" s="48" t="n"/>
+      <c r="Y16" s="18" t="n"/>
       <c r="Z16" s="48" t="n"/>
-      <c r="AA16" s="18" t="n"/>
+      <c r="AA16" s="48" t="n"/>
       <c r="AB16" s="18" t="n"/>
       <c r="AC16" s="18" t="n"/>
       <c r="AD16" s="18" t="n"/>
       <c r="AE16" s="18" t="n"/>
-      <c r="AF16" s="20" t="n"/>
-      <c r="AG16" s="13">
-        <f>IF($A16="","",IF(AH16&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH16">
-        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($P16="",1,0)+IF($S16="",1,0)+IF($T16="",1,0)+IF($U16="",1,0)+IF($W16="",1,0)+IF($AA16="",1,0)+IF($AB16="",1,0)+IF(AND($N16="契約期間満了",$Q16=""),1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0)+IF(AND($AD16="外国",$AE16=""),1,0)+IF(AND($AD16="外国",$AF16=""),1,0))</f>
+      <c r="AF16" s="18" t="n"/>
+      <c r="AG16" s="18" t="n"/>
+      <c r="AH16" s="20" t="n"/>
+      <c r="AI16" s="13">
+        <f>IF($A16="","",IF(AJ16&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ16">
+        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($Q16="",1,0)+IF($T16="",1,0)+IF($U16="",1,0)+IF($V16="",1,0)+IF($X16="",1,0)+IF($AB16="",1,0)+IF($AD16="",1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0)+IF(AND($N16="契約期間満了",$S16=""),1,0)+IF(AND($AF16="外国",$AG16=""),1,0)+IF(AND($AF16="外国",$AH16=""),1,0)+IF(AND($AB16="未回収",$AC16=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2507,29 +2590,31 @@
       </c>
       <c r="N17" s="18" t="n"/>
       <c r="O17" s="18" t="n"/>
-      <c r="P17" s="18" t="n"/>
+      <c r="P17" s="20" t="n"/>
       <c r="Q17" s="18" t="n"/>
       <c r="R17" s="18" t="n"/>
-      <c r="S17" s="20" t="n"/>
-      <c r="T17" s="47" t="n"/>
-      <c r="U17" s="18" t="n"/>
+      <c r="S17" s="18" t="n"/>
+      <c r="T17" s="20" t="n"/>
+      <c r="U17" s="47" t="n"/>
       <c r="V17" s="18" t="n"/>
       <c r="W17" s="18" t="n"/>
       <c r="X17" s="18" t="n"/>
-      <c r="Y17" s="48" t="n"/>
+      <c r="Y17" s="18" t="n"/>
       <c r="Z17" s="48" t="n"/>
-      <c r="AA17" s="18" t="n"/>
+      <c r="AA17" s="48" t="n"/>
       <c r="AB17" s="18" t="n"/>
       <c r="AC17" s="18" t="n"/>
       <c r="AD17" s="18" t="n"/>
       <c r="AE17" s="18" t="n"/>
-      <c r="AF17" s="20" t="n"/>
-      <c r="AG17" s="13">
-        <f>IF($A17="","",IF(AH17&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH17">
-        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($P17="",1,0)+IF($S17="",1,0)+IF($T17="",1,0)+IF($U17="",1,0)+IF($W17="",1,0)+IF($AA17="",1,0)+IF($AB17="",1,0)+IF(AND($N17="契約期間満了",$Q17=""),1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0)+IF(AND($AD17="外国",$AE17=""),1,0)+IF(AND($AD17="外国",$AF17=""),1,0))</f>
+      <c r="AF17" s="18" t="n"/>
+      <c r="AG17" s="18" t="n"/>
+      <c r="AH17" s="20" t="n"/>
+      <c r="AI17" s="13">
+        <f>IF($A17="","",IF(AJ17&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ17">
+        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($Q17="",1,0)+IF($T17="",1,0)+IF($U17="",1,0)+IF($V17="",1,0)+IF($X17="",1,0)+IF($AB17="",1,0)+IF($AD17="",1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0)+IF(AND($N17="契約期間満了",$S17=""),1,0)+IF(AND($AF17="外国",$AG17=""),1,0)+IF(AND($AF17="外国",$AH17=""),1,0)+IF(AND($AB17="未回収",$AC17=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2552,29 +2637,31 @@
       </c>
       <c r="N18" s="18" t="n"/>
       <c r="O18" s="18" t="n"/>
-      <c r="P18" s="18" t="n"/>
+      <c r="P18" s="20" t="n"/>
       <c r="Q18" s="18" t="n"/>
       <c r="R18" s="18" t="n"/>
-      <c r="S18" s="20" t="n"/>
-      <c r="T18" s="47" t="n"/>
-      <c r="U18" s="18" t="n"/>
+      <c r="S18" s="18" t="n"/>
+      <c r="T18" s="20" t="n"/>
+      <c r="U18" s="47" t="n"/>
       <c r="V18" s="18" t="n"/>
       <c r="W18" s="18" t="n"/>
       <c r="X18" s="18" t="n"/>
-      <c r="Y18" s="48" t="n"/>
+      <c r="Y18" s="18" t="n"/>
       <c r="Z18" s="48" t="n"/>
-      <c r="AA18" s="18" t="n"/>
+      <c r="AA18" s="48" t="n"/>
       <c r="AB18" s="18" t="n"/>
       <c r="AC18" s="18" t="n"/>
       <c r="AD18" s="18" t="n"/>
       <c r="AE18" s="18" t="n"/>
-      <c r="AF18" s="20" t="n"/>
-      <c r="AG18" s="13">
-        <f>IF($A18="","",IF(AH18&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH18">
-        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($P18="",1,0)+IF($S18="",1,0)+IF($T18="",1,0)+IF($U18="",1,0)+IF($W18="",1,0)+IF($AA18="",1,0)+IF($AB18="",1,0)+IF(AND($N18="契約期間満了",$Q18=""),1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0)+IF(AND($AD18="外国",$AE18=""),1,0)+IF(AND($AD18="外国",$AF18=""),1,0))</f>
+      <c r="AF18" s="18" t="n"/>
+      <c r="AG18" s="18" t="n"/>
+      <c r="AH18" s="20" t="n"/>
+      <c r="AI18" s="13">
+        <f>IF($A18="","",IF(AJ18&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ18">
+        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($Q18="",1,0)+IF($T18="",1,0)+IF($U18="",1,0)+IF($V18="",1,0)+IF($X18="",1,0)+IF($AB18="",1,0)+IF($AD18="",1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0)+IF(AND($N18="契約期間満了",$S18=""),1,0)+IF(AND($AF18="外国",$AG18=""),1,0)+IF(AND($AF18="外国",$AH18=""),1,0)+IF(AND($AB18="未回収",$AC18=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2597,29 +2684,31 @@
       </c>
       <c r="N19" s="18" t="n"/>
       <c r="O19" s="18" t="n"/>
-      <c r="P19" s="18" t="n"/>
+      <c r="P19" s="20" t="n"/>
       <c r="Q19" s="18" t="n"/>
       <c r="R19" s="18" t="n"/>
-      <c r="S19" s="20" t="n"/>
-      <c r="T19" s="47" t="n"/>
-      <c r="U19" s="18" t="n"/>
+      <c r="S19" s="18" t="n"/>
+      <c r="T19" s="20" t="n"/>
+      <c r="U19" s="47" t="n"/>
       <c r="V19" s="18" t="n"/>
       <c r="W19" s="18" t="n"/>
       <c r="X19" s="18" t="n"/>
-      <c r="Y19" s="48" t="n"/>
+      <c r="Y19" s="18" t="n"/>
       <c r="Z19" s="48" t="n"/>
-      <c r="AA19" s="18" t="n"/>
+      <c r="AA19" s="48" t="n"/>
       <c r="AB19" s="18" t="n"/>
       <c r="AC19" s="18" t="n"/>
       <c r="AD19" s="18" t="n"/>
       <c r="AE19" s="18" t="n"/>
-      <c r="AF19" s="20" t="n"/>
-      <c r="AG19" s="13">
-        <f>IF($A19="","",IF(AH19&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH19">
-        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($P19="",1,0)+IF($S19="",1,0)+IF($T19="",1,0)+IF($U19="",1,0)+IF($W19="",1,0)+IF($AA19="",1,0)+IF($AB19="",1,0)+IF(AND($N19="契約期間満了",$Q19=""),1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0)+IF(AND($AD19="外国",$AE19=""),1,0)+IF(AND($AD19="外国",$AF19=""),1,0))</f>
+      <c r="AF19" s="18" t="n"/>
+      <c r="AG19" s="18" t="n"/>
+      <c r="AH19" s="20" t="n"/>
+      <c r="AI19" s="13">
+        <f>IF($A19="","",IF(AJ19&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ19">
+        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($Q19="",1,0)+IF($T19="",1,0)+IF($U19="",1,0)+IF($V19="",1,0)+IF($X19="",1,0)+IF($AB19="",1,0)+IF($AD19="",1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0)+IF(AND($N19="契約期間満了",$S19=""),1,0)+IF(AND($AF19="外国",$AG19=""),1,0)+IF(AND($AF19="外国",$AH19=""),1,0)+IF(AND($AB19="未回収",$AC19=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2642,29 +2731,31 @@
       </c>
       <c r="N20" s="18" t="n"/>
       <c r="O20" s="18" t="n"/>
-      <c r="P20" s="18" t="n"/>
+      <c r="P20" s="20" t="n"/>
       <c r="Q20" s="18" t="n"/>
       <c r="R20" s="18" t="n"/>
-      <c r="S20" s="20" t="n"/>
-      <c r="T20" s="47" t="n"/>
-      <c r="U20" s="18" t="n"/>
+      <c r="S20" s="18" t="n"/>
+      <c r="T20" s="20" t="n"/>
+      <c r="U20" s="47" t="n"/>
       <c r="V20" s="18" t="n"/>
       <c r="W20" s="18" t="n"/>
       <c r="X20" s="18" t="n"/>
-      <c r="Y20" s="48" t="n"/>
+      <c r="Y20" s="18" t="n"/>
       <c r="Z20" s="48" t="n"/>
-      <c r="AA20" s="18" t="n"/>
+      <c r="AA20" s="48" t="n"/>
       <c r="AB20" s="18" t="n"/>
       <c r="AC20" s="18" t="n"/>
       <c r="AD20" s="18" t="n"/>
       <c r="AE20" s="18" t="n"/>
-      <c r="AF20" s="20" t="n"/>
-      <c r="AG20" s="13">
-        <f>IF($A20="","",IF(AH20&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH20">
-        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($P20="",1,0)+IF($S20="",1,0)+IF($T20="",1,0)+IF($U20="",1,0)+IF($W20="",1,0)+IF($AA20="",1,0)+IF($AB20="",1,0)+IF(AND($N20="契約期間満了",$Q20=""),1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0)+IF(AND($AD20="外国",$AE20=""),1,0)+IF(AND($AD20="外国",$AF20=""),1,0))</f>
+      <c r="AF20" s="18" t="n"/>
+      <c r="AG20" s="18" t="n"/>
+      <c r="AH20" s="20" t="n"/>
+      <c r="AI20" s="13">
+        <f>IF($A20="","",IF(AJ20&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ20">
+        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($Q20="",1,0)+IF($T20="",1,0)+IF($U20="",1,0)+IF($V20="",1,0)+IF($X20="",1,0)+IF($AB20="",1,0)+IF($AD20="",1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0)+IF(AND($N20="契約期間満了",$S20=""),1,0)+IF(AND($AF20="外国",$AG20=""),1,0)+IF(AND($AF20="外国",$AH20=""),1,0)+IF(AND($AB20="未回収",$AC20=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2687,29 +2778,31 @@
       </c>
       <c r="N21" s="18" t="n"/>
       <c r="O21" s="18" t="n"/>
-      <c r="P21" s="18" t="n"/>
+      <c r="P21" s="20" t="n"/>
       <c r="Q21" s="18" t="n"/>
       <c r="R21" s="18" t="n"/>
-      <c r="S21" s="20" t="n"/>
-      <c r="T21" s="47" t="n"/>
-      <c r="U21" s="18" t="n"/>
+      <c r="S21" s="18" t="n"/>
+      <c r="T21" s="20" t="n"/>
+      <c r="U21" s="47" t="n"/>
       <c r="V21" s="18" t="n"/>
       <c r="W21" s="18" t="n"/>
       <c r="X21" s="18" t="n"/>
-      <c r="Y21" s="48" t="n"/>
+      <c r="Y21" s="18" t="n"/>
       <c r="Z21" s="48" t="n"/>
-      <c r="AA21" s="18" t="n"/>
+      <c r="AA21" s="48" t="n"/>
       <c r="AB21" s="18" t="n"/>
       <c r="AC21" s="18" t="n"/>
       <c r="AD21" s="18" t="n"/>
       <c r="AE21" s="18" t="n"/>
-      <c r="AF21" s="20" t="n"/>
-      <c r="AG21" s="13">
-        <f>IF($A21="","",IF(AH21&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH21">
-        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($P21="",1,0)+IF($S21="",1,0)+IF($T21="",1,0)+IF($U21="",1,0)+IF($W21="",1,0)+IF($AA21="",1,0)+IF($AB21="",1,0)+IF(AND($N21="契約期間満了",$Q21=""),1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0)+IF(AND($AD21="外国",$AE21=""),1,0)+IF(AND($AD21="外国",$AF21=""),1,0))</f>
+      <c r="AF21" s="18" t="n"/>
+      <c r="AG21" s="18" t="n"/>
+      <c r="AH21" s="20" t="n"/>
+      <c r="AI21" s="13">
+        <f>IF($A21="","",IF(AJ21&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ21">
+        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($Q21="",1,0)+IF($T21="",1,0)+IF($U21="",1,0)+IF($V21="",1,0)+IF($X21="",1,0)+IF($AB21="",1,0)+IF($AD21="",1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0)+IF(AND($N21="契約期間満了",$S21=""),1,0)+IF(AND($AF21="外国",$AG21=""),1,0)+IF(AND($AF21="外国",$AH21=""),1,0)+IF(AND($AB21="未回収",$AC21=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2732,29 +2825,31 @@
       </c>
       <c r="N22" s="18" t="n"/>
       <c r="O22" s="18" t="n"/>
-      <c r="P22" s="18" t="n"/>
+      <c r="P22" s="20" t="n"/>
       <c r="Q22" s="18" t="n"/>
       <c r="R22" s="18" t="n"/>
-      <c r="S22" s="20" t="n"/>
-      <c r="T22" s="47" t="n"/>
-      <c r="U22" s="18" t="n"/>
+      <c r="S22" s="18" t="n"/>
+      <c r="T22" s="20" t="n"/>
+      <c r="U22" s="47" t="n"/>
       <c r="V22" s="18" t="n"/>
       <c r="W22" s="18" t="n"/>
       <c r="X22" s="18" t="n"/>
-      <c r="Y22" s="48" t="n"/>
+      <c r="Y22" s="18" t="n"/>
       <c r="Z22" s="48" t="n"/>
-      <c r="AA22" s="18" t="n"/>
+      <c r="AA22" s="48" t="n"/>
       <c r="AB22" s="18" t="n"/>
       <c r="AC22" s="18" t="n"/>
       <c r="AD22" s="18" t="n"/>
       <c r="AE22" s="18" t="n"/>
-      <c r="AF22" s="20" t="n"/>
-      <c r="AG22" s="13">
-        <f>IF($A22="","",IF(AH22&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH22">
-        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($P22="",1,0)+IF($S22="",1,0)+IF($T22="",1,0)+IF($U22="",1,0)+IF($W22="",1,0)+IF($AA22="",1,0)+IF($AB22="",1,0)+IF(AND($N22="契約期間満了",$Q22=""),1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0)+IF(AND($AD22="外国",$AE22=""),1,0)+IF(AND($AD22="外国",$AF22=""),1,0))</f>
+      <c r="AF22" s="18" t="n"/>
+      <c r="AG22" s="18" t="n"/>
+      <c r="AH22" s="20" t="n"/>
+      <c r="AI22" s="13">
+        <f>IF($A22="","",IF(AJ22&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ22">
+        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($Q22="",1,0)+IF($T22="",1,0)+IF($U22="",1,0)+IF($V22="",1,0)+IF($X22="",1,0)+IF($AB22="",1,0)+IF($AD22="",1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0)+IF(AND($N22="契約期間満了",$S22=""),1,0)+IF(AND($AF22="外国",$AG22=""),1,0)+IF(AND($AF22="外国",$AH22=""),1,0)+IF(AND($AB22="未回収",$AC22=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2777,29 +2872,31 @@
       </c>
       <c r="N23" s="18" t="n"/>
       <c r="O23" s="18" t="n"/>
-      <c r="P23" s="18" t="n"/>
+      <c r="P23" s="20" t="n"/>
       <c r="Q23" s="18" t="n"/>
       <c r="R23" s="18" t="n"/>
-      <c r="S23" s="20" t="n"/>
-      <c r="T23" s="47" t="n"/>
-      <c r="U23" s="18" t="n"/>
+      <c r="S23" s="18" t="n"/>
+      <c r="T23" s="20" t="n"/>
+      <c r="U23" s="47" t="n"/>
       <c r="V23" s="18" t="n"/>
       <c r="W23" s="18" t="n"/>
       <c r="X23" s="18" t="n"/>
-      <c r="Y23" s="48" t="n"/>
+      <c r="Y23" s="18" t="n"/>
       <c r="Z23" s="48" t="n"/>
-      <c r="AA23" s="18" t="n"/>
+      <c r="AA23" s="48" t="n"/>
       <c r="AB23" s="18" t="n"/>
       <c r="AC23" s="18" t="n"/>
       <c r="AD23" s="18" t="n"/>
       <c r="AE23" s="18" t="n"/>
-      <c r="AF23" s="20" t="n"/>
-      <c r="AG23" s="13">
-        <f>IF($A23="","",IF(AH23&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH23">
-        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($P23="",1,0)+IF($S23="",1,0)+IF($T23="",1,0)+IF($U23="",1,0)+IF($W23="",1,0)+IF($AA23="",1,0)+IF($AB23="",1,0)+IF(AND($N23="契約期間満了",$Q23=""),1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0)+IF(AND($AD23="外国",$AE23=""),1,0)+IF(AND($AD23="外国",$AF23=""),1,0))</f>
+      <c r="AF23" s="18" t="n"/>
+      <c r="AG23" s="18" t="n"/>
+      <c r="AH23" s="20" t="n"/>
+      <c r="AI23" s="13">
+        <f>IF($A23="","",IF(AJ23&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ23">
+        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($Q23="",1,0)+IF($T23="",1,0)+IF($U23="",1,0)+IF($V23="",1,0)+IF($X23="",1,0)+IF($AB23="",1,0)+IF($AD23="",1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0)+IF(AND($N23="契約期間満了",$S23=""),1,0)+IF(AND($AF23="外国",$AG23=""),1,0)+IF(AND($AF23="外国",$AH23=""),1,0)+IF(AND($AB23="未回収",$AC23=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2822,29 +2919,31 @@
       </c>
       <c r="N24" s="18" t="n"/>
       <c r="O24" s="18" t="n"/>
-      <c r="P24" s="18" t="n"/>
+      <c r="P24" s="20" t="n"/>
       <c r="Q24" s="18" t="n"/>
       <c r="R24" s="18" t="n"/>
-      <c r="S24" s="20" t="n"/>
-      <c r="T24" s="47" t="n"/>
-      <c r="U24" s="18" t="n"/>
+      <c r="S24" s="18" t="n"/>
+      <c r="T24" s="20" t="n"/>
+      <c r="U24" s="47" t="n"/>
       <c r="V24" s="18" t="n"/>
       <c r="W24" s="18" t="n"/>
       <c r="X24" s="18" t="n"/>
-      <c r="Y24" s="48" t="n"/>
+      <c r="Y24" s="18" t="n"/>
       <c r="Z24" s="48" t="n"/>
-      <c r="AA24" s="18" t="n"/>
+      <c r="AA24" s="48" t="n"/>
       <c r="AB24" s="18" t="n"/>
       <c r="AC24" s="18" t="n"/>
       <c r="AD24" s="18" t="n"/>
       <c r="AE24" s="18" t="n"/>
-      <c r="AF24" s="20" t="n"/>
-      <c r="AG24" s="13">
-        <f>IF($A24="","",IF(AH24&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH24">
-        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($P24="",1,0)+IF($S24="",1,0)+IF($T24="",1,0)+IF($U24="",1,0)+IF($W24="",1,0)+IF($AA24="",1,0)+IF($AB24="",1,0)+IF(AND($N24="契約期間満了",$Q24=""),1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0)+IF(AND($AD24="外国",$AE24=""),1,0)+IF(AND($AD24="外国",$AF24=""),1,0))</f>
+      <c r="AF24" s="18" t="n"/>
+      <c r="AG24" s="18" t="n"/>
+      <c r="AH24" s="20" t="n"/>
+      <c r="AI24" s="13">
+        <f>IF($A24="","",IF(AJ24&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ24">
+        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($Q24="",1,0)+IF($T24="",1,0)+IF($U24="",1,0)+IF($V24="",1,0)+IF($X24="",1,0)+IF($AB24="",1,0)+IF($AD24="",1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0)+IF(AND($N24="契約期間満了",$S24=""),1,0)+IF(AND($AF24="外国",$AG24=""),1,0)+IF(AND($AF24="外国",$AH24=""),1,0)+IF(AND($AB24="未回収",$AC24=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2867,29 +2966,31 @@
       </c>
       <c r="N25" s="18" t="n"/>
       <c r="O25" s="18" t="n"/>
-      <c r="P25" s="18" t="n"/>
+      <c r="P25" s="20" t="n"/>
       <c r="Q25" s="18" t="n"/>
       <c r="R25" s="18" t="n"/>
-      <c r="S25" s="20" t="n"/>
-      <c r="T25" s="47" t="n"/>
-      <c r="U25" s="18" t="n"/>
+      <c r="S25" s="18" t="n"/>
+      <c r="T25" s="20" t="n"/>
+      <c r="U25" s="47" t="n"/>
       <c r="V25" s="18" t="n"/>
       <c r="W25" s="18" t="n"/>
       <c r="X25" s="18" t="n"/>
-      <c r="Y25" s="48" t="n"/>
+      <c r="Y25" s="18" t="n"/>
       <c r="Z25" s="48" t="n"/>
-      <c r="AA25" s="18" t="n"/>
+      <c r="AA25" s="48" t="n"/>
       <c r="AB25" s="18" t="n"/>
       <c r="AC25" s="18" t="n"/>
       <c r="AD25" s="18" t="n"/>
       <c r="AE25" s="18" t="n"/>
-      <c r="AF25" s="20" t="n"/>
-      <c r="AG25" s="13">
-        <f>IF($A25="","",IF(AH25&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH25">
-        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($P25="",1,0)+IF($S25="",1,0)+IF($T25="",1,0)+IF($U25="",1,0)+IF($W25="",1,0)+IF($AA25="",1,0)+IF($AB25="",1,0)+IF(AND($N25="契約期間満了",$Q25=""),1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0)+IF(AND($AD25="外国",$AE25=""),1,0)+IF(AND($AD25="外国",$AF25=""),1,0))</f>
+      <c r="AF25" s="18" t="n"/>
+      <c r="AG25" s="18" t="n"/>
+      <c r="AH25" s="20" t="n"/>
+      <c r="AI25" s="13">
+        <f>IF($A25="","",IF(AJ25&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ25">
+        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($Q25="",1,0)+IF($T25="",1,0)+IF($U25="",1,0)+IF($V25="",1,0)+IF($X25="",1,0)+IF($AB25="",1,0)+IF($AD25="",1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0)+IF(AND($N25="契約期間満了",$S25=""),1,0)+IF(AND($AF25="外国",$AG25=""),1,0)+IF(AND($AF25="外国",$AH25=""),1,0)+IF(AND($AB25="未回収",$AC25=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2912,29 +3013,31 @@
       </c>
       <c r="N26" s="18" t="n"/>
       <c r="O26" s="18" t="n"/>
-      <c r="P26" s="18" t="n"/>
+      <c r="P26" s="20" t="n"/>
       <c r="Q26" s="18" t="n"/>
       <c r="R26" s="18" t="n"/>
-      <c r="S26" s="20" t="n"/>
-      <c r="T26" s="47" t="n"/>
-      <c r="U26" s="18" t="n"/>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="20" t="n"/>
+      <c r="U26" s="47" t="n"/>
       <c r="V26" s="18" t="n"/>
       <c r="W26" s="18" t="n"/>
       <c r="X26" s="18" t="n"/>
-      <c r="Y26" s="48" t="n"/>
+      <c r="Y26" s="18" t="n"/>
       <c r="Z26" s="48" t="n"/>
-      <c r="AA26" s="18" t="n"/>
+      <c r="AA26" s="48" t="n"/>
       <c r="AB26" s="18" t="n"/>
       <c r="AC26" s="18" t="n"/>
       <c r="AD26" s="18" t="n"/>
       <c r="AE26" s="18" t="n"/>
-      <c r="AF26" s="20" t="n"/>
-      <c r="AG26" s="13">
-        <f>IF($A26="","",IF(AH26&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH26">
-        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($P26="",1,0)+IF($S26="",1,0)+IF($T26="",1,0)+IF($U26="",1,0)+IF($W26="",1,0)+IF($AA26="",1,0)+IF($AB26="",1,0)+IF(AND($N26="契約期間満了",$Q26=""),1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0)+IF(AND($AD26="外国",$AE26=""),1,0)+IF(AND($AD26="外国",$AF26=""),1,0))</f>
+      <c r="AF26" s="18" t="n"/>
+      <c r="AG26" s="18" t="n"/>
+      <c r="AH26" s="20" t="n"/>
+      <c r="AI26" s="13">
+        <f>IF($A26="","",IF(AJ26&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ26">
+        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($Q26="",1,0)+IF($T26="",1,0)+IF($U26="",1,0)+IF($V26="",1,0)+IF($X26="",1,0)+IF($AB26="",1,0)+IF($AD26="",1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0)+IF(AND($N26="契約期間満了",$S26=""),1,0)+IF(AND($AF26="外国",$AG26=""),1,0)+IF(AND($AF26="外国",$AH26=""),1,0)+IF(AND($AB26="未回収",$AC26=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2957,29 +3060,31 @@
       </c>
       <c r="N27" s="18" t="n"/>
       <c r="O27" s="18" t="n"/>
-      <c r="P27" s="18" t="n"/>
+      <c r="P27" s="20" t="n"/>
       <c r="Q27" s="18" t="n"/>
       <c r="R27" s="18" t="n"/>
-      <c r="S27" s="20" t="n"/>
-      <c r="T27" s="47" t="n"/>
-      <c r="U27" s="18" t="n"/>
+      <c r="S27" s="18" t="n"/>
+      <c r="T27" s="20" t="n"/>
+      <c r="U27" s="47" t="n"/>
       <c r="V27" s="18" t="n"/>
       <c r="W27" s="18" t="n"/>
       <c r="X27" s="18" t="n"/>
-      <c r="Y27" s="48" t="n"/>
+      <c r="Y27" s="18" t="n"/>
       <c r="Z27" s="48" t="n"/>
-      <c r="AA27" s="18" t="n"/>
+      <c r="AA27" s="48" t="n"/>
       <c r="AB27" s="18" t="n"/>
       <c r="AC27" s="18" t="n"/>
       <c r="AD27" s="18" t="n"/>
       <c r="AE27" s="18" t="n"/>
-      <c r="AF27" s="20" t="n"/>
-      <c r="AG27" s="13">
-        <f>IF($A27="","",IF(AH27&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH27">
-        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($P27="",1,0)+IF($S27="",1,0)+IF($T27="",1,0)+IF($U27="",1,0)+IF($W27="",1,0)+IF($AA27="",1,0)+IF($AB27="",1,0)+IF(AND($N27="契約期間満了",$Q27=""),1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0)+IF(AND($AD27="外国",$AE27=""),1,0)+IF(AND($AD27="外国",$AF27=""),1,0))</f>
+      <c r="AF27" s="18" t="n"/>
+      <c r="AG27" s="18" t="n"/>
+      <c r="AH27" s="20" t="n"/>
+      <c r="AI27" s="13">
+        <f>IF($A27="","",IF(AJ27&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ27">
+        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($Q27="",1,0)+IF($T27="",1,0)+IF($U27="",1,0)+IF($V27="",1,0)+IF($X27="",1,0)+IF($AB27="",1,0)+IF($AD27="",1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0)+IF(AND($N27="契約期間満了",$S27=""),1,0)+IF(AND($AF27="外国",$AG27=""),1,0)+IF(AND($AF27="外国",$AH27=""),1,0)+IF(AND($AB27="未回収",$AC27=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3002,29 +3107,31 @@
       </c>
       <c r="N28" s="18" t="n"/>
       <c r="O28" s="18" t="n"/>
-      <c r="P28" s="18" t="n"/>
+      <c r="P28" s="20" t="n"/>
       <c r="Q28" s="18" t="n"/>
       <c r="R28" s="18" t="n"/>
-      <c r="S28" s="20" t="n"/>
-      <c r="T28" s="47" t="n"/>
-      <c r="U28" s="18" t="n"/>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="20" t="n"/>
+      <c r="U28" s="47" t="n"/>
       <c r="V28" s="18" t="n"/>
       <c r="W28" s="18" t="n"/>
       <c r="X28" s="18" t="n"/>
-      <c r="Y28" s="48" t="n"/>
+      <c r="Y28" s="18" t="n"/>
       <c r="Z28" s="48" t="n"/>
-      <c r="AA28" s="18" t="n"/>
+      <c r="AA28" s="48" t="n"/>
       <c r="AB28" s="18" t="n"/>
       <c r="AC28" s="18" t="n"/>
       <c r="AD28" s="18" t="n"/>
       <c r="AE28" s="18" t="n"/>
-      <c r="AF28" s="20" t="n"/>
-      <c r="AG28" s="13">
-        <f>IF($A28="","",IF(AH28&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH28">
-        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($P28="",1,0)+IF($S28="",1,0)+IF($T28="",1,0)+IF($U28="",1,0)+IF($W28="",1,0)+IF($AA28="",1,0)+IF($AB28="",1,0)+IF(AND($N28="契約期間満了",$Q28=""),1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0)+IF(AND($AD28="外国",$AE28=""),1,0)+IF(AND($AD28="外国",$AF28=""),1,0))</f>
+      <c r="AF28" s="18" t="n"/>
+      <c r="AG28" s="18" t="n"/>
+      <c r="AH28" s="20" t="n"/>
+      <c r="AI28" s="13">
+        <f>IF($A28="","",IF(AJ28&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ28">
+        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($Q28="",1,0)+IF($T28="",1,0)+IF($U28="",1,0)+IF($V28="",1,0)+IF($X28="",1,0)+IF($AB28="",1,0)+IF($AD28="",1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0)+IF(AND($N28="契約期間満了",$S28=""),1,0)+IF(AND($AF28="外国",$AG28=""),1,0)+IF(AND($AF28="外国",$AH28=""),1,0)+IF(AND($AB28="未回収",$AC28=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3047,29 +3154,31 @@
       </c>
       <c r="N29" s="18" t="n"/>
       <c r="O29" s="18" t="n"/>
-      <c r="P29" s="18" t="n"/>
+      <c r="P29" s="20" t="n"/>
       <c r="Q29" s="18" t="n"/>
       <c r="R29" s="18" t="n"/>
-      <c r="S29" s="20" t="n"/>
-      <c r="T29" s="47" t="n"/>
-      <c r="U29" s="18" t="n"/>
+      <c r="S29" s="18" t="n"/>
+      <c r="T29" s="20" t="n"/>
+      <c r="U29" s="47" t="n"/>
       <c r="V29" s="18" t="n"/>
       <c r="W29" s="18" t="n"/>
       <c r="X29" s="18" t="n"/>
-      <c r="Y29" s="48" t="n"/>
+      <c r="Y29" s="18" t="n"/>
       <c r="Z29" s="48" t="n"/>
-      <c r="AA29" s="18" t="n"/>
+      <c r="AA29" s="48" t="n"/>
       <c r="AB29" s="18" t="n"/>
       <c r="AC29" s="18" t="n"/>
       <c r="AD29" s="18" t="n"/>
       <c r="AE29" s="18" t="n"/>
-      <c r="AF29" s="20" t="n"/>
-      <c r="AG29" s="13">
-        <f>IF($A29="","",IF(AH29&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH29">
-        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($P29="",1,0)+IF($S29="",1,0)+IF($T29="",1,0)+IF($U29="",1,0)+IF($W29="",1,0)+IF($AA29="",1,0)+IF($AB29="",1,0)+IF(AND($N29="契約期間満了",$Q29=""),1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0)+IF(AND($AD29="外国",$AE29=""),1,0)+IF(AND($AD29="外国",$AF29=""),1,0))</f>
+      <c r="AF29" s="18" t="n"/>
+      <c r="AG29" s="18" t="n"/>
+      <c r="AH29" s="20" t="n"/>
+      <c r="AI29" s="13">
+        <f>IF($A29="","",IF(AJ29&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ29">
+        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($Q29="",1,0)+IF($T29="",1,0)+IF($U29="",1,0)+IF($V29="",1,0)+IF($X29="",1,0)+IF($AB29="",1,0)+IF($AD29="",1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0)+IF(AND($N29="契約期間満了",$S29=""),1,0)+IF(AND($AF29="外国",$AG29=""),1,0)+IF(AND($AF29="外国",$AH29=""),1,0)+IF(AND($AB29="未回収",$AC29=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3092,29 +3201,31 @@
       </c>
       <c r="N30" s="18" t="n"/>
       <c r="O30" s="18" t="n"/>
-      <c r="P30" s="18" t="n"/>
+      <c r="P30" s="20" t="n"/>
       <c r="Q30" s="18" t="n"/>
       <c r="R30" s="18" t="n"/>
-      <c r="S30" s="20" t="n"/>
-      <c r="T30" s="47" t="n"/>
-      <c r="U30" s="18" t="n"/>
+      <c r="S30" s="18" t="n"/>
+      <c r="T30" s="20" t="n"/>
+      <c r="U30" s="47" t="n"/>
       <c r="V30" s="18" t="n"/>
       <c r="W30" s="18" t="n"/>
       <c r="X30" s="18" t="n"/>
-      <c r="Y30" s="48" t="n"/>
+      <c r="Y30" s="18" t="n"/>
       <c r="Z30" s="48" t="n"/>
-      <c r="AA30" s="18" t="n"/>
+      <c r="AA30" s="48" t="n"/>
       <c r="AB30" s="18" t="n"/>
       <c r="AC30" s="18" t="n"/>
       <c r="AD30" s="18" t="n"/>
       <c r="AE30" s="18" t="n"/>
-      <c r="AF30" s="20" t="n"/>
-      <c r="AG30" s="13">
-        <f>IF($A30="","",IF(AH30&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH30">
-        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($P30="",1,0)+IF($S30="",1,0)+IF($T30="",1,0)+IF($U30="",1,0)+IF($W30="",1,0)+IF($AA30="",1,0)+IF($AB30="",1,0)+IF(AND($N30="契約期間満了",$Q30=""),1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0)+IF(AND($AD30="外国",$AE30=""),1,0)+IF(AND($AD30="外国",$AF30=""),1,0))</f>
+      <c r="AF30" s="18" t="n"/>
+      <c r="AG30" s="18" t="n"/>
+      <c r="AH30" s="20" t="n"/>
+      <c r="AI30" s="13">
+        <f>IF($A30="","",IF(AJ30&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ30">
+        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($Q30="",1,0)+IF($T30="",1,0)+IF($U30="",1,0)+IF($V30="",1,0)+IF($X30="",1,0)+IF($AB30="",1,0)+IF($AD30="",1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0)+IF(AND($N30="契約期間満了",$S30=""),1,0)+IF(AND($AF30="外国",$AG30=""),1,0)+IF(AND($AF30="外国",$AH30=""),1,0)+IF(AND($AB30="未回収",$AC30=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3137,29 +3248,31 @@
       </c>
       <c r="N31" s="18" t="n"/>
       <c r="O31" s="18" t="n"/>
-      <c r="P31" s="18" t="n"/>
+      <c r="P31" s="20" t="n"/>
       <c r="Q31" s="18" t="n"/>
       <c r="R31" s="18" t="n"/>
-      <c r="S31" s="20" t="n"/>
-      <c r="T31" s="47" t="n"/>
-      <c r="U31" s="18" t="n"/>
+      <c r="S31" s="18" t="n"/>
+      <c r="T31" s="20" t="n"/>
+      <c r="U31" s="47" t="n"/>
       <c r="V31" s="18" t="n"/>
       <c r="W31" s="18" t="n"/>
       <c r="X31" s="18" t="n"/>
-      <c r="Y31" s="48" t="n"/>
+      <c r="Y31" s="18" t="n"/>
       <c r="Z31" s="48" t="n"/>
-      <c r="AA31" s="18" t="n"/>
+      <c r="AA31" s="48" t="n"/>
       <c r="AB31" s="18" t="n"/>
       <c r="AC31" s="18" t="n"/>
       <c r="AD31" s="18" t="n"/>
       <c r="AE31" s="18" t="n"/>
-      <c r="AF31" s="20" t="n"/>
-      <c r="AG31" s="13">
-        <f>IF($A31="","",IF(AH31&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH31">
-        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($P31="",1,0)+IF($S31="",1,0)+IF($T31="",1,0)+IF($U31="",1,0)+IF($W31="",1,0)+IF($AA31="",1,0)+IF($AB31="",1,0)+IF(AND($N31="契約期間満了",$Q31=""),1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0)+IF(AND($AD31="外国",$AE31=""),1,0)+IF(AND($AD31="外国",$AF31=""),1,0))</f>
+      <c r="AF31" s="18" t="n"/>
+      <c r="AG31" s="18" t="n"/>
+      <c r="AH31" s="20" t="n"/>
+      <c r="AI31" s="13">
+        <f>IF($A31="","",IF(AJ31&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ31">
+        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($Q31="",1,0)+IF($T31="",1,0)+IF($U31="",1,0)+IF($V31="",1,0)+IF($X31="",1,0)+IF($AB31="",1,0)+IF($AD31="",1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0)+IF(AND($N31="契約期間満了",$S31=""),1,0)+IF(AND($AF31="外国",$AG31=""),1,0)+IF(AND($AF31="外国",$AH31=""),1,0)+IF(AND($AB31="未回収",$AC31=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3182,29 +3295,31 @@
       </c>
       <c r="N32" s="18" t="n"/>
       <c r="O32" s="18" t="n"/>
-      <c r="P32" s="18" t="n"/>
+      <c r="P32" s="20" t="n"/>
       <c r="Q32" s="18" t="n"/>
       <c r="R32" s="18" t="n"/>
-      <c r="S32" s="20" t="n"/>
-      <c r="T32" s="47" t="n"/>
-      <c r="U32" s="18" t="n"/>
+      <c r="S32" s="18" t="n"/>
+      <c r="T32" s="20" t="n"/>
+      <c r="U32" s="47" t="n"/>
       <c r="V32" s="18" t="n"/>
       <c r="W32" s="18" t="n"/>
       <c r="X32" s="18" t="n"/>
-      <c r="Y32" s="48" t="n"/>
+      <c r="Y32" s="18" t="n"/>
       <c r="Z32" s="48" t="n"/>
-      <c r="AA32" s="18" t="n"/>
+      <c r="AA32" s="48" t="n"/>
       <c r="AB32" s="18" t="n"/>
       <c r="AC32" s="18" t="n"/>
       <c r="AD32" s="18" t="n"/>
       <c r="AE32" s="18" t="n"/>
-      <c r="AF32" s="20" t="n"/>
-      <c r="AG32" s="13">
-        <f>IF($A32="","",IF(AH32&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH32">
-        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($P32="",1,0)+IF($S32="",1,0)+IF($T32="",1,0)+IF($U32="",1,0)+IF($W32="",1,0)+IF($AA32="",1,0)+IF($AB32="",1,0)+IF(AND($N32="契約期間満了",$Q32=""),1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0)+IF(AND($AD32="外国",$AE32=""),1,0)+IF(AND($AD32="外国",$AF32=""),1,0))</f>
+      <c r="AF32" s="18" t="n"/>
+      <c r="AG32" s="18" t="n"/>
+      <c r="AH32" s="20" t="n"/>
+      <c r="AI32" s="13">
+        <f>IF($A32="","",IF(AJ32&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ32">
+        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($Q32="",1,0)+IF($T32="",1,0)+IF($U32="",1,0)+IF($V32="",1,0)+IF($X32="",1,0)+IF($AB32="",1,0)+IF($AD32="",1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0)+IF(AND($N32="契約期間満了",$S32=""),1,0)+IF(AND($AF32="外国",$AG32=""),1,0)+IF(AND($AF32="外国",$AH32=""),1,0)+IF(AND($AB32="未回収",$AC32=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3227,29 +3342,31 @@
       </c>
       <c r="N33" s="18" t="n"/>
       <c r="O33" s="18" t="n"/>
-      <c r="P33" s="18" t="n"/>
+      <c r="P33" s="20" t="n"/>
       <c r="Q33" s="18" t="n"/>
       <c r="R33" s="18" t="n"/>
-      <c r="S33" s="20" t="n"/>
-      <c r="T33" s="47" t="n"/>
-      <c r="U33" s="18" t="n"/>
+      <c r="S33" s="18" t="n"/>
+      <c r="T33" s="20" t="n"/>
+      <c r="U33" s="47" t="n"/>
       <c r="V33" s="18" t="n"/>
       <c r="W33" s="18" t="n"/>
       <c r="X33" s="18" t="n"/>
-      <c r="Y33" s="48" t="n"/>
+      <c r="Y33" s="18" t="n"/>
       <c r="Z33" s="48" t="n"/>
-      <c r="AA33" s="18" t="n"/>
+      <c r="AA33" s="48" t="n"/>
       <c r="AB33" s="18" t="n"/>
       <c r="AC33" s="18" t="n"/>
       <c r="AD33" s="18" t="n"/>
       <c r="AE33" s="18" t="n"/>
-      <c r="AF33" s="20" t="n"/>
-      <c r="AG33" s="13">
-        <f>IF($A33="","",IF(AH33&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH33">
-        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($P33="",1,0)+IF($S33="",1,0)+IF($T33="",1,0)+IF($U33="",1,0)+IF($W33="",1,0)+IF($AA33="",1,0)+IF($AB33="",1,0)+IF(AND($N33="契約期間満了",$Q33=""),1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0)+IF(AND($AD33="外国",$AE33=""),1,0)+IF(AND($AD33="外国",$AF33=""),1,0))</f>
+      <c r="AF33" s="18" t="n"/>
+      <c r="AG33" s="18" t="n"/>
+      <c r="AH33" s="20" t="n"/>
+      <c r="AI33" s="13">
+        <f>IF($A33="","",IF(AJ33&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ33">
+        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($Q33="",1,0)+IF($T33="",1,0)+IF($U33="",1,0)+IF($V33="",1,0)+IF($X33="",1,0)+IF($AB33="",1,0)+IF($AD33="",1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0)+IF(AND($N33="契約期間満了",$S33=""),1,0)+IF(AND($AF33="外国",$AG33=""),1,0)+IF(AND($AF33="外国",$AH33=""),1,0)+IF(AND($AB33="未回収",$AC33=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3272,29 +3389,31 @@
       </c>
       <c r="N34" s="18" t="n"/>
       <c r="O34" s="18" t="n"/>
-      <c r="P34" s="18" t="n"/>
+      <c r="P34" s="20" t="n"/>
       <c r="Q34" s="18" t="n"/>
       <c r="R34" s="18" t="n"/>
-      <c r="S34" s="20" t="n"/>
-      <c r="T34" s="47" t="n"/>
-      <c r="U34" s="18" t="n"/>
+      <c r="S34" s="18" t="n"/>
+      <c r="T34" s="20" t="n"/>
+      <c r="U34" s="47" t="n"/>
       <c r="V34" s="18" t="n"/>
       <c r="W34" s="18" t="n"/>
       <c r="X34" s="18" t="n"/>
-      <c r="Y34" s="48" t="n"/>
+      <c r="Y34" s="18" t="n"/>
       <c r="Z34" s="48" t="n"/>
-      <c r="AA34" s="18" t="n"/>
+      <c r="AA34" s="48" t="n"/>
       <c r="AB34" s="18" t="n"/>
       <c r="AC34" s="18" t="n"/>
       <c r="AD34" s="18" t="n"/>
       <c r="AE34" s="18" t="n"/>
-      <c r="AF34" s="20" t="n"/>
-      <c r="AG34" s="13">
-        <f>IF($A34="","",IF(AH34&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH34">
-        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($P34="",1,0)+IF($S34="",1,0)+IF($T34="",1,0)+IF($U34="",1,0)+IF($W34="",1,0)+IF($AA34="",1,0)+IF($AB34="",1,0)+IF(AND($N34="契約期間満了",$Q34=""),1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0)+IF(AND($AD34="外国",$AE34=""),1,0)+IF(AND($AD34="外国",$AF34=""),1,0))</f>
+      <c r="AF34" s="18" t="n"/>
+      <c r="AG34" s="18" t="n"/>
+      <c r="AH34" s="20" t="n"/>
+      <c r="AI34" s="13">
+        <f>IF($A34="","",IF(AJ34&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ34">
+        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($Q34="",1,0)+IF($T34="",1,0)+IF($U34="",1,0)+IF($V34="",1,0)+IF($X34="",1,0)+IF($AB34="",1,0)+IF($AD34="",1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0)+IF(AND($N34="契約期間満了",$S34=""),1,0)+IF(AND($AF34="外国",$AG34=""),1,0)+IF(AND($AF34="外国",$AH34=""),1,0)+IF(AND($AB34="未回収",$AC34=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3317,29 +3436,31 @@
       </c>
       <c r="N35" s="18" t="n"/>
       <c r="O35" s="18" t="n"/>
-      <c r="P35" s="18" t="n"/>
+      <c r="P35" s="20" t="n"/>
       <c r="Q35" s="18" t="n"/>
       <c r="R35" s="18" t="n"/>
-      <c r="S35" s="20" t="n"/>
-      <c r="T35" s="47" t="n"/>
-      <c r="U35" s="18" t="n"/>
+      <c r="S35" s="18" t="n"/>
+      <c r="T35" s="20" t="n"/>
+      <c r="U35" s="47" t="n"/>
       <c r="V35" s="18" t="n"/>
       <c r="W35" s="18" t="n"/>
       <c r="X35" s="18" t="n"/>
-      <c r="Y35" s="48" t="n"/>
+      <c r="Y35" s="18" t="n"/>
       <c r="Z35" s="48" t="n"/>
-      <c r="AA35" s="18" t="n"/>
+      <c r="AA35" s="48" t="n"/>
       <c r="AB35" s="18" t="n"/>
       <c r="AC35" s="18" t="n"/>
       <c r="AD35" s="18" t="n"/>
       <c r="AE35" s="18" t="n"/>
-      <c r="AF35" s="20" t="n"/>
-      <c r="AG35" s="13">
-        <f>IF($A35="","",IF(AH35&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH35">
-        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($P35="",1,0)+IF($S35="",1,0)+IF($T35="",1,0)+IF($U35="",1,0)+IF($W35="",1,0)+IF($AA35="",1,0)+IF($AB35="",1,0)+IF(AND($N35="契約期間満了",$Q35=""),1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0)+IF(AND($AD35="外国",$AE35=""),1,0)+IF(AND($AD35="外国",$AF35=""),1,0))</f>
+      <c r="AF35" s="18" t="n"/>
+      <c r="AG35" s="18" t="n"/>
+      <c r="AH35" s="20" t="n"/>
+      <c r="AI35" s="13">
+        <f>IF($A35="","",IF(AJ35&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ35">
+        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($Q35="",1,0)+IF($T35="",1,0)+IF($U35="",1,0)+IF($V35="",1,0)+IF($X35="",1,0)+IF($AB35="",1,0)+IF($AD35="",1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0)+IF(AND($N35="契約期間満了",$S35=""),1,0)+IF(AND($AF35="外国",$AG35=""),1,0)+IF(AND($AF35="外国",$AH35=""),1,0)+IF(AND($AB35="未回収",$AC35=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3362,29 +3483,31 @@
       </c>
       <c r="N36" s="18" t="n"/>
       <c r="O36" s="18" t="n"/>
-      <c r="P36" s="18" t="n"/>
+      <c r="P36" s="20" t="n"/>
       <c r="Q36" s="18" t="n"/>
       <c r="R36" s="18" t="n"/>
-      <c r="S36" s="20" t="n"/>
-      <c r="T36" s="47" t="n"/>
-      <c r="U36" s="18" t="n"/>
+      <c r="S36" s="18" t="n"/>
+      <c r="T36" s="20" t="n"/>
+      <c r="U36" s="47" t="n"/>
       <c r="V36" s="18" t="n"/>
       <c r="W36" s="18" t="n"/>
       <c r="X36" s="18" t="n"/>
-      <c r="Y36" s="48" t="n"/>
+      <c r="Y36" s="18" t="n"/>
       <c r="Z36" s="48" t="n"/>
-      <c r="AA36" s="18" t="n"/>
+      <c r="AA36" s="48" t="n"/>
       <c r="AB36" s="18" t="n"/>
       <c r="AC36" s="18" t="n"/>
       <c r="AD36" s="18" t="n"/>
       <c r="AE36" s="18" t="n"/>
-      <c r="AF36" s="20" t="n"/>
-      <c r="AG36" s="13">
-        <f>IF($A36="","",IF(AH36&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH36">
-        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($P36="",1,0)+IF($S36="",1,0)+IF($T36="",1,0)+IF($U36="",1,0)+IF($W36="",1,0)+IF($AA36="",1,0)+IF($AB36="",1,0)+IF(AND($N36="契約期間満了",$Q36=""),1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0)+IF(AND($AD36="外国",$AE36=""),1,0)+IF(AND($AD36="外国",$AF36=""),1,0))</f>
+      <c r="AF36" s="18" t="n"/>
+      <c r="AG36" s="18" t="n"/>
+      <c r="AH36" s="20" t="n"/>
+      <c r="AI36" s="13">
+        <f>IF($A36="","",IF(AJ36&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ36">
+        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($Q36="",1,0)+IF($T36="",1,0)+IF($U36="",1,0)+IF($V36="",1,0)+IF($X36="",1,0)+IF($AB36="",1,0)+IF($AD36="",1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0)+IF(AND($N36="契約期間満了",$S36=""),1,0)+IF(AND($AF36="外国",$AG36=""),1,0)+IF(AND($AF36="外国",$AH36=""),1,0)+IF(AND($AB36="未回収",$AC36=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3407,29 +3530,31 @@
       </c>
       <c r="N37" s="18" t="n"/>
       <c r="O37" s="18" t="n"/>
-      <c r="P37" s="18" t="n"/>
+      <c r="P37" s="20" t="n"/>
       <c r="Q37" s="18" t="n"/>
       <c r="R37" s="18" t="n"/>
-      <c r="S37" s="20" t="n"/>
-      <c r="T37" s="47" t="n"/>
-      <c r="U37" s="18" t="n"/>
+      <c r="S37" s="18" t="n"/>
+      <c r="T37" s="20" t="n"/>
+      <c r="U37" s="47" t="n"/>
       <c r="V37" s="18" t="n"/>
       <c r="W37" s="18" t="n"/>
       <c r="X37" s="18" t="n"/>
-      <c r="Y37" s="48" t="n"/>
+      <c r="Y37" s="18" t="n"/>
       <c r="Z37" s="48" t="n"/>
-      <c r="AA37" s="18" t="n"/>
+      <c r="AA37" s="48" t="n"/>
       <c r="AB37" s="18" t="n"/>
       <c r="AC37" s="18" t="n"/>
       <c r="AD37" s="18" t="n"/>
       <c r="AE37" s="18" t="n"/>
-      <c r="AF37" s="20" t="n"/>
-      <c r="AG37" s="13">
-        <f>IF($A37="","",IF(AH37&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH37">
-        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($P37="",1,0)+IF($S37="",1,0)+IF($T37="",1,0)+IF($U37="",1,0)+IF($W37="",1,0)+IF($AA37="",1,0)+IF($AB37="",1,0)+IF(AND($N37="契約期間満了",$Q37=""),1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0)+IF(AND($AD37="外国",$AE37=""),1,0)+IF(AND($AD37="外国",$AF37=""),1,0))</f>
+      <c r="AF37" s="18" t="n"/>
+      <c r="AG37" s="18" t="n"/>
+      <c r="AH37" s="20" t="n"/>
+      <c r="AI37" s="13">
+        <f>IF($A37="","",IF(AJ37&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ37">
+        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($Q37="",1,0)+IF($T37="",1,0)+IF($U37="",1,0)+IF($V37="",1,0)+IF($X37="",1,0)+IF($AB37="",1,0)+IF($AD37="",1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0)+IF(AND($N37="契約期間満了",$S37=""),1,0)+IF(AND($AF37="外国",$AG37=""),1,0)+IF(AND($AF37="外国",$AH37=""),1,0)+IF(AND($AB37="未回収",$AC37=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3452,29 +3577,31 @@
       </c>
       <c r="N38" s="18" t="n"/>
       <c r="O38" s="18" t="n"/>
-      <c r="P38" s="18" t="n"/>
+      <c r="P38" s="20" t="n"/>
       <c r="Q38" s="18" t="n"/>
       <c r="R38" s="18" t="n"/>
-      <c r="S38" s="20" t="n"/>
-      <c r="T38" s="47" t="n"/>
-      <c r="U38" s="18" t="n"/>
+      <c r="S38" s="18" t="n"/>
+      <c r="T38" s="20" t="n"/>
+      <c r="U38" s="47" t="n"/>
       <c r="V38" s="18" t="n"/>
       <c r="W38" s="18" t="n"/>
       <c r="X38" s="18" t="n"/>
-      <c r="Y38" s="48" t="n"/>
+      <c r="Y38" s="18" t="n"/>
       <c r="Z38" s="48" t="n"/>
-      <c r="AA38" s="18" t="n"/>
+      <c r="AA38" s="48" t="n"/>
       <c r="AB38" s="18" t="n"/>
       <c r="AC38" s="18" t="n"/>
       <c r="AD38" s="18" t="n"/>
       <c r="AE38" s="18" t="n"/>
-      <c r="AF38" s="20" t="n"/>
-      <c r="AG38" s="13">
-        <f>IF($A38="","",IF(AH38&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH38">
-        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($P38="",1,0)+IF($S38="",1,0)+IF($T38="",1,0)+IF($U38="",1,0)+IF($W38="",1,0)+IF($AA38="",1,0)+IF($AB38="",1,0)+IF(AND($N38="契約期間満了",$Q38=""),1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0)+IF(AND($AD38="外国",$AE38=""),1,0)+IF(AND($AD38="外国",$AF38=""),1,0))</f>
+      <c r="AF38" s="18" t="n"/>
+      <c r="AG38" s="18" t="n"/>
+      <c r="AH38" s="20" t="n"/>
+      <c r="AI38" s="13">
+        <f>IF($A38="","",IF(AJ38&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ38">
+        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($Q38="",1,0)+IF($T38="",1,0)+IF($U38="",1,0)+IF($V38="",1,0)+IF($X38="",1,0)+IF($AB38="",1,0)+IF($AD38="",1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0)+IF(AND($N38="契約期間満了",$S38=""),1,0)+IF(AND($AF38="外国",$AG38=""),1,0)+IF(AND($AF38="外国",$AH38=""),1,0)+IF(AND($AB38="未回収",$AC38=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3497,29 +3624,31 @@
       </c>
       <c r="N39" s="18" t="n"/>
       <c r="O39" s="18" t="n"/>
-      <c r="P39" s="18" t="n"/>
+      <c r="P39" s="20" t="n"/>
       <c r="Q39" s="18" t="n"/>
       <c r="R39" s="18" t="n"/>
-      <c r="S39" s="20" t="n"/>
-      <c r="T39" s="47" t="n"/>
-      <c r="U39" s="18" t="n"/>
+      <c r="S39" s="18" t="n"/>
+      <c r="T39" s="20" t="n"/>
+      <c r="U39" s="47" t="n"/>
       <c r="V39" s="18" t="n"/>
       <c r="W39" s="18" t="n"/>
       <c r="X39" s="18" t="n"/>
-      <c r="Y39" s="48" t="n"/>
+      <c r="Y39" s="18" t="n"/>
       <c r="Z39" s="48" t="n"/>
-      <c r="AA39" s="18" t="n"/>
+      <c r="AA39" s="48" t="n"/>
       <c r="AB39" s="18" t="n"/>
       <c r="AC39" s="18" t="n"/>
       <c r="AD39" s="18" t="n"/>
       <c r="AE39" s="18" t="n"/>
-      <c r="AF39" s="20" t="n"/>
-      <c r="AG39" s="13">
-        <f>IF($A39="","",IF(AH39&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH39">
-        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($P39="",1,0)+IF($S39="",1,0)+IF($T39="",1,0)+IF($U39="",1,0)+IF($W39="",1,0)+IF($AA39="",1,0)+IF($AB39="",1,0)+IF(AND($N39="契約期間満了",$Q39=""),1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0)+IF(AND($AD39="外国",$AE39=""),1,0)+IF(AND($AD39="外国",$AF39=""),1,0))</f>
+      <c r="AF39" s="18" t="n"/>
+      <c r="AG39" s="18" t="n"/>
+      <c r="AH39" s="20" t="n"/>
+      <c r="AI39" s="13">
+        <f>IF($A39="","",IF(AJ39&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ39">
+        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($Q39="",1,0)+IF($T39="",1,0)+IF($U39="",1,0)+IF($V39="",1,0)+IF($X39="",1,0)+IF($AB39="",1,0)+IF($AD39="",1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0)+IF(AND($N39="契約期間満了",$S39=""),1,0)+IF(AND($AF39="外国",$AG39=""),1,0)+IF(AND($AF39="外国",$AH39=""),1,0)+IF(AND($AB39="未回収",$AC39=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3542,29 +3671,31 @@
       </c>
       <c r="N40" s="18" t="n"/>
       <c r="O40" s="18" t="n"/>
-      <c r="P40" s="18" t="n"/>
+      <c r="P40" s="20" t="n"/>
       <c r="Q40" s="18" t="n"/>
       <c r="R40" s="18" t="n"/>
-      <c r="S40" s="20" t="n"/>
-      <c r="T40" s="47" t="n"/>
-      <c r="U40" s="18" t="n"/>
+      <c r="S40" s="18" t="n"/>
+      <c r="T40" s="20" t="n"/>
+      <c r="U40" s="47" t="n"/>
       <c r="V40" s="18" t="n"/>
       <c r="W40" s="18" t="n"/>
       <c r="X40" s="18" t="n"/>
-      <c r="Y40" s="48" t="n"/>
+      <c r="Y40" s="18" t="n"/>
       <c r="Z40" s="48" t="n"/>
-      <c r="AA40" s="18" t="n"/>
+      <c r="AA40" s="48" t="n"/>
       <c r="AB40" s="18" t="n"/>
       <c r="AC40" s="18" t="n"/>
       <c r="AD40" s="18" t="n"/>
       <c r="AE40" s="18" t="n"/>
-      <c r="AF40" s="20" t="n"/>
-      <c r="AG40" s="13">
-        <f>IF($A40="","",IF(AH40&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH40">
-        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($P40="",1,0)+IF($S40="",1,0)+IF($T40="",1,0)+IF($U40="",1,0)+IF($W40="",1,0)+IF($AA40="",1,0)+IF($AB40="",1,0)+IF(AND($N40="契約期間満了",$Q40=""),1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0)+IF(AND($AD40="外国",$AE40=""),1,0)+IF(AND($AD40="外国",$AF40=""),1,0))</f>
+      <c r="AF40" s="18" t="n"/>
+      <c r="AG40" s="18" t="n"/>
+      <c r="AH40" s="20" t="n"/>
+      <c r="AI40" s="13">
+        <f>IF($A40="","",IF(AJ40&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ40">
+        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($Q40="",1,0)+IF($T40="",1,0)+IF($U40="",1,0)+IF($V40="",1,0)+IF($X40="",1,0)+IF($AB40="",1,0)+IF($AD40="",1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0)+IF(AND($N40="契約期間満了",$S40=""),1,0)+IF(AND($AF40="外国",$AG40=""),1,0)+IF(AND($AF40="外国",$AH40=""),1,0)+IF(AND($AB40="未回収",$AC40=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3587,29 +3718,31 @@
       </c>
       <c r="N41" s="18" t="n"/>
       <c r="O41" s="18" t="n"/>
-      <c r="P41" s="18" t="n"/>
+      <c r="P41" s="20" t="n"/>
       <c r="Q41" s="18" t="n"/>
       <c r="R41" s="18" t="n"/>
-      <c r="S41" s="20" t="n"/>
-      <c r="T41" s="47" t="n"/>
-      <c r="U41" s="18" t="n"/>
+      <c r="S41" s="18" t="n"/>
+      <c r="T41" s="20" t="n"/>
+      <c r="U41" s="47" t="n"/>
       <c r="V41" s="18" t="n"/>
       <c r="W41" s="18" t="n"/>
       <c r="X41" s="18" t="n"/>
-      <c r="Y41" s="48" t="n"/>
+      <c r="Y41" s="18" t="n"/>
       <c r="Z41" s="48" t="n"/>
-      <c r="AA41" s="18" t="n"/>
+      <c r="AA41" s="48" t="n"/>
       <c r="AB41" s="18" t="n"/>
       <c r="AC41" s="18" t="n"/>
       <c r="AD41" s="18" t="n"/>
       <c r="AE41" s="18" t="n"/>
-      <c r="AF41" s="20" t="n"/>
-      <c r="AG41" s="13">
-        <f>IF($A41="","",IF(AH41&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH41">
-        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($P41="",1,0)+IF($S41="",1,0)+IF($T41="",1,0)+IF($U41="",1,0)+IF($W41="",1,0)+IF($AA41="",1,0)+IF($AB41="",1,0)+IF(AND($N41="契約期間満了",$Q41=""),1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0)+IF(AND($AD41="外国",$AE41=""),1,0)+IF(AND($AD41="外国",$AF41=""),1,0))</f>
+      <c r="AF41" s="18" t="n"/>
+      <c r="AG41" s="18" t="n"/>
+      <c r="AH41" s="20" t="n"/>
+      <c r="AI41" s="13">
+        <f>IF($A41="","",IF(AJ41&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ41">
+        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($Q41="",1,0)+IF($T41="",1,0)+IF($U41="",1,0)+IF($V41="",1,0)+IF($X41="",1,0)+IF($AB41="",1,0)+IF($AD41="",1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0)+IF(AND($N41="契約期間満了",$S41=""),1,0)+IF(AND($AF41="外国",$AG41=""),1,0)+IF(AND($AF41="外国",$AH41=""),1,0)+IF(AND($AB41="未回収",$AC41=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3632,29 +3765,31 @@
       </c>
       <c r="N42" s="18" t="n"/>
       <c r="O42" s="18" t="n"/>
-      <c r="P42" s="18" t="n"/>
+      <c r="P42" s="20" t="n"/>
       <c r="Q42" s="18" t="n"/>
       <c r="R42" s="18" t="n"/>
-      <c r="S42" s="20" t="n"/>
-      <c r="T42" s="47" t="n"/>
-      <c r="U42" s="18" t="n"/>
+      <c r="S42" s="18" t="n"/>
+      <c r="T42" s="20" t="n"/>
+      <c r="U42" s="47" t="n"/>
       <c r="V42" s="18" t="n"/>
       <c r="W42" s="18" t="n"/>
       <c r="X42" s="18" t="n"/>
-      <c r="Y42" s="48" t="n"/>
+      <c r="Y42" s="18" t="n"/>
       <c r="Z42" s="48" t="n"/>
-      <c r="AA42" s="18" t="n"/>
+      <c r="AA42" s="48" t="n"/>
       <c r="AB42" s="18" t="n"/>
       <c r="AC42" s="18" t="n"/>
       <c r="AD42" s="18" t="n"/>
       <c r="AE42" s="18" t="n"/>
-      <c r="AF42" s="20" t="n"/>
-      <c r="AG42" s="13">
-        <f>IF($A42="","",IF(AH42&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH42">
-        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($P42="",1,0)+IF($S42="",1,0)+IF($T42="",1,0)+IF($U42="",1,0)+IF($W42="",1,0)+IF($AA42="",1,0)+IF($AB42="",1,0)+IF(AND($N42="契約期間満了",$Q42=""),1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0)+IF(AND($AD42="外国",$AE42=""),1,0)+IF(AND($AD42="外国",$AF42=""),1,0))</f>
+      <c r="AF42" s="18" t="n"/>
+      <c r="AG42" s="18" t="n"/>
+      <c r="AH42" s="20" t="n"/>
+      <c r="AI42" s="13">
+        <f>IF($A42="","",IF(AJ42&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ42">
+        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($Q42="",1,0)+IF($T42="",1,0)+IF($U42="",1,0)+IF($V42="",1,0)+IF($X42="",1,0)+IF($AB42="",1,0)+IF($AD42="",1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0)+IF(AND($N42="契約期間満了",$S42=""),1,0)+IF(AND($AF42="外国",$AG42=""),1,0)+IF(AND($AF42="外国",$AH42=""),1,0)+IF(AND($AB42="未回収",$AC42=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3677,29 +3812,31 @@
       </c>
       <c r="N43" s="18" t="n"/>
       <c r="O43" s="18" t="n"/>
-      <c r="P43" s="18" t="n"/>
+      <c r="P43" s="20" t="n"/>
       <c r="Q43" s="18" t="n"/>
       <c r="R43" s="18" t="n"/>
-      <c r="S43" s="20" t="n"/>
-      <c r="T43" s="47" t="n"/>
-      <c r="U43" s="18" t="n"/>
+      <c r="S43" s="18" t="n"/>
+      <c r="T43" s="20" t="n"/>
+      <c r="U43" s="47" t="n"/>
       <c r="V43" s="18" t="n"/>
       <c r="W43" s="18" t="n"/>
       <c r="X43" s="18" t="n"/>
-      <c r="Y43" s="48" t="n"/>
+      <c r="Y43" s="18" t="n"/>
       <c r="Z43" s="48" t="n"/>
-      <c r="AA43" s="18" t="n"/>
+      <c r="AA43" s="48" t="n"/>
       <c r="AB43" s="18" t="n"/>
       <c r="AC43" s="18" t="n"/>
       <c r="AD43" s="18" t="n"/>
       <c r="AE43" s="18" t="n"/>
-      <c r="AF43" s="20" t="n"/>
-      <c r="AG43" s="13">
-        <f>IF($A43="","",IF(AH43&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH43">
-        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($P43="",1,0)+IF($S43="",1,0)+IF($T43="",1,0)+IF($U43="",1,0)+IF($W43="",1,0)+IF($AA43="",1,0)+IF($AB43="",1,0)+IF(AND($N43="契約期間満了",$Q43=""),1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0)+IF(AND($AD43="外国",$AE43=""),1,0)+IF(AND($AD43="外国",$AF43=""),1,0))</f>
+      <c r="AF43" s="18" t="n"/>
+      <c r="AG43" s="18" t="n"/>
+      <c r="AH43" s="20" t="n"/>
+      <c r="AI43" s="13">
+        <f>IF($A43="","",IF(AJ43&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ43">
+        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($Q43="",1,0)+IF($T43="",1,0)+IF($U43="",1,0)+IF($V43="",1,0)+IF($X43="",1,0)+IF($AB43="",1,0)+IF($AD43="",1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0)+IF(AND($N43="契約期間満了",$S43=""),1,0)+IF(AND($AF43="外国",$AG43=""),1,0)+IF(AND($AF43="外国",$AH43=""),1,0)+IF(AND($AB43="未回収",$AC43=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3722,29 +3859,31 @@
       </c>
       <c r="N44" s="18" t="n"/>
       <c r="O44" s="18" t="n"/>
-      <c r="P44" s="18" t="n"/>
+      <c r="P44" s="20" t="n"/>
       <c r="Q44" s="18" t="n"/>
       <c r="R44" s="18" t="n"/>
-      <c r="S44" s="20" t="n"/>
-      <c r="T44" s="47" t="n"/>
-      <c r="U44" s="18" t="n"/>
+      <c r="S44" s="18" t="n"/>
+      <c r="T44" s="20" t="n"/>
+      <c r="U44" s="47" t="n"/>
       <c r="V44" s="18" t="n"/>
       <c r="W44" s="18" t="n"/>
       <c r="X44" s="18" t="n"/>
-      <c r="Y44" s="48" t="n"/>
+      <c r="Y44" s="18" t="n"/>
       <c r="Z44" s="48" t="n"/>
-      <c r="AA44" s="18" t="n"/>
+      <c r="AA44" s="48" t="n"/>
       <c r="AB44" s="18" t="n"/>
       <c r="AC44" s="18" t="n"/>
       <c r="AD44" s="18" t="n"/>
       <c r="AE44" s="18" t="n"/>
-      <c r="AF44" s="20" t="n"/>
-      <c r="AG44" s="13">
-        <f>IF($A44="","",IF(AH44&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH44">
-        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($P44="",1,0)+IF($S44="",1,0)+IF($T44="",1,0)+IF($U44="",1,0)+IF($W44="",1,0)+IF($AA44="",1,0)+IF($AB44="",1,0)+IF(AND($N44="契約期間満了",$Q44=""),1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0)+IF(AND($AD44="外国",$AE44=""),1,0)+IF(AND($AD44="外国",$AF44=""),1,0))</f>
+      <c r="AF44" s="18" t="n"/>
+      <c r="AG44" s="18" t="n"/>
+      <c r="AH44" s="20" t="n"/>
+      <c r="AI44" s="13">
+        <f>IF($A44="","",IF(AJ44&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ44">
+        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($Q44="",1,0)+IF($T44="",1,0)+IF($U44="",1,0)+IF($V44="",1,0)+IF($X44="",1,0)+IF($AB44="",1,0)+IF($AD44="",1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0)+IF(AND($N44="契約期間満了",$S44=""),1,0)+IF(AND($AF44="外国",$AG44=""),1,0)+IF(AND($AF44="外国",$AH44=""),1,0)+IF(AND($AB44="未回収",$AC44=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3767,29 +3906,31 @@
       </c>
       <c r="N45" s="18" t="n"/>
       <c r="O45" s="18" t="n"/>
-      <c r="P45" s="18" t="n"/>
+      <c r="P45" s="20" t="n"/>
       <c r="Q45" s="18" t="n"/>
       <c r="R45" s="18" t="n"/>
-      <c r="S45" s="20" t="n"/>
-      <c r="T45" s="47" t="n"/>
-      <c r="U45" s="18" t="n"/>
+      <c r="S45" s="18" t="n"/>
+      <c r="T45" s="20" t="n"/>
+      <c r="U45" s="47" t="n"/>
       <c r="V45" s="18" t="n"/>
       <c r="W45" s="18" t="n"/>
       <c r="X45" s="18" t="n"/>
-      <c r="Y45" s="48" t="n"/>
+      <c r="Y45" s="18" t="n"/>
       <c r="Z45" s="48" t="n"/>
-      <c r="AA45" s="18" t="n"/>
+      <c r="AA45" s="48" t="n"/>
       <c r="AB45" s="18" t="n"/>
       <c r="AC45" s="18" t="n"/>
       <c r="AD45" s="18" t="n"/>
       <c r="AE45" s="18" t="n"/>
-      <c r="AF45" s="20" t="n"/>
-      <c r="AG45" s="13">
-        <f>IF($A45="","",IF(AH45&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH45">
-        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($P45="",1,0)+IF($S45="",1,0)+IF($T45="",1,0)+IF($U45="",1,0)+IF($W45="",1,0)+IF($AA45="",1,0)+IF($AB45="",1,0)+IF(AND($N45="契約期間満了",$Q45=""),1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0)+IF(AND($AD45="外国",$AE45=""),1,0)+IF(AND($AD45="外国",$AF45=""),1,0))</f>
+      <c r="AF45" s="18" t="n"/>
+      <c r="AG45" s="18" t="n"/>
+      <c r="AH45" s="20" t="n"/>
+      <c r="AI45" s="13">
+        <f>IF($A45="","",IF(AJ45&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ45">
+        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($Q45="",1,0)+IF($T45="",1,0)+IF($U45="",1,0)+IF($V45="",1,0)+IF($X45="",1,0)+IF($AB45="",1,0)+IF($AD45="",1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0)+IF(AND($N45="契約期間満了",$S45=""),1,0)+IF(AND($AF45="外国",$AG45=""),1,0)+IF(AND($AF45="外国",$AH45=""),1,0)+IF(AND($AB45="未回収",$AC45=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3812,29 +3953,31 @@
       </c>
       <c r="N46" s="18" t="n"/>
       <c r="O46" s="18" t="n"/>
-      <c r="P46" s="18" t="n"/>
+      <c r="P46" s="20" t="n"/>
       <c r="Q46" s="18" t="n"/>
       <c r="R46" s="18" t="n"/>
-      <c r="S46" s="20" t="n"/>
-      <c r="T46" s="47" t="n"/>
-      <c r="U46" s="18" t="n"/>
+      <c r="S46" s="18" t="n"/>
+      <c r="T46" s="20" t="n"/>
+      <c r="U46" s="47" t="n"/>
       <c r="V46" s="18" t="n"/>
       <c r="W46" s="18" t="n"/>
       <c r="X46" s="18" t="n"/>
-      <c r="Y46" s="48" t="n"/>
+      <c r="Y46" s="18" t="n"/>
       <c r="Z46" s="48" t="n"/>
-      <c r="AA46" s="18" t="n"/>
+      <c r="AA46" s="48" t="n"/>
       <c r="AB46" s="18" t="n"/>
       <c r="AC46" s="18" t="n"/>
       <c r="AD46" s="18" t="n"/>
       <c r="AE46" s="18" t="n"/>
-      <c r="AF46" s="20" t="n"/>
-      <c r="AG46" s="13">
-        <f>IF($A46="","",IF(AH46&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH46">
-        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($P46="",1,0)+IF($S46="",1,0)+IF($T46="",1,0)+IF($U46="",1,0)+IF($W46="",1,0)+IF($AA46="",1,0)+IF($AB46="",1,0)+IF(AND($N46="契約期間満了",$Q46=""),1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0)+IF(AND($AD46="外国",$AE46=""),1,0)+IF(AND($AD46="外国",$AF46=""),1,0))</f>
+      <c r="AF46" s="18" t="n"/>
+      <c r="AG46" s="18" t="n"/>
+      <c r="AH46" s="20" t="n"/>
+      <c r="AI46" s="13">
+        <f>IF($A46="","",IF(AJ46&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ46">
+        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($Q46="",1,0)+IF($T46="",1,0)+IF($U46="",1,0)+IF($V46="",1,0)+IF($X46="",1,0)+IF($AB46="",1,0)+IF($AD46="",1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0)+IF(AND($N46="契約期間満了",$S46=""),1,0)+IF(AND($AF46="外国",$AG46=""),1,0)+IF(AND($AF46="外国",$AH46=""),1,0)+IF(AND($AB46="未回収",$AC46=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3857,29 +4000,31 @@
       </c>
       <c r="N47" s="18" t="n"/>
       <c r="O47" s="18" t="n"/>
-      <c r="P47" s="18" t="n"/>
+      <c r="P47" s="20" t="n"/>
       <c r="Q47" s="18" t="n"/>
       <c r="R47" s="18" t="n"/>
-      <c r="S47" s="20" t="n"/>
-      <c r="T47" s="47" t="n"/>
-      <c r="U47" s="18" t="n"/>
+      <c r="S47" s="18" t="n"/>
+      <c r="T47" s="20" t="n"/>
+      <c r="U47" s="47" t="n"/>
       <c r="V47" s="18" t="n"/>
       <c r="W47" s="18" t="n"/>
       <c r="X47" s="18" t="n"/>
-      <c r="Y47" s="48" t="n"/>
+      <c r="Y47" s="18" t="n"/>
       <c r="Z47" s="48" t="n"/>
-      <c r="AA47" s="18" t="n"/>
+      <c r="AA47" s="48" t="n"/>
       <c r="AB47" s="18" t="n"/>
       <c r="AC47" s="18" t="n"/>
       <c r="AD47" s="18" t="n"/>
       <c r="AE47" s="18" t="n"/>
-      <c r="AF47" s="20" t="n"/>
-      <c r="AG47" s="13">
-        <f>IF($A47="","",IF(AH47&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH47">
-        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($P47="",1,0)+IF($S47="",1,0)+IF($T47="",1,0)+IF($U47="",1,0)+IF($W47="",1,0)+IF($AA47="",1,0)+IF($AB47="",1,0)+IF(AND($N47="契約期間満了",$Q47=""),1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0)+IF(AND($AD47="外国",$AE47=""),1,0)+IF(AND($AD47="外国",$AF47=""),1,0))</f>
+      <c r="AF47" s="18" t="n"/>
+      <c r="AG47" s="18" t="n"/>
+      <c r="AH47" s="20" t="n"/>
+      <c r="AI47" s="13">
+        <f>IF($A47="","",IF(AJ47&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ47">
+        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($Q47="",1,0)+IF($T47="",1,0)+IF($U47="",1,0)+IF($V47="",1,0)+IF($X47="",1,0)+IF($AB47="",1,0)+IF($AD47="",1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0)+IF(AND($N47="契約期間満了",$S47=""),1,0)+IF(AND($AF47="外国",$AG47=""),1,0)+IF(AND($AF47="外国",$AH47=""),1,0)+IF(AND($AB47="未回収",$AC47=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3902,29 +4047,31 @@
       </c>
       <c r="N48" s="18" t="n"/>
       <c r="O48" s="18" t="n"/>
-      <c r="P48" s="18" t="n"/>
+      <c r="P48" s="20" t="n"/>
       <c r="Q48" s="18" t="n"/>
       <c r="R48" s="18" t="n"/>
-      <c r="S48" s="20" t="n"/>
-      <c r="T48" s="47" t="n"/>
-      <c r="U48" s="18" t="n"/>
+      <c r="S48" s="18" t="n"/>
+      <c r="T48" s="20" t="n"/>
+      <c r="U48" s="47" t="n"/>
       <c r="V48" s="18" t="n"/>
       <c r="W48" s="18" t="n"/>
       <c r="X48" s="18" t="n"/>
-      <c r="Y48" s="48" t="n"/>
+      <c r="Y48" s="18" t="n"/>
       <c r="Z48" s="48" t="n"/>
-      <c r="AA48" s="18" t="n"/>
+      <c r="AA48" s="48" t="n"/>
       <c r="AB48" s="18" t="n"/>
       <c r="AC48" s="18" t="n"/>
       <c r="AD48" s="18" t="n"/>
       <c r="AE48" s="18" t="n"/>
-      <c r="AF48" s="20" t="n"/>
-      <c r="AG48" s="13">
-        <f>IF($A48="","",IF(AH48&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH48">
-        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($P48="",1,0)+IF($S48="",1,0)+IF($T48="",1,0)+IF($U48="",1,0)+IF($W48="",1,0)+IF($AA48="",1,0)+IF($AB48="",1,0)+IF(AND($N48="契約期間満了",$Q48=""),1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0)+IF(AND($AD48="外国",$AE48=""),1,0)+IF(AND($AD48="外国",$AF48=""),1,0))</f>
+      <c r="AF48" s="18" t="n"/>
+      <c r="AG48" s="18" t="n"/>
+      <c r="AH48" s="20" t="n"/>
+      <c r="AI48" s="13">
+        <f>IF($A48="","",IF(AJ48&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ48">
+        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($Q48="",1,0)+IF($T48="",1,0)+IF($U48="",1,0)+IF($V48="",1,0)+IF($X48="",1,0)+IF($AB48="",1,0)+IF($AD48="",1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0)+IF(AND($N48="契約期間満了",$S48=""),1,0)+IF(AND($AF48="外国",$AG48=""),1,0)+IF(AND($AF48="外国",$AH48=""),1,0)+IF(AND($AB48="未回収",$AC48=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3947,29 +4094,31 @@
       </c>
       <c r="N49" s="18" t="n"/>
       <c r="O49" s="18" t="n"/>
-      <c r="P49" s="18" t="n"/>
+      <c r="P49" s="20" t="n"/>
       <c r="Q49" s="18" t="n"/>
       <c r="R49" s="18" t="n"/>
-      <c r="S49" s="20" t="n"/>
-      <c r="T49" s="47" t="n"/>
-      <c r="U49" s="18" t="n"/>
+      <c r="S49" s="18" t="n"/>
+      <c r="T49" s="20" t="n"/>
+      <c r="U49" s="47" t="n"/>
       <c r="V49" s="18" t="n"/>
       <c r="W49" s="18" t="n"/>
       <c r="X49" s="18" t="n"/>
-      <c r="Y49" s="48" t="n"/>
+      <c r="Y49" s="18" t="n"/>
       <c r="Z49" s="48" t="n"/>
-      <c r="AA49" s="18" t="n"/>
+      <c r="AA49" s="48" t="n"/>
       <c r="AB49" s="18" t="n"/>
       <c r="AC49" s="18" t="n"/>
       <c r="AD49" s="18" t="n"/>
       <c r="AE49" s="18" t="n"/>
-      <c r="AF49" s="20" t="n"/>
-      <c r="AG49" s="13">
-        <f>IF($A49="","",IF(AH49&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH49">
-        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($P49="",1,0)+IF($S49="",1,0)+IF($T49="",1,0)+IF($U49="",1,0)+IF($W49="",1,0)+IF($AA49="",1,0)+IF($AB49="",1,0)+IF(AND($N49="契約期間満了",$Q49=""),1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0)+IF(AND($AD49="外国",$AE49=""),1,0)+IF(AND($AD49="外国",$AF49=""),1,0))</f>
+      <c r="AF49" s="18" t="n"/>
+      <c r="AG49" s="18" t="n"/>
+      <c r="AH49" s="20" t="n"/>
+      <c r="AI49" s="13">
+        <f>IF($A49="","",IF(AJ49&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ49">
+        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($Q49="",1,0)+IF($T49="",1,0)+IF($U49="",1,0)+IF($V49="",1,0)+IF($X49="",1,0)+IF($AB49="",1,0)+IF($AD49="",1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0)+IF(AND($N49="契約期間満了",$S49=""),1,0)+IF(AND($AF49="外国",$AG49=""),1,0)+IF(AND($AF49="外国",$AH49=""),1,0)+IF(AND($AB49="未回収",$AC49=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3992,29 +4141,31 @@
       </c>
       <c r="N50" s="18" t="n"/>
       <c r="O50" s="18" t="n"/>
-      <c r="P50" s="18" t="n"/>
+      <c r="P50" s="20" t="n"/>
       <c r="Q50" s="18" t="n"/>
       <c r="R50" s="18" t="n"/>
-      <c r="S50" s="20" t="n"/>
-      <c r="T50" s="47" t="n"/>
-      <c r="U50" s="18" t="n"/>
+      <c r="S50" s="18" t="n"/>
+      <c r="T50" s="20" t="n"/>
+      <c r="U50" s="47" t="n"/>
       <c r="V50" s="18" t="n"/>
       <c r="W50" s="18" t="n"/>
       <c r="X50" s="18" t="n"/>
-      <c r="Y50" s="48" t="n"/>
+      <c r="Y50" s="18" t="n"/>
       <c r="Z50" s="48" t="n"/>
-      <c r="AA50" s="18" t="n"/>
+      <c r="AA50" s="48" t="n"/>
       <c r="AB50" s="18" t="n"/>
       <c r="AC50" s="18" t="n"/>
       <c r="AD50" s="18" t="n"/>
       <c r="AE50" s="18" t="n"/>
-      <c r="AF50" s="20" t="n"/>
-      <c r="AG50" s="13">
-        <f>IF($A50="","",IF(AH50&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH50">
-        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($P50="",1,0)+IF($S50="",1,0)+IF($T50="",1,0)+IF($U50="",1,0)+IF($W50="",1,0)+IF($AA50="",1,0)+IF($AB50="",1,0)+IF(AND($N50="契約期間満了",$Q50=""),1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0)+IF(AND($AD50="外国",$AE50=""),1,0)+IF(AND($AD50="外国",$AF50=""),1,0))</f>
+      <c r="AF50" s="18" t="n"/>
+      <c r="AG50" s="18" t="n"/>
+      <c r="AH50" s="20" t="n"/>
+      <c r="AI50" s="13">
+        <f>IF($A50="","",IF(AJ50&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ50">
+        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($Q50="",1,0)+IF($T50="",1,0)+IF($U50="",1,0)+IF($V50="",1,0)+IF($X50="",1,0)+IF($AB50="",1,0)+IF($AD50="",1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0)+IF(AND($N50="契約期間満了",$S50=""),1,0)+IF(AND($AF50="外国",$AG50=""),1,0)+IF(AND($AF50="外国",$AH50=""),1,0)+IF(AND($AB50="未回収",$AC50=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4037,29 +4188,31 @@
       </c>
       <c r="N51" s="18" t="n"/>
       <c r="O51" s="18" t="n"/>
-      <c r="P51" s="18" t="n"/>
+      <c r="P51" s="20" t="n"/>
       <c r="Q51" s="18" t="n"/>
       <c r="R51" s="18" t="n"/>
-      <c r="S51" s="20" t="n"/>
-      <c r="T51" s="47" t="n"/>
-      <c r="U51" s="18" t="n"/>
+      <c r="S51" s="18" t="n"/>
+      <c r="T51" s="20" t="n"/>
+      <c r="U51" s="47" t="n"/>
       <c r="V51" s="18" t="n"/>
       <c r="W51" s="18" t="n"/>
       <c r="X51" s="18" t="n"/>
-      <c r="Y51" s="48" t="n"/>
+      <c r="Y51" s="18" t="n"/>
       <c r="Z51" s="48" t="n"/>
-      <c r="AA51" s="18" t="n"/>
+      <c r="AA51" s="48" t="n"/>
       <c r="AB51" s="18" t="n"/>
       <c r="AC51" s="18" t="n"/>
       <c r="AD51" s="18" t="n"/>
       <c r="AE51" s="18" t="n"/>
-      <c r="AF51" s="20" t="n"/>
-      <c r="AG51" s="13">
-        <f>IF($A51="","",IF(AH51&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH51">
-        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($P51="",1,0)+IF($S51="",1,0)+IF($T51="",1,0)+IF($U51="",1,0)+IF($W51="",1,0)+IF($AA51="",1,0)+IF($AB51="",1,0)+IF(AND($N51="契約期間満了",$Q51=""),1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0)+IF(AND($AD51="外国",$AE51=""),1,0)+IF(AND($AD51="外国",$AF51=""),1,0))</f>
+      <c r="AF51" s="18" t="n"/>
+      <c r="AG51" s="18" t="n"/>
+      <c r="AH51" s="20" t="n"/>
+      <c r="AI51" s="13">
+        <f>IF($A51="","",IF(AJ51&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ51">
+        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($Q51="",1,0)+IF($T51="",1,0)+IF($U51="",1,0)+IF($V51="",1,0)+IF($X51="",1,0)+IF($AB51="",1,0)+IF($AD51="",1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0)+IF(AND($N51="契約期間満了",$S51=""),1,0)+IF(AND($AF51="外国",$AG51=""),1,0)+IF(AND($AF51="外国",$AH51=""),1,0)+IF(AND($AB51="未回収",$AC51=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4082,29 +4235,31 @@
       </c>
       <c r="N52" s="18" t="n"/>
       <c r="O52" s="18" t="n"/>
-      <c r="P52" s="18" t="n"/>
+      <c r="P52" s="20" t="n"/>
       <c r="Q52" s="18" t="n"/>
       <c r="R52" s="18" t="n"/>
-      <c r="S52" s="20" t="n"/>
-      <c r="T52" s="47" t="n"/>
-      <c r="U52" s="18" t="n"/>
+      <c r="S52" s="18" t="n"/>
+      <c r="T52" s="20" t="n"/>
+      <c r="U52" s="47" t="n"/>
       <c r="V52" s="18" t="n"/>
       <c r="W52" s="18" t="n"/>
       <c r="X52" s="18" t="n"/>
-      <c r="Y52" s="48" t="n"/>
+      <c r="Y52" s="18" t="n"/>
       <c r="Z52" s="48" t="n"/>
-      <c r="AA52" s="18" t="n"/>
+      <c r="AA52" s="48" t="n"/>
       <c r="AB52" s="18" t="n"/>
       <c r="AC52" s="18" t="n"/>
       <c r="AD52" s="18" t="n"/>
       <c r="AE52" s="18" t="n"/>
-      <c r="AF52" s="20" t="n"/>
-      <c r="AG52" s="13">
-        <f>IF($A52="","",IF(AH52&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH52">
-        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($P52="",1,0)+IF($S52="",1,0)+IF($T52="",1,0)+IF($U52="",1,0)+IF($W52="",1,0)+IF($AA52="",1,0)+IF($AB52="",1,0)+IF(AND($N52="契約期間満了",$Q52=""),1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0)+IF(AND($AD52="外国",$AE52=""),1,0)+IF(AND($AD52="外国",$AF52=""),1,0))</f>
+      <c r="AF52" s="18" t="n"/>
+      <c r="AG52" s="18" t="n"/>
+      <c r="AH52" s="20" t="n"/>
+      <c r="AI52" s="13">
+        <f>IF($A52="","",IF(AJ52&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ52">
+        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($Q52="",1,0)+IF($T52="",1,0)+IF($U52="",1,0)+IF($V52="",1,0)+IF($X52="",1,0)+IF($AB52="",1,0)+IF($AD52="",1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0)+IF(AND($N52="契約期間満了",$S52=""),1,0)+IF(AND($AF52="外国",$AG52=""),1,0)+IF(AND($AF52="外国",$AH52=""),1,0)+IF(AND($AB52="未回収",$AC52=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4127,29 +4282,31 @@
       </c>
       <c r="N53" s="18" t="n"/>
       <c r="O53" s="18" t="n"/>
-      <c r="P53" s="18" t="n"/>
+      <c r="P53" s="20" t="n"/>
       <c r="Q53" s="18" t="n"/>
       <c r="R53" s="18" t="n"/>
-      <c r="S53" s="20" t="n"/>
-      <c r="T53" s="47" t="n"/>
-      <c r="U53" s="18" t="n"/>
+      <c r="S53" s="18" t="n"/>
+      <c r="T53" s="20" t="n"/>
+      <c r="U53" s="47" t="n"/>
       <c r="V53" s="18" t="n"/>
       <c r="W53" s="18" t="n"/>
       <c r="X53" s="18" t="n"/>
-      <c r="Y53" s="48" t="n"/>
+      <c r="Y53" s="18" t="n"/>
       <c r="Z53" s="48" t="n"/>
-      <c r="AA53" s="18" t="n"/>
+      <c r="AA53" s="48" t="n"/>
       <c r="AB53" s="18" t="n"/>
       <c r="AC53" s="18" t="n"/>
       <c r="AD53" s="18" t="n"/>
       <c r="AE53" s="18" t="n"/>
-      <c r="AF53" s="20" t="n"/>
-      <c r="AG53" s="13">
-        <f>IF($A53="","",IF(AH53&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH53">
-        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($P53="",1,0)+IF($S53="",1,0)+IF($T53="",1,0)+IF($U53="",1,0)+IF($W53="",1,0)+IF($AA53="",1,0)+IF($AB53="",1,0)+IF(AND($N53="契約期間満了",$Q53=""),1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0)+IF(AND($AD53="外国",$AE53=""),1,0)+IF(AND($AD53="外国",$AF53=""),1,0))</f>
+      <c r="AF53" s="18" t="n"/>
+      <c r="AG53" s="18" t="n"/>
+      <c r="AH53" s="20" t="n"/>
+      <c r="AI53" s="13">
+        <f>IF($A53="","",IF(AJ53&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ53">
+        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($Q53="",1,0)+IF($T53="",1,0)+IF($U53="",1,0)+IF($V53="",1,0)+IF($X53="",1,0)+IF($AB53="",1,0)+IF($AD53="",1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0)+IF(AND($N53="契約期間満了",$S53=""),1,0)+IF(AND($AF53="外国",$AG53=""),1,0)+IF(AND($AF53="外国",$AH53=""),1,0)+IF(AND($AB53="未回収",$AC53=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4172,29 +4329,31 @@
       </c>
       <c r="N54" s="18" t="n"/>
       <c r="O54" s="18" t="n"/>
-      <c r="P54" s="18" t="n"/>
+      <c r="P54" s="20" t="n"/>
       <c r="Q54" s="18" t="n"/>
       <c r="R54" s="18" t="n"/>
-      <c r="S54" s="20" t="n"/>
-      <c r="T54" s="47" t="n"/>
-      <c r="U54" s="18" t="n"/>
+      <c r="S54" s="18" t="n"/>
+      <c r="T54" s="20" t="n"/>
+      <c r="U54" s="47" t="n"/>
       <c r="V54" s="18" t="n"/>
       <c r="W54" s="18" t="n"/>
       <c r="X54" s="18" t="n"/>
-      <c r="Y54" s="48" t="n"/>
+      <c r="Y54" s="18" t="n"/>
       <c r="Z54" s="48" t="n"/>
-      <c r="AA54" s="18" t="n"/>
+      <c r="AA54" s="48" t="n"/>
       <c r="AB54" s="18" t="n"/>
       <c r="AC54" s="18" t="n"/>
       <c r="AD54" s="18" t="n"/>
       <c r="AE54" s="18" t="n"/>
-      <c r="AF54" s="20" t="n"/>
-      <c r="AG54" s="13">
-        <f>IF($A54="","",IF(AH54&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH54">
-        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($P54="",1,0)+IF($S54="",1,0)+IF($T54="",1,0)+IF($U54="",1,0)+IF($W54="",1,0)+IF($AA54="",1,0)+IF($AB54="",1,0)+IF(AND($N54="契約期間満了",$Q54=""),1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0)+IF(AND($AD54="外国",$AE54=""),1,0)+IF(AND($AD54="外国",$AF54=""),1,0))</f>
+      <c r="AF54" s="18" t="n"/>
+      <c r="AG54" s="18" t="n"/>
+      <c r="AH54" s="20" t="n"/>
+      <c r="AI54" s="13">
+        <f>IF($A54="","",IF(AJ54&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ54">
+        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($Q54="",1,0)+IF($T54="",1,0)+IF($U54="",1,0)+IF($V54="",1,0)+IF($X54="",1,0)+IF($AB54="",1,0)+IF($AD54="",1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0)+IF(AND($N54="契約期間満了",$S54=""),1,0)+IF(AND($AF54="外国",$AG54=""),1,0)+IF(AND($AF54="外国",$AH54=""),1,0)+IF(AND($AB54="未回収",$AC54=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4217,29 +4376,31 @@
       </c>
       <c r="N55" s="18" t="n"/>
       <c r="O55" s="18" t="n"/>
-      <c r="P55" s="18" t="n"/>
+      <c r="P55" s="20" t="n"/>
       <c r="Q55" s="18" t="n"/>
       <c r="R55" s="18" t="n"/>
-      <c r="S55" s="20" t="n"/>
-      <c r="T55" s="47" t="n"/>
-      <c r="U55" s="18" t="n"/>
+      <c r="S55" s="18" t="n"/>
+      <c r="T55" s="20" t="n"/>
+      <c r="U55" s="47" t="n"/>
       <c r="V55" s="18" t="n"/>
       <c r="W55" s="18" t="n"/>
       <c r="X55" s="18" t="n"/>
-      <c r="Y55" s="48" t="n"/>
+      <c r="Y55" s="18" t="n"/>
       <c r="Z55" s="48" t="n"/>
-      <c r="AA55" s="18" t="n"/>
+      <c r="AA55" s="48" t="n"/>
       <c r="AB55" s="18" t="n"/>
       <c r="AC55" s="18" t="n"/>
       <c r="AD55" s="18" t="n"/>
       <c r="AE55" s="18" t="n"/>
-      <c r="AF55" s="20" t="n"/>
-      <c r="AG55" s="13">
-        <f>IF($A55="","",IF(AH55&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH55">
-        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($P55="",1,0)+IF($S55="",1,0)+IF($T55="",1,0)+IF($U55="",1,0)+IF($W55="",1,0)+IF($AA55="",1,0)+IF($AB55="",1,0)+IF(AND($N55="契約期間満了",$Q55=""),1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0)+IF(AND($AD55="外国",$AE55=""),1,0)+IF(AND($AD55="外国",$AF55=""),1,0))</f>
+      <c r="AF55" s="18" t="n"/>
+      <c r="AG55" s="18" t="n"/>
+      <c r="AH55" s="20" t="n"/>
+      <c r="AI55" s="13">
+        <f>IF($A55="","",IF(AJ55&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ55">
+        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($Q55="",1,0)+IF($T55="",1,0)+IF($U55="",1,0)+IF($V55="",1,0)+IF($X55="",1,0)+IF($AB55="",1,0)+IF($AD55="",1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0)+IF(AND($N55="契約期間満了",$S55=""),1,0)+IF(AND($AF55="外国",$AG55=""),1,0)+IF(AND($AF55="外国",$AH55=""),1,0)+IF(AND($AB55="未回収",$AC55=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4262,29 +4423,31 @@
       </c>
       <c r="N56" s="18" t="n"/>
       <c r="O56" s="18" t="n"/>
-      <c r="P56" s="18" t="n"/>
+      <c r="P56" s="20" t="n"/>
       <c r="Q56" s="18" t="n"/>
       <c r="R56" s="18" t="n"/>
-      <c r="S56" s="20" t="n"/>
-      <c r="T56" s="47" t="n"/>
-      <c r="U56" s="18" t="n"/>
+      <c r="S56" s="18" t="n"/>
+      <c r="T56" s="20" t="n"/>
+      <c r="U56" s="47" t="n"/>
       <c r="V56" s="18" t="n"/>
       <c r="W56" s="18" t="n"/>
       <c r="X56" s="18" t="n"/>
-      <c r="Y56" s="48" t="n"/>
+      <c r="Y56" s="18" t="n"/>
       <c r="Z56" s="48" t="n"/>
-      <c r="AA56" s="18" t="n"/>
+      <c r="AA56" s="48" t="n"/>
       <c r="AB56" s="18" t="n"/>
       <c r="AC56" s="18" t="n"/>
       <c r="AD56" s="18" t="n"/>
       <c r="AE56" s="18" t="n"/>
-      <c r="AF56" s="20" t="n"/>
-      <c r="AG56" s="13">
-        <f>IF($A56="","",IF(AH56&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH56">
-        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($P56="",1,0)+IF($S56="",1,0)+IF($T56="",1,0)+IF($U56="",1,0)+IF($W56="",1,0)+IF($AA56="",1,0)+IF($AB56="",1,0)+IF(AND($N56="契約期間満了",$Q56=""),1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0)+IF(AND($AD56="外国",$AE56=""),1,0)+IF(AND($AD56="外国",$AF56=""),1,0))</f>
+      <c r="AF56" s="18" t="n"/>
+      <c r="AG56" s="18" t="n"/>
+      <c r="AH56" s="20" t="n"/>
+      <c r="AI56" s="13">
+        <f>IF($A56="","",IF(AJ56&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ56">
+        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($Q56="",1,0)+IF($T56="",1,0)+IF($U56="",1,0)+IF($V56="",1,0)+IF($X56="",1,0)+IF($AB56="",1,0)+IF($AD56="",1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0)+IF(AND($N56="契約期間満了",$S56=""),1,0)+IF(AND($AF56="外国",$AG56=""),1,0)+IF(AND($AF56="外国",$AH56=""),1,0)+IF(AND($AB56="未回収",$AC56=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4307,29 +4470,31 @@
       </c>
       <c r="N57" s="18" t="n"/>
       <c r="O57" s="18" t="n"/>
-      <c r="P57" s="18" t="n"/>
+      <c r="P57" s="20" t="n"/>
       <c r="Q57" s="18" t="n"/>
       <c r="R57" s="18" t="n"/>
-      <c r="S57" s="20" t="n"/>
-      <c r="T57" s="47" t="n"/>
-      <c r="U57" s="18" t="n"/>
+      <c r="S57" s="18" t="n"/>
+      <c r="T57" s="20" t="n"/>
+      <c r="U57" s="47" t="n"/>
       <c r="V57" s="18" t="n"/>
       <c r="W57" s="18" t="n"/>
       <c r="X57" s="18" t="n"/>
-      <c r="Y57" s="48" t="n"/>
+      <c r="Y57" s="18" t="n"/>
       <c r="Z57" s="48" t="n"/>
-      <c r="AA57" s="18" t="n"/>
+      <c r="AA57" s="48" t="n"/>
       <c r="AB57" s="18" t="n"/>
       <c r="AC57" s="18" t="n"/>
       <c r="AD57" s="18" t="n"/>
       <c r="AE57" s="18" t="n"/>
-      <c r="AF57" s="20" t="n"/>
-      <c r="AG57" s="13">
-        <f>IF($A57="","",IF(AH57&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH57">
-        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($P57="",1,0)+IF($S57="",1,0)+IF($T57="",1,0)+IF($U57="",1,0)+IF($W57="",1,0)+IF($AA57="",1,0)+IF($AB57="",1,0)+IF(AND($N57="契約期間満了",$Q57=""),1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0)+IF(AND($AD57="外国",$AE57=""),1,0)+IF(AND($AD57="外国",$AF57=""),1,0))</f>
+      <c r="AF57" s="18" t="n"/>
+      <c r="AG57" s="18" t="n"/>
+      <c r="AH57" s="20" t="n"/>
+      <c r="AI57" s="13">
+        <f>IF($A57="","",IF(AJ57&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ57">
+        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($Q57="",1,0)+IF($T57="",1,0)+IF($U57="",1,0)+IF($V57="",1,0)+IF($X57="",1,0)+IF($AB57="",1,0)+IF($AD57="",1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0)+IF(AND($N57="契約期間満了",$S57=""),1,0)+IF(AND($AF57="外国",$AG57=""),1,0)+IF(AND($AF57="外国",$AH57=""),1,0)+IF(AND($AB57="未回収",$AC57=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4352,29 +4517,31 @@
       </c>
       <c r="N58" s="18" t="n"/>
       <c r="O58" s="18" t="n"/>
-      <c r="P58" s="18" t="n"/>
+      <c r="P58" s="20" t="n"/>
       <c r="Q58" s="18" t="n"/>
       <c r="R58" s="18" t="n"/>
-      <c r="S58" s="20" t="n"/>
-      <c r="T58" s="47" t="n"/>
-      <c r="U58" s="18" t="n"/>
+      <c r="S58" s="18" t="n"/>
+      <c r="T58" s="20" t="n"/>
+      <c r="U58" s="47" t="n"/>
       <c r="V58" s="18" t="n"/>
       <c r="W58" s="18" t="n"/>
       <c r="X58" s="18" t="n"/>
-      <c r="Y58" s="48" t="n"/>
+      <c r="Y58" s="18" t="n"/>
       <c r="Z58" s="48" t="n"/>
-      <c r="AA58" s="18" t="n"/>
+      <c r="AA58" s="48" t="n"/>
       <c r="AB58" s="18" t="n"/>
       <c r="AC58" s="18" t="n"/>
       <c r="AD58" s="18" t="n"/>
       <c r="AE58" s="18" t="n"/>
-      <c r="AF58" s="20" t="n"/>
-      <c r="AG58" s="13">
-        <f>IF($A58="","",IF(AH58&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AH58">
-        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($P58="",1,0)+IF($S58="",1,0)+IF($T58="",1,0)+IF($U58="",1,0)+IF($W58="",1,0)+IF($AA58="",1,0)+IF($AB58="",1,0)+IF(AND($N58="契約期間満了",$Q58=""),1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0)+IF(AND($AD58="外国",$AE58=""),1,0)+IF(AND($AD58="外国",$AF58=""),1,0))</f>
+      <c r="AF58" s="18" t="n"/>
+      <c r="AG58" s="18" t="n"/>
+      <c r="AH58" s="20" t="n"/>
+      <c r="AI58" s="13">
+        <f>IF($A58="","",IF(AJ58&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AJ58">
+        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($Q58="",1,0)+IF($T58="",1,0)+IF($U58="",1,0)+IF($V58="",1,0)+IF($X58="",1,0)+IF($AB58="",1,0)+IF($AD58="",1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0)+IF(AND($N58="契約期間満了",$S58=""),1,0)+IF(AND($AF58="外国",$AG58=""),1,0)+IF(AND($AF58="外国",$AH58=""),1,0)+IF(AND($AB58="未回収",$AC58=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4384,17 +4551,17 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="L6:S6"/>
+    <mergeCell ref="R1:AH1"/>
+    <mergeCell ref="AB6:AD6"/>
+    <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="AC6"/>
-    <mergeCell ref="S6:Z6"/>
-    <mergeCell ref="Q1:AF1"/>
-    <mergeCell ref="L6:R6"/>
+    <mergeCell ref="T6:AA6"/>
+    <mergeCell ref="AE6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
@@ -4422,10 +4589,10 @@
     <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",B9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",LENB(B9)&lt;&gt;LEN(B9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",ISERROR(FIND("　",B9)),ISERROR(FIND(" ",B9)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4433,7 +4600,7 @@
     <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",C9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(C9),C9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4441,10 +4608,10 @@
     <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",D9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="33" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LEN(D9)&lt;&gt;12)</formula>
     </cfRule>
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LENB(D9)&lt;&gt;LEN(D9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4452,10 +4619,10 @@
     <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",E9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LEN(E9)&lt;&gt;10)</formula>
     </cfRule>
-    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LENB(E9)&lt;&gt;LEN(E9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4463,10 +4630,10 @@
     <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",F9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="33" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LEN(F9)&lt;&gt;11)</formula>
     </cfRule>
-    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LENB(F9)&lt;&gt;LEN(F9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4474,10 +4641,10 @@
     <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",G9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LEN(SUBSTITUTE(G9,"-",""))&lt;&gt;7)</formula>
     </cfRule>
-    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LENB(G9)&lt;&gt;LEN(G9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4490,7 +4657,7 @@
     <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",I9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
       <formula>AND(I9&lt;&gt;"",LENB(I9)&lt;&gt;LEN(I9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4498,7 +4665,7 @@
     <cfRule type="expression" priority="13" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",L9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="49" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(L9),L9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4507,109 +4674,122 @@
       <formula>AND($A9&lt;&gt;"",N9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P9:P58">
+  <conditionalFormatting sqref="Q9:Q58">
     <cfRule type="expression" priority="15" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",P9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S9:S58">
-    <cfRule type="expression" priority="16" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",S9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(S9),S9&gt;80000)</formula>
+      <formula>AND($A9&lt;&gt;"",Q9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T9:T58">
-    <cfRule type="expression" priority="17" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="16" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",T9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(T9),T9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9:U58">
-    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="17" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",U9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W9:W58">
-    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",W9="")</formula>
+  <conditionalFormatting sqref="V9:V58">
+    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",V9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA9:AA58">
-    <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",AA9="")</formula>
+  <conditionalFormatting sqref="X9:X58">
+    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",X9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB9:AB58">
+    <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",AB9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD9:AD58">
     <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",AB9="")</formula>
+      <formula>AND($A9&lt;&gt;"",AD9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A58">
     <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
       <formula>AND($A9="",OR($L9&lt;&gt;"",$N9&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",LENB(A9)&lt;&gt;LEN(A9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",ISERROR(FIND("　",A9)),ISERROR(FIND(" ",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q9:Q58">
+  <conditionalFormatting sqref="R9:R58">
     <cfRule type="expression" priority="23" dxfId="2" stopIfTrue="1">
-      <formula>AND($N9="契約期間満了",Q9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="27" dxfId="3" stopIfTrue="1">
-      <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),Q9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R9:R58">
-    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",R9="")</formula>
     </cfRule>
     <cfRule type="expression" priority="28" dxfId="3" stopIfTrue="1">
       <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),R9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE9:AE58">
-    <cfRule type="expression" priority="25" dxfId="2" stopIfTrue="1">
-      <formula>AND($AD9="外国",AE9="")</formula>
+  <conditionalFormatting sqref="S9:S58">
+    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
+      <formula>AND($N9="契約期間満了",S9="")</formula>
     </cfRule>
     <cfRule type="expression" priority="29" dxfId="3" stopIfTrue="1">
-      <formula>AND($AD9&lt;&gt;"",NOT($AD9="外国"),AE9="")</formula>
+      <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),S9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF9:AF58">
-    <cfRule type="expression" priority="26" dxfId="2" stopIfTrue="1">
-      <formula>AND($AD9="外国",AF9="")</formula>
+  <conditionalFormatting sqref="AG9:AG58">
+    <cfRule type="expression" priority="25" dxfId="2" stopIfTrue="1">
+      <formula>AND($AF9="外国",AG9="")</formula>
     </cfRule>
     <cfRule type="expression" priority="30" dxfId="3" stopIfTrue="1">
-      <formula>AND($AD9&lt;&gt;"",NOT($AD9="外国"),AF9="")</formula>
+      <formula>AND($AF9&lt;&gt;"",NOT($AF9="外国"),AG9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="49" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(AF9),AF9&gt;80000)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH9:AH58">
+    <cfRule type="expression" priority="26" dxfId="2" stopIfTrue="1">
+      <formula>AND($AF9="外国",AH9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="31" dxfId="3" stopIfTrue="1">
+      <formula>AND($AF9&lt;&gt;"",NOT($AF9="外国"),AH9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AH9),AH9&gt;80000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC9:AC58">
+    <cfRule type="expression" priority="27" dxfId="2" stopIfTrue="1">
+      <formula>AND($AB9="未回収",AC9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="3" stopIfTrue="1">
+      <formula>AND($AB9&lt;&gt;"",NOT($AB9="未回収"),AC9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J58">
-    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
       <formula>AND(J9&lt;&gt;"",LENB(J9)&lt;&gt;LEN(J9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K58">
-    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
       <formula>AND(K9&lt;&gt;"",LENB(K9)&lt;&gt;LEN(K9))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG9:AG58">
-    <cfRule type="expression" priority="50" dxfId="0" stopIfTrue="1">
-      <formula>AG9="CSV可"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
-      <formula>AG9="未入力"</formula>
+  <conditionalFormatting sqref="P9:P58">
+    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(P9),P9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="21">
+  <conditionalFormatting sqref="AI9:AI58">
+    <cfRule type="expression" priority="53" dxfId="0" stopIfTrue="1">
+      <formula>AI9="CSV可"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" dxfId="1" stopIfTrue="1">
+      <formula>AI9="未入力"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="22">
     <dataValidation sqref="C8:C58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦の生年月日。例 1990/4/1。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
@@ -4640,44 +4820,48 @@
     <dataValidation sqref="O8:O58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="分かる場合のみ選択。空欄で構いません。最終判断は当事務所とハローワークが行います。" type="list" errorStyle="stop">
       <formula1>m_離職理由区分</formula1>
     </dataValidation>
-    <dataValidation sqref="Q8:Q58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="有期契約（退職理由＝契約期間満了）のとき必須。&#10;契約書に更新の定めがあったか。離職理由区分・給付制限・所定給付日数の判定に直結します。" type="list" errorStyle="stop">
-      <formula1>m_契約更新条項</formula1>
-    </dataValidation>
-    <dataValidation sqref="R8:R58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="有期契約（退職理由＝契約期間満了）のとき必須。&#10;本人が契約更新を希望していたか。雇止めの離職理由区分の判定に使用します。" type="list" errorStyle="stop">
-      <formula1>m_更新希望</formula1>
-    </dataValidation>
-    <dataValidation sqref="S8:S58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="この会社で雇用保険に入った日。雇用保険被保険者証・資格取得等確認通知書に載っています。" type="whole" errorStyle="warning" operator="between">
+    <dataValidation sqref="P8:P58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="会社から伝えた日、または本人から申し出があった日。分かる範囲で。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation sqref="T8:T58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="契約上の1週間の所定労働時間。実労働時間ではありません（例 40、29.5）。" type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="R8:R58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="有期契約（退職理由＝契約期間満了）のとき必須。&#10;契約書に更新の定めがあったか。離職理由区分・給付制限・所定給付日数の判定に直結します。" type="list" errorStyle="stop">
+      <formula1>m_契約更新条項</formula1>
+    </dataValidation>
+    <dataValidation sqref="S8:S58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="有期契約（退職理由＝契約期間満了）のとき必須。&#10;本人が契約更新を希望していたか。雇止めの離職理由区分の判定に使用します。" type="list" errorStyle="stop">
+      <formula1>m_更新希望</formula1>
+    </dataValidation>
+    <dataValidation sqref="T8:T58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="この会社で雇用保険に入った日。雇用保険被保険者証・資格取得等確認通知書に載っています。" type="whole" errorStyle="warning" operator="between">
+      <formula1>1</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation sqref="U8:U58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="契約上の1週間の所定労働時間。実労働時間ではありません（例 40、29.5）。" type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>80</formula2>
     </dataValidation>
-    <dataValidation sqref="U8:U58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人が離職票（基本手当の申請）を希望するか。" type="list" errorStyle="stop">
+    <dataValidation sqref="V8:V58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人が離職票（基本手当の申請）を希望するか。" type="list" errorStyle="stop">
       <formula1>m_ありなし</formula1>
     </dataValidation>
-    <dataValidation sqref="W8:W58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="離職証明書の賃金欄と被保険者期間の確認のため、離職前1年分の賃金台帳・出勤簿があるか。賃金支払基礎日数11日以上の月が12か月に満たないときは2年分。" type="list" errorStyle="stop">
+    <dataValidation sqref="X8:X58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="離職証明書の賃金欄と被保険者期間の確認のため、離職前1年分の賃金台帳・出勤簿があるか。賃金支払基礎日数11日以上の月が12か月に満たないときは2年分。" type="list" errorStyle="stop">
       <formula1>m_ありなし</formula1>
     </dataValidation>
-    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
+    <dataValidation sqref="AB8:AB58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
       <formula1>m_回収状況</formula1>
     </dataValidation>
-    <dataValidation sqref="AB8:AB58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職後の医療保険の予定（任意継続・扶養・国保）。" type="list" errorStyle="stop">
+    <dataValidation sqref="AD8:AD58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職後の医療保険の予定（任意継続・扶養・国保）。" type="list" errorStyle="stop">
       <formula1>m_退職後</formula1>
     </dataValidation>
-    <dataValidation sqref="AD8:AD58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="日本国籍の方は『日本』。外国籍の方は『外国』を選び、右の2欄もご記入ください。" type="list" errorStyle="stop">
+    <dataValidation sqref="AF8:AF58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="日本国籍の方は『日本』。外国籍の方は『外国』を選び、右の2欄もご記入ください。" type="list" errorStyle="stop">
       <formula1>m_国籍</formula1>
     </dataValidation>
-    <dataValidation sqref="AF8:AF58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="在留カードの『在留期間（満了日）』。西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
+    <dataValidation sqref="AH8:AH58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="在留カードの『在留期間（満了日）』。西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
@@ -5373,7 +5557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5649,7 +5833,7 @@
     <row r="16">
       <c r="A16" s="50" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B16" s="50" t="inlineStr">
@@ -5659,7 +5843,7 @@
       </c>
       <c r="C16" s="50" t="inlineStr">
         <is>
-          <t>雇用保険 資格取得年月日</t>
+          <t>退職の話が出た日</t>
         </is>
       </c>
       <c r="D16" s="50" t="n">
@@ -5669,7 +5853,7 @@
     <row r="17">
       <c r="A17" s="50" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B17" s="50" t="inlineStr">
@@ -5679,10 +5863,30 @@
       </c>
       <c r="C17" s="50" t="inlineStr">
         <is>
+          <t>雇用保険 資格取得年月日</t>
+        </is>
+      </c>
+      <c r="D17" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>AH</t>
+        </is>
+      </c>
+      <c r="B18" s="50" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="inlineStr">
+        <is>
           <t>在留期間の満了日【外国籍のとき必須】</t>
         </is>
       </c>
-      <c r="D17" s="50" t="n">
+      <c r="D18" s="50" t="n">
         <v>0</v>
       </c>
     </row>

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -1459,7 +1459,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="53.5" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
           <t>健康保険・厚生年金の事業所整理記号</t>
@@ -1468,11 +1468,11 @@
       <c r="C9" s="18" t="n"/>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>毎月20日ごろ年金事務所から届く『保険料納入告知額・領収済額通知書』に載っています。口座振替の会社は別名の紙で届きます。例）12-アイウ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
+          <t>毎月20日ごろ年金事務所から届く『保険料納入告知額・領収済額通知書』に載っています。口座振替の会社は別名の紙で届きます。例）12-アイウ。2回目以降のご注文で、前回お知らせいただいていれば『前回と同じ』とご記入ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="53.5" customHeight="1">
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t>同 事業所番号</t>
@@ -1481,11 +1481,11 @@
       <c r="C10" s="18" t="n"/>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>同じ紙の整理記号の隣にある番号です。5桁。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="37" customHeight="1">
+          <t>同じ紙の整理記号の隣にある番号です。5桁。2回目以降のご注文で、前回お知らせいただいていれば『前回と同じ』とご記入ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t>雇用保険の事業所番号</t>
@@ -1494,7 +1494,7 @@
       <c r="C11" s="18" t="n"/>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>『雇用保険適用事業所設置届 事業主控』または資格取得等確認通知書に載っています。4桁-6桁-1桁。例）1610-123456-7</t>
+          <t>『雇用保険適用事業所設置届 事業主控』または資格取得等確認通知書に載っています。4桁-6桁-1桁。例）1610-123456-7。2回目以降のご注文で、前回お知らせいただいていれば『前回と同じ』とご記入ください。</t>
         </is>
       </c>
     </row>

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -636,55 +636,50 @@
     </comment>
     <comment ref="X7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職証明書の賃金欄作成のための賃金台帳・出勤簿の添付確認。</t>
+        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
       </text>
     </comment>
     <comment ref="Y7" authorId="0" shapeId="0">
       <text>
-        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
+        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
       </text>
     </comment>
     <comment ref="Z7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
+        <t>用途：直近賞与の参考値。</t>
       </text>
     </comment>
     <comment ref="AA7" authorId="0" shapeId="0">
       <text>
-        <t>用途：直近賞与の参考値。</t>
+        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
       </text>
     </comment>
     <comment ref="AB7" authorId="0" shapeId="0">
       <text>
-        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
+        <t>用途：健康保険被保険者証等回収不能届に書く品目。</t>
       </text>
     </comment>
     <comment ref="AC7" authorId="0" shapeId="0">
       <text>
-        <t>用途：健康保険被保険者証等回収不能届に書く品目。</t>
+        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
       </text>
     </comment>
     <comment ref="AD7" authorId="0" shapeId="0">
       <text>
-        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
+        <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
       </text>
     </comment>
     <comment ref="AE7" authorId="0" shapeId="0">
       <text>
-        <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
+        <t>用途：外国人雇用状況の届出（資格取得届・喪失届と一体）の国籍欄。</t>
       </text>
     </comment>
     <comment ref="AF7" authorId="0" shapeId="0">
       <text>
-        <t>用途：外国人雇用状況の届出（資格取得届・喪失届と一体）の国籍欄。</t>
+        <t>用途：同 在留資格欄。外国籍の方のみ。</t>
       </text>
     </comment>
     <comment ref="AG7" authorId="0" shapeId="0">
-      <text>
-        <t>用途：同 在留資格欄。外国籍の方のみ。</t>
-      </text>
-    </comment>
-    <comment ref="AH7" authorId="0" shapeId="0">
       <text>
         <t>用途：同 在留期間欄。外国籍の方のみ。</t>
       </text>
@@ -1681,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1707,19 +1702,18 @@
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="32" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="36" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
-    <col width="24" customWidth="1" min="33" max="33"/>
-    <col width="22" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="36" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1728,7 +1722,7 @@
           <t>退職 情報</t>
         </is>
       </c>
-      <c r="R1" s="26" t="inlineStr">
+      <c r="Q1" s="26" t="inlineStr">
         <is>
           <t>※離職理由区分は目安。最終判断は社労士・ハローワークが行います。</t>
         </is>
@@ -1784,11 +1778,11 @@
         <v/>
       </c>
       <c r="C4" s="29">
-        <f>COUNTIF(AJ9:AJ58,0)</f>
+        <f>COUNTIF(AI9:AI58,0)</f>
         <v/>
       </c>
       <c r="E4" s="29">
-        <f>SUM(AJ9:AJ58)</f>
+        <f>SUM(AI9:AI58)</f>
         <v/>
       </c>
       <c r="G4" s="30">
@@ -1826,17 +1820,17 @@
           <t>雇用保険</t>
         </is>
       </c>
-      <c r="AB6" s="35" t="inlineStr">
+      <c r="AA6" s="35" t="inlineStr">
         <is>
           <t>社会保険</t>
         </is>
       </c>
-      <c r="AE6" s="36" t="inlineStr">
+      <c r="AD6" s="36" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AF6" s="37" t="inlineStr">
+      <c r="AE6" s="37" t="inlineStr">
         <is>
           <t>外国籍のとき</t>
         </is>
@@ -1939,10 +1933,10 @@
 【任】</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>離職理由の具体的事情
-【必】</t>
+【条件により必須】</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
@@ -1981,73 +1975,67 @@
 【任】</t>
         </is>
       </c>
-      <c r="X7" s="6" t="inlineStr">
-        <is>
-          <t>賃金台帳・出勤簿の添付
-【必】</t>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>賃金締切日
+【条件により必須】</t>
         </is>
       </c>
       <c r="Y7" s="7" t="inlineStr">
-        <is>
-          <t>賃金締切日
-【任】</t>
-        </is>
-      </c>
-      <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>離職前賃金（直近1か月・円）
 【任】</t>
         </is>
       </c>
-      <c r="AA7" s="7" t="inlineStr">
+      <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>直近の賞与（円）
 【任】</t>
         </is>
       </c>
-      <c r="AB7" s="6" t="inlineStr">
+      <c r="AA7" s="6" t="inlineStr">
         <is>
           <t>資格確認書等の回収
 【必】</t>
         </is>
       </c>
-      <c r="AC7" s="7" t="inlineStr">
+      <c r="AB7" s="7" t="inlineStr">
         <is>
           <t>回収できなかったもの
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AD7" s="6" t="inlineStr">
+      <c r="AC7" s="7" t="inlineStr">
         <is>
           <t>退職後の希望
-【必】</t>
-        </is>
-      </c>
-      <c r="AE7" s="7" t="inlineStr">
+【任】</t>
+        </is>
+      </c>
+      <c r="AD7" s="7" t="inlineStr">
         <is>
           <t>備考（連絡事項）
 【任】</t>
         </is>
       </c>
-      <c r="AF7" s="7" t="inlineStr">
+      <c r="AE7" s="7" t="inlineStr">
         <is>
           <t>国籍・地域
 【任】</t>
         </is>
       </c>
-      <c r="AG7" s="7" t="inlineStr">
+      <c r="AF7" s="7" t="inlineStr">
         <is>
           <t>在留資格【外国籍のとき必須】
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AH7" s="7" t="inlineStr">
+      <c r="AG7" s="7" t="inlineStr">
         <is>
           <t>在留期間の満了日【外国籍のとき必須】
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AI7" s="38" t="inlineStr">
+      <c r="AH7" s="38" t="inlineStr">
         <is>
           <t>行ステータス
 （CSV可否）</t>
@@ -2157,43 +2145,38 @@
       <c r="W8" s="40" t="n"/>
       <c r="X8" s="40" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="Y8" s="40" t="inlineStr">
-        <is>
           <t>毎月末日</t>
         </is>
       </c>
+      <c r="Y8" s="44" t="n">
+        <v>300000</v>
+      </c>
       <c r="Z8" s="44" t="n">
-        <v>300000</v>
-      </c>
-      <c r="AA8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" s="40" t="inlineStr">
+      <c r="AA8" s="40" t="inlineStr">
         <is>
           <t>回収済</t>
         </is>
       </c>
-      <c r="AC8" s="40" t="inlineStr"/>
+      <c r="AB8" s="40" t="inlineStr"/>
+      <c r="AC8" s="40" t="inlineStr">
+        <is>
+          <t>家族の扶養に入る</t>
+        </is>
+      </c>
       <c r="AD8" s="40" t="inlineStr">
         <is>
-          <t>家族の扶養に入る</t>
+          <t>← この行は記入例です</t>
         </is>
       </c>
       <c r="AE8" s="40" t="inlineStr">
         <is>
-          <t>← この行は記入例です</t>
-        </is>
-      </c>
-      <c r="AF8" s="40" t="inlineStr">
-        <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="AG8" s="40" t="n"/>
-      <c r="AH8" s="41" t="n"/>
+      <c r="AF8" s="40" t="n"/>
+      <c r="AG8" s="41" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
@@ -2223,22 +2206,21 @@
       <c r="V9" s="18" t="n"/>
       <c r="W9" s="18" t="n"/>
       <c r="X9" s="18" t="n"/>
-      <c r="Y9" s="18" t="n"/>
+      <c r="Y9" s="48" t="n"/>
       <c r="Z9" s="48" t="n"/>
-      <c r="AA9" s="48" t="n"/>
+      <c r="AA9" s="18" t="n"/>
       <c r="AB9" s="18" t="n"/>
       <c r="AC9" s="18" t="n"/>
       <c r="AD9" s="18" t="n"/>
       <c r="AE9" s="18" t="n"/>
       <c r="AF9" s="18" t="n"/>
-      <c r="AG9" s="18" t="n"/>
-      <c r="AH9" s="20" t="n"/>
-      <c r="AI9" s="13">
-        <f>IF($A9="","",IF(AJ9&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ9">
-        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($Q9="",1,0)+IF($T9="",1,0)+IF($U9="",1,0)+IF($V9="",1,0)+IF($X9="",1,0)+IF($AB9="",1,0)+IF($AD9="",1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0)+IF(AND($N9="契約期間満了",$S9=""),1,0)+IF(AND($AF9="外国",$AG9=""),1,0)+IF(AND($AF9="外国",$AH9=""),1,0)+IF(AND($AB9="未回収",$AC9=""),1,0))</f>
+      <c r="AG9" s="20" t="n"/>
+      <c r="AH9" s="13">
+        <f>IF($A9="","",IF(AI9&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI9">
+        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($T9="",1,0)+IF($U9="",1,0)+IF($V9="",1,0)+IF($AA9="",1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0)+IF(AND($N9="契約期間満了",$S9=""),1,0)+IF(AND($AE9="外国",$AF9=""),1,0)+IF(AND($AE9="外国",$AG9=""),1,0)+IF(AND($AA9="未回収",$AB9=""),1,0)+IF(AND($V9="あり",$Q9=""),1,0)+IF(AND($V9="あり",$X9=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2270,22 +2252,21 @@
       <c r="V10" s="18" t="n"/>
       <c r="W10" s="18" t="n"/>
       <c r="X10" s="18" t="n"/>
-      <c r="Y10" s="18" t="n"/>
+      <c r="Y10" s="48" t="n"/>
       <c r="Z10" s="48" t="n"/>
-      <c r="AA10" s="48" t="n"/>
+      <c r="AA10" s="18" t="n"/>
       <c r="AB10" s="18" t="n"/>
       <c r="AC10" s="18" t="n"/>
       <c r="AD10" s="18" t="n"/>
       <c r="AE10" s="18" t="n"/>
       <c r="AF10" s="18" t="n"/>
-      <c r="AG10" s="18" t="n"/>
-      <c r="AH10" s="20" t="n"/>
-      <c r="AI10" s="13">
-        <f>IF($A10="","",IF(AJ10&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ10">
-        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($Q10="",1,0)+IF($T10="",1,0)+IF($U10="",1,0)+IF($V10="",1,0)+IF($X10="",1,0)+IF($AB10="",1,0)+IF($AD10="",1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0)+IF(AND($N10="契約期間満了",$S10=""),1,0)+IF(AND($AF10="外国",$AG10=""),1,0)+IF(AND($AF10="外国",$AH10=""),1,0)+IF(AND($AB10="未回収",$AC10=""),1,0))</f>
+      <c r="AG10" s="20" t="n"/>
+      <c r="AH10" s="13">
+        <f>IF($A10="","",IF(AI10&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI10">
+        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($T10="",1,0)+IF($U10="",1,0)+IF($V10="",1,0)+IF($AA10="",1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0)+IF(AND($N10="契約期間満了",$S10=""),1,0)+IF(AND($AE10="外国",$AF10=""),1,0)+IF(AND($AE10="外国",$AG10=""),1,0)+IF(AND($AA10="未回収",$AB10=""),1,0)+IF(AND($V10="あり",$Q10=""),1,0)+IF(AND($V10="あり",$X10=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2317,22 +2298,21 @@
       <c r="V11" s="18" t="n"/>
       <c r="W11" s="18" t="n"/>
       <c r="X11" s="18" t="n"/>
-      <c r="Y11" s="18" t="n"/>
+      <c r="Y11" s="48" t="n"/>
       <c r="Z11" s="48" t="n"/>
-      <c r="AA11" s="48" t="n"/>
+      <c r="AA11" s="18" t="n"/>
       <c r="AB11" s="18" t="n"/>
       <c r="AC11" s="18" t="n"/>
       <c r="AD11" s="18" t="n"/>
       <c r="AE11" s="18" t="n"/>
       <c r="AF11" s="18" t="n"/>
-      <c r="AG11" s="18" t="n"/>
-      <c r="AH11" s="20" t="n"/>
-      <c r="AI11" s="13">
-        <f>IF($A11="","",IF(AJ11&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ11">
-        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($Q11="",1,0)+IF($T11="",1,0)+IF($U11="",1,0)+IF($V11="",1,0)+IF($X11="",1,0)+IF($AB11="",1,0)+IF($AD11="",1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0)+IF(AND($N11="契約期間満了",$S11=""),1,0)+IF(AND($AF11="外国",$AG11=""),1,0)+IF(AND($AF11="外国",$AH11=""),1,0)+IF(AND($AB11="未回収",$AC11=""),1,0))</f>
+      <c r="AG11" s="20" t="n"/>
+      <c r="AH11" s="13">
+        <f>IF($A11="","",IF(AI11&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI11">
+        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($T11="",1,0)+IF($U11="",1,0)+IF($V11="",1,0)+IF($AA11="",1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0)+IF(AND($N11="契約期間満了",$S11=""),1,0)+IF(AND($AE11="外国",$AF11=""),1,0)+IF(AND($AE11="外国",$AG11=""),1,0)+IF(AND($AA11="未回収",$AB11=""),1,0)+IF(AND($V11="あり",$Q11=""),1,0)+IF(AND($V11="あり",$X11=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2364,22 +2344,21 @@
       <c r="V12" s="18" t="n"/>
       <c r="W12" s="18" t="n"/>
       <c r="X12" s="18" t="n"/>
-      <c r="Y12" s="18" t="n"/>
+      <c r="Y12" s="48" t="n"/>
       <c r="Z12" s="48" t="n"/>
-      <c r="AA12" s="48" t="n"/>
+      <c r="AA12" s="18" t="n"/>
       <c r="AB12" s="18" t="n"/>
       <c r="AC12" s="18" t="n"/>
       <c r="AD12" s="18" t="n"/>
       <c r="AE12" s="18" t="n"/>
       <c r="AF12" s="18" t="n"/>
-      <c r="AG12" s="18" t="n"/>
-      <c r="AH12" s="20" t="n"/>
-      <c r="AI12" s="13">
-        <f>IF($A12="","",IF(AJ12&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ12">
-        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($Q12="",1,0)+IF($T12="",1,0)+IF($U12="",1,0)+IF($V12="",1,0)+IF($X12="",1,0)+IF($AB12="",1,0)+IF($AD12="",1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0)+IF(AND($N12="契約期間満了",$S12=""),1,0)+IF(AND($AF12="外国",$AG12=""),1,0)+IF(AND($AF12="外国",$AH12=""),1,0)+IF(AND($AB12="未回収",$AC12=""),1,0))</f>
+      <c r="AG12" s="20" t="n"/>
+      <c r="AH12" s="13">
+        <f>IF($A12="","",IF(AI12&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI12">
+        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($T12="",1,0)+IF($U12="",1,0)+IF($V12="",1,0)+IF($AA12="",1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0)+IF(AND($N12="契約期間満了",$S12=""),1,0)+IF(AND($AE12="外国",$AF12=""),1,0)+IF(AND($AE12="外国",$AG12=""),1,0)+IF(AND($AA12="未回収",$AB12=""),1,0)+IF(AND($V12="あり",$Q12=""),1,0)+IF(AND($V12="あり",$X12=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2411,22 +2390,21 @@
       <c r="V13" s="18" t="n"/>
       <c r="W13" s="18" t="n"/>
       <c r="X13" s="18" t="n"/>
-      <c r="Y13" s="18" t="n"/>
+      <c r="Y13" s="48" t="n"/>
       <c r="Z13" s="48" t="n"/>
-      <c r="AA13" s="48" t="n"/>
+      <c r="AA13" s="18" t="n"/>
       <c r="AB13" s="18" t="n"/>
       <c r="AC13" s="18" t="n"/>
       <c r="AD13" s="18" t="n"/>
       <c r="AE13" s="18" t="n"/>
       <c r="AF13" s="18" t="n"/>
-      <c r="AG13" s="18" t="n"/>
-      <c r="AH13" s="20" t="n"/>
-      <c r="AI13" s="13">
-        <f>IF($A13="","",IF(AJ13&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ13">
-        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($Q13="",1,0)+IF($T13="",1,0)+IF($U13="",1,0)+IF($V13="",1,0)+IF($X13="",1,0)+IF($AB13="",1,0)+IF($AD13="",1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0)+IF(AND($N13="契約期間満了",$S13=""),1,0)+IF(AND($AF13="外国",$AG13=""),1,0)+IF(AND($AF13="外国",$AH13=""),1,0)+IF(AND($AB13="未回収",$AC13=""),1,0))</f>
+      <c r="AG13" s="20" t="n"/>
+      <c r="AH13" s="13">
+        <f>IF($A13="","",IF(AI13&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI13">
+        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($T13="",1,0)+IF($U13="",1,0)+IF($V13="",1,0)+IF($AA13="",1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0)+IF(AND($N13="契約期間満了",$S13=""),1,0)+IF(AND($AE13="外国",$AF13=""),1,0)+IF(AND($AE13="外国",$AG13=""),1,0)+IF(AND($AA13="未回収",$AB13=""),1,0)+IF(AND($V13="あり",$Q13=""),1,0)+IF(AND($V13="あり",$X13=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2458,22 +2436,21 @@
       <c r="V14" s="18" t="n"/>
       <c r="W14" s="18" t="n"/>
       <c r="X14" s="18" t="n"/>
-      <c r="Y14" s="18" t="n"/>
+      <c r="Y14" s="48" t="n"/>
       <c r="Z14" s="48" t="n"/>
-      <c r="AA14" s="48" t="n"/>
+      <c r="AA14" s="18" t="n"/>
       <c r="AB14" s="18" t="n"/>
       <c r="AC14" s="18" t="n"/>
       <c r="AD14" s="18" t="n"/>
       <c r="AE14" s="18" t="n"/>
       <c r="AF14" s="18" t="n"/>
-      <c r="AG14" s="18" t="n"/>
-      <c r="AH14" s="20" t="n"/>
-      <c r="AI14" s="13">
-        <f>IF($A14="","",IF(AJ14&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ14">
-        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($Q14="",1,0)+IF($T14="",1,0)+IF($U14="",1,0)+IF($V14="",1,0)+IF($X14="",1,0)+IF($AB14="",1,0)+IF($AD14="",1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0)+IF(AND($N14="契約期間満了",$S14=""),1,0)+IF(AND($AF14="外国",$AG14=""),1,0)+IF(AND($AF14="外国",$AH14=""),1,0)+IF(AND($AB14="未回収",$AC14=""),1,0))</f>
+      <c r="AG14" s="20" t="n"/>
+      <c r="AH14" s="13">
+        <f>IF($A14="","",IF(AI14&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI14">
+        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($T14="",1,0)+IF($U14="",1,0)+IF($V14="",1,0)+IF($AA14="",1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0)+IF(AND($N14="契約期間満了",$S14=""),1,0)+IF(AND($AE14="外国",$AF14=""),1,0)+IF(AND($AE14="外国",$AG14=""),1,0)+IF(AND($AA14="未回収",$AB14=""),1,0)+IF(AND($V14="あり",$Q14=""),1,0)+IF(AND($V14="あり",$X14=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2505,22 +2482,21 @@
       <c r="V15" s="18" t="n"/>
       <c r="W15" s="18" t="n"/>
       <c r="X15" s="18" t="n"/>
-      <c r="Y15" s="18" t="n"/>
+      <c r="Y15" s="48" t="n"/>
       <c r="Z15" s="48" t="n"/>
-      <c r="AA15" s="48" t="n"/>
+      <c r="AA15" s="18" t="n"/>
       <c r="AB15" s="18" t="n"/>
       <c r="AC15" s="18" t="n"/>
       <c r="AD15" s="18" t="n"/>
       <c r="AE15" s="18" t="n"/>
       <c r="AF15" s="18" t="n"/>
-      <c r="AG15" s="18" t="n"/>
-      <c r="AH15" s="20" t="n"/>
-      <c r="AI15" s="13">
-        <f>IF($A15="","",IF(AJ15&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ15">
-        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($Q15="",1,0)+IF($T15="",1,0)+IF($U15="",1,0)+IF($V15="",1,0)+IF($X15="",1,0)+IF($AB15="",1,0)+IF($AD15="",1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0)+IF(AND($N15="契約期間満了",$S15=""),1,0)+IF(AND($AF15="外国",$AG15=""),1,0)+IF(AND($AF15="外国",$AH15=""),1,0)+IF(AND($AB15="未回収",$AC15=""),1,0))</f>
+      <c r="AG15" s="20" t="n"/>
+      <c r="AH15" s="13">
+        <f>IF($A15="","",IF(AI15&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI15">
+        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($T15="",1,0)+IF($U15="",1,0)+IF($V15="",1,0)+IF($AA15="",1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0)+IF(AND($N15="契約期間満了",$S15=""),1,0)+IF(AND($AE15="外国",$AF15=""),1,0)+IF(AND($AE15="外国",$AG15=""),1,0)+IF(AND($AA15="未回収",$AB15=""),1,0)+IF(AND($V15="あり",$Q15=""),1,0)+IF(AND($V15="あり",$X15=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2552,22 +2528,21 @@
       <c r="V16" s="18" t="n"/>
       <c r="W16" s="18" t="n"/>
       <c r="X16" s="18" t="n"/>
-      <c r="Y16" s="18" t="n"/>
+      <c r="Y16" s="48" t="n"/>
       <c r="Z16" s="48" t="n"/>
-      <c r="AA16" s="48" t="n"/>
+      <c r="AA16" s="18" t="n"/>
       <c r="AB16" s="18" t="n"/>
       <c r="AC16" s="18" t="n"/>
       <c r="AD16" s="18" t="n"/>
       <c r="AE16" s="18" t="n"/>
       <c r="AF16" s="18" t="n"/>
-      <c r="AG16" s="18" t="n"/>
-      <c r="AH16" s="20" t="n"/>
-      <c r="AI16" s="13">
-        <f>IF($A16="","",IF(AJ16&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ16">
-        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($Q16="",1,0)+IF($T16="",1,0)+IF($U16="",1,0)+IF($V16="",1,0)+IF($X16="",1,0)+IF($AB16="",1,0)+IF($AD16="",1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0)+IF(AND($N16="契約期間満了",$S16=""),1,0)+IF(AND($AF16="外国",$AG16=""),1,0)+IF(AND($AF16="外国",$AH16=""),1,0)+IF(AND($AB16="未回収",$AC16=""),1,0))</f>
+      <c r="AG16" s="20" t="n"/>
+      <c r="AH16" s="13">
+        <f>IF($A16="","",IF(AI16&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI16">
+        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($T16="",1,0)+IF($U16="",1,0)+IF($V16="",1,0)+IF($AA16="",1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0)+IF(AND($N16="契約期間満了",$S16=""),1,0)+IF(AND($AE16="外国",$AF16=""),1,0)+IF(AND($AE16="外国",$AG16=""),1,0)+IF(AND($AA16="未回収",$AB16=""),1,0)+IF(AND($V16="あり",$Q16=""),1,0)+IF(AND($V16="あり",$X16=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2599,22 +2574,21 @@
       <c r="V17" s="18" t="n"/>
       <c r="W17" s="18" t="n"/>
       <c r="X17" s="18" t="n"/>
-      <c r="Y17" s="18" t="n"/>
+      <c r="Y17" s="48" t="n"/>
       <c r="Z17" s="48" t="n"/>
-      <c r="AA17" s="48" t="n"/>
+      <c r="AA17" s="18" t="n"/>
       <c r="AB17" s="18" t="n"/>
       <c r="AC17" s="18" t="n"/>
       <c r="AD17" s="18" t="n"/>
       <c r="AE17" s="18" t="n"/>
       <c r="AF17" s="18" t="n"/>
-      <c r="AG17" s="18" t="n"/>
-      <c r="AH17" s="20" t="n"/>
-      <c r="AI17" s="13">
-        <f>IF($A17="","",IF(AJ17&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ17">
-        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($Q17="",1,0)+IF($T17="",1,0)+IF($U17="",1,0)+IF($V17="",1,0)+IF($X17="",1,0)+IF($AB17="",1,0)+IF($AD17="",1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0)+IF(AND($N17="契約期間満了",$S17=""),1,0)+IF(AND($AF17="外国",$AG17=""),1,0)+IF(AND($AF17="外国",$AH17=""),1,0)+IF(AND($AB17="未回収",$AC17=""),1,0))</f>
+      <c r="AG17" s="20" t="n"/>
+      <c r="AH17" s="13">
+        <f>IF($A17="","",IF(AI17&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI17">
+        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($T17="",1,0)+IF($U17="",1,0)+IF($V17="",1,0)+IF($AA17="",1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0)+IF(AND($N17="契約期間満了",$S17=""),1,0)+IF(AND($AE17="外国",$AF17=""),1,0)+IF(AND($AE17="外国",$AG17=""),1,0)+IF(AND($AA17="未回収",$AB17=""),1,0)+IF(AND($V17="あり",$Q17=""),1,0)+IF(AND($V17="あり",$X17=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2646,22 +2620,21 @@
       <c r="V18" s="18" t="n"/>
       <c r="W18" s="18" t="n"/>
       <c r="X18" s="18" t="n"/>
-      <c r="Y18" s="18" t="n"/>
+      <c r="Y18" s="48" t="n"/>
       <c r="Z18" s="48" t="n"/>
-      <c r="AA18" s="48" t="n"/>
+      <c r="AA18" s="18" t="n"/>
       <c r="AB18" s="18" t="n"/>
       <c r="AC18" s="18" t="n"/>
       <c r="AD18" s="18" t="n"/>
       <c r="AE18" s="18" t="n"/>
       <c r="AF18" s="18" t="n"/>
-      <c r="AG18" s="18" t="n"/>
-      <c r="AH18" s="20" t="n"/>
-      <c r="AI18" s="13">
-        <f>IF($A18="","",IF(AJ18&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ18">
-        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($Q18="",1,0)+IF($T18="",1,0)+IF($U18="",1,0)+IF($V18="",1,0)+IF($X18="",1,0)+IF($AB18="",1,0)+IF($AD18="",1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0)+IF(AND($N18="契約期間満了",$S18=""),1,0)+IF(AND($AF18="外国",$AG18=""),1,0)+IF(AND($AF18="外国",$AH18=""),1,0)+IF(AND($AB18="未回収",$AC18=""),1,0))</f>
+      <c r="AG18" s="20" t="n"/>
+      <c r="AH18" s="13">
+        <f>IF($A18="","",IF(AI18&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI18">
+        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($T18="",1,0)+IF($U18="",1,0)+IF($V18="",1,0)+IF($AA18="",1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0)+IF(AND($N18="契約期間満了",$S18=""),1,0)+IF(AND($AE18="外国",$AF18=""),1,0)+IF(AND($AE18="外国",$AG18=""),1,0)+IF(AND($AA18="未回収",$AB18=""),1,0)+IF(AND($V18="あり",$Q18=""),1,0)+IF(AND($V18="あり",$X18=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2693,22 +2666,21 @@
       <c r="V19" s="18" t="n"/>
       <c r="W19" s="18" t="n"/>
       <c r="X19" s="18" t="n"/>
-      <c r="Y19" s="18" t="n"/>
+      <c r="Y19" s="48" t="n"/>
       <c r="Z19" s="48" t="n"/>
-      <c r="AA19" s="48" t="n"/>
+      <c r="AA19" s="18" t="n"/>
       <c r="AB19" s="18" t="n"/>
       <c r="AC19" s="18" t="n"/>
       <c r="AD19" s="18" t="n"/>
       <c r="AE19" s="18" t="n"/>
       <c r="AF19" s="18" t="n"/>
-      <c r="AG19" s="18" t="n"/>
-      <c r="AH19" s="20" t="n"/>
-      <c r="AI19" s="13">
-        <f>IF($A19="","",IF(AJ19&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ19">
-        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($Q19="",1,0)+IF($T19="",1,0)+IF($U19="",1,0)+IF($V19="",1,0)+IF($X19="",1,0)+IF($AB19="",1,0)+IF($AD19="",1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0)+IF(AND($N19="契約期間満了",$S19=""),1,0)+IF(AND($AF19="外国",$AG19=""),1,0)+IF(AND($AF19="外国",$AH19=""),1,0)+IF(AND($AB19="未回収",$AC19=""),1,0))</f>
+      <c r="AG19" s="20" t="n"/>
+      <c r="AH19" s="13">
+        <f>IF($A19="","",IF(AI19&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI19">
+        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($T19="",1,0)+IF($U19="",1,0)+IF($V19="",1,0)+IF($AA19="",1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0)+IF(AND($N19="契約期間満了",$S19=""),1,0)+IF(AND($AE19="外国",$AF19=""),1,0)+IF(AND($AE19="外国",$AG19=""),1,0)+IF(AND($AA19="未回収",$AB19=""),1,0)+IF(AND($V19="あり",$Q19=""),1,0)+IF(AND($V19="あり",$X19=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2740,22 +2712,21 @@
       <c r="V20" s="18" t="n"/>
       <c r="W20" s="18" t="n"/>
       <c r="X20" s="18" t="n"/>
-      <c r="Y20" s="18" t="n"/>
+      <c r="Y20" s="48" t="n"/>
       <c r="Z20" s="48" t="n"/>
-      <c r="AA20" s="48" t="n"/>
+      <c r="AA20" s="18" t="n"/>
       <c r="AB20" s="18" t="n"/>
       <c r="AC20" s="18" t="n"/>
       <c r="AD20" s="18" t="n"/>
       <c r="AE20" s="18" t="n"/>
       <c r="AF20" s="18" t="n"/>
-      <c r="AG20" s="18" t="n"/>
-      <c r="AH20" s="20" t="n"/>
-      <c r="AI20" s="13">
-        <f>IF($A20="","",IF(AJ20&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ20">
-        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($Q20="",1,0)+IF($T20="",1,0)+IF($U20="",1,0)+IF($V20="",1,0)+IF($X20="",1,0)+IF($AB20="",1,0)+IF($AD20="",1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0)+IF(AND($N20="契約期間満了",$S20=""),1,0)+IF(AND($AF20="外国",$AG20=""),1,0)+IF(AND($AF20="外国",$AH20=""),1,0)+IF(AND($AB20="未回収",$AC20=""),1,0))</f>
+      <c r="AG20" s="20" t="n"/>
+      <c r="AH20" s="13">
+        <f>IF($A20="","",IF(AI20&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI20">
+        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($T20="",1,0)+IF($U20="",1,0)+IF($V20="",1,0)+IF($AA20="",1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0)+IF(AND($N20="契約期間満了",$S20=""),1,0)+IF(AND($AE20="外国",$AF20=""),1,0)+IF(AND($AE20="外国",$AG20=""),1,0)+IF(AND($AA20="未回収",$AB20=""),1,0)+IF(AND($V20="あり",$Q20=""),1,0)+IF(AND($V20="あり",$X20=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2787,22 +2758,21 @@
       <c r="V21" s="18" t="n"/>
       <c r="W21" s="18" t="n"/>
       <c r="X21" s="18" t="n"/>
-      <c r="Y21" s="18" t="n"/>
+      <c r="Y21" s="48" t="n"/>
       <c r="Z21" s="48" t="n"/>
-      <c r="AA21" s="48" t="n"/>
+      <c r="AA21" s="18" t="n"/>
       <c r="AB21" s="18" t="n"/>
       <c r="AC21" s="18" t="n"/>
       <c r="AD21" s="18" t="n"/>
       <c r="AE21" s="18" t="n"/>
       <c r="AF21" s="18" t="n"/>
-      <c r="AG21" s="18" t="n"/>
-      <c r="AH21" s="20" t="n"/>
-      <c r="AI21" s="13">
-        <f>IF($A21="","",IF(AJ21&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ21">
-        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($Q21="",1,0)+IF($T21="",1,0)+IF($U21="",1,0)+IF($V21="",1,0)+IF($X21="",1,0)+IF($AB21="",1,0)+IF($AD21="",1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0)+IF(AND($N21="契約期間満了",$S21=""),1,0)+IF(AND($AF21="外国",$AG21=""),1,0)+IF(AND($AF21="外国",$AH21=""),1,0)+IF(AND($AB21="未回収",$AC21=""),1,0))</f>
+      <c r="AG21" s="20" t="n"/>
+      <c r="AH21" s="13">
+        <f>IF($A21="","",IF(AI21&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI21">
+        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($T21="",1,0)+IF($U21="",1,0)+IF($V21="",1,0)+IF($AA21="",1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0)+IF(AND($N21="契約期間満了",$S21=""),1,0)+IF(AND($AE21="外国",$AF21=""),1,0)+IF(AND($AE21="外国",$AG21=""),1,0)+IF(AND($AA21="未回収",$AB21=""),1,0)+IF(AND($V21="あり",$Q21=""),1,0)+IF(AND($V21="あり",$X21=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2834,22 +2804,21 @@
       <c r="V22" s="18" t="n"/>
       <c r="W22" s="18" t="n"/>
       <c r="X22" s="18" t="n"/>
-      <c r="Y22" s="18" t="n"/>
+      <c r="Y22" s="48" t="n"/>
       <c r="Z22" s="48" t="n"/>
-      <c r="AA22" s="48" t="n"/>
+      <c r="AA22" s="18" t="n"/>
       <c r="AB22" s="18" t="n"/>
       <c r="AC22" s="18" t="n"/>
       <c r="AD22" s="18" t="n"/>
       <c r="AE22" s="18" t="n"/>
       <c r="AF22" s="18" t="n"/>
-      <c r="AG22" s="18" t="n"/>
-      <c r="AH22" s="20" t="n"/>
-      <c r="AI22" s="13">
-        <f>IF($A22="","",IF(AJ22&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ22">
-        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($Q22="",1,0)+IF($T22="",1,0)+IF($U22="",1,0)+IF($V22="",1,0)+IF($X22="",1,0)+IF($AB22="",1,0)+IF($AD22="",1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0)+IF(AND($N22="契約期間満了",$S22=""),1,0)+IF(AND($AF22="外国",$AG22=""),1,0)+IF(AND($AF22="外国",$AH22=""),1,0)+IF(AND($AB22="未回収",$AC22=""),1,0))</f>
+      <c r="AG22" s="20" t="n"/>
+      <c r="AH22" s="13">
+        <f>IF($A22="","",IF(AI22&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI22">
+        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($T22="",1,0)+IF($U22="",1,0)+IF($V22="",1,0)+IF($AA22="",1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0)+IF(AND($N22="契約期間満了",$S22=""),1,0)+IF(AND($AE22="外国",$AF22=""),1,0)+IF(AND($AE22="外国",$AG22=""),1,0)+IF(AND($AA22="未回収",$AB22=""),1,0)+IF(AND($V22="あり",$Q22=""),1,0)+IF(AND($V22="あり",$X22=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2881,22 +2850,21 @@
       <c r="V23" s="18" t="n"/>
       <c r="W23" s="18" t="n"/>
       <c r="X23" s="18" t="n"/>
-      <c r="Y23" s="18" t="n"/>
+      <c r="Y23" s="48" t="n"/>
       <c r="Z23" s="48" t="n"/>
-      <c r="AA23" s="48" t="n"/>
+      <c r="AA23" s="18" t="n"/>
       <c r="AB23" s="18" t="n"/>
       <c r="AC23" s="18" t="n"/>
       <c r="AD23" s="18" t="n"/>
       <c r="AE23" s="18" t="n"/>
       <c r="AF23" s="18" t="n"/>
-      <c r="AG23" s="18" t="n"/>
-      <c r="AH23" s="20" t="n"/>
-      <c r="AI23" s="13">
-        <f>IF($A23="","",IF(AJ23&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ23">
-        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($Q23="",1,0)+IF($T23="",1,0)+IF($U23="",1,0)+IF($V23="",1,0)+IF($X23="",1,0)+IF($AB23="",1,0)+IF($AD23="",1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0)+IF(AND($N23="契約期間満了",$S23=""),1,0)+IF(AND($AF23="外国",$AG23=""),1,0)+IF(AND($AF23="外国",$AH23=""),1,0)+IF(AND($AB23="未回収",$AC23=""),1,0))</f>
+      <c r="AG23" s="20" t="n"/>
+      <c r="AH23" s="13">
+        <f>IF($A23="","",IF(AI23&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI23">
+        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($T23="",1,0)+IF($U23="",1,0)+IF($V23="",1,0)+IF($AA23="",1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0)+IF(AND($N23="契約期間満了",$S23=""),1,0)+IF(AND($AE23="外国",$AF23=""),1,0)+IF(AND($AE23="外国",$AG23=""),1,0)+IF(AND($AA23="未回収",$AB23=""),1,0)+IF(AND($V23="あり",$Q23=""),1,0)+IF(AND($V23="あり",$X23=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2928,22 +2896,21 @@
       <c r="V24" s="18" t="n"/>
       <c r="W24" s="18" t="n"/>
       <c r="X24" s="18" t="n"/>
-      <c r="Y24" s="18" t="n"/>
+      <c r="Y24" s="48" t="n"/>
       <c r="Z24" s="48" t="n"/>
-      <c r="AA24" s="48" t="n"/>
+      <c r="AA24" s="18" t="n"/>
       <c r="AB24" s="18" t="n"/>
       <c r="AC24" s="18" t="n"/>
       <c r="AD24" s="18" t="n"/>
       <c r="AE24" s="18" t="n"/>
       <c r="AF24" s="18" t="n"/>
-      <c r="AG24" s="18" t="n"/>
-      <c r="AH24" s="20" t="n"/>
-      <c r="AI24" s="13">
-        <f>IF($A24="","",IF(AJ24&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ24">
-        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($Q24="",1,0)+IF($T24="",1,0)+IF($U24="",1,0)+IF($V24="",1,0)+IF($X24="",1,0)+IF($AB24="",1,0)+IF($AD24="",1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0)+IF(AND($N24="契約期間満了",$S24=""),1,0)+IF(AND($AF24="外国",$AG24=""),1,0)+IF(AND($AF24="外国",$AH24=""),1,0)+IF(AND($AB24="未回収",$AC24=""),1,0))</f>
+      <c r="AG24" s="20" t="n"/>
+      <c r="AH24" s="13">
+        <f>IF($A24="","",IF(AI24&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI24">
+        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($T24="",1,0)+IF($U24="",1,0)+IF($V24="",1,0)+IF($AA24="",1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0)+IF(AND($N24="契約期間満了",$S24=""),1,0)+IF(AND($AE24="外国",$AF24=""),1,0)+IF(AND($AE24="外国",$AG24=""),1,0)+IF(AND($AA24="未回収",$AB24=""),1,0)+IF(AND($V24="あり",$Q24=""),1,0)+IF(AND($V24="あり",$X24=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2975,22 +2942,21 @@
       <c r="V25" s="18" t="n"/>
       <c r="W25" s="18" t="n"/>
       <c r="X25" s="18" t="n"/>
-      <c r="Y25" s="18" t="n"/>
+      <c r="Y25" s="48" t="n"/>
       <c r="Z25" s="48" t="n"/>
-      <c r="AA25" s="48" t="n"/>
+      <c r="AA25" s="18" t="n"/>
       <c r="AB25" s="18" t="n"/>
       <c r="AC25" s="18" t="n"/>
       <c r="AD25" s="18" t="n"/>
       <c r="AE25" s="18" t="n"/>
       <c r="AF25" s="18" t="n"/>
-      <c r="AG25" s="18" t="n"/>
-      <c r="AH25" s="20" t="n"/>
-      <c r="AI25" s="13">
-        <f>IF($A25="","",IF(AJ25&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ25">
-        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($Q25="",1,0)+IF($T25="",1,0)+IF($U25="",1,0)+IF($V25="",1,0)+IF($X25="",1,0)+IF($AB25="",1,0)+IF($AD25="",1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0)+IF(AND($N25="契約期間満了",$S25=""),1,0)+IF(AND($AF25="外国",$AG25=""),1,0)+IF(AND($AF25="外国",$AH25=""),1,0)+IF(AND($AB25="未回収",$AC25=""),1,0))</f>
+      <c r="AG25" s="20" t="n"/>
+      <c r="AH25" s="13">
+        <f>IF($A25="","",IF(AI25&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI25">
+        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($T25="",1,0)+IF($U25="",1,0)+IF($V25="",1,0)+IF($AA25="",1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0)+IF(AND($N25="契約期間満了",$S25=""),1,0)+IF(AND($AE25="外国",$AF25=""),1,0)+IF(AND($AE25="外国",$AG25=""),1,0)+IF(AND($AA25="未回収",$AB25=""),1,0)+IF(AND($V25="あり",$Q25=""),1,0)+IF(AND($V25="あり",$X25=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3022,22 +2988,21 @@
       <c r="V26" s="18" t="n"/>
       <c r="W26" s="18" t="n"/>
       <c r="X26" s="18" t="n"/>
-      <c r="Y26" s="18" t="n"/>
+      <c r="Y26" s="48" t="n"/>
       <c r="Z26" s="48" t="n"/>
-      <c r="AA26" s="48" t="n"/>
+      <c r="AA26" s="18" t="n"/>
       <c r="AB26" s="18" t="n"/>
       <c r="AC26" s="18" t="n"/>
       <c r="AD26" s="18" t="n"/>
       <c r="AE26" s="18" t="n"/>
       <c r="AF26" s="18" t="n"/>
-      <c r="AG26" s="18" t="n"/>
-      <c r="AH26" s="20" t="n"/>
-      <c r="AI26" s="13">
-        <f>IF($A26="","",IF(AJ26&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ26">
-        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($Q26="",1,0)+IF($T26="",1,0)+IF($U26="",1,0)+IF($V26="",1,0)+IF($X26="",1,0)+IF($AB26="",1,0)+IF($AD26="",1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0)+IF(AND($N26="契約期間満了",$S26=""),1,0)+IF(AND($AF26="外国",$AG26=""),1,0)+IF(AND($AF26="外国",$AH26=""),1,0)+IF(AND($AB26="未回収",$AC26=""),1,0))</f>
+      <c r="AG26" s="20" t="n"/>
+      <c r="AH26" s="13">
+        <f>IF($A26="","",IF(AI26&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI26">
+        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($T26="",1,0)+IF($U26="",1,0)+IF($V26="",1,0)+IF($AA26="",1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0)+IF(AND($N26="契約期間満了",$S26=""),1,0)+IF(AND($AE26="外国",$AF26=""),1,0)+IF(AND($AE26="外国",$AG26=""),1,0)+IF(AND($AA26="未回収",$AB26=""),1,0)+IF(AND($V26="あり",$Q26=""),1,0)+IF(AND($V26="あり",$X26=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3069,22 +3034,21 @@
       <c r="V27" s="18" t="n"/>
       <c r="W27" s="18" t="n"/>
       <c r="X27" s="18" t="n"/>
-      <c r="Y27" s="18" t="n"/>
+      <c r="Y27" s="48" t="n"/>
       <c r="Z27" s="48" t="n"/>
-      <c r="AA27" s="48" t="n"/>
+      <c r="AA27" s="18" t="n"/>
       <c r="AB27" s="18" t="n"/>
       <c r="AC27" s="18" t="n"/>
       <c r="AD27" s="18" t="n"/>
       <c r="AE27" s="18" t="n"/>
       <c r="AF27" s="18" t="n"/>
-      <c r="AG27" s="18" t="n"/>
-      <c r="AH27" s="20" t="n"/>
-      <c r="AI27" s="13">
-        <f>IF($A27="","",IF(AJ27&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ27">
-        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($Q27="",1,0)+IF($T27="",1,0)+IF($U27="",1,0)+IF($V27="",1,0)+IF($X27="",1,0)+IF($AB27="",1,0)+IF($AD27="",1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0)+IF(AND($N27="契約期間満了",$S27=""),1,0)+IF(AND($AF27="外国",$AG27=""),1,0)+IF(AND($AF27="外国",$AH27=""),1,0)+IF(AND($AB27="未回収",$AC27=""),1,0))</f>
+      <c r="AG27" s="20" t="n"/>
+      <c r="AH27" s="13">
+        <f>IF($A27="","",IF(AI27&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI27">
+        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($T27="",1,0)+IF($U27="",1,0)+IF($V27="",1,0)+IF($AA27="",1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0)+IF(AND($N27="契約期間満了",$S27=""),1,0)+IF(AND($AE27="外国",$AF27=""),1,0)+IF(AND($AE27="外国",$AG27=""),1,0)+IF(AND($AA27="未回収",$AB27=""),1,0)+IF(AND($V27="あり",$Q27=""),1,0)+IF(AND($V27="あり",$X27=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3116,22 +3080,21 @@
       <c r="V28" s="18" t="n"/>
       <c r="W28" s="18" t="n"/>
       <c r="X28" s="18" t="n"/>
-      <c r="Y28" s="18" t="n"/>
+      <c r="Y28" s="48" t="n"/>
       <c r="Z28" s="48" t="n"/>
-      <c r="AA28" s="48" t="n"/>
+      <c r="AA28" s="18" t="n"/>
       <c r="AB28" s="18" t="n"/>
       <c r="AC28" s="18" t="n"/>
       <c r="AD28" s="18" t="n"/>
       <c r="AE28" s="18" t="n"/>
       <c r="AF28" s="18" t="n"/>
-      <c r="AG28" s="18" t="n"/>
-      <c r="AH28" s="20" t="n"/>
-      <c r="AI28" s="13">
-        <f>IF($A28="","",IF(AJ28&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ28">
-        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($Q28="",1,0)+IF($T28="",1,0)+IF($U28="",1,0)+IF($V28="",1,0)+IF($X28="",1,0)+IF($AB28="",1,0)+IF($AD28="",1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0)+IF(AND($N28="契約期間満了",$S28=""),1,0)+IF(AND($AF28="外国",$AG28=""),1,0)+IF(AND($AF28="外国",$AH28=""),1,0)+IF(AND($AB28="未回収",$AC28=""),1,0))</f>
+      <c r="AG28" s="20" t="n"/>
+      <c r="AH28" s="13">
+        <f>IF($A28="","",IF(AI28&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI28">
+        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($T28="",1,0)+IF($U28="",1,0)+IF($V28="",1,0)+IF($AA28="",1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0)+IF(AND($N28="契約期間満了",$S28=""),1,0)+IF(AND($AE28="外国",$AF28=""),1,0)+IF(AND($AE28="外国",$AG28=""),1,0)+IF(AND($AA28="未回収",$AB28=""),1,0)+IF(AND($V28="あり",$Q28=""),1,0)+IF(AND($V28="あり",$X28=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3163,22 +3126,21 @@
       <c r="V29" s="18" t="n"/>
       <c r="W29" s="18" t="n"/>
       <c r="X29" s="18" t="n"/>
-      <c r="Y29" s="18" t="n"/>
+      <c r="Y29" s="48" t="n"/>
       <c r="Z29" s="48" t="n"/>
-      <c r="AA29" s="48" t="n"/>
+      <c r="AA29" s="18" t="n"/>
       <c r="AB29" s="18" t="n"/>
       <c r="AC29" s="18" t="n"/>
       <c r="AD29" s="18" t="n"/>
       <c r="AE29" s="18" t="n"/>
       <c r="AF29" s="18" t="n"/>
-      <c r="AG29" s="18" t="n"/>
-      <c r="AH29" s="20" t="n"/>
-      <c r="AI29" s="13">
-        <f>IF($A29="","",IF(AJ29&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ29">
-        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($Q29="",1,0)+IF($T29="",1,0)+IF($U29="",1,0)+IF($V29="",1,0)+IF($X29="",1,0)+IF($AB29="",1,0)+IF($AD29="",1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0)+IF(AND($N29="契約期間満了",$S29=""),1,0)+IF(AND($AF29="外国",$AG29=""),1,0)+IF(AND($AF29="外国",$AH29=""),1,0)+IF(AND($AB29="未回収",$AC29=""),1,0))</f>
+      <c r="AG29" s="20" t="n"/>
+      <c r="AH29" s="13">
+        <f>IF($A29="","",IF(AI29&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI29">
+        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($T29="",1,0)+IF($U29="",1,0)+IF($V29="",1,0)+IF($AA29="",1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0)+IF(AND($N29="契約期間満了",$S29=""),1,0)+IF(AND($AE29="外国",$AF29=""),1,0)+IF(AND($AE29="外国",$AG29=""),1,0)+IF(AND($AA29="未回収",$AB29=""),1,0)+IF(AND($V29="あり",$Q29=""),1,0)+IF(AND($V29="あり",$X29=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3210,22 +3172,21 @@
       <c r="V30" s="18" t="n"/>
       <c r="W30" s="18" t="n"/>
       <c r="X30" s="18" t="n"/>
-      <c r="Y30" s="18" t="n"/>
+      <c r="Y30" s="48" t="n"/>
       <c r="Z30" s="48" t="n"/>
-      <c r="AA30" s="48" t="n"/>
+      <c r="AA30" s="18" t="n"/>
       <c r="AB30" s="18" t="n"/>
       <c r="AC30" s="18" t="n"/>
       <c r="AD30" s="18" t="n"/>
       <c r="AE30" s="18" t="n"/>
       <c r="AF30" s="18" t="n"/>
-      <c r="AG30" s="18" t="n"/>
-      <c r="AH30" s="20" t="n"/>
-      <c r="AI30" s="13">
-        <f>IF($A30="","",IF(AJ30&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ30">
-        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($Q30="",1,0)+IF($T30="",1,0)+IF($U30="",1,0)+IF($V30="",1,0)+IF($X30="",1,0)+IF($AB30="",1,0)+IF($AD30="",1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0)+IF(AND($N30="契約期間満了",$S30=""),1,0)+IF(AND($AF30="外国",$AG30=""),1,0)+IF(AND($AF30="外国",$AH30=""),1,0)+IF(AND($AB30="未回収",$AC30=""),1,0))</f>
+      <c r="AG30" s="20" t="n"/>
+      <c r="AH30" s="13">
+        <f>IF($A30="","",IF(AI30&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI30">
+        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($T30="",1,0)+IF($U30="",1,0)+IF($V30="",1,0)+IF($AA30="",1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0)+IF(AND($N30="契約期間満了",$S30=""),1,0)+IF(AND($AE30="外国",$AF30=""),1,0)+IF(AND($AE30="外国",$AG30=""),1,0)+IF(AND($AA30="未回収",$AB30=""),1,0)+IF(AND($V30="あり",$Q30=""),1,0)+IF(AND($V30="あり",$X30=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3257,22 +3218,21 @@
       <c r="V31" s="18" t="n"/>
       <c r="W31" s="18" t="n"/>
       <c r="X31" s="18" t="n"/>
-      <c r="Y31" s="18" t="n"/>
+      <c r="Y31" s="48" t="n"/>
       <c r="Z31" s="48" t="n"/>
-      <c r="AA31" s="48" t="n"/>
+      <c r="AA31" s="18" t="n"/>
       <c r="AB31" s="18" t="n"/>
       <c r="AC31" s="18" t="n"/>
       <c r="AD31" s="18" t="n"/>
       <c r="AE31" s="18" t="n"/>
       <c r="AF31" s="18" t="n"/>
-      <c r="AG31" s="18" t="n"/>
-      <c r="AH31" s="20" t="n"/>
-      <c r="AI31" s="13">
-        <f>IF($A31="","",IF(AJ31&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ31">
-        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($Q31="",1,0)+IF($T31="",1,0)+IF($U31="",1,0)+IF($V31="",1,0)+IF($X31="",1,0)+IF($AB31="",1,0)+IF($AD31="",1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0)+IF(AND($N31="契約期間満了",$S31=""),1,0)+IF(AND($AF31="外国",$AG31=""),1,0)+IF(AND($AF31="外国",$AH31=""),1,0)+IF(AND($AB31="未回収",$AC31=""),1,0))</f>
+      <c r="AG31" s="20" t="n"/>
+      <c r="AH31" s="13">
+        <f>IF($A31="","",IF(AI31&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI31">
+        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($T31="",1,0)+IF($U31="",1,0)+IF($V31="",1,0)+IF($AA31="",1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0)+IF(AND($N31="契約期間満了",$S31=""),1,0)+IF(AND($AE31="外国",$AF31=""),1,0)+IF(AND($AE31="外国",$AG31=""),1,0)+IF(AND($AA31="未回収",$AB31=""),1,0)+IF(AND($V31="あり",$Q31=""),1,0)+IF(AND($V31="あり",$X31=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3304,22 +3264,21 @@
       <c r="V32" s="18" t="n"/>
       <c r="W32" s="18" t="n"/>
       <c r="X32" s="18" t="n"/>
-      <c r="Y32" s="18" t="n"/>
+      <c r="Y32" s="48" t="n"/>
       <c r="Z32" s="48" t="n"/>
-      <c r="AA32" s="48" t="n"/>
+      <c r="AA32" s="18" t="n"/>
       <c r="AB32" s="18" t="n"/>
       <c r="AC32" s="18" t="n"/>
       <c r="AD32" s="18" t="n"/>
       <c r="AE32" s="18" t="n"/>
       <c r="AF32" s="18" t="n"/>
-      <c r="AG32" s="18" t="n"/>
-      <c r="AH32" s="20" t="n"/>
-      <c r="AI32" s="13">
-        <f>IF($A32="","",IF(AJ32&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ32">
-        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($Q32="",1,0)+IF($T32="",1,0)+IF($U32="",1,0)+IF($V32="",1,0)+IF($X32="",1,0)+IF($AB32="",1,0)+IF($AD32="",1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0)+IF(AND($N32="契約期間満了",$S32=""),1,0)+IF(AND($AF32="外国",$AG32=""),1,0)+IF(AND($AF32="外国",$AH32=""),1,0)+IF(AND($AB32="未回収",$AC32=""),1,0))</f>
+      <c r="AG32" s="20" t="n"/>
+      <c r="AH32" s="13">
+        <f>IF($A32="","",IF(AI32&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI32">
+        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($T32="",1,0)+IF($U32="",1,0)+IF($V32="",1,0)+IF($AA32="",1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0)+IF(AND($N32="契約期間満了",$S32=""),1,0)+IF(AND($AE32="外国",$AF32=""),1,0)+IF(AND($AE32="外国",$AG32=""),1,0)+IF(AND($AA32="未回収",$AB32=""),1,0)+IF(AND($V32="あり",$Q32=""),1,0)+IF(AND($V32="あり",$X32=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3351,22 +3310,21 @@
       <c r="V33" s="18" t="n"/>
       <c r="W33" s="18" t="n"/>
       <c r="X33" s="18" t="n"/>
-      <c r="Y33" s="18" t="n"/>
+      <c r="Y33" s="48" t="n"/>
       <c r="Z33" s="48" t="n"/>
-      <c r="AA33" s="48" t="n"/>
+      <c r="AA33" s="18" t="n"/>
       <c r="AB33" s="18" t="n"/>
       <c r="AC33" s="18" t="n"/>
       <c r="AD33" s="18" t="n"/>
       <c r="AE33" s="18" t="n"/>
       <c r="AF33" s="18" t="n"/>
-      <c r="AG33" s="18" t="n"/>
-      <c r="AH33" s="20" t="n"/>
-      <c r="AI33" s="13">
-        <f>IF($A33="","",IF(AJ33&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ33">
-        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($Q33="",1,0)+IF($T33="",1,0)+IF($U33="",1,0)+IF($V33="",1,0)+IF($X33="",1,0)+IF($AB33="",1,0)+IF($AD33="",1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0)+IF(AND($N33="契約期間満了",$S33=""),1,0)+IF(AND($AF33="外国",$AG33=""),1,0)+IF(AND($AF33="外国",$AH33=""),1,0)+IF(AND($AB33="未回収",$AC33=""),1,0))</f>
+      <c r="AG33" s="20" t="n"/>
+      <c r="AH33" s="13">
+        <f>IF($A33="","",IF(AI33&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI33">
+        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($T33="",1,0)+IF($U33="",1,0)+IF($V33="",1,0)+IF($AA33="",1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0)+IF(AND($N33="契約期間満了",$S33=""),1,0)+IF(AND($AE33="外国",$AF33=""),1,0)+IF(AND($AE33="外国",$AG33=""),1,0)+IF(AND($AA33="未回収",$AB33=""),1,0)+IF(AND($V33="あり",$Q33=""),1,0)+IF(AND($V33="あり",$X33=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3398,22 +3356,21 @@
       <c r="V34" s="18" t="n"/>
       <c r="W34" s="18" t="n"/>
       <c r="X34" s="18" t="n"/>
-      <c r="Y34" s="18" t="n"/>
+      <c r="Y34" s="48" t="n"/>
       <c r="Z34" s="48" t="n"/>
-      <c r="AA34" s="48" t="n"/>
+      <c r="AA34" s="18" t="n"/>
       <c r="AB34" s="18" t="n"/>
       <c r="AC34" s="18" t="n"/>
       <c r="AD34" s="18" t="n"/>
       <c r="AE34" s="18" t="n"/>
       <c r="AF34" s="18" t="n"/>
-      <c r="AG34" s="18" t="n"/>
-      <c r="AH34" s="20" t="n"/>
-      <c r="AI34" s="13">
-        <f>IF($A34="","",IF(AJ34&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ34">
-        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($Q34="",1,0)+IF($T34="",1,0)+IF($U34="",1,0)+IF($V34="",1,0)+IF($X34="",1,0)+IF($AB34="",1,0)+IF($AD34="",1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0)+IF(AND($N34="契約期間満了",$S34=""),1,0)+IF(AND($AF34="外国",$AG34=""),1,0)+IF(AND($AF34="外国",$AH34=""),1,0)+IF(AND($AB34="未回収",$AC34=""),1,0))</f>
+      <c r="AG34" s="20" t="n"/>
+      <c r="AH34" s="13">
+        <f>IF($A34="","",IF(AI34&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI34">
+        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($T34="",1,0)+IF($U34="",1,0)+IF($V34="",1,0)+IF($AA34="",1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0)+IF(AND($N34="契約期間満了",$S34=""),1,0)+IF(AND($AE34="外国",$AF34=""),1,0)+IF(AND($AE34="外国",$AG34=""),1,0)+IF(AND($AA34="未回収",$AB34=""),1,0)+IF(AND($V34="あり",$Q34=""),1,0)+IF(AND($V34="あり",$X34=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3445,22 +3402,21 @@
       <c r="V35" s="18" t="n"/>
       <c r="W35" s="18" t="n"/>
       <c r="X35" s="18" t="n"/>
-      <c r="Y35" s="18" t="n"/>
+      <c r="Y35" s="48" t="n"/>
       <c r="Z35" s="48" t="n"/>
-      <c r="AA35" s="48" t="n"/>
+      <c r="AA35" s="18" t="n"/>
       <c r="AB35" s="18" t="n"/>
       <c r="AC35" s="18" t="n"/>
       <c r="AD35" s="18" t="n"/>
       <c r="AE35" s="18" t="n"/>
       <c r="AF35" s="18" t="n"/>
-      <c r="AG35" s="18" t="n"/>
-      <c r="AH35" s="20" t="n"/>
-      <c r="AI35" s="13">
-        <f>IF($A35="","",IF(AJ35&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ35">
-        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($Q35="",1,0)+IF($T35="",1,0)+IF($U35="",1,0)+IF($V35="",1,0)+IF($X35="",1,0)+IF($AB35="",1,0)+IF($AD35="",1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0)+IF(AND($N35="契約期間満了",$S35=""),1,0)+IF(AND($AF35="外国",$AG35=""),1,0)+IF(AND($AF35="外国",$AH35=""),1,0)+IF(AND($AB35="未回収",$AC35=""),1,0))</f>
+      <c r="AG35" s="20" t="n"/>
+      <c r="AH35" s="13">
+        <f>IF($A35="","",IF(AI35&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI35">
+        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($T35="",1,0)+IF($U35="",1,0)+IF($V35="",1,0)+IF($AA35="",1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0)+IF(AND($N35="契約期間満了",$S35=""),1,0)+IF(AND($AE35="外国",$AF35=""),1,0)+IF(AND($AE35="外国",$AG35=""),1,0)+IF(AND($AA35="未回収",$AB35=""),1,0)+IF(AND($V35="あり",$Q35=""),1,0)+IF(AND($V35="あり",$X35=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3492,22 +3448,21 @@
       <c r="V36" s="18" t="n"/>
       <c r="W36" s="18" t="n"/>
       <c r="X36" s="18" t="n"/>
-      <c r="Y36" s="18" t="n"/>
+      <c r="Y36" s="48" t="n"/>
       <c r="Z36" s="48" t="n"/>
-      <c r="AA36" s="48" t="n"/>
+      <c r="AA36" s="18" t="n"/>
       <c r="AB36" s="18" t="n"/>
       <c r="AC36" s="18" t="n"/>
       <c r="AD36" s="18" t="n"/>
       <c r="AE36" s="18" t="n"/>
       <c r="AF36" s="18" t="n"/>
-      <c r="AG36" s="18" t="n"/>
-      <c r="AH36" s="20" t="n"/>
-      <c r="AI36" s="13">
-        <f>IF($A36="","",IF(AJ36&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ36">
-        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($Q36="",1,0)+IF($T36="",1,0)+IF($U36="",1,0)+IF($V36="",1,0)+IF($X36="",1,0)+IF($AB36="",1,0)+IF($AD36="",1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0)+IF(AND($N36="契約期間満了",$S36=""),1,0)+IF(AND($AF36="外国",$AG36=""),1,0)+IF(AND($AF36="外国",$AH36=""),1,0)+IF(AND($AB36="未回収",$AC36=""),1,0))</f>
+      <c r="AG36" s="20" t="n"/>
+      <c r="AH36" s="13">
+        <f>IF($A36="","",IF(AI36&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI36">
+        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($T36="",1,0)+IF($U36="",1,0)+IF($V36="",1,0)+IF($AA36="",1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0)+IF(AND($N36="契約期間満了",$S36=""),1,0)+IF(AND($AE36="外国",$AF36=""),1,0)+IF(AND($AE36="外国",$AG36=""),1,0)+IF(AND($AA36="未回収",$AB36=""),1,0)+IF(AND($V36="あり",$Q36=""),1,0)+IF(AND($V36="あり",$X36=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3539,22 +3494,21 @@
       <c r="V37" s="18" t="n"/>
       <c r="W37" s="18" t="n"/>
       <c r="X37" s="18" t="n"/>
-      <c r="Y37" s="18" t="n"/>
+      <c r="Y37" s="48" t="n"/>
       <c r="Z37" s="48" t="n"/>
-      <c r="AA37" s="48" t="n"/>
+      <c r="AA37" s="18" t="n"/>
       <c r="AB37" s="18" t="n"/>
       <c r="AC37" s="18" t="n"/>
       <c r="AD37" s="18" t="n"/>
       <c r="AE37" s="18" t="n"/>
       <c r="AF37" s="18" t="n"/>
-      <c r="AG37" s="18" t="n"/>
-      <c r="AH37" s="20" t="n"/>
-      <c r="AI37" s="13">
-        <f>IF($A37="","",IF(AJ37&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ37">
-        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($Q37="",1,0)+IF($T37="",1,0)+IF($U37="",1,0)+IF($V37="",1,0)+IF($X37="",1,0)+IF($AB37="",1,0)+IF($AD37="",1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0)+IF(AND($N37="契約期間満了",$S37=""),1,0)+IF(AND($AF37="外国",$AG37=""),1,0)+IF(AND($AF37="外国",$AH37=""),1,0)+IF(AND($AB37="未回収",$AC37=""),1,0))</f>
+      <c r="AG37" s="20" t="n"/>
+      <c r="AH37" s="13">
+        <f>IF($A37="","",IF(AI37&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI37">
+        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($T37="",1,0)+IF($U37="",1,0)+IF($V37="",1,0)+IF($AA37="",1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0)+IF(AND($N37="契約期間満了",$S37=""),1,0)+IF(AND($AE37="外国",$AF37=""),1,0)+IF(AND($AE37="外国",$AG37=""),1,0)+IF(AND($AA37="未回収",$AB37=""),1,0)+IF(AND($V37="あり",$Q37=""),1,0)+IF(AND($V37="あり",$X37=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3586,22 +3540,21 @@
       <c r="V38" s="18" t="n"/>
       <c r="W38" s="18" t="n"/>
       <c r="X38" s="18" t="n"/>
-      <c r="Y38" s="18" t="n"/>
+      <c r="Y38" s="48" t="n"/>
       <c r="Z38" s="48" t="n"/>
-      <c r="AA38" s="48" t="n"/>
+      <c r="AA38" s="18" t="n"/>
       <c r="AB38" s="18" t="n"/>
       <c r="AC38" s="18" t="n"/>
       <c r="AD38" s="18" t="n"/>
       <c r="AE38" s="18" t="n"/>
       <c r="AF38" s="18" t="n"/>
-      <c r="AG38" s="18" t="n"/>
-      <c r="AH38" s="20" t="n"/>
-      <c r="AI38" s="13">
-        <f>IF($A38="","",IF(AJ38&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ38">
-        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($Q38="",1,0)+IF($T38="",1,0)+IF($U38="",1,0)+IF($V38="",1,0)+IF($X38="",1,0)+IF($AB38="",1,0)+IF($AD38="",1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0)+IF(AND($N38="契約期間満了",$S38=""),1,0)+IF(AND($AF38="外国",$AG38=""),1,0)+IF(AND($AF38="外国",$AH38=""),1,0)+IF(AND($AB38="未回収",$AC38=""),1,0))</f>
+      <c r="AG38" s="20" t="n"/>
+      <c r="AH38" s="13">
+        <f>IF($A38="","",IF(AI38&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI38">
+        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($T38="",1,0)+IF($U38="",1,0)+IF($V38="",1,0)+IF($AA38="",1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0)+IF(AND($N38="契約期間満了",$S38=""),1,0)+IF(AND($AE38="外国",$AF38=""),1,0)+IF(AND($AE38="外国",$AG38=""),1,0)+IF(AND($AA38="未回収",$AB38=""),1,0)+IF(AND($V38="あり",$Q38=""),1,0)+IF(AND($V38="あり",$X38=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3633,22 +3586,21 @@
       <c r="V39" s="18" t="n"/>
       <c r="W39" s="18" t="n"/>
       <c r="X39" s="18" t="n"/>
-      <c r="Y39" s="18" t="n"/>
+      <c r="Y39" s="48" t="n"/>
       <c r="Z39" s="48" t="n"/>
-      <c r="AA39" s="48" t="n"/>
+      <c r="AA39" s="18" t="n"/>
       <c r="AB39" s="18" t="n"/>
       <c r="AC39" s="18" t="n"/>
       <c r="AD39" s="18" t="n"/>
       <c r="AE39" s="18" t="n"/>
       <c r="AF39" s="18" t="n"/>
-      <c r="AG39" s="18" t="n"/>
-      <c r="AH39" s="20" t="n"/>
-      <c r="AI39" s="13">
-        <f>IF($A39="","",IF(AJ39&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ39">
-        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($Q39="",1,0)+IF($T39="",1,0)+IF($U39="",1,0)+IF($V39="",1,0)+IF($X39="",1,0)+IF($AB39="",1,0)+IF($AD39="",1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0)+IF(AND($N39="契約期間満了",$S39=""),1,0)+IF(AND($AF39="外国",$AG39=""),1,0)+IF(AND($AF39="外国",$AH39=""),1,0)+IF(AND($AB39="未回収",$AC39=""),1,0))</f>
+      <c r="AG39" s="20" t="n"/>
+      <c r="AH39" s="13">
+        <f>IF($A39="","",IF(AI39&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI39">
+        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($T39="",1,0)+IF($U39="",1,0)+IF($V39="",1,0)+IF($AA39="",1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0)+IF(AND($N39="契約期間満了",$S39=""),1,0)+IF(AND($AE39="外国",$AF39=""),1,0)+IF(AND($AE39="外国",$AG39=""),1,0)+IF(AND($AA39="未回収",$AB39=""),1,0)+IF(AND($V39="あり",$Q39=""),1,0)+IF(AND($V39="あり",$X39=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3680,22 +3632,21 @@
       <c r="V40" s="18" t="n"/>
       <c r="W40" s="18" t="n"/>
       <c r="X40" s="18" t="n"/>
-      <c r="Y40" s="18" t="n"/>
+      <c r="Y40" s="48" t="n"/>
       <c r="Z40" s="48" t="n"/>
-      <c r="AA40" s="48" t="n"/>
+      <c r="AA40" s="18" t="n"/>
       <c r="AB40" s="18" t="n"/>
       <c r="AC40" s="18" t="n"/>
       <c r="AD40" s="18" t="n"/>
       <c r="AE40" s="18" t="n"/>
       <c r="AF40" s="18" t="n"/>
-      <c r="AG40" s="18" t="n"/>
-      <c r="AH40" s="20" t="n"/>
-      <c r="AI40" s="13">
-        <f>IF($A40="","",IF(AJ40&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ40">
-        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($Q40="",1,0)+IF($T40="",1,0)+IF($U40="",1,0)+IF($V40="",1,0)+IF($X40="",1,0)+IF($AB40="",1,0)+IF($AD40="",1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0)+IF(AND($N40="契約期間満了",$S40=""),1,0)+IF(AND($AF40="外国",$AG40=""),1,0)+IF(AND($AF40="外国",$AH40=""),1,0)+IF(AND($AB40="未回収",$AC40=""),1,0))</f>
+      <c r="AG40" s="20" t="n"/>
+      <c r="AH40" s="13">
+        <f>IF($A40="","",IF(AI40&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI40">
+        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($T40="",1,0)+IF($U40="",1,0)+IF($V40="",1,0)+IF($AA40="",1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0)+IF(AND($N40="契約期間満了",$S40=""),1,0)+IF(AND($AE40="外国",$AF40=""),1,0)+IF(AND($AE40="外国",$AG40=""),1,0)+IF(AND($AA40="未回収",$AB40=""),1,0)+IF(AND($V40="あり",$Q40=""),1,0)+IF(AND($V40="あり",$X40=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3727,22 +3678,21 @@
       <c r="V41" s="18" t="n"/>
       <c r="W41" s="18" t="n"/>
       <c r="X41" s="18" t="n"/>
-      <c r="Y41" s="18" t="n"/>
+      <c r="Y41" s="48" t="n"/>
       <c r="Z41" s="48" t="n"/>
-      <c r="AA41" s="48" t="n"/>
+      <c r="AA41" s="18" t="n"/>
       <c r="AB41" s="18" t="n"/>
       <c r="AC41" s="18" t="n"/>
       <c r="AD41" s="18" t="n"/>
       <c r="AE41" s="18" t="n"/>
       <c r="AF41" s="18" t="n"/>
-      <c r="AG41" s="18" t="n"/>
-      <c r="AH41" s="20" t="n"/>
-      <c r="AI41" s="13">
-        <f>IF($A41="","",IF(AJ41&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ41">
-        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($Q41="",1,0)+IF($T41="",1,0)+IF($U41="",1,0)+IF($V41="",1,0)+IF($X41="",1,0)+IF($AB41="",1,0)+IF($AD41="",1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0)+IF(AND($N41="契約期間満了",$S41=""),1,0)+IF(AND($AF41="外国",$AG41=""),1,0)+IF(AND($AF41="外国",$AH41=""),1,0)+IF(AND($AB41="未回収",$AC41=""),1,0))</f>
+      <c r="AG41" s="20" t="n"/>
+      <c r="AH41" s="13">
+        <f>IF($A41="","",IF(AI41&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI41">
+        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($T41="",1,0)+IF($U41="",1,0)+IF($V41="",1,0)+IF($AA41="",1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0)+IF(AND($N41="契約期間満了",$S41=""),1,0)+IF(AND($AE41="外国",$AF41=""),1,0)+IF(AND($AE41="外国",$AG41=""),1,0)+IF(AND($AA41="未回収",$AB41=""),1,0)+IF(AND($V41="あり",$Q41=""),1,0)+IF(AND($V41="あり",$X41=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3774,22 +3724,21 @@
       <c r="V42" s="18" t="n"/>
       <c r="W42" s="18" t="n"/>
       <c r="X42" s="18" t="n"/>
-      <c r="Y42" s="18" t="n"/>
+      <c r="Y42" s="48" t="n"/>
       <c r="Z42" s="48" t="n"/>
-      <c r="AA42" s="48" t="n"/>
+      <c r="AA42" s="18" t="n"/>
       <c r="AB42" s="18" t="n"/>
       <c r="AC42" s="18" t="n"/>
       <c r="AD42" s="18" t="n"/>
       <c r="AE42" s="18" t="n"/>
       <c r="AF42" s="18" t="n"/>
-      <c r="AG42" s="18" t="n"/>
-      <c r="AH42" s="20" t="n"/>
-      <c r="AI42" s="13">
-        <f>IF($A42="","",IF(AJ42&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ42">
-        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($Q42="",1,0)+IF($T42="",1,0)+IF($U42="",1,0)+IF($V42="",1,0)+IF($X42="",1,0)+IF($AB42="",1,0)+IF($AD42="",1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0)+IF(AND($N42="契約期間満了",$S42=""),1,0)+IF(AND($AF42="外国",$AG42=""),1,0)+IF(AND($AF42="外国",$AH42=""),1,0)+IF(AND($AB42="未回収",$AC42=""),1,0))</f>
+      <c r="AG42" s="20" t="n"/>
+      <c r="AH42" s="13">
+        <f>IF($A42="","",IF(AI42&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI42">
+        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($T42="",1,0)+IF($U42="",1,0)+IF($V42="",1,0)+IF($AA42="",1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0)+IF(AND($N42="契約期間満了",$S42=""),1,0)+IF(AND($AE42="外国",$AF42=""),1,0)+IF(AND($AE42="外国",$AG42=""),1,0)+IF(AND($AA42="未回収",$AB42=""),1,0)+IF(AND($V42="あり",$Q42=""),1,0)+IF(AND($V42="あり",$X42=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3821,22 +3770,21 @@
       <c r="V43" s="18" t="n"/>
       <c r="W43" s="18" t="n"/>
       <c r="X43" s="18" t="n"/>
-      <c r="Y43" s="18" t="n"/>
+      <c r="Y43" s="48" t="n"/>
       <c r="Z43" s="48" t="n"/>
-      <c r="AA43" s="48" t="n"/>
+      <c r="AA43" s="18" t="n"/>
       <c r="AB43" s="18" t="n"/>
       <c r="AC43" s="18" t="n"/>
       <c r="AD43" s="18" t="n"/>
       <c r="AE43" s="18" t="n"/>
       <c r="AF43" s="18" t="n"/>
-      <c r="AG43" s="18" t="n"/>
-      <c r="AH43" s="20" t="n"/>
-      <c r="AI43" s="13">
-        <f>IF($A43="","",IF(AJ43&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ43">
-        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($Q43="",1,0)+IF($T43="",1,0)+IF($U43="",1,0)+IF($V43="",1,0)+IF($X43="",1,0)+IF($AB43="",1,0)+IF($AD43="",1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0)+IF(AND($N43="契約期間満了",$S43=""),1,0)+IF(AND($AF43="外国",$AG43=""),1,0)+IF(AND($AF43="外国",$AH43=""),1,0)+IF(AND($AB43="未回収",$AC43=""),1,0))</f>
+      <c r="AG43" s="20" t="n"/>
+      <c r="AH43" s="13">
+        <f>IF($A43="","",IF(AI43&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI43">
+        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($T43="",1,0)+IF($U43="",1,0)+IF($V43="",1,0)+IF($AA43="",1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0)+IF(AND($N43="契約期間満了",$S43=""),1,0)+IF(AND($AE43="外国",$AF43=""),1,0)+IF(AND($AE43="外国",$AG43=""),1,0)+IF(AND($AA43="未回収",$AB43=""),1,0)+IF(AND($V43="あり",$Q43=""),1,0)+IF(AND($V43="あり",$X43=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3868,22 +3816,21 @@
       <c r="V44" s="18" t="n"/>
       <c r="W44" s="18" t="n"/>
       <c r="X44" s="18" t="n"/>
-      <c r="Y44" s="18" t="n"/>
+      <c r="Y44" s="48" t="n"/>
       <c r="Z44" s="48" t="n"/>
-      <c r="AA44" s="48" t="n"/>
+      <c r="AA44" s="18" t="n"/>
       <c r="AB44" s="18" t="n"/>
       <c r="AC44" s="18" t="n"/>
       <c r="AD44" s="18" t="n"/>
       <c r="AE44" s="18" t="n"/>
       <c r="AF44" s="18" t="n"/>
-      <c r="AG44" s="18" t="n"/>
-      <c r="AH44" s="20" t="n"/>
-      <c r="AI44" s="13">
-        <f>IF($A44="","",IF(AJ44&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ44">
-        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($Q44="",1,0)+IF($T44="",1,0)+IF($U44="",1,0)+IF($V44="",1,0)+IF($X44="",1,0)+IF($AB44="",1,0)+IF($AD44="",1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0)+IF(AND($N44="契約期間満了",$S44=""),1,0)+IF(AND($AF44="外国",$AG44=""),1,0)+IF(AND($AF44="外国",$AH44=""),1,0)+IF(AND($AB44="未回収",$AC44=""),1,0))</f>
+      <c r="AG44" s="20" t="n"/>
+      <c r="AH44" s="13">
+        <f>IF($A44="","",IF(AI44&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI44">
+        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($T44="",1,0)+IF($U44="",1,0)+IF($V44="",1,0)+IF($AA44="",1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0)+IF(AND($N44="契約期間満了",$S44=""),1,0)+IF(AND($AE44="外国",$AF44=""),1,0)+IF(AND($AE44="外国",$AG44=""),1,0)+IF(AND($AA44="未回収",$AB44=""),1,0)+IF(AND($V44="あり",$Q44=""),1,0)+IF(AND($V44="あり",$X44=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3915,22 +3862,21 @@
       <c r="V45" s="18" t="n"/>
       <c r="W45" s="18" t="n"/>
       <c r="X45" s="18" t="n"/>
-      <c r="Y45" s="18" t="n"/>
+      <c r="Y45" s="48" t="n"/>
       <c r="Z45" s="48" t="n"/>
-      <c r="AA45" s="48" t="n"/>
+      <c r="AA45" s="18" t="n"/>
       <c r="AB45" s="18" t="n"/>
       <c r="AC45" s="18" t="n"/>
       <c r="AD45" s="18" t="n"/>
       <c r="AE45" s="18" t="n"/>
       <c r="AF45" s="18" t="n"/>
-      <c r="AG45" s="18" t="n"/>
-      <c r="AH45" s="20" t="n"/>
-      <c r="AI45" s="13">
-        <f>IF($A45="","",IF(AJ45&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ45">
-        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($Q45="",1,0)+IF($T45="",1,0)+IF($U45="",1,0)+IF($V45="",1,0)+IF($X45="",1,0)+IF($AB45="",1,0)+IF($AD45="",1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0)+IF(AND($N45="契約期間満了",$S45=""),1,0)+IF(AND($AF45="外国",$AG45=""),1,0)+IF(AND($AF45="外国",$AH45=""),1,0)+IF(AND($AB45="未回収",$AC45=""),1,0))</f>
+      <c r="AG45" s="20" t="n"/>
+      <c r="AH45" s="13">
+        <f>IF($A45="","",IF(AI45&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI45">
+        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($T45="",1,0)+IF($U45="",1,0)+IF($V45="",1,0)+IF($AA45="",1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0)+IF(AND($N45="契約期間満了",$S45=""),1,0)+IF(AND($AE45="外国",$AF45=""),1,0)+IF(AND($AE45="外国",$AG45=""),1,0)+IF(AND($AA45="未回収",$AB45=""),1,0)+IF(AND($V45="あり",$Q45=""),1,0)+IF(AND($V45="あり",$X45=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3962,22 +3908,21 @@
       <c r="V46" s="18" t="n"/>
       <c r="W46" s="18" t="n"/>
       <c r="X46" s="18" t="n"/>
-      <c r="Y46" s="18" t="n"/>
+      <c r="Y46" s="48" t="n"/>
       <c r="Z46" s="48" t="n"/>
-      <c r="AA46" s="48" t="n"/>
+      <c r="AA46" s="18" t="n"/>
       <c r="AB46" s="18" t="n"/>
       <c r="AC46" s="18" t="n"/>
       <c r="AD46" s="18" t="n"/>
       <c r="AE46" s="18" t="n"/>
       <c r="AF46" s="18" t="n"/>
-      <c r="AG46" s="18" t="n"/>
-      <c r="AH46" s="20" t="n"/>
-      <c r="AI46" s="13">
-        <f>IF($A46="","",IF(AJ46&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ46">
-        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($Q46="",1,0)+IF($T46="",1,0)+IF($U46="",1,0)+IF($V46="",1,0)+IF($X46="",1,0)+IF($AB46="",1,0)+IF($AD46="",1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0)+IF(AND($N46="契約期間満了",$S46=""),1,0)+IF(AND($AF46="外国",$AG46=""),1,0)+IF(AND($AF46="外国",$AH46=""),1,0)+IF(AND($AB46="未回収",$AC46=""),1,0))</f>
+      <c r="AG46" s="20" t="n"/>
+      <c r="AH46" s="13">
+        <f>IF($A46="","",IF(AI46&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI46">
+        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($T46="",1,0)+IF($U46="",1,0)+IF($V46="",1,0)+IF($AA46="",1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0)+IF(AND($N46="契約期間満了",$S46=""),1,0)+IF(AND($AE46="外国",$AF46=""),1,0)+IF(AND($AE46="外国",$AG46=""),1,0)+IF(AND($AA46="未回収",$AB46=""),1,0)+IF(AND($V46="あり",$Q46=""),1,0)+IF(AND($V46="あり",$X46=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4009,22 +3954,21 @@
       <c r="V47" s="18" t="n"/>
       <c r="W47" s="18" t="n"/>
       <c r="X47" s="18" t="n"/>
-      <c r="Y47" s="18" t="n"/>
+      <c r="Y47" s="48" t="n"/>
       <c r="Z47" s="48" t="n"/>
-      <c r="AA47" s="48" t="n"/>
+      <c r="AA47" s="18" t="n"/>
       <c r="AB47" s="18" t="n"/>
       <c r="AC47" s="18" t="n"/>
       <c r="AD47" s="18" t="n"/>
       <c r="AE47" s="18" t="n"/>
       <c r="AF47" s="18" t="n"/>
-      <c r="AG47" s="18" t="n"/>
-      <c r="AH47" s="20" t="n"/>
-      <c r="AI47" s="13">
-        <f>IF($A47="","",IF(AJ47&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ47">
-        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($Q47="",1,0)+IF($T47="",1,0)+IF($U47="",1,0)+IF($V47="",1,0)+IF($X47="",1,0)+IF($AB47="",1,0)+IF($AD47="",1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0)+IF(AND($N47="契約期間満了",$S47=""),1,0)+IF(AND($AF47="外国",$AG47=""),1,0)+IF(AND($AF47="外国",$AH47=""),1,0)+IF(AND($AB47="未回収",$AC47=""),1,0))</f>
+      <c r="AG47" s="20" t="n"/>
+      <c r="AH47" s="13">
+        <f>IF($A47="","",IF(AI47&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI47">
+        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($T47="",1,0)+IF($U47="",1,0)+IF($V47="",1,0)+IF($AA47="",1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0)+IF(AND($N47="契約期間満了",$S47=""),1,0)+IF(AND($AE47="外国",$AF47=""),1,0)+IF(AND($AE47="外国",$AG47=""),1,0)+IF(AND($AA47="未回収",$AB47=""),1,0)+IF(AND($V47="あり",$Q47=""),1,0)+IF(AND($V47="あり",$X47=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4056,22 +4000,21 @@
       <c r="V48" s="18" t="n"/>
       <c r="W48" s="18" t="n"/>
       <c r="X48" s="18" t="n"/>
-      <c r="Y48" s="18" t="n"/>
+      <c r="Y48" s="48" t="n"/>
       <c r="Z48" s="48" t="n"/>
-      <c r="AA48" s="48" t="n"/>
+      <c r="AA48" s="18" t="n"/>
       <c r="AB48" s="18" t="n"/>
       <c r="AC48" s="18" t="n"/>
       <c r="AD48" s="18" t="n"/>
       <c r="AE48" s="18" t="n"/>
       <c r="AF48" s="18" t="n"/>
-      <c r="AG48" s="18" t="n"/>
-      <c r="AH48" s="20" t="n"/>
-      <c r="AI48" s="13">
-        <f>IF($A48="","",IF(AJ48&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ48">
-        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($Q48="",1,0)+IF($T48="",1,0)+IF($U48="",1,0)+IF($V48="",1,0)+IF($X48="",1,0)+IF($AB48="",1,0)+IF($AD48="",1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0)+IF(AND($N48="契約期間満了",$S48=""),1,0)+IF(AND($AF48="外国",$AG48=""),1,0)+IF(AND($AF48="外国",$AH48=""),1,0)+IF(AND($AB48="未回収",$AC48=""),1,0))</f>
+      <c r="AG48" s="20" t="n"/>
+      <c r="AH48" s="13">
+        <f>IF($A48="","",IF(AI48&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI48">
+        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($T48="",1,0)+IF($U48="",1,0)+IF($V48="",1,0)+IF($AA48="",1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0)+IF(AND($N48="契約期間満了",$S48=""),1,0)+IF(AND($AE48="外国",$AF48=""),1,0)+IF(AND($AE48="外国",$AG48=""),1,0)+IF(AND($AA48="未回収",$AB48=""),1,0)+IF(AND($V48="あり",$Q48=""),1,0)+IF(AND($V48="あり",$X48=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4103,22 +4046,21 @@
       <c r="V49" s="18" t="n"/>
       <c r="W49" s="18" t="n"/>
       <c r="X49" s="18" t="n"/>
-      <c r="Y49" s="18" t="n"/>
+      <c r="Y49" s="48" t="n"/>
       <c r="Z49" s="48" t="n"/>
-      <c r="AA49" s="48" t="n"/>
+      <c r="AA49" s="18" t="n"/>
       <c r="AB49" s="18" t="n"/>
       <c r="AC49" s="18" t="n"/>
       <c r="AD49" s="18" t="n"/>
       <c r="AE49" s="18" t="n"/>
       <c r="AF49" s="18" t="n"/>
-      <c r="AG49" s="18" t="n"/>
-      <c r="AH49" s="20" t="n"/>
-      <c r="AI49" s="13">
-        <f>IF($A49="","",IF(AJ49&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ49">
-        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($Q49="",1,0)+IF($T49="",1,0)+IF($U49="",1,0)+IF($V49="",1,0)+IF($X49="",1,0)+IF($AB49="",1,0)+IF($AD49="",1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0)+IF(AND($N49="契約期間満了",$S49=""),1,0)+IF(AND($AF49="外国",$AG49=""),1,0)+IF(AND($AF49="外国",$AH49=""),1,0)+IF(AND($AB49="未回収",$AC49=""),1,0))</f>
+      <c r="AG49" s="20" t="n"/>
+      <c r="AH49" s="13">
+        <f>IF($A49="","",IF(AI49&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI49">
+        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($T49="",1,0)+IF($U49="",1,0)+IF($V49="",1,0)+IF($AA49="",1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0)+IF(AND($N49="契約期間満了",$S49=""),1,0)+IF(AND($AE49="外国",$AF49=""),1,0)+IF(AND($AE49="外国",$AG49=""),1,0)+IF(AND($AA49="未回収",$AB49=""),1,0)+IF(AND($V49="あり",$Q49=""),1,0)+IF(AND($V49="あり",$X49=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4150,22 +4092,21 @@
       <c r="V50" s="18" t="n"/>
       <c r="W50" s="18" t="n"/>
       <c r="X50" s="18" t="n"/>
-      <c r="Y50" s="18" t="n"/>
+      <c r="Y50" s="48" t="n"/>
       <c r="Z50" s="48" t="n"/>
-      <c r="AA50" s="48" t="n"/>
+      <c r="AA50" s="18" t="n"/>
       <c r="AB50" s="18" t="n"/>
       <c r="AC50" s="18" t="n"/>
       <c r="AD50" s="18" t="n"/>
       <c r="AE50" s="18" t="n"/>
       <c r="AF50" s="18" t="n"/>
-      <c r="AG50" s="18" t="n"/>
-      <c r="AH50" s="20" t="n"/>
-      <c r="AI50" s="13">
-        <f>IF($A50="","",IF(AJ50&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ50">
-        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($Q50="",1,0)+IF($T50="",1,0)+IF($U50="",1,0)+IF($V50="",1,0)+IF($X50="",1,0)+IF($AB50="",1,0)+IF($AD50="",1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0)+IF(AND($N50="契約期間満了",$S50=""),1,0)+IF(AND($AF50="外国",$AG50=""),1,0)+IF(AND($AF50="外国",$AH50=""),1,0)+IF(AND($AB50="未回収",$AC50=""),1,0))</f>
+      <c r="AG50" s="20" t="n"/>
+      <c r="AH50" s="13">
+        <f>IF($A50="","",IF(AI50&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI50">
+        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($T50="",1,0)+IF($U50="",1,0)+IF($V50="",1,0)+IF($AA50="",1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0)+IF(AND($N50="契約期間満了",$S50=""),1,0)+IF(AND($AE50="外国",$AF50=""),1,0)+IF(AND($AE50="外国",$AG50=""),1,0)+IF(AND($AA50="未回収",$AB50=""),1,0)+IF(AND($V50="あり",$Q50=""),1,0)+IF(AND($V50="あり",$X50=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4197,22 +4138,21 @@
       <c r="V51" s="18" t="n"/>
       <c r="W51" s="18" t="n"/>
       <c r="X51" s="18" t="n"/>
-      <c r="Y51" s="18" t="n"/>
+      <c r="Y51" s="48" t="n"/>
       <c r="Z51" s="48" t="n"/>
-      <c r="AA51" s="48" t="n"/>
+      <c r="AA51" s="18" t="n"/>
       <c r="AB51" s="18" t="n"/>
       <c r="AC51" s="18" t="n"/>
       <c r="AD51" s="18" t="n"/>
       <c r="AE51" s="18" t="n"/>
       <c r="AF51" s="18" t="n"/>
-      <c r="AG51" s="18" t="n"/>
-      <c r="AH51" s="20" t="n"/>
-      <c r="AI51" s="13">
-        <f>IF($A51="","",IF(AJ51&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ51">
-        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($Q51="",1,0)+IF($T51="",1,0)+IF($U51="",1,0)+IF($V51="",1,0)+IF($X51="",1,0)+IF($AB51="",1,0)+IF($AD51="",1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0)+IF(AND($N51="契約期間満了",$S51=""),1,0)+IF(AND($AF51="外国",$AG51=""),1,0)+IF(AND($AF51="外国",$AH51=""),1,0)+IF(AND($AB51="未回収",$AC51=""),1,0))</f>
+      <c r="AG51" s="20" t="n"/>
+      <c r="AH51" s="13">
+        <f>IF($A51="","",IF(AI51&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI51">
+        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($T51="",1,0)+IF($U51="",1,0)+IF($V51="",1,0)+IF($AA51="",1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0)+IF(AND($N51="契約期間満了",$S51=""),1,0)+IF(AND($AE51="外国",$AF51=""),1,0)+IF(AND($AE51="外国",$AG51=""),1,0)+IF(AND($AA51="未回収",$AB51=""),1,0)+IF(AND($V51="あり",$Q51=""),1,0)+IF(AND($V51="あり",$X51=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4244,22 +4184,21 @@
       <c r="V52" s="18" t="n"/>
       <c r="W52" s="18" t="n"/>
       <c r="X52" s="18" t="n"/>
-      <c r="Y52" s="18" t="n"/>
+      <c r="Y52" s="48" t="n"/>
       <c r="Z52" s="48" t="n"/>
-      <c r="AA52" s="48" t="n"/>
+      <c r="AA52" s="18" t="n"/>
       <c r="AB52" s="18" t="n"/>
       <c r="AC52" s="18" t="n"/>
       <c r="AD52" s="18" t="n"/>
       <c r="AE52" s="18" t="n"/>
       <c r="AF52" s="18" t="n"/>
-      <c r="AG52" s="18" t="n"/>
-      <c r="AH52" s="20" t="n"/>
-      <c r="AI52" s="13">
-        <f>IF($A52="","",IF(AJ52&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ52">
-        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($Q52="",1,0)+IF($T52="",1,0)+IF($U52="",1,0)+IF($V52="",1,0)+IF($X52="",1,0)+IF($AB52="",1,0)+IF($AD52="",1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0)+IF(AND($N52="契約期間満了",$S52=""),1,0)+IF(AND($AF52="外国",$AG52=""),1,0)+IF(AND($AF52="外国",$AH52=""),1,0)+IF(AND($AB52="未回収",$AC52=""),1,0))</f>
+      <c r="AG52" s="20" t="n"/>
+      <c r="AH52" s="13">
+        <f>IF($A52="","",IF(AI52&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI52">
+        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($T52="",1,0)+IF($U52="",1,0)+IF($V52="",1,0)+IF($AA52="",1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0)+IF(AND($N52="契約期間満了",$S52=""),1,0)+IF(AND($AE52="外国",$AF52=""),1,0)+IF(AND($AE52="外国",$AG52=""),1,0)+IF(AND($AA52="未回収",$AB52=""),1,0)+IF(AND($V52="あり",$Q52=""),1,0)+IF(AND($V52="あり",$X52=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4291,22 +4230,21 @@
       <c r="V53" s="18" t="n"/>
       <c r="W53" s="18" t="n"/>
       <c r="X53" s="18" t="n"/>
-      <c r="Y53" s="18" t="n"/>
+      <c r="Y53" s="48" t="n"/>
       <c r="Z53" s="48" t="n"/>
-      <c r="AA53" s="48" t="n"/>
+      <c r="AA53" s="18" t="n"/>
       <c r="AB53" s="18" t="n"/>
       <c r="AC53" s="18" t="n"/>
       <c r="AD53" s="18" t="n"/>
       <c r="AE53" s="18" t="n"/>
       <c r="AF53" s="18" t="n"/>
-      <c r="AG53" s="18" t="n"/>
-      <c r="AH53" s="20" t="n"/>
-      <c r="AI53" s="13">
-        <f>IF($A53="","",IF(AJ53&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ53">
-        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($Q53="",1,0)+IF($T53="",1,0)+IF($U53="",1,0)+IF($V53="",1,0)+IF($X53="",1,0)+IF($AB53="",1,0)+IF($AD53="",1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0)+IF(AND($N53="契約期間満了",$S53=""),1,0)+IF(AND($AF53="外国",$AG53=""),1,0)+IF(AND($AF53="外国",$AH53=""),1,0)+IF(AND($AB53="未回収",$AC53=""),1,0))</f>
+      <c r="AG53" s="20" t="n"/>
+      <c r="AH53" s="13">
+        <f>IF($A53="","",IF(AI53&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI53">
+        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($T53="",1,0)+IF($U53="",1,0)+IF($V53="",1,0)+IF($AA53="",1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0)+IF(AND($N53="契約期間満了",$S53=""),1,0)+IF(AND($AE53="外国",$AF53=""),1,0)+IF(AND($AE53="外国",$AG53=""),1,0)+IF(AND($AA53="未回収",$AB53=""),1,0)+IF(AND($V53="あり",$Q53=""),1,0)+IF(AND($V53="あり",$X53=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4338,22 +4276,21 @@
       <c r="V54" s="18" t="n"/>
       <c r="W54" s="18" t="n"/>
       <c r="X54" s="18" t="n"/>
-      <c r="Y54" s="18" t="n"/>
+      <c r="Y54" s="48" t="n"/>
       <c r="Z54" s="48" t="n"/>
-      <c r="AA54" s="48" t="n"/>
+      <c r="AA54" s="18" t="n"/>
       <c r="AB54" s="18" t="n"/>
       <c r="AC54" s="18" t="n"/>
       <c r="AD54" s="18" t="n"/>
       <c r="AE54" s="18" t="n"/>
       <c r="AF54" s="18" t="n"/>
-      <c r="AG54" s="18" t="n"/>
-      <c r="AH54" s="20" t="n"/>
-      <c r="AI54" s="13">
-        <f>IF($A54="","",IF(AJ54&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ54">
-        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($Q54="",1,0)+IF($T54="",1,0)+IF($U54="",1,0)+IF($V54="",1,0)+IF($X54="",1,0)+IF($AB54="",1,0)+IF($AD54="",1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0)+IF(AND($N54="契約期間満了",$S54=""),1,0)+IF(AND($AF54="外国",$AG54=""),1,0)+IF(AND($AF54="外国",$AH54=""),1,0)+IF(AND($AB54="未回収",$AC54=""),1,0))</f>
+      <c r="AG54" s="20" t="n"/>
+      <c r="AH54" s="13">
+        <f>IF($A54="","",IF(AI54&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI54">
+        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($T54="",1,0)+IF($U54="",1,0)+IF($V54="",1,0)+IF($AA54="",1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0)+IF(AND($N54="契約期間満了",$S54=""),1,0)+IF(AND($AE54="外国",$AF54=""),1,0)+IF(AND($AE54="外国",$AG54=""),1,0)+IF(AND($AA54="未回収",$AB54=""),1,0)+IF(AND($V54="あり",$Q54=""),1,0)+IF(AND($V54="あり",$X54=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4385,22 +4322,21 @@
       <c r="V55" s="18" t="n"/>
       <c r="W55" s="18" t="n"/>
       <c r="X55" s="18" t="n"/>
-      <c r="Y55" s="18" t="n"/>
+      <c r="Y55" s="48" t="n"/>
       <c r="Z55" s="48" t="n"/>
-      <c r="AA55" s="48" t="n"/>
+      <c r="AA55" s="18" t="n"/>
       <c r="AB55" s="18" t="n"/>
       <c r="AC55" s="18" t="n"/>
       <c r="AD55" s="18" t="n"/>
       <c r="AE55" s="18" t="n"/>
       <c r="AF55" s="18" t="n"/>
-      <c r="AG55" s="18" t="n"/>
-      <c r="AH55" s="20" t="n"/>
-      <c r="AI55" s="13">
-        <f>IF($A55="","",IF(AJ55&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ55">
-        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($Q55="",1,0)+IF($T55="",1,0)+IF($U55="",1,0)+IF($V55="",1,0)+IF($X55="",1,0)+IF($AB55="",1,0)+IF($AD55="",1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0)+IF(AND($N55="契約期間満了",$S55=""),1,0)+IF(AND($AF55="外国",$AG55=""),1,0)+IF(AND($AF55="外国",$AH55=""),1,0)+IF(AND($AB55="未回収",$AC55=""),1,0))</f>
+      <c r="AG55" s="20" t="n"/>
+      <c r="AH55" s="13">
+        <f>IF($A55="","",IF(AI55&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI55">
+        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($T55="",1,0)+IF($U55="",1,0)+IF($V55="",1,0)+IF($AA55="",1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0)+IF(AND($N55="契約期間満了",$S55=""),1,0)+IF(AND($AE55="外国",$AF55=""),1,0)+IF(AND($AE55="外国",$AG55=""),1,0)+IF(AND($AA55="未回収",$AB55=""),1,0)+IF(AND($V55="あり",$Q55=""),1,0)+IF(AND($V55="あり",$X55=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4432,22 +4368,21 @@
       <c r="V56" s="18" t="n"/>
       <c r="W56" s="18" t="n"/>
       <c r="X56" s="18" t="n"/>
-      <c r="Y56" s="18" t="n"/>
+      <c r="Y56" s="48" t="n"/>
       <c r="Z56" s="48" t="n"/>
-      <c r="AA56" s="48" t="n"/>
+      <c r="AA56" s="18" t="n"/>
       <c r="AB56" s="18" t="n"/>
       <c r="AC56" s="18" t="n"/>
       <c r="AD56" s="18" t="n"/>
       <c r="AE56" s="18" t="n"/>
       <c r="AF56" s="18" t="n"/>
-      <c r="AG56" s="18" t="n"/>
-      <c r="AH56" s="20" t="n"/>
-      <c r="AI56" s="13">
-        <f>IF($A56="","",IF(AJ56&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ56">
-        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($Q56="",1,0)+IF($T56="",1,0)+IF($U56="",1,0)+IF($V56="",1,0)+IF($X56="",1,0)+IF($AB56="",1,0)+IF($AD56="",1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0)+IF(AND($N56="契約期間満了",$S56=""),1,0)+IF(AND($AF56="外国",$AG56=""),1,0)+IF(AND($AF56="外国",$AH56=""),1,0)+IF(AND($AB56="未回収",$AC56=""),1,0))</f>
+      <c r="AG56" s="20" t="n"/>
+      <c r="AH56" s="13">
+        <f>IF($A56="","",IF(AI56&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI56">
+        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($T56="",1,0)+IF($U56="",1,0)+IF($V56="",1,0)+IF($AA56="",1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0)+IF(AND($N56="契約期間満了",$S56=""),1,0)+IF(AND($AE56="外国",$AF56=""),1,0)+IF(AND($AE56="外国",$AG56=""),1,0)+IF(AND($AA56="未回収",$AB56=""),1,0)+IF(AND($V56="あり",$Q56=""),1,0)+IF(AND($V56="あり",$X56=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4479,22 +4414,21 @@
       <c r="V57" s="18" t="n"/>
       <c r="W57" s="18" t="n"/>
       <c r="X57" s="18" t="n"/>
-      <c r="Y57" s="18" t="n"/>
+      <c r="Y57" s="48" t="n"/>
       <c r="Z57" s="48" t="n"/>
-      <c r="AA57" s="48" t="n"/>
+      <c r="AA57" s="18" t="n"/>
       <c r="AB57" s="18" t="n"/>
       <c r="AC57" s="18" t="n"/>
       <c r="AD57" s="18" t="n"/>
       <c r="AE57" s="18" t="n"/>
       <c r="AF57" s="18" t="n"/>
-      <c r="AG57" s="18" t="n"/>
-      <c r="AH57" s="20" t="n"/>
-      <c r="AI57" s="13">
-        <f>IF($A57="","",IF(AJ57&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ57">
-        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($Q57="",1,0)+IF($T57="",1,0)+IF($U57="",1,0)+IF($V57="",1,0)+IF($X57="",1,0)+IF($AB57="",1,0)+IF($AD57="",1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0)+IF(AND($N57="契約期間満了",$S57=""),1,0)+IF(AND($AF57="外国",$AG57=""),1,0)+IF(AND($AF57="外国",$AH57=""),1,0)+IF(AND($AB57="未回収",$AC57=""),1,0))</f>
+      <c r="AG57" s="20" t="n"/>
+      <c r="AH57" s="13">
+        <f>IF($A57="","",IF(AI57&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI57">
+        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($T57="",1,0)+IF($U57="",1,0)+IF($V57="",1,0)+IF($AA57="",1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0)+IF(AND($N57="契約期間満了",$S57=""),1,0)+IF(AND($AE57="外国",$AF57=""),1,0)+IF(AND($AE57="外国",$AG57=""),1,0)+IF(AND($AA57="未回収",$AB57=""),1,0)+IF(AND($V57="あり",$Q57=""),1,0)+IF(AND($V57="あり",$X57=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4526,22 +4460,21 @@
       <c r="V58" s="18" t="n"/>
       <c r="W58" s="18" t="n"/>
       <c r="X58" s="18" t="n"/>
-      <c r="Y58" s="18" t="n"/>
+      <c r="Y58" s="48" t="n"/>
       <c r="Z58" s="48" t="n"/>
-      <c r="AA58" s="48" t="n"/>
+      <c r="AA58" s="18" t="n"/>
       <c r="AB58" s="18" t="n"/>
       <c r="AC58" s="18" t="n"/>
       <c r="AD58" s="18" t="n"/>
       <c r="AE58" s="18" t="n"/>
       <c r="AF58" s="18" t="n"/>
-      <c r="AG58" s="18" t="n"/>
-      <c r="AH58" s="20" t="n"/>
-      <c r="AI58" s="13">
-        <f>IF($A58="","",IF(AJ58&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AJ58">
-        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($Q58="",1,0)+IF($T58="",1,0)+IF($U58="",1,0)+IF($V58="",1,0)+IF($X58="",1,0)+IF($AB58="",1,0)+IF($AD58="",1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0)+IF(AND($N58="契約期間満了",$S58=""),1,0)+IF(AND($AF58="外国",$AG58=""),1,0)+IF(AND($AF58="外国",$AH58=""),1,0)+IF(AND($AB58="未回収",$AC58=""),1,0))</f>
+      <c r="AG58" s="20" t="n"/>
+      <c r="AH58" s="13">
+        <f>IF($A58="","",IF(AI58&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AI58">
+        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($T58="",1,0)+IF($U58="",1,0)+IF($V58="",1,0)+IF($AA58="",1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0)+IF(AND($N58="契約期間満了",$S58=""),1,0)+IF(AND($AE58="外国",$AF58=""),1,0)+IF(AND($AE58="外国",$AG58=""),1,0)+IF(AND($AA58="未回収",$AB58=""),1,0)+IF(AND($V58="あり",$Q58=""),1,0)+IF(AND($V58="あり",$X58=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4551,17 +4484,17 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="AE6:AG6"/>
+    <mergeCell ref="AD6"/>
     <mergeCell ref="L6:S6"/>
-    <mergeCell ref="R1:AH1"/>
-    <mergeCell ref="AB6:AD6"/>
-    <mergeCell ref="AF6:AH6"/>
+    <mergeCell ref="A1:P1"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="T6:AA6"/>
-    <mergeCell ref="AE6"/>
+    <mergeCell ref="T6:Z6"/>
+    <mergeCell ref="AA6:AC6"/>
+    <mergeCell ref="Q1:AG1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
@@ -4589,10 +4522,10 @@
     <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",B9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",LENB(B9)&lt;&gt;LEN(B9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",ISERROR(FIND("　",B9)),ISERROR(FIND(" ",B9)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4600,7 +4533,7 @@
     <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",C9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(C9),C9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4608,10 +4541,10 @@
     <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",D9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="33" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LEN(D9)&lt;&gt;12)</formula>
     </cfRule>
-    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LENB(D9)&lt;&gt;LEN(D9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4619,10 +4552,10 @@
     <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",E9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LEN(E9)&lt;&gt;10)</formula>
     </cfRule>
-    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LENB(E9)&lt;&gt;LEN(E9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4630,10 +4563,10 @@
     <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",F9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LEN(F9)&lt;&gt;11)</formula>
     </cfRule>
-    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LENB(F9)&lt;&gt;LEN(F9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4641,10 +4574,10 @@
     <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",G9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LEN(SUBSTITUTE(G9,"-",""))&lt;&gt;7)</formula>
     </cfRule>
-    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LENB(G9)&lt;&gt;LEN(G9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4657,7 +4590,7 @@
     <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",I9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
       <formula>AND(I9&lt;&gt;"",LENB(I9)&lt;&gt;LEN(I9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4665,7 +4598,7 @@
     <cfRule type="expression" priority="13" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",L9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="49" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(L9),L9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4674,122 +4607,123 @@
       <formula>AND($A9&lt;&gt;"",N9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q9:Q58">
+  <conditionalFormatting sqref="T9:T58">
     <cfRule type="expression" priority="15" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",Q9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T9:T58">
-    <cfRule type="expression" priority="16" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",T9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(T9),T9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9:U58">
-    <cfRule type="expression" priority="17" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="16" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",U9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9:V58">
-    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="17" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",V9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X9:X58">
-    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",X9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB9:AB58">
-    <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",AB9="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD9:AD58">
-    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",AD9="")</formula>
+  <conditionalFormatting sqref="AA9:AA58">
+    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+      <formula>AND($A9&lt;&gt;"",AA9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A58">
-    <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
       <formula>AND($A9="",OR($L9&lt;&gt;"",$N9&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",LENB(A9)&lt;&gt;LEN(A9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",ISERROR(FIND("　",A9)),ISERROR(FIND(" ",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:R58">
-    <cfRule type="expression" priority="23" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",R9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="27" dxfId="3" stopIfTrue="1">
       <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),R9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S9:S58">
-    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",S9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="28" dxfId="3" stopIfTrue="1">
       <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),S9="")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AF9:AF58">
+    <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
+      <formula>AND($AE9="外国",AF9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" dxfId="3" stopIfTrue="1">
+      <formula>AND($AE9&lt;&gt;"",NOT($AE9="外国"),AF9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AG9:AG58">
-    <cfRule type="expression" priority="25" dxfId="2" stopIfTrue="1">
-      <formula>AND($AF9="外国",AG9="")</formula>
+    <cfRule type="expression" priority="23" dxfId="2" stopIfTrue="1">
+      <formula>AND($AE9="外国",AG9="")</formula>
     </cfRule>
     <cfRule type="expression" priority="30" dxfId="3" stopIfTrue="1">
-      <formula>AND($AF9&lt;&gt;"",NOT($AF9="外国"),AG9="")</formula>
+      <formula>AND($AE9&lt;&gt;"",NOT($AE9="外国"),AG9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="53" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AG9),AG9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH9:AH58">
-    <cfRule type="expression" priority="26" dxfId="2" stopIfTrue="1">
-      <formula>AND($AF9="外国",AH9="")</formula>
+  <conditionalFormatting sqref="AB9:AB58">
+    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
+      <formula>AND($AA9="未回収",AB9="")</formula>
     </cfRule>
     <cfRule type="expression" priority="31" dxfId="3" stopIfTrue="1">
-      <formula>AND($AF9&lt;&gt;"",NOT($AF9="外国"),AH9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(AH9),AH9&gt;80000)</formula>
+      <formula>AND($AA9&lt;&gt;"",NOT($AA9="未回収"),AB9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC9:AC58">
-    <cfRule type="expression" priority="27" dxfId="2" stopIfTrue="1">
-      <formula>AND($AB9="未回収",AC9="")</formula>
+  <conditionalFormatting sqref="Q9:Q58">
+    <cfRule type="expression" priority="25" dxfId="2" stopIfTrue="1">
+      <formula>AND($V9="あり",Q9="")</formula>
     </cfRule>
     <cfRule type="expression" priority="32" dxfId="3" stopIfTrue="1">
-      <formula>AND($AB9&lt;&gt;"",NOT($AB9="未回収"),AC9="")</formula>
+      <formula>AND($V9&lt;&gt;"",NOT($V9="あり"),Q9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X9:X58">
+    <cfRule type="expression" priority="26" dxfId="2" stopIfTrue="1">
+      <formula>AND($V9="あり",X9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="33" dxfId="3" stopIfTrue="1">
+      <formula>AND($V9&lt;&gt;"",NOT($V9="あり"),X9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J58">
-    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
       <formula>AND(J9&lt;&gt;"",LENB(J9)&lt;&gt;LEN(J9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K58">
-    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="49" dxfId="1" stopIfTrue="1">
       <formula>AND(K9&lt;&gt;"",LENB(K9)&lt;&gt;LEN(K9))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P58">
-    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(P9),P9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI9:AI58">
-    <cfRule type="expression" priority="53" dxfId="0" stopIfTrue="1">
-      <formula>AI9="CSV可"</formula>
+  <conditionalFormatting sqref="AH9:AH58">
+    <cfRule type="expression" priority="54" dxfId="0" stopIfTrue="1">
+      <formula>AH9="CSV可"</formula>
     </cfRule>
-    <cfRule type="expression" priority="54" dxfId="1" stopIfTrue="1">
-      <formula>AI9="未入力"</formula>
+    <cfRule type="expression" priority="55" dxfId="1" stopIfTrue="1">
+      <formula>AH9="未入力"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="22">
+  <dataValidations count="21">
     <dataValidation sqref="C8:C58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦の生年月日。例 1990/4/1。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
@@ -4841,27 +4775,24 @@
     <dataValidation sqref="V8:V58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人が離職票（基本手当の申請）を希望するか。" type="list" errorStyle="stop">
       <formula1>m_ありなし</formula1>
     </dataValidation>
-    <dataValidation sqref="X8:X58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="離職証明書の賃金欄と被保険者期間の確認のため、離職前1年分の賃金台帳・出勤簿があるか。賃金支払基礎日数11日以上の月が12か月に満たないときは2年分。" type="list" errorStyle="stop">
-      <formula1>m_ありなし</formula1>
-    </dataValidation>
-    <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="AB8:AB58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
+    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
       <formula1>m_回収状況</formula1>
     </dataValidation>
-    <dataValidation sqref="AD8:AD58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職後の医療保険の予定（任意継続・扶養・国保）。" type="list" errorStyle="stop">
+    <dataValidation sqref="AC8:AC58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="分かれば。任意継続を希望される方には手続きのご案内をお送りします。空欄で構いません。" type="list" errorStyle="stop">
       <formula1>m_退職後</formula1>
     </dataValidation>
-    <dataValidation sqref="AF8:AF58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="日本国籍の方は『日本』。外国籍の方は『外国』を選び、右の2欄もご記入ください。" type="list" errorStyle="stop">
+    <dataValidation sqref="AE8:AE58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="日本国籍の方は『日本』。外国籍の方は『外国』を選び、右の2欄もご記入ください。" type="list" errorStyle="stop">
       <formula1>m_国籍</formula1>
     </dataValidation>
-    <dataValidation sqref="AH8:AH58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="在留カードの『在留期間（満了日）』。西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
+    <dataValidation sqref="AG8:AG58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="在留カードの『在留期間（満了日）』。西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
@@ -5873,7 +5804,7 @@
     <row r="18">
       <c r="A18" s="50" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>AG</t>
         </is>
       </c>
       <c r="B18" s="50" t="inlineStr">

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -84,13 +84,13 @@
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
     <font>
@@ -263,44 +263,44 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -314,7 +314,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -342,28 +342,28 @@
     <xf numFmtId="9" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -977,7 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1003,56 +1003,12 @@
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>この書類について</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20.5" customHeight="1">
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>事務所名</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>みなの社会保険労務士事務所</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20.5" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>076-460-2562 / contact@minano-sr.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20.5" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>バージョン</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>1.0（更新日 2026-09-11）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
           <t>目的</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="53.5" customHeight="1">
-      <c r="C10" s="5" t="inlineStr">
+    <row r="5" ht="53.5" customHeight="1">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>退職される方の『雇用保険 資格喪失届・離職証明書』『健康保険・厚生年金 資格喪失届』の
 手続きに必要な情報を回収します。このフォーム1本で手続きに着手できるよう、
@@ -1060,303 +1016,341 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>入力の流れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="37" customHeight="1">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>1. シート『提出チェック・添付・返送』の①に、貴社名・ご担当者名と事業所の番号をご記入ください（届出に必ず要ります。2回目以降は『前回と同じ』で結構です）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="37" customHeight="1">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2. シート『退職 情報』の9行目から、1行に1名ずつご記入ください（58行目まで・50名分）。行の挿入はしないでください。薄黄＝必ず記入、薄灰＝該当すれば記入です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="37" customHeight="1">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>3. 『提出チェック・添付・返送』の提出可否が「提出可」になったら、受任メールのリンクから案件ページを開き、このファイルをそのまま送ってください。</t>
+        </is>
+      </c>
+    </row>
     <row r="11"/>
     <row r="12" ht="24" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>入力の流れ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="37" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>1. 『本人情報』に対象者の氏名・生年月日・番号類・住所を入力します（入社時と同じ内容）。本人しか分からない項目は、会社内で本人に確認のうえご記入ください。</t>
+          <t>色の凡例</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20.5" customHeight="1">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>ヘッダーが薄い黄色。必ず入力してください。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20.5" customHeight="1">
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>2. 退職事由・雇用保険・社会保険の各項目を入力します。</t>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ヘッダーが薄い灰色。該当する場合に入力。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20.5" customHeight="1">
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>3. 離職証明書の賃金欄のため、賃金台帳・出勤簿を別途添付してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>色の凡例</t>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>灰色。自動で計算されます（上書きしないでください）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20.5" customHeight="1">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>未入力警告</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>必須の空欄が薄い赤で点灯。入力で消えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20.5" customHeight="1">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>形式警告</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>桁数・形式が想定と違うと薄い橙で点灯。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20.5" customHeight="1">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>ヘッダーが薄い黄色。必ず入力してください。</t>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>暗い灰の斜線（ハッチ）。その条件では記入不要な欄。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20.5" customHeight="1">
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>ヘッダーが薄い灰色。該当する場合に入力。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20.5" customHeight="1">
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>灰色。自動で計算されます（上書きしないでください）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20.5" customHeight="1">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>未入力警告</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>必須の空欄が薄い赤で点灯。入力で消えます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20.5" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>形式警告</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>桁数・形式が想定と違うと薄い橙で点灯。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20.5" customHeight="1">
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>暗い灰の斜線（ハッチ）。その条件では記入不要な欄。</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>問題なし</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>薄い緑。入力・判定が正常なことを示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="37" customHeight="1">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>見出しの印</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>【必】必ず記入／【任】該当すれば記入／【条件により必須】選んだ区分によって必要になる欄（必要なときだけ薄赤に点灯し、不要なときは斜線になります）／【自動】自動計算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="37" customHeight="1">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>記入例</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>水色・斜体の1行は記入例です。その下の行からご記入ください（記入例の行は消していただいても構いません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>ご注意</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20.5" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>問題なし</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>薄い緑。入力・判定が正常なことを示します。</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>離職理由区分は『目安』です。最終判断は社労士・ハローワークが行います。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="37" customHeight="1">
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>見出しの印</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>【必】必ず記入／【任】該当すれば記入／【条件により必須】選んだ区分によって必要になる欄（必要なときだけ薄赤に点灯し、不要なときは斜線になります）／【自動】自動計算。</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>資格確認書・高齢受給者証・限度額適用認定証などは本人/被扶養者分を回収のうえご返送ください（回収できないときは当方で回収不能届を出します）。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="37" customHeight="1">
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>記入例</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>水色・斜体の1行は記入例です。その下の行からご記入ください（記入例の行は消していただいても構いません）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>ご注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="37" customHeight="1">
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>水色・斜体の8行目は記入例です。9行目からご記入ください（記入例は消していただいても構いません）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20.5" customHeight="1">
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>離職理由区分は『目安』です。最終判断は社労士・ハローワークが行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="37" customHeight="1">
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>資格確認書・高齢受給者証・限度額適用認定証などは本人/被扶養者分を回収のうえご返送ください（回収できないときは当方で回収不能届を出します）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="37" customHeight="1">
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>住民税の異動届（給与所得者異動届出書）と退職所得の受給に関する申告書は税務の手続きで、当事務所の受任範囲に含みません。貴社または顧問税理士でお手続きください。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="37" customHeight="1">
-      <c r="C33" s="5" t="inlineStr">
+    <row r="27" ht="37" customHeight="1">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>提出期限の目安：健康保険・厚生年金の資格喪失届は退職日の翌日から5日以内、雇用保険の資格喪失届・離職証明書は10日以内です。お早めにご返送ください。</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35" ht="24" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="28"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>本人情報の集め方</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="70" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
+    <row r="30" ht="70" customHeight="1">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>本人情報は入社時と同じ内容をご記入ください。本人しか分からない項目（マイナンバー・基礎年金番号・雇用保険被保険者番号など）は、会社内で本人に確認のうえご記入ください。
 当事務所の書式「入社時 本人情報記入シート」（https://minano-sr.com/shoshiki/D-52.html）を印刷して本人に書いてもらう方法が簡単です。</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20.5" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
+    <row r="31" ht="53.5" customHeight="1">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>2名以上のとき</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>1行に1名ずつご記入ください（行を追加して複数名をまとめて送れます）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39" ht="24" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>9行目から58行目に、1行に1名ずつご記入ください（50名まで）。
+行の挿入はしないでください。挿入した行には自動計算の式が入らず、必須の未入力を見逃したまま『提出可』と表示されます。51名以上のときはご連絡ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="24" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>マイナンバー等 機微情報の取扱い</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="53.5" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
+    <row r="34" ht="53.5" customHeight="1">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>入力時</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>マイナンバー（12桁）は半角数字・ハイフン無しで入力します。会社所定の安全な経路で別提出する場合は、番号を入力せず『別経路提出』を選んでください。未回収の場合は『後日提出』を選択します。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="37" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
+    <row r="35" ht="37" customHeight="1">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>基礎年金番号</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>10桁（年金手帳・基礎年金番号通知書に記載）。不明なときはドロップダウンから『後日提出』を選べば未入力扱いになりません（分かり次第ご連絡ください）。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="37" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
+    <row r="36" ht="37" customHeight="1">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>雇用保険被保険者番号</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>11桁（雇用保険被保険者証・離職票に記載）。前職が無い方は『なし』、番号が不明なときは『後日提出』を選択してください。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="53.5" customHeight="1">
-      <c r="B43" s="4" t="inlineStr">
+    <row r="37" ht="53.5" customHeight="1">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>返送方法</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>受任メールのリンクから案件ページを開き、記入したこのファイルをそのままお送りください。ZIPにする必要はありません。この経路は暗号化されており、メール添付より安全です。メールに直接添付して送るのは避けてください（マイナンバー等の特定個人情報を含みます）。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="37" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+    <row r="38" ht="37" customHeight="1">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>社内保管</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>記入途中のファイルは関係者以外がアクセスできない場所に保管し、提出後は社内ルールに従って適切に削除・保管してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40" ht="24" customHeight="1">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>この書類について</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20.5" customHeight="1">
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>事務所名</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>みなの社会保険労務士事務所</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20.5" customHeight="1">
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>076-460-2562 / contact@minano-sr.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20.5" customHeight="1">
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>バージョン</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>1.0（更新日 2026-09-11）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B12:C12"/>
   </mergeCells>
@@ -1837,199 +1831,199 @@
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>氏名（漢字）
 【必】</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>氏名（フリガナ）
 【必】</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>生年月日
 【必】</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>マイナンバー(12桁)
 【必】</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>基礎年金番号(10桁)
 【必】</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>雇用保険被保険者番号(11桁)
 【必】</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>郵便番号
 【必】</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>都道府県
 【必】</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>市区町村以下
 【必】</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>建物名・部屋番号
 【任】</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>電話番号
 【任】</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>離職日（退職日）
 【必】</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>資格喪失日（自動）
 【自動】</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>退職理由
 【必】</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>離職理由区分（分かる場合のみ・当方で判定します）
 【任】</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>退職の話が出た日
 【任】</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>離職理由の具体的事情
 【条件により必須】</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>契約更新条項（有期契約のみ）
 【条件により必須】</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="6" t="inlineStr">
         <is>
           <t>本人の更新希望（有期契約のみ）
 【条件により必須】</t>
         </is>
       </c>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>雇用保険 資格取得年月日
 【必】</t>
         </is>
       </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>1週間の所定労働時間(時間)
 【必】</t>
         </is>
       </c>
-      <c r="V7" s="6" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>離職票の交付希望
 【必】</t>
         </is>
       </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="W7" s="6" t="inlineStr">
         <is>
           <t>離職票の送付先（転居する場合）
 【任】</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>賃金締切日
 【条件により必須】</t>
         </is>
       </c>
-      <c r="Y7" s="7" t="inlineStr">
+      <c r="Y7" s="6" t="inlineStr">
         <is>
           <t>離職前賃金（直近1か月・円）
 【任】</t>
         </is>
       </c>
-      <c r="Z7" s="7" t="inlineStr">
+      <c r="Z7" s="6" t="inlineStr">
         <is>
           <t>直近の賞与（円）
 【任】</t>
         </is>
       </c>
-      <c r="AA7" s="6" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>資格確認書等の回収
 【必】</t>
         </is>
       </c>
-      <c r="AB7" s="7" t="inlineStr">
+      <c r="AB7" s="6" t="inlineStr">
         <is>
           <t>回収できなかったもの
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AC7" s="7" t="inlineStr">
+      <c r="AC7" s="6" t="inlineStr">
         <is>
           <t>退職後の希望
 【任】</t>
         </is>
       </c>
-      <c r="AD7" s="7" t="inlineStr">
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>備考（連絡事項）
 【任】</t>
         </is>
       </c>
-      <c r="AE7" s="7" t="inlineStr">
+      <c r="AE7" s="6" t="inlineStr">
         <is>
           <t>国籍・地域
 【任】</t>
         </is>
       </c>
-      <c r="AF7" s="7" t="inlineStr">
+      <c r="AF7" s="6" t="inlineStr">
         <is>
           <t>在留資格【外国籍のとき必須】
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AG7" s="7" t="inlineStr">
+      <c r="AG7" s="6" t="inlineStr">
         <is>
           <t>在留期間の満了日【外国籍のとき必須】
 【条件により必須】</t>
@@ -2215,7 +2209,7 @@
       <c r="AE9" s="18" t="n"/>
       <c r="AF9" s="18" t="n"/>
       <c r="AG9" s="20" t="n"/>
-      <c r="AH9" s="13">
+      <c r="AH9" s="12">
         <f>IF($A9="","",IF(AI9&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2261,7 +2255,7 @@
       <c r="AE10" s="18" t="n"/>
       <c r="AF10" s="18" t="n"/>
       <c r="AG10" s="20" t="n"/>
-      <c r="AH10" s="13">
+      <c r="AH10" s="12">
         <f>IF($A10="","",IF(AI10&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2307,7 +2301,7 @@
       <c r="AE11" s="18" t="n"/>
       <c r="AF11" s="18" t="n"/>
       <c r="AG11" s="20" t="n"/>
-      <c r="AH11" s="13">
+      <c r="AH11" s="12">
         <f>IF($A11="","",IF(AI11&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2353,7 +2347,7 @@
       <c r="AE12" s="18" t="n"/>
       <c r="AF12" s="18" t="n"/>
       <c r="AG12" s="20" t="n"/>
-      <c r="AH12" s="13">
+      <c r="AH12" s="12">
         <f>IF($A12="","",IF(AI12&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2399,7 +2393,7 @@
       <c r="AE13" s="18" t="n"/>
       <c r="AF13" s="18" t="n"/>
       <c r="AG13" s="20" t="n"/>
-      <c r="AH13" s="13">
+      <c r="AH13" s="12">
         <f>IF($A13="","",IF(AI13&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2445,7 +2439,7 @@
       <c r="AE14" s="18" t="n"/>
       <c r="AF14" s="18" t="n"/>
       <c r="AG14" s="20" t="n"/>
-      <c r="AH14" s="13">
+      <c r="AH14" s="12">
         <f>IF($A14="","",IF(AI14&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2491,7 +2485,7 @@
       <c r="AE15" s="18" t="n"/>
       <c r="AF15" s="18" t="n"/>
       <c r="AG15" s="20" t="n"/>
-      <c r="AH15" s="13">
+      <c r="AH15" s="12">
         <f>IF($A15="","",IF(AI15&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2537,7 +2531,7 @@
       <c r="AE16" s="18" t="n"/>
       <c r="AF16" s="18" t="n"/>
       <c r="AG16" s="20" t="n"/>
-      <c r="AH16" s="13">
+      <c r="AH16" s="12">
         <f>IF($A16="","",IF(AI16&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2583,7 +2577,7 @@
       <c r="AE17" s="18" t="n"/>
       <c r="AF17" s="18" t="n"/>
       <c r="AG17" s="20" t="n"/>
-      <c r="AH17" s="13">
+      <c r="AH17" s="12">
         <f>IF($A17="","",IF(AI17&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2629,7 +2623,7 @@
       <c r="AE18" s="18" t="n"/>
       <c r="AF18" s="18" t="n"/>
       <c r="AG18" s="20" t="n"/>
-      <c r="AH18" s="13">
+      <c r="AH18" s="12">
         <f>IF($A18="","",IF(AI18&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2675,7 +2669,7 @@
       <c r="AE19" s="18" t="n"/>
       <c r="AF19" s="18" t="n"/>
       <c r="AG19" s="20" t="n"/>
-      <c r="AH19" s="13">
+      <c r="AH19" s="12">
         <f>IF($A19="","",IF(AI19&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2721,7 +2715,7 @@
       <c r="AE20" s="18" t="n"/>
       <c r="AF20" s="18" t="n"/>
       <c r="AG20" s="20" t="n"/>
-      <c r="AH20" s="13">
+      <c r="AH20" s="12">
         <f>IF($A20="","",IF(AI20&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2767,7 +2761,7 @@
       <c r="AE21" s="18" t="n"/>
       <c r="AF21" s="18" t="n"/>
       <c r="AG21" s="20" t="n"/>
-      <c r="AH21" s="13">
+      <c r="AH21" s="12">
         <f>IF($A21="","",IF(AI21&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2813,7 +2807,7 @@
       <c r="AE22" s="18" t="n"/>
       <c r="AF22" s="18" t="n"/>
       <c r="AG22" s="20" t="n"/>
-      <c r="AH22" s="13">
+      <c r="AH22" s="12">
         <f>IF($A22="","",IF(AI22&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2859,7 +2853,7 @@
       <c r="AE23" s="18" t="n"/>
       <c r="AF23" s="18" t="n"/>
       <c r="AG23" s="20" t="n"/>
-      <c r="AH23" s="13">
+      <c r="AH23" s="12">
         <f>IF($A23="","",IF(AI23&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2905,7 +2899,7 @@
       <c r="AE24" s="18" t="n"/>
       <c r="AF24" s="18" t="n"/>
       <c r="AG24" s="20" t="n"/>
-      <c r="AH24" s="13">
+      <c r="AH24" s="12">
         <f>IF($A24="","",IF(AI24&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2951,7 +2945,7 @@
       <c r="AE25" s="18" t="n"/>
       <c r="AF25" s="18" t="n"/>
       <c r="AG25" s="20" t="n"/>
-      <c r="AH25" s="13">
+      <c r="AH25" s="12">
         <f>IF($A25="","",IF(AI25&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -2997,7 +2991,7 @@
       <c r="AE26" s="18" t="n"/>
       <c r="AF26" s="18" t="n"/>
       <c r="AG26" s="20" t="n"/>
-      <c r="AH26" s="13">
+      <c r="AH26" s="12">
         <f>IF($A26="","",IF(AI26&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3043,7 +3037,7 @@
       <c r="AE27" s="18" t="n"/>
       <c r="AF27" s="18" t="n"/>
       <c r="AG27" s="20" t="n"/>
-      <c r="AH27" s="13">
+      <c r="AH27" s="12">
         <f>IF($A27="","",IF(AI27&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3089,7 +3083,7 @@
       <c r="AE28" s="18" t="n"/>
       <c r="AF28" s="18" t="n"/>
       <c r="AG28" s="20" t="n"/>
-      <c r="AH28" s="13">
+      <c r="AH28" s="12">
         <f>IF($A28="","",IF(AI28&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3135,7 +3129,7 @@
       <c r="AE29" s="18" t="n"/>
       <c r="AF29" s="18" t="n"/>
       <c r="AG29" s="20" t="n"/>
-      <c r="AH29" s="13">
+      <c r="AH29" s="12">
         <f>IF($A29="","",IF(AI29&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3181,7 +3175,7 @@
       <c r="AE30" s="18" t="n"/>
       <c r="AF30" s="18" t="n"/>
       <c r="AG30" s="20" t="n"/>
-      <c r="AH30" s="13">
+      <c r="AH30" s="12">
         <f>IF($A30="","",IF(AI30&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3227,7 +3221,7 @@
       <c r="AE31" s="18" t="n"/>
       <c r="AF31" s="18" t="n"/>
       <c r="AG31" s="20" t="n"/>
-      <c r="AH31" s="13">
+      <c r="AH31" s="12">
         <f>IF($A31="","",IF(AI31&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3273,7 +3267,7 @@
       <c r="AE32" s="18" t="n"/>
       <c r="AF32" s="18" t="n"/>
       <c r="AG32" s="20" t="n"/>
-      <c r="AH32" s="13">
+      <c r="AH32" s="12">
         <f>IF($A32="","",IF(AI32&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3319,7 +3313,7 @@
       <c r="AE33" s="18" t="n"/>
       <c r="AF33" s="18" t="n"/>
       <c r="AG33" s="20" t="n"/>
-      <c r="AH33" s="13">
+      <c r="AH33" s="12">
         <f>IF($A33="","",IF(AI33&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3365,7 +3359,7 @@
       <c r="AE34" s="18" t="n"/>
       <c r="AF34" s="18" t="n"/>
       <c r="AG34" s="20" t="n"/>
-      <c r="AH34" s="13">
+      <c r="AH34" s="12">
         <f>IF($A34="","",IF(AI34&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3411,7 +3405,7 @@
       <c r="AE35" s="18" t="n"/>
       <c r="AF35" s="18" t="n"/>
       <c r="AG35" s="20" t="n"/>
-      <c r="AH35" s="13">
+      <c r="AH35" s="12">
         <f>IF($A35="","",IF(AI35&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3457,7 +3451,7 @@
       <c r="AE36" s="18" t="n"/>
       <c r="AF36" s="18" t="n"/>
       <c r="AG36" s="20" t="n"/>
-      <c r="AH36" s="13">
+      <c r="AH36" s="12">
         <f>IF($A36="","",IF(AI36&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3503,7 +3497,7 @@
       <c r="AE37" s="18" t="n"/>
       <c r="AF37" s="18" t="n"/>
       <c r="AG37" s="20" t="n"/>
-      <c r="AH37" s="13">
+      <c r="AH37" s="12">
         <f>IF($A37="","",IF(AI37&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3549,7 +3543,7 @@
       <c r="AE38" s="18" t="n"/>
       <c r="AF38" s="18" t="n"/>
       <c r="AG38" s="20" t="n"/>
-      <c r="AH38" s="13">
+      <c r="AH38" s="12">
         <f>IF($A38="","",IF(AI38&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3595,7 +3589,7 @@
       <c r="AE39" s="18" t="n"/>
       <c r="AF39" s="18" t="n"/>
       <c r="AG39" s="20" t="n"/>
-      <c r="AH39" s="13">
+      <c r="AH39" s="12">
         <f>IF($A39="","",IF(AI39&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3641,7 +3635,7 @@
       <c r="AE40" s="18" t="n"/>
       <c r="AF40" s="18" t="n"/>
       <c r="AG40" s="20" t="n"/>
-      <c r="AH40" s="13">
+      <c r="AH40" s="12">
         <f>IF($A40="","",IF(AI40&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3687,7 +3681,7 @@
       <c r="AE41" s="18" t="n"/>
       <c r="AF41" s="18" t="n"/>
       <c r="AG41" s="20" t="n"/>
-      <c r="AH41" s="13">
+      <c r="AH41" s="12">
         <f>IF($A41="","",IF(AI41&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3733,7 +3727,7 @@
       <c r="AE42" s="18" t="n"/>
       <c r="AF42" s="18" t="n"/>
       <c r="AG42" s="20" t="n"/>
-      <c r="AH42" s="13">
+      <c r="AH42" s="12">
         <f>IF($A42="","",IF(AI42&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3779,7 +3773,7 @@
       <c r="AE43" s="18" t="n"/>
       <c r="AF43" s="18" t="n"/>
       <c r="AG43" s="20" t="n"/>
-      <c r="AH43" s="13">
+      <c r="AH43" s="12">
         <f>IF($A43="","",IF(AI43&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3825,7 +3819,7 @@
       <c r="AE44" s="18" t="n"/>
       <c r="AF44" s="18" t="n"/>
       <c r="AG44" s="20" t="n"/>
-      <c r="AH44" s="13">
+      <c r="AH44" s="12">
         <f>IF($A44="","",IF(AI44&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3871,7 +3865,7 @@
       <c r="AE45" s="18" t="n"/>
       <c r="AF45" s="18" t="n"/>
       <c r="AG45" s="20" t="n"/>
-      <c r="AH45" s="13">
+      <c r="AH45" s="12">
         <f>IF($A45="","",IF(AI45&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3917,7 +3911,7 @@
       <c r="AE46" s="18" t="n"/>
       <c r="AF46" s="18" t="n"/>
       <c r="AG46" s="20" t="n"/>
-      <c r="AH46" s="13">
+      <c r="AH46" s="12">
         <f>IF($A46="","",IF(AI46&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -3963,7 +3957,7 @@
       <c r="AE47" s="18" t="n"/>
       <c r="AF47" s="18" t="n"/>
       <c r="AG47" s="20" t="n"/>
-      <c r="AH47" s="13">
+      <c r="AH47" s="12">
         <f>IF($A47="","",IF(AI47&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4009,7 +4003,7 @@
       <c r="AE48" s="18" t="n"/>
       <c r="AF48" s="18" t="n"/>
       <c r="AG48" s="20" t="n"/>
-      <c r="AH48" s="13">
+      <c r="AH48" s="12">
         <f>IF($A48="","",IF(AI48&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4055,7 +4049,7 @@
       <c r="AE49" s="18" t="n"/>
       <c r="AF49" s="18" t="n"/>
       <c r="AG49" s="20" t="n"/>
-      <c r="AH49" s="13">
+      <c r="AH49" s="12">
         <f>IF($A49="","",IF(AI49&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4101,7 +4095,7 @@
       <c r="AE50" s="18" t="n"/>
       <c r="AF50" s="18" t="n"/>
       <c r="AG50" s="20" t="n"/>
-      <c r="AH50" s="13">
+      <c r="AH50" s="12">
         <f>IF($A50="","",IF(AI50&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4147,7 +4141,7 @@
       <c r="AE51" s="18" t="n"/>
       <c r="AF51" s="18" t="n"/>
       <c r="AG51" s="20" t="n"/>
-      <c r="AH51" s="13">
+      <c r="AH51" s="12">
         <f>IF($A51="","",IF(AI51&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4193,7 +4187,7 @@
       <c r="AE52" s="18" t="n"/>
       <c r="AF52" s="18" t="n"/>
       <c r="AG52" s="20" t="n"/>
-      <c r="AH52" s="13">
+      <c r="AH52" s="12">
         <f>IF($A52="","",IF(AI52&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4239,7 +4233,7 @@
       <c r="AE53" s="18" t="n"/>
       <c r="AF53" s="18" t="n"/>
       <c r="AG53" s="20" t="n"/>
-      <c r="AH53" s="13">
+      <c r="AH53" s="12">
         <f>IF($A53="","",IF(AI53&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4285,7 +4279,7 @@
       <c r="AE54" s="18" t="n"/>
       <c r="AF54" s="18" t="n"/>
       <c r="AG54" s="20" t="n"/>
-      <c r="AH54" s="13">
+      <c r="AH54" s="12">
         <f>IF($A54="","",IF(AI54&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4331,7 +4325,7 @@
       <c r="AE55" s="18" t="n"/>
       <c r="AF55" s="18" t="n"/>
       <c r="AG55" s="20" t="n"/>
-      <c r="AH55" s="13">
+      <c r="AH55" s="12">
         <f>IF($A55="","",IF(AI55&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4377,7 +4371,7 @@
       <c r="AE56" s="18" t="n"/>
       <c r="AF56" s="18" t="n"/>
       <c r="AG56" s="20" t="n"/>
-      <c r="AH56" s="13">
+      <c r="AH56" s="12">
         <f>IF($A56="","",IF(AI56&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4423,7 +4417,7 @@
       <c r="AE57" s="18" t="n"/>
       <c r="AF57" s="18" t="n"/>
       <c r="AG57" s="20" t="n"/>
-      <c r="AH57" s="13">
+      <c r="AH57" s="12">
         <f>IF($A57="","",IF(AI57&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>
@@ -4469,7 +4463,7 @@
       <c r="AE58" s="18" t="n"/>
       <c r="AF58" s="18" t="n"/>
       <c r="AG58" s="20" t="n"/>
-      <c r="AH58" s="13">
+      <c r="AH58" s="12">
         <f>IF($A58="","",IF(AI58&gt;0,"未入力","CSV可"))</f>
         <v/>
       </c>

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -1020,7 +1020,7 @@
     <row r="7" ht="24" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>入力の流れ</t>
+          <t>入力の流れ（所要時間の目安：1名あたり 4 分ほど）</t>
         </is>
       </c>
     </row>

--- a/go/xlsx/taishoku-juryo-form.xlsx
+++ b/go/xlsx/taishoku-juryo-form.xlsx
@@ -30,6 +30,7 @@
     <definedName name="m_退職金">'_マスタ（非表示）'!$N$2:$N$4</definedName>
     <definedName name="m_退職所得申告">'_マスタ（非表示）'!$O$2:$O$4</definedName>
     <definedName name="m_国籍">'_マスタ（非表示）'!$P$2:$P$3</definedName>
+    <definedName name="m_退職後給与">'_マスタ（非表示）'!$Q$2:$Q$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'退職 情報'!$1:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -636,50 +637,60 @@
     </comment>
     <comment ref="X7" authorId="0" shapeId="0">
       <text>
-        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
+        <t>用途：離職証明書の賃金欄・未計算欄の書き分け。</t>
       </text>
     </comment>
     <comment ref="Y7" authorId="0" shapeId="0">
       <text>
-        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
+        <t>用途：同 支払日。</t>
       </text>
     </comment>
     <comment ref="Z7" authorId="0" shapeId="0">
       <text>
-        <t>用途：直近賞与の参考値。</t>
+        <t>用途：賃金締切日（離職証明書の賃金支払対象期間の区切り）。</t>
       </text>
     </comment>
     <comment ref="AA7" authorId="0" shapeId="0">
       <text>
-        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
+        <t>用途：離職前賃金の参考値（正確な額は賃金台帳で算定）。</t>
       </text>
     </comment>
     <comment ref="AB7" authorId="0" shapeId="0">
       <text>
-        <t>用途：健康保険被保険者証等回収不能届に書く品目。</t>
+        <t>用途：直近賞与の参考値。</t>
       </text>
     </comment>
     <comment ref="AC7" authorId="0" shapeId="0">
       <text>
-        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
+        <t>用途：資格喪失届に添付する資格確認書等の回収状況（回収不能なら回収不能届）。</t>
       </text>
     </comment>
     <comment ref="AD7" authorId="0" shapeId="0">
       <text>
-        <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
+        <t>用途：健康保険被保険者証等回収不能届に書く品目。</t>
       </text>
     </comment>
     <comment ref="AE7" authorId="0" shapeId="0">
       <text>
-        <t>用途：外国人雇用状況の届出（資格取得届・喪失届と一体）の国籍欄。</t>
+        <t>用途：退職後の医療保険の予定（任意継続・扶養・国保）。手続き案内用。</t>
       </text>
     </comment>
     <comment ref="AF7" authorId="0" shapeId="0">
       <text>
+        <t>用途：連絡事項（係争の有無・特記など）。自由記入。</t>
+      </text>
+    </comment>
+    <comment ref="AG7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：外国人雇用状況の届出（資格取得届・喪失届と一体）の国籍欄。</t>
+      </text>
+    </comment>
+    <comment ref="AH7" authorId="0" shapeId="0">
+      <text>
         <t>用途：同 在留資格欄。外国籍の方のみ。</t>
       </text>
     </comment>
-    <comment ref="AG7" authorId="0" shapeId="0">
+    <comment ref="AI7" authorId="0" shapeId="0">
       <text>
         <t>用途：同 在留期間欄。外国籍の方のみ。</t>
       </text>
@@ -1670,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI58"/>
+  <dimension ref="A1:AK58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1696,18 +1707,20 @@
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="17" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="32" customWidth="1" min="28" max="28"/>
-    <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="36" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="32" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="36" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1716,7 +1729,7 @@
           <t>退職 情報</t>
         </is>
       </c>
-      <c r="Q1" s="26" t="inlineStr">
+      <c r="R1" s="26" t="inlineStr">
         <is>
           <t>※離職理由区分は目安。最終判断は社労士・ハローワークが行います。</t>
         </is>
@@ -1772,11 +1785,11 @@
         <v/>
       </c>
       <c r="C4" s="29">
-        <f>COUNTIF(AI9:AI58,0)</f>
+        <f>COUNTIF(AK9:AK58,0)</f>
         <v/>
       </c>
       <c r="E4" s="29">
-        <f>SUM(AI9:AI58)</f>
+        <f>SUM(AK9:AK58)</f>
         <v/>
       </c>
       <c r="G4" s="30">
@@ -1814,17 +1827,17 @@
           <t>雇用保険</t>
         </is>
       </c>
-      <c r="AA6" s="35" t="inlineStr">
+      <c r="AC6" s="35" t="inlineStr">
         <is>
           <t>社会保険</t>
         </is>
       </c>
-      <c r="AD6" s="36" t="inlineStr">
+      <c r="AF6" s="36" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AE6" s="37" t="inlineStr">
+      <c r="AG6" s="37" t="inlineStr">
         <is>
           <t>外国籍のとき</t>
         </is>
@@ -1971,65 +1984,77 @@
       </c>
       <c r="X7" s="6" t="inlineStr">
         <is>
+          <t>退職日より後に払う給与は
+【条件により必須】</t>
+        </is>
+      </c>
+      <c r="Y7" s="6" t="inlineStr">
+        <is>
+          <t>その支払日
+【条件により必須】</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="inlineStr">
+        <is>
           <t>賃金締切日
 【条件により必須】</t>
         </is>
       </c>
-      <c r="Y7" s="6" t="inlineStr">
+      <c r="AA7" s="6" t="inlineStr">
         <is>
           <t>離職前賃金（直近1か月・円）
 【任】</t>
         </is>
       </c>
-      <c r="Z7" s="6" t="inlineStr">
+      <c r="AB7" s="6" t="inlineStr">
         <is>
           <t>直近の賞与（円）
 【任】</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>資格確認書等の回収
 【必】</t>
         </is>
       </c>
-      <c r="AB7" s="6" t="inlineStr">
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>回収できなかったもの
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AC7" s="6" t="inlineStr">
+      <c r="AE7" s="6" t="inlineStr">
         <is>
           <t>退職後の希望
 【任】</t>
         </is>
       </c>
-      <c r="AD7" s="6" t="inlineStr">
+      <c r="AF7" s="6" t="inlineStr">
         <is>
           <t>備考（連絡事項）
 【任】</t>
         </is>
       </c>
-      <c r="AE7" s="6" t="inlineStr">
+      <c r="AG7" s="6" t="inlineStr">
         <is>
           <t>国籍・地域
 【任】</t>
         </is>
       </c>
-      <c r="AF7" s="6" t="inlineStr">
+      <c r="AH7" s="6" t="inlineStr">
         <is>
           <t>在留資格【外国籍のとき必須】
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AG7" s="6" t="inlineStr">
+      <c r="AI7" s="6" t="inlineStr">
         <is>
           <t>在留期間の満了日【外国籍のとき必須】
 【条件により必須】</t>
         </is>
       </c>
-      <c r="AH7" s="38" t="inlineStr">
+      <c r="AJ7" s="38" t="inlineStr">
         <is>
           <t>行ステータス
 （CSV可否）</t>
@@ -2139,38 +2164,44 @@
       <c r="W8" s="40" t="n"/>
       <c r="X8" s="40" t="inlineStr">
         <is>
+          <t>ない</t>
+        </is>
+      </c>
+      <c r="Y8" s="41" t="inlineStr"/>
+      <c r="Z8" s="40" t="inlineStr">
+        <is>
           <t>毎月末日</t>
         </is>
       </c>
-      <c r="Y8" s="44" t="n">
+      <c r="AA8" s="44" t="n">
         <v>300000</v>
       </c>
-      <c r="Z8" s="44" t="n">
+      <c r="AB8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" s="40" t="inlineStr">
+      <c r="AC8" s="40" t="inlineStr">
         <is>
           <t>回収済</t>
         </is>
       </c>
-      <c r="AB8" s="40" t="inlineStr"/>
-      <c r="AC8" s="40" t="inlineStr">
+      <c r="AD8" s="40" t="inlineStr"/>
+      <c r="AE8" s="40" t="inlineStr">
         <is>
           <t>家族の扶養に入る</t>
         </is>
       </c>
-      <c r="AD8" s="40" t="inlineStr">
+      <c r="AF8" s="40" t="inlineStr">
         <is>
           <t>← この行は記入例です</t>
         </is>
       </c>
-      <c r="AE8" s="40" t="inlineStr">
+      <c r="AG8" s="40" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="AF8" s="40" t="n"/>
-      <c r="AG8" s="41" t="n"/>
+      <c r="AH8" s="40" t="n"/>
+      <c r="AI8" s="41" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
@@ -2200,21 +2231,23 @@
       <c r="V9" s="18" t="n"/>
       <c r="W9" s="18" t="n"/>
       <c r="X9" s="18" t="n"/>
-      <c r="Y9" s="48" t="n"/>
-      <c r="Z9" s="48" t="n"/>
-      <c r="AA9" s="18" t="n"/>
-      <c r="AB9" s="18" t="n"/>
+      <c r="Y9" s="20" t="n"/>
+      <c r="Z9" s="18" t="n"/>
+      <c r="AA9" s="48" t="n"/>
+      <c r="AB9" s="48" t="n"/>
       <c r="AC9" s="18" t="n"/>
       <c r="AD9" s="18" t="n"/>
       <c r="AE9" s="18" t="n"/>
       <c r="AF9" s="18" t="n"/>
-      <c r="AG9" s="20" t="n"/>
-      <c r="AH9" s="12">
-        <f>IF($A9="","",IF(AI9&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI9">
-        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($T9="",1,0)+IF($U9="",1,0)+IF($V9="",1,0)+IF($AA9="",1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0)+IF(AND($N9="契約期間満了",$S9=""),1,0)+IF(AND($AE9="外国",$AF9=""),1,0)+IF(AND($AE9="外国",$AG9=""),1,0)+IF(AND($AA9="未回収",$AB9=""),1,0)+IF(AND($V9="あり",$Q9=""),1,0)+IF(AND($V9="あり",$X9=""),1,0))</f>
+      <c r="AG9" s="18" t="n"/>
+      <c r="AH9" s="18" t="n"/>
+      <c r="AI9" s="20" t="n"/>
+      <c r="AJ9" s="12">
+        <f>IF($A9="","",IF(AK9&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK9">
+        <f>IF($A9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($N9="",1,0)+IF($T9="",1,0)+IF($U9="",1,0)+IF($V9="",1,0)+IF($AC9="",1,0)+IF(AND($N9="契約期間満了",$R9=""),1,0)+IF(AND($N9="契約期間満了",$S9=""),1,0)+IF(AND($AG9="外国",$AH9=""),1,0)+IF(AND($AG9="外国",$AI9=""),1,0)+IF(AND($AC9="未回収",$AD9=""),1,0)+IF(AND($V9="あり",$X9=""),1,0)+IF(AND($X9="ある",$Y9=""),1,0)+IF(AND($V9="あり",$Q9=""),1,0)+IF(AND($V9="あり",$Z9=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2246,21 +2279,23 @@
       <c r="V10" s="18" t="n"/>
       <c r="W10" s="18" t="n"/>
       <c r="X10" s="18" t="n"/>
-      <c r="Y10" s="48" t="n"/>
-      <c r="Z10" s="48" t="n"/>
-      <c r="AA10" s="18" t="n"/>
-      <c r="AB10" s="18" t="n"/>
+      <c r="Y10" s="20" t="n"/>
+      <c r="Z10" s="18" t="n"/>
+      <c r="AA10" s="48" t="n"/>
+      <c r="AB10" s="48" t="n"/>
       <c r="AC10" s="18" t="n"/>
       <c r="AD10" s="18" t="n"/>
       <c r="AE10" s="18" t="n"/>
       <c r="AF10" s="18" t="n"/>
-      <c r="AG10" s="20" t="n"/>
-      <c r="AH10" s="12">
-        <f>IF($A10="","",IF(AI10&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI10">
-        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($T10="",1,0)+IF($U10="",1,0)+IF($V10="",1,0)+IF($AA10="",1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0)+IF(AND($N10="契約期間満了",$S10=""),1,0)+IF(AND($AE10="外国",$AF10=""),1,0)+IF(AND($AE10="外国",$AG10=""),1,0)+IF(AND($AA10="未回収",$AB10=""),1,0)+IF(AND($V10="あり",$Q10=""),1,0)+IF(AND($V10="あり",$X10=""),1,0))</f>
+      <c r="AG10" s="18" t="n"/>
+      <c r="AH10" s="18" t="n"/>
+      <c r="AI10" s="20" t="n"/>
+      <c r="AJ10" s="12">
+        <f>IF($A10="","",IF(AK10&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK10">
+        <f>IF($A10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($N10="",1,0)+IF($T10="",1,0)+IF($U10="",1,0)+IF($V10="",1,0)+IF($AC10="",1,0)+IF(AND($N10="契約期間満了",$R10=""),1,0)+IF(AND($N10="契約期間満了",$S10=""),1,0)+IF(AND($AG10="外国",$AH10=""),1,0)+IF(AND($AG10="外国",$AI10=""),1,0)+IF(AND($AC10="未回収",$AD10=""),1,0)+IF(AND($V10="あり",$X10=""),1,0)+IF(AND($X10="ある",$Y10=""),1,0)+IF(AND($V10="あり",$Q10=""),1,0)+IF(AND($V10="あり",$Z10=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2292,21 +2327,23 @@
       <c r="V11" s="18" t="n"/>
       <c r="W11" s="18" t="n"/>
       <c r="X11" s="18" t="n"/>
-      <c r="Y11" s="48" t="n"/>
-      <c r="Z11" s="48" t="n"/>
-      <c r="AA11" s="18" t="n"/>
-      <c r="AB11" s="18" t="n"/>
+      <c r="Y11" s="20" t="n"/>
+      <c r="Z11" s="18" t="n"/>
+      <c r="AA11" s="48" t="n"/>
+      <c r="AB11" s="48" t="n"/>
       <c r="AC11" s="18" t="n"/>
       <c r="AD11" s="18" t="n"/>
       <c r="AE11" s="18" t="n"/>
       <c r="AF11" s="18" t="n"/>
-      <c r="AG11" s="20" t="n"/>
-      <c r="AH11" s="12">
-        <f>IF($A11="","",IF(AI11&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI11">
-        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($T11="",1,0)+IF($U11="",1,0)+IF($V11="",1,0)+IF($AA11="",1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0)+IF(AND($N11="契約期間満了",$S11=""),1,0)+IF(AND($AE11="外国",$AF11=""),1,0)+IF(AND($AE11="外国",$AG11=""),1,0)+IF(AND($AA11="未回収",$AB11=""),1,0)+IF(AND($V11="あり",$Q11=""),1,0)+IF(AND($V11="あり",$X11=""),1,0))</f>
+      <c r="AG11" s="18" t="n"/>
+      <c r="AH11" s="18" t="n"/>
+      <c r="AI11" s="20" t="n"/>
+      <c r="AJ11" s="12">
+        <f>IF($A11="","",IF(AK11&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK11">
+        <f>IF($A11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($N11="",1,0)+IF($T11="",1,0)+IF($U11="",1,0)+IF($V11="",1,0)+IF($AC11="",1,0)+IF(AND($N11="契約期間満了",$R11=""),1,0)+IF(AND($N11="契約期間満了",$S11=""),1,0)+IF(AND($AG11="外国",$AH11=""),1,0)+IF(AND($AG11="外国",$AI11=""),1,0)+IF(AND($AC11="未回収",$AD11=""),1,0)+IF(AND($V11="あり",$X11=""),1,0)+IF(AND($X11="ある",$Y11=""),1,0)+IF(AND($V11="あり",$Q11=""),1,0)+IF(AND($V11="あり",$Z11=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2338,21 +2375,23 @@
       <c r="V12" s="18" t="n"/>
       <c r="W12" s="18" t="n"/>
       <c r="X12" s="18" t="n"/>
-      <c r="Y12" s="48" t="n"/>
-      <c r="Z12" s="48" t="n"/>
-      <c r="AA12" s="18" t="n"/>
-      <c r="AB12" s="18" t="n"/>
+      <c r="Y12" s="20" t="n"/>
+      <c r="Z12" s="18" t="n"/>
+      <c r="AA12" s="48" t="n"/>
+      <c r="AB12" s="48" t="n"/>
       <c r="AC12" s="18" t="n"/>
       <c r="AD12" s="18" t="n"/>
       <c r="AE12" s="18" t="n"/>
       <c r="AF12" s="18" t="n"/>
-      <c r="AG12" s="20" t="n"/>
-      <c r="AH12" s="12">
-        <f>IF($A12="","",IF(AI12&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI12">
-        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($T12="",1,0)+IF($U12="",1,0)+IF($V12="",1,0)+IF($AA12="",1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0)+IF(AND($N12="契約期間満了",$S12=""),1,0)+IF(AND($AE12="外国",$AF12=""),1,0)+IF(AND($AE12="外国",$AG12=""),1,0)+IF(AND($AA12="未回収",$AB12=""),1,0)+IF(AND($V12="あり",$Q12=""),1,0)+IF(AND($V12="あり",$X12=""),1,0))</f>
+      <c r="AG12" s="18" t="n"/>
+      <c r="AH12" s="18" t="n"/>
+      <c r="AI12" s="20" t="n"/>
+      <c r="AJ12" s="12">
+        <f>IF($A12="","",IF(AK12&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK12">
+        <f>IF($A12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($N12="",1,0)+IF($T12="",1,0)+IF($U12="",1,0)+IF($V12="",1,0)+IF($AC12="",1,0)+IF(AND($N12="契約期間満了",$R12=""),1,0)+IF(AND($N12="契約期間満了",$S12=""),1,0)+IF(AND($AG12="外国",$AH12=""),1,0)+IF(AND($AG12="外国",$AI12=""),1,0)+IF(AND($AC12="未回収",$AD12=""),1,0)+IF(AND($V12="あり",$X12=""),1,0)+IF(AND($X12="ある",$Y12=""),1,0)+IF(AND($V12="あり",$Q12=""),1,0)+IF(AND($V12="あり",$Z12=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2384,21 +2423,23 @@
       <c r="V13" s="18" t="n"/>
       <c r="W13" s="18" t="n"/>
       <c r="X13" s="18" t="n"/>
-      <c r="Y13" s="48" t="n"/>
-      <c r="Z13" s="48" t="n"/>
-      <c r="AA13" s="18" t="n"/>
-      <c r="AB13" s="18" t="n"/>
+      <c r="Y13" s="20" t="n"/>
+      <c r="Z13" s="18" t="n"/>
+      <c r="AA13" s="48" t="n"/>
+      <c r="AB13" s="48" t="n"/>
       <c r="AC13" s="18" t="n"/>
       <c r="AD13" s="18" t="n"/>
       <c r="AE13" s="18" t="n"/>
       <c r="AF13" s="18" t="n"/>
-      <c r="AG13" s="20" t="n"/>
-      <c r="AH13" s="12">
-        <f>IF($A13="","",IF(AI13&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI13">
-        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($T13="",1,0)+IF($U13="",1,0)+IF($V13="",1,0)+IF($AA13="",1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0)+IF(AND($N13="契約期間満了",$S13=""),1,0)+IF(AND($AE13="外国",$AF13=""),1,0)+IF(AND($AE13="外国",$AG13=""),1,0)+IF(AND($AA13="未回収",$AB13=""),1,0)+IF(AND($V13="あり",$Q13=""),1,0)+IF(AND($V13="あり",$X13=""),1,0))</f>
+      <c r="AG13" s="18" t="n"/>
+      <c r="AH13" s="18" t="n"/>
+      <c r="AI13" s="20" t="n"/>
+      <c r="AJ13" s="12">
+        <f>IF($A13="","",IF(AK13&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK13">
+        <f>IF($A13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($N13="",1,0)+IF($T13="",1,0)+IF($U13="",1,0)+IF($V13="",1,0)+IF($AC13="",1,0)+IF(AND($N13="契約期間満了",$R13=""),1,0)+IF(AND($N13="契約期間満了",$S13=""),1,0)+IF(AND($AG13="外国",$AH13=""),1,0)+IF(AND($AG13="外国",$AI13=""),1,0)+IF(AND($AC13="未回収",$AD13=""),1,0)+IF(AND($V13="あり",$X13=""),1,0)+IF(AND($X13="ある",$Y13=""),1,0)+IF(AND($V13="あり",$Q13=""),1,0)+IF(AND($V13="あり",$Z13=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2430,21 +2471,23 @@
       <c r="V14" s="18" t="n"/>
       <c r="W14" s="18" t="n"/>
       <c r="X14" s="18" t="n"/>
-      <c r="Y14" s="48" t="n"/>
-      <c r="Z14" s="48" t="n"/>
-      <c r="AA14" s="18" t="n"/>
-      <c r="AB14" s="18" t="n"/>
+      <c r="Y14" s="20" t="n"/>
+      <c r="Z14" s="18" t="n"/>
+      <c r="AA14" s="48" t="n"/>
+      <c r="AB14" s="48" t="n"/>
       <c r="AC14" s="18" t="n"/>
       <c r="AD14" s="18" t="n"/>
       <c r="AE14" s="18" t="n"/>
       <c r="AF14" s="18" t="n"/>
-      <c r="AG14" s="20" t="n"/>
-      <c r="AH14" s="12">
-        <f>IF($A14="","",IF(AI14&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI14">
-        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($T14="",1,0)+IF($U14="",1,0)+IF($V14="",1,0)+IF($AA14="",1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0)+IF(AND($N14="契約期間満了",$S14=""),1,0)+IF(AND($AE14="外国",$AF14=""),1,0)+IF(AND($AE14="外国",$AG14=""),1,0)+IF(AND($AA14="未回収",$AB14=""),1,0)+IF(AND($V14="あり",$Q14=""),1,0)+IF(AND($V14="あり",$X14=""),1,0))</f>
+      <c r="AG14" s="18" t="n"/>
+      <c r="AH14" s="18" t="n"/>
+      <c r="AI14" s="20" t="n"/>
+      <c r="AJ14" s="12">
+        <f>IF($A14="","",IF(AK14&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK14">
+        <f>IF($A14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($N14="",1,0)+IF($T14="",1,0)+IF($U14="",1,0)+IF($V14="",1,0)+IF($AC14="",1,0)+IF(AND($N14="契約期間満了",$R14=""),1,0)+IF(AND($N14="契約期間満了",$S14=""),1,0)+IF(AND($AG14="外国",$AH14=""),1,0)+IF(AND($AG14="外国",$AI14=""),1,0)+IF(AND($AC14="未回収",$AD14=""),1,0)+IF(AND($V14="あり",$X14=""),1,0)+IF(AND($X14="ある",$Y14=""),1,0)+IF(AND($V14="あり",$Q14=""),1,0)+IF(AND($V14="あり",$Z14=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2476,21 +2519,23 @@
       <c r="V15" s="18" t="n"/>
       <c r="W15" s="18" t="n"/>
       <c r="X15" s="18" t="n"/>
-      <c r="Y15" s="48" t="n"/>
-      <c r="Z15" s="48" t="n"/>
-      <c r="AA15" s="18" t="n"/>
-      <c r="AB15" s="18" t="n"/>
+      <c r="Y15" s="20" t="n"/>
+      <c r="Z15" s="18" t="n"/>
+      <c r="AA15" s="48" t="n"/>
+      <c r="AB15" s="48" t="n"/>
       <c r="AC15" s="18" t="n"/>
       <c r="AD15" s="18" t="n"/>
       <c r="AE15" s="18" t="n"/>
       <c r="AF15" s="18" t="n"/>
-      <c r="AG15" s="20" t="n"/>
-      <c r="AH15" s="12">
-        <f>IF($A15="","",IF(AI15&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI15">
-        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($T15="",1,0)+IF($U15="",1,0)+IF($V15="",1,0)+IF($AA15="",1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0)+IF(AND($N15="契約期間満了",$S15=""),1,0)+IF(AND($AE15="外国",$AF15=""),1,0)+IF(AND($AE15="外国",$AG15=""),1,0)+IF(AND($AA15="未回収",$AB15=""),1,0)+IF(AND($V15="あり",$Q15=""),1,0)+IF(AND($V15="あり",$X15=""),1,0))</f>
+      <c r="AG15" s="18" t="n"/>
+      <c r="AH15" s="18" t="n"/>
+      <c r="AI15" s="20" t="n"/>
+      <c r="AJ15" s="12">
+        <f>IF($A15="","",IF(AK15&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK15">
+        <f>IF($A15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($N15="",1,0)+IF($T15="",1,0)+IF($U15="",1,0)+IF($V15="",1,0)+IF($AC15="",1,0)+IF(AND($N15="契約期間満了",$R15=""),1,0)+IF(AND($N15="契約期間満了",$S15=""),1,0)+IF(AND($AG15="外国",$AH15=""),1,0)+IF(AND($AG15="外国",$AI15=""),1,0)+IF(AND($AC15="未回収",$AD15=""),1,0)+IF(AND($V15="あり",$X15=""),1,0)+IF(AND($X15="ある",$Y15=""),1,0)+IF(AND($V15="あり",$Q15=""),1,0)+IF(AND($V15="あり",$Z15=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2522,21 +2567,23 @@
       <c r="V16" s="18" t="n"/>
       <c r="W16" s="18" t="n"/>
       <c r="X16" s="18" t="n"/>
-      <c r="Y16" s="48" t="n"/>
-      <c r="Z16" s="48" t="n"/>
-      <c r="AA16" s="18" t="n"/>
-      <c r="AB16" s="18" t="n"/>
+      <c r="Y16" s="20" t="n"/>
+      <c r="Z16" s="18" t="n"/>
+      <c r="AA16" s="48" t="n"/>
+      <c r="AB16" s="48" t="n"/>
       <c r="AC16" s="18" t="n"/>
       <c r="AD16" s="18" t="n"/>
       <c r="AE16" s="18" t="n"/>
       <c r="AF16" s="18" t="n"/>
-      <c r="AG16" s="20" t="n"/>
-      <c r="AH16" s="12">
-        <f>IF($A16="","",IF(AI16&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI16">
-        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($T16="",1,0)+IF($U16="",1,0)+IF($V16="",1,0)+IF($AA16="",1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0)+IF(AND($N16="契約期間満了",$S16=""),1,0)+IF(AND($AE16="外国",$AF16=""),1,0)+IF(AND($AE16="外国",$AG16=""),1,0)+IF(AND($AA16="未回収",$AB16=""),1,0)+IF(AND($V16="あり",$Q16=""),1,0)+IF(AND($V16="あり",$X16=""),1,0))</f>
+      <c r="AG16" s="18" t="n"/>
+      <c r="AH16" s="18" t="n"/>
+      <c r="AI16" s="20" t="n"/>
+      <c r="AJ16" s="12">
+        <f>IF($A16="","",IF(AK16&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK16">
+        <f>IF($A16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($N16="",1,0)+IF($T16="",1,0)+IF($U16="",1,0)+IF($V16="",1,0)+IF($AC16="",1,0)+IF(AND($N16="契約期間満了",$R16=""),1,0)+IF(AND($N16="契約期間満了",$S16=""),1,0)+IF(AND($AG16="外国",$AH16=""),1,0)+IF(AND($AG16="外国",$AI16=""),1,0)+IF(AND($AC16="未回収",$AD16=""),1,0)+IF(AND($V16="あり",$X16=""),1,0)+IF(AND($X16="ある",$Y16=""),1,0)+IF(AND($V16="あり",$Q16=""),1,0)+IF(AND($V16="あり",$Z16=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2568,21 +2615,23 @@
       <c r="V17" s="18" t="n"/>
       <c r="W17" s="18" t="n"/>
       <c r="X17" s="18" t="n"/>
-      <c r="Y17" s="48" t="n"/>
-      <c r="Z17" s="48" t="n"/>
-      <c r="AA17" s="18" t="n"/>
-      <c r="AB17" s="18" t="n"/>
+      <c r="Y17" s="20" t="n"/>
+      <c r="Z17" s="18" t="n"/>
+      <c r="AA17" s="48" t="n"/>
+      <c r="AB17" s="48" t="n"/>
       <c r="AC17" s="18" t="n"/>
       <c r="AD17" s="18" t="n"/>
       <c r="AE17" s="18" t="n"/>
       <c r="AF17" s="18" t="n"/>
-      <c r="AG17" s="20" t="n"/>
-      <c r="AH17" s="12">
-        <f>IF($A17="","",IF(AI17&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI17">
-        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($T17="",1,0)+IF($U17="",1,0)+IF($V17="",1,0)+IF($AA17="",1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0)+IF(AND($N17="契約期間満了",$S17=""),1,0)+IF(AND($AE17="外国",$AF17=""),1,0)+IF(AND($AE17="外国",$AG17=""),1,0)+IF(AND($AA17="未回収",$AB17=""),1,0)+IF(AND($V17="あり",$Q17=""),1,0)+IF(AND($V17="あり",$X17=""),1,0))</f>
+      <c r="AG17" s="18" t="n"/>
+      <c r="AH17" s="18" t="n"/>
+      <c r="AI17" s="20" t="n"/>
+      <c r="AJ17" s="12">
+        <f>IF($A17="","",IF(AK17&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK17">
+        <f>IF($A17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($N17="",1,0)+IF($T17="",1,0)+IF($U17="",1,0)+IF($V17="",1,0)+IF($AC17="",1,0)+IF(AND($N17="契約期間満了",$R17=""),1,0)+IF(AND($N17="契約期間満了",$S17=""),1,0)+IF(AND($AG17="外国",$AH17=""),1,0)+IF(AND($AG17="外国",$AI17=""),1,0)+IF(AND($AC17="未回収",$AD17=""),1,0)+IF(AND($V17="あり",$X17=""),1,0)+IF(AND($X17="ある",$Y17=""),1,0)+IF(AND($V17="あり",$Q17=""),1,0)+IF(AND($V17="あり",$Z17=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2614,21 +2663,23 @@
       <c r="V18" s="18" t="n"/>
       <c r="W18" s="18" t="n"/>
       <c r="X18" s="18" t="n"/>
-      <c r="Y18" s="48" t="n"/>
-      <c r="Z18" s="48" t="n"/>
-      <c r="AA18" s="18" t="n"/>
-      <c r="AB18" s="18" t="n"/>
+      <c r="Y18" s="20" t="n"/>
+      <c r="Z18" s="18" t="n"/>
+      <c r="AA18" s="48" t="n"/>
+      <c r="AB18" s="48" t="n"/>
       <c r="AC18" s="18" t="n"/>
       <c r="AD18" s="18" t="n"/>
       <c r="AE18" s="18" t="n"/>
       <c r="AF18" s="18" t="n"/>
-      <c r="AG18" s="20" t="n"/>
-      <c r="AH18" s="12">
-        <f>IF($A18="","",IF(AI18&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI18">
-        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($T18="",1,0)+IF($U18="",1,0)+IF($V18="",1,0)+IF($AA18="",1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0)+IF(AND($N18="契約期間満了",$S18=""),1,0)+IF(AND($AE18="外国",$AF18=""),1,0)+IF(AND($AE18="外国",$AG18=""),1,0)+IF(AND($AA18="未回収",$AB18=""),1,0)+IF(AND($V18="あり",$Q18=""),1,0)+IF(AND($V18="あり",$X18=""),1,0))</f>
+      <c r="AG18" s="18" t="n"/>
+      <c r="AH18" s="18" t="n"/>
+      <c r="AI18" s="20" t="n"/>
+      <c r="AJ18" s="12">
+        <f>IF($A18="","",IF(AK18&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK18">
+        <f>IF($A18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($N18="",1,0)+IF($T18="",1,0)+IF($U18="",1,0)+IF($V18="",1,0)+IF($AC18="",1,0)+IF(AND($N18="契約期間満了",$R18=""),1,0)+IF(AND($N18="契約期間満了",$S18=""),1,0)+IF(AND($AG18="外国",$AH18=""),1,0)+IF(AND($AG18="外国",$AI18=""),1,0)+IF(AND($AC18="未回収",$AD18=""),1,0)+IF(AND($V18="あり",$X18=""),1,0)+IF(AND($X18="ある",$Y18=""),1,0)+IF(AND($V18="あり",$Q18=""),1,0)+IF(AND($V18="あり",$Z18=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2660,21 +2711,23 @@
       <c r="V19" s="18" t="n"/>
       <c r="W19" s="18" t="n"/>
       <c r="X19" s="18" t="n"/>
-      <c r="Y19" s="48" t="n"/>
-      <c r="Z19" s="48" t="n"/>
-      <c r="AA19" s="18" t="n"/>
-      <c r="AB19" s="18" t="n"/>
+      <c r="Y19" s="20" t="n"/>
+      <c r="Z19" s="18" t="n"/>
+      <c r="AA19" s="48" t="n"/>
+      <c r="AB19" s="48" t="n"/>
       <c r="AC19" s="18" t="n"/>
       <c r="AD19" s="18" t="n"/>
       <c r="AE19" s="18" t="n"/>
       <c r="AF19" s="18" t="n"/>
-      <c r="AG19" s="20" t="n"/>
-      <c r="AH19" s="12">
-        <f>IF($A19="","",IF(AI19&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI19">
-        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($T19="",1,0)+IF($U19="",1,0)+IF($V19="",1,0)+IF($AA19="",1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0)+IF(AND($N19="契約期間満了",$S19=""),1,0)+IF(AND($AE19="外国",$AF19=""),1,0)+IF(AND($AE19="外国",$AG19=""),1,0)+IF(AND($AA19="未回収",$AB19=""),1,0)+IF(AND($V19="あり",$Q19=""),1,0)+IF(AND($V19="あり",$X19=""),1,0))</f>
+      <c r="AG19" s="18" t="n"/>
+      <c r="AH19" s="18" t="n"/>
+      <c r="AI19" s="20" t="n"/>
+      <c r="AJ19" s="12">
+        <f>IF($A19="","",IF(AK19&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK19">
+        <f>IF($A19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($N19="",1,0)+IF($T19="",1,0)+IF($U19="",1,0)+IF($V19="",1,0)+IF($AC19="",1,0)+IF(AND($N19="契約期間満了",$R19=""),1,0)+IF(AND($N19="契約期間満了",$S19=""),1,0)+IF(AND($AG19="外国",$AH19=""),1,0)+IF(AND($AG19="外国",$AI19=""),1,0)+IF(AND($AC19="未回収",$AD19=""),1,0)+IF(AND($V19="あり",$X19=""),1,0)+IF(AND($X19="ある",$Y19=""),1,0)+IF(AND($V19="あり",$Q19=""),1,0)+IF(AND($V19="あり",$Z19=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2706,21 +2759,23 @@
       <c r="V20" s="18" t="n"/>
       <c r="W20" s="18" t="n"/>
       <c r="X20" s="18" t="n"/>
-      <c r="Y20" s="48" t="n"/>
-      <c r="Z20" s="48" t="n"/>
-      <c r="AA20" s="18" t="n"/>
-      <c r="AB20" s="18" t="n"/>
+      <c r="Y20" s="20" t="n"/>
+      <c r="Z20" s="18" t="n"/>
+      <c r="AA20" s="48" t="n"/>
+      <c r="AB20" s="48" t="n"/>
       <c r="AC20" s="18" t="n"/>
       <c r="AD20" s="18" t="n"/>
       <c r="AE20" s="18" t="n"/>
       <c r="AF20" s="18" t="n"/>
-      <c r="AG20" s="20" t="n"/>
-      <c r="AH20" s="12">
-        <f>IF($A20="","",IF(AI20&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI20">
-        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($T20="",1,0)+IF($U20="",1,0)+IF($V20="",1,0)+IF($AA20="",1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0)+IF(AND($N20="契約期間満了",$S20=""),1,0)+IF(AND($AE20="外国",$AF20=""),1,0)+IF(AND($AE20="外国",$AG20=""),1,0)+IF(AND($AA20="未回収",$AB20=""),1,0)+IF(AND($V20="あり",$Q20=""),1,0)+IF(AND($V20="あり",$X20=""),1,0))</f>
+      <c r="AG20" s="18" t="n"/>
+      <c r="AH20" s="18" t="n"/>
+      <c r="AI20" s="20" t="n"/>
+      <c r="AJ20" s="12">
+        <f>IF($A20="","",IF(AK20&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK20">
+        <f>IF($A20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($N20="",1,0)+IF($T20="",1,0)+IF($U20="",1,0)+IF($V20="",1,0)+IF($AC20="",1,0)+IF(AND($N20="契約期間満了",$R20=""),1,0)+IF(AND($N20="契約期間満了",$S20=""),1,0)+IF(AND($AG20="外国",$AH20=""),1,0)+IF(AND($AG20="外国",$AI20=""),1,0)+IF(AND($AC20="未回収",$AD20=""),1,0)+IF(AND($V20="あり",$X20=""),1,0)+IF(AND($X20="ある",$Y20=""),1,0)+IF(AND($V20="あり",$Q20=""),1,0)+IF(AND($V20="あり",$Z20=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2752,21 +2807,23 @@
       <c r="V21" s="18" t="n"/>
       <c r="W21" s="18" t="n"/>
       <c r="X21" s="18" t="n"/>
-      <c r="Y21" s="48" t="n"/>
-      <c r="Z21" s="48" t="n"/>
-      <c r="AA21" s="18" t="n"/>
-      <c r="AB21" s="18" t="n"/>
+      <c r="Y21" s="20" t="n"/>
+      <c r="Z21" s="18" t="n"/>
+      <c r="AA21" s="48" t="n"/>
+      <c r="AB21" s="48" t="n"/>
       <c r="AC21" s="18" t="n"/>
       <c r="AD21" s="18" t="n"/>
       <c r="AE21" s="18" t="n"/>
       <c r="AF21" s="18" t="n"/>
-      <c r="AG21" s="20" t="n"/>
-      <c r="AH21" s="12">
-        <f>IF($A21="","",IF(AI21&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI21">
-        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($T21="",1,0)+IF($U21="",1,0)+IF($V21="",1,0)+IF($AA21="",1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0)+IF(AND($N21="契約期間満了",$S21=""),1,0)+IF(AND($AE21="外国",$AF21=""),1,0)+IF(AND($AE21="外国",$AG21=""),1,0)+IF(AND($AA21="未回収",$AB21=""),1,0)+IF(AND($V21="あり",$Q21=""),1,0)+IF(AND($V21="あり",$X21=""),1,0))</f>
+      <c r="AG21" s="18" t="n"/>
+      <c r="AH21" s="18" t="n"/>
+      <c r="AI21" s="20" t="n"/>
+      <c r="AJ21" s="12">
+        <f>IF($A21="","",IF(AK21&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK21">
+        <f>IF($A21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($N21="",1,0)+IF($T21="",1,0)+IF($U21="",1,0)+IF($V21="",1,0)+IF($AC21="",1,0)+IF(AND($N21="契約期間満了",$R21=""),1,0)+IF(AND($N21="契約期間満了",$S21=""),1,0)+IF(AND($AG21="外国",$AH21=""),1,0)+IF(AND($AG21="外国",$AI21=""),1,0)+IF(AND($AC21="未回収",$AD21=""),1,0)+IF(AND($V21="あり",$X21=""),1,0)+IF(AND($X21="ある",$Y21=""),1,0)+IF(AND($V21="あり",$Q21=""),1,0)+IF(AND($V21="あり",$Z21=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2798,21 +2855,23 @@
       <c r="V22" s="18" t="n"/>
       <c r="W22" s="18" t="n"/>
       <c r="X22" s="18" t="n"/>
-      <c r="Y22" s="48" t="n"/>
-      <c r="Z22" s="48" t="n"/>
-      <c r="AA22" s="18" t="n"/>
-      <c r="AB22" s="18" t="n"/>
+      <c r="Y22" s="20" t="n"/>
+      <c r="Z22" s="18" t="n"/>
+      <c r="AA22" s="48" t="n"/>
+      <c r="AB22" s="48" t="n"/>
       <c r="AC22" s="18" t="n"/>
       <c r="AD22" s="18" t="n"/>
       <c r="AE22" s="18" t="n"/>
       <c r="AF22" s="18" t="n"/>
-      <c r="AG22" s="20" t="n"/>
-      <c r="AH22" s="12">
-        <f>IF($A22="","",IF(AI22&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI22">
-        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($T22="",1,0)+IF($U22="",1,0)+IF($V22="",1,0)+IF($AA22="",1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0)+IF(AND($N22="契約期間満了",$S22=""),1,0)+IF(AND($AE22="外国",$AF22=""),1,0)+IF(AND($AE22="外国",$AG22=""),1,0)+IF(AND($AA22="未回収",$AB22=""),1,0)+IF(AND($V22="あり",$Q22=""),1,0)+IF(AND($V22="あり",$X22=""),1,0))</f>
+      <c r="AG22" s="18" t="n"/>
+      <c r="AH22" s="18" t="n"/>
+      <c r="AI22" s="20" t="n"/>
+      <c r="AJ22" s="12">
+        <f>IF($A22="","",IF(AK22&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK22">
+        <f>IF($A22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($N22="",1,0)+IF($T22="",1,0)+IF($U22="",1,0)+IF($V22="",1,0)+IF($AC22="",1,0)+IF(AND($N22="契約期間満了",$R22=""),1,0)+IF(AND($N22="契約期間満了",$S22=""),1,0)+IF(AND($AG22="外国",$AH22=""),1,0)+IF(AND($AG22="外国",$AI22=""),1,0)+IF(AND($AC22="未回収",$AD22=""),1,0)+IF(AND($V22="あり",$X22=""),1,0)+IF(AND($X22="ある",$Y22=""),1,0)+IF(AND($V22="あり",$Q22=""),1,0)+IF(AND($V22="あり",$Z22=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2844,21 +2903,23 @@
       <c r="V23" s="18" t="n"/>
       <c r="W23" s="18" t="n"/>
       <c r="X23" s="18" t="n"/>
-      <c r="Y23" s="48" t="n"/>
-      <c r="Z23" s="48" t="n"/>
-      <c r="AA23" s="18" t="n"/>
-      <c r="AB23" s="18" t="n"/>
+      <c r="Y23" s="20" t="n"/>
+      <c r="Z23" s="18" t="n"/>
+      <c r="AA23" s="48" t="n"/>
+      <c r="AB23" s="48" t="n"/>
       <c r="AC23" s="18" t="n"/>
       <c r="AD23" s="18" t="n"/>
       <c r="AE23" s="18" t="n"/>
       <c r="AF23" s="18" t="n"/>
-      <c r="AG23" s="20" t="n"/>
-      <c r="AH23" s="12">
-        <f>IF($A23="","",IF(AI23&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI23">
-        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($T23="",1,0)+IF($U23="",1,0)+IF($V23="",1,0)+IF($AA23="",1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0)+IF(AND($N23="契約期間満了",$S23=""),1,0)+IF(AND($AE23="外国",$AF23=""),1,0)+IF(AND($AE23="外国",$AG23=""),1,0)+IF(AND($AA23="未回収",$AB23=""),1,0)+IF(AND($V23="あり",$Q23=""),1,0)+IF(AND($V23="あり",$X23=""),1,0))</f>
+      <c r="AG23" s="18" t="n"/>
+      <c r="AH23" s="18" t="n"/>
+      <c r="AI23" s="20" t="n"/>
+      <c r="AJ23" s="12">
+        <f>IF($A23="","",IF(AK23&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK23">
+        <f>IF($A23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($N23="",1,0)+IF($T23="",1,0)+IF($U23="",1,0)+IF($V23="",1,0)+IF($AC23="",1,0)+IF(AND($N23="契約期間満了",$R23=""),1,0)+IF(AND($N23="契約期間満了",$S23=""),1,0)+IF(AND($AG23="外国",$AH23=""),1,0)+IF(AND($AG23="外国",$AI23=""),1,0)+IF(AND($AC23="未回収",$AD23=""),1,0)+IF(AND($V23="あり",$X23=""),1,0)+IF(AND($X23="ある",$Y23=""),1,0)+IF(AND($V23="あり",$Q23=""),1,0)+IF(AND($V23="あり",$Z23=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2890,21 +2951,23 @@
       <c r="V24" s="18" t="n"/>
       <c r="W24" s="18" t="n"/>
       <c r="X24" s="18" t="n"/>
-      <c r="Y24" s="48" t="n"/>
-      <c r="Z24" s="48" t="n"/>
-      <c r="AA24" s="18" t="n"/>
-      <c r="AB24" s="18" t="n"/>
+      <c r="Y24" s="20" t="n"/>
+      <c r="Z24" s="18" t="n"/>
+      <c r="AA24" s="48" t="n"/>
+      <c r="AB24" s="48" t="n"/>
       <c r="AC24" s="18" t="n"/>
       <c r="AD24" s="18" t="n"/>
       <c r="AE24" s="18" t="n"/>
       <c r="AF24" s="18" t="n"/>
-      <c r="AG24" s="20" t="n"/>
-      <c r="AH24" s="12">
-        <f>IF($A24="","",IF(AI24&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI24">
-        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($T24="",1,0)+IF($U24="",1,0)+IF($V24="",1,0)+IF($AA24="",1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0)+IF(AND($N24="契約期間満了",$S24=""),1,0)+IF(AND($AE24="外国",$AF24=""),1,0)+IF(AND($AE24="外国",$AG24=""),1,0)+IF(AND($AA24="未回収",$AB24=""),1,0)+IF(AND($V24="あり",$Q24=""),1,0)+IF(AND($V24="あり",$X24=""),1,0))</f>
+      <c r="AG24" s="18" t="n"/>
+      <c r="AH24" s="18" t="n"/>
+      <c r="AI24" s="20" t="n"/>
+      <c r="AJ24" s="12">
+        <f>IF($A24="","",IF(AK24&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK24">
+        <f>IF($A24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($N24="",1,0)+IF($T24="",1,0)+IF($U24="",1,0)+IF($V24="",1,0)+IF($AC24="",1,0)+IF(AND($N24="契約期間満了",$R24=""),1,0)+IF(AND($N24="契約期間満了",$S24=""),1,0)+IF(AND($AG24="外国",$AH24=""),1,0)+IF(AND($AG24="外国",$AI24=""),1,0)+IF(AND($AC24="未回収",$AD24=""),1,0)+IF(AND($V24="あり",$X24=""),1,0)+IF(AND($X24="ある",$Y24=""),1,0)+IF(AND($V24="あり",$Q24=""),1,0)+IF(AND($V24="あり",$Z24=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2936,21 +2999,23 @@
       <c r="V25" s="18" t="n"/>
       <c r="W25" s="18" t="n"/>
       <c r="X25" s="18" t="n"/>
-      <c r="Y25" s="48" t="n"/>
-      <c r="Z25" s="48" t="n"/>
-      <c r="AA25" s="18" t="n"/>
-      <c r="AB25" s="18" t="n"/>
+      <c r="Y25" s="20" t="n"/>
+      <c r="Z25" s="18" t="n"/>
+      <c r="AA25" s="48" t="n"/>
+      <c r="AB25" s="48" t="n"/>
       <c r="AC25" s="18" t="n"/>
       <c r="AD25" s="18" t="n"/>
       <c r="AE25" s="18" t="n"/>
       <c r="AF25" s="18" t="n"/>
-      <c r="AG25" s="20" t="n"/>
-      <c r="AH25" s="12">
-        <f>IF($A25="","",IF(AI25&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI25">
-        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($T25="",1,0)+IF($U25="",1,0)+IF($V25="",1,0)+IF($AA25="",1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0)+IF(AND($N25="契約期間満了",$S25=""),1,0)+IF(AND($AE25="外国",$AF25=""),1,0)+IF(AND($AE25="外国",$AG25=""),1,0)+IF(AND($AA25="未回収",$AB25=""),1,0)+IF(AND($V25="あり",$Q25=""),1,0)+IF(AND($V25="あり",$X25=""),1,0))</f>
+      <c r="AG25" s="18" t="n"/>
+      <c r="AH25" s="18" t="n"/>
+      <c r="AI25" s="20" t="n"/>
+      <c r="AJ25" s="12">
+        <f>IF($A25="","",IF(AK25&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK25">
+        <f>IF($A25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($N25="",1,0)+IF($T25="",1,0)+IF($U25="",1,0)+IF($V25="",1,0)+IF($AC25="",1,0)+IF(AND($N25="契約期間満了",$R25=""),1,0)+IF(AND($N25="契約期間満了",$S25=""),1,0)+IF(AND($AG25="外国",$AH25=""),1,0)+IF(AND($AG25="外国",$AI25=""),1,0)+IF(AND($AC25="未回収",$AD25=""),1,0)+IF(AND($V25="あり",$X25=""),1,0)+IF(AND($X25="ある",$Y25=""),1,0)+IF(AND($V25="あり",$Q25=""),1,0)+IF(AND($V25="あり",$Z25=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2982,21 +3047,23 @@
       <c r="V26" s="18" t="n"/>
       <c r="W26" s="18" t="n"/>
       <c r="X26" s="18" t="n"/>
-      <c r="Y26" s="48" t="n"/>
-      <c r="Z26" s="48" t="n"/>
-      <c r="AA26" s="18" t="n"/>
-      <c r="AB26" s="18" t="n"/>
+      <c r="Y26" s="20" t="n"/>
+      <c r="Z26" s="18" t="n"/>
+      <c r="AA26" s="48" t="n"/>
+      <c r="AB26" s="48" t="n"/>
       <c r="AC26" s="18" t="n"/>
       <c r="AD26" s="18" t="n"/>
       <c r="AE26" s="18" t="n"/>
       <c r="AF26" s="18" t="n"/>
-      <c r="AG26" s="20" t="n"/>
-      <c r="AH26" s="12">
-        <f>IF($A26="","",IF(AI26&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI26">
-        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($T26="",1,0)+IF($U26="",1,0)+IF($V26="",1,0)+IF($AA26="",1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0)+IF(AND($N26="契約期間満了",$S26=""),1,0)+IF(AND($AE26="外国",$AF26=""),1,0)+IF(AND($AE26="外国",$AG26=""),1,0)+IF(AND($AA26="未回収",$AB26=""),1,0)+IF(AND($V26="あり",$Q26=""),1,0)+IF(AND($V26="あり",$X26=""),1,0))</f>
+      <c r="AG26" s="18" t="n"/>
+      <c r="AH26" s="18" t="n"/>
+      <c r="AI26" s="20" t="n"/>
+      <c r="AJ26" s="12">
+        <f>IF($A26="","",IF(AK26&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK26">
+        <f>IF($A26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($N26="",1,0)+IF($T26="",1,0)+IF($U26="",1,0)+IF($V26="",1,0)+IF($AC26="",1,0)+IF(AND($N26="契約期間満了",$R26=""),1,0)+IF(AND($N26="契約期間満了",$S26=""),1,0)+IF(AND($AG26="外国",$AH26=""),1,0)+IF(AND($AG26="外国",$AI26=""),1,0)+IF(AND($AC26="未回収",$AD26=""),1,0)+IF(AND($V26="あり",$X26=""),1,0)+IF(AND($X26="ある",$Y26=""),1,0)+IF(AND($V26="あり",$Q26=""),1,0)+IF(AND($V26="あり",$Z26=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3028,21 +3095,23 @@
       <c r="V27" s="18" t="n"/>
       <c r="W27" s="18" t="n"/>
       <c r="X27" s="18" t="n"/>
-      <c r="Y27" s="48" t="n"/>
-      <c r="Z27" s="48" t="n"/>
-      <c r="AA27" s="18" t="n"/>
-      <c r="AB27" s="18" t="n"/>
+      <c r="Y27" s="20" t="n"/>
+      <c r="Z27" s="18" t="n"/>
+      <c r="AA27" s="48" t="n"/>
+      <c r="AB27" s="48" t="n"/>
       <c r="AC27" s="18" t="n"/>
       <c r="AD27" s="18" t="n"/>
       <c r="AE27" s="18" t="n"/>
       <c r="AF27" s="18" t="n"/>
-      <c r="AG27" s="20" t="n"/>
-      <c r="AH27" s="12">
-        <f>IF($A27="","",IF(AI27&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI27">
-        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($T27="",1,0)+IF($U27="",1,0)+IF($V27="",1,0)+IF($AA27="",1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0)+IF(AND($N27="契約期間満了",$S27=""),1,0)+IF(AND($AE27="外国",$AF27=""),1,0)+IF(AND($AE27="外国",$AG27=""),1,0)+IF(AND($AA27="未回収",$AB27=""),1,0)+IF(AND($V27="あり",$Q27=""),1,0)+IF(AND($V27="あり",$X27=""),1,0))</f>
+      <c r="AG27" s="18" t="n"/>
+      <c r="AH27" s="18" t="n"/>
+      <c r="AI27" s="20" t="n"/>
+      <c r="AJ27" s="12">
+        <f>IF($A27="","",IF(AK27&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK27">
+        <f>IF($A27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($N27="",1,0)+IF($T27="",1,0)+IF($U27="",1,0)+IF($V27="",1,0)+IF($AC27="",1,0)+IF(AND($N27="契約期間満了",$R27=""),1,0)+IF(AND($N27="契約期間満了",$S27=""),1,0)+IF(AND($AG27="外国",$AH27=""),1,0)+IF(AND($AG27="外国",$AI27=""),1,0)+IF(AND($AC27="未回収",$AD27=""),1,0)+IF(AND($V27="あり",$X27=""),1,0)+IF(AND($X27="ある",$Y27=""),1,0)+IF(AND($V27="あり",$Q27=""),1,0)+IF(AND($V27="あり",$Z27=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3074,21 +3143,23 @@
       <c r="V28" s="18" t="n"/>
       <c r="W28" s="18" t="n"/>
       <c r="X28" s="18" t="n"/>
-      <c r="Y28" s="48" t="n"/>
-      <c r="Z28" s="48" t="n"/>
-      <c r="AA28" s="18" t="n"/>
-      <c r="AB28" s="18" t="n"/>
+      <c r="Y28" s="20" t="n"/>
+      <c r="Z28" s="18" t="n"/>
+      <c r="AA28" s="48" t="n"/>
+      <c r="AB28" s="48" t="n"/>
       <c r="AC28" s="18" t="n"/>
       <c r="AD28" s="18" t="n"/>
       <c r="AE28" s="18" t="n"/>
       <c r="AF28" s="18" t="n"/>
-      <c r="AG28" s="20" t="n"/>
-      <c r="AH28" s="12">
-        <f>IF($A28="","",IF(AI28&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI28">
-        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($T28="",1,0)+IF($U28="",1,0)+IF($V28="",1,0)+IF($AA28="",1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0)+IF(AND($N28="契約期間満了",$S28=""),1,0)+IF(AND($AE28="外国",$AF28=""),1,0)+IF(AND($AE28="外国",$AG28=""),1,0)+IF(AND($AA28="未回収",$AB28=""),1,0)+IF(AND($V28="あり",$Q28=""),1,0)+IF(AND($V28="あり",$X28=""),1,0))</f>
+      <c r="AG28" s="18" t="n"/>
+      <c r="AH28" s="18" t="n"/>
+      <c r="AI28" s="20" t="n"/>
+      <c r="AJ28" s="12">
+        <f>IF($A28="","",IF(AK28&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK28">
+        <f>IF($A28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($N28="",1,0)+IF($T28="",1,0)+IF($U28="",1,0)+IF($V28="",1,0)+IF($AC28="",1,0)+IF(AND($N28="契約期間満了",$R28=""),1,0)+IF(AND($N28="契約期間満了",$S28=""),1,0)+IF(AND($AG28="外国",$AH28=""),1,0)+IF(AND($AG28="外国",$AI28=""),1,0)+IF(AND($AC28="未回収",$AD28=""),1,0)+IF(AND($V28="あり",$X28=""),1,0)+IF(AND($X28="ある",$Y28=""),1,0)+IF(AND($V28="あり",$Q28=""),1,0)+IF(AND($V28="あり",$Z28=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3120,21 +3191,23 @@
       <c r="V29" s="18" t="n"/>
       <c r="W29" s="18" t="n"/>
       <c r="X29" s="18" t="n"/>
-      <c r="Y29" s="48" t="n"/>
-      <c r="Z29" s="48" t="n"/>
-      <c r="AA29" s="18" t="n"/>
-      <c r="AB29" s="18" t="n"/>
+      <c r="Y29" s="20" t="n"/>
+      <c r="Z29" s="18" t="n"/>
+      <c r="AA29" s="48" t="n"/>
+      <c r="AB29" s="48" t="n"/>
       <c r="AC29" s="18" t="n"/>
       <c r="AD29" s="18" t="n"/>
       <c r="AE29" s="18" t="n"/>
       <c r="AF29" s="18" t="n"/>
-      <c r="AG29" s="20" t="n"/>
-      <c r="AH29" s="12">
-        <f>IF($A29="","",IF(AI29&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI29">
-        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($T29="",1,0)+IF($U29="",1,0)+IF($V29="",1,0)+IF($AA29="",1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0)+IF(AND($N29="契約期間満了",$S29=""),1,0)+IF(AND($AE29="外国",$AF29=""),1,0)+IF(AND($AE29="外国",$AG29=""),1,0)+IF(AND($AA29="未回収",$AB29=""),1,0)+IF(AND($V29="あり",$Q29=""),1,0)+IF(AND($V29="あり",$X29=""),1,0))</f>
+      <c r="AG29" s="18" t="n"/>
+      <c r="AH29" s="18" t="n"/>
+      <c r="AI29" s="20" t="n"/>
+      <c r="AJ29" s="12">
+        <f>IF($A29="","",IF(AK29&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK29">
+        <f>IF($A29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($N29="",1,0)+IF($T29="",1,0)+IF($U29="",1,0)+IF($V29="",1,0)+IF($AC29="",1,0)+IF(AND($N29="契約期間満了",$R29=""),1,0)+IF(AND($N29="契約期間満了",$S29=""),1,0)+IF(AND($AG29="外国",$AH29=""),1,0)+IF(AND($AG29="外国",$AI29=""),1,0)+IF(AND($AC29="未回収",$AD29=""),1,0)+IF(AND($V29="あり",$X29=""),1,0)+IF(AND($X29="ある",$Y29=""),1,0)+IF(AND($V29="あり",$Q29=""),1,0)+IF(AND($V29="あり",$Z29=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3166,21 +3239,23 @@
       <c r="V30" s="18" t="n"/>
       <c r="W30" s="18" t="n"/>
       <c r="X30" s="18" t="n"/>
-      <c r="Y30" s="48" t="n"/>
-      <c r="Z30" s="48" t="n"/>
-      <c r="AA30" s="18" t="n"/>
-      <c r="AB30" s="18" t="n"/>
+      <c r="Y30" s="20" t="n"/>
+      <c r="Z30" s="18" t="n"/>
+      <c r="AA30" s="48" t="n"/>
+      <c r="AB30" s="48" t="n"/>
       <c r="AC30" s="18" t="n"/>
       <c r="AD30" s="18" t="n"/>
       <c r="AE30" s="18" t="n"/>
       <c r="AF30" s="18" t="n"/>
-      <c r="AG30" s="20" t="n"/>
-      <c r="AH30" s="12">
-        <f>IF($A30="","",IF(AI30&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI30">
-        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($T30="",1,0)+IF($U30="",1,0)+IF($V30="",1,0)+IF($AA30="",1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0)+IF(AND($N30="契約期間満了",$S30=""),1,0)+IF(AND($AE30="外国",$AF30=""),1,0)+IF(AND($AE30="外国",$AG30=""),1,0)+IF(AND($AA30="未回収",$AB30=""),1,0)+IF(AND($V30="あり",$Q30=""),1,0)+IF(AND($V30="あり",$X30=""),1,0))</f>
+      <c r="AG30" s="18" t="n"/>
+      <c r="AH30" s="18" t="n"/>
+      <c r="AI30" s="20" t="n"/>
+      <c r="AJ30" s="12">
+        <f>IF($A30="","",IF(AK30&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK30">
+        <f>IF($A30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($N30="",1,0)+IF($T30="",1,0)+IF($U30="",1,0)+IF($V30="",1,0)+IF($AC30="",1,0)+IF(AND($N30="契約期間満了",$R30=""),1,0)+IF(AND($N30="契約期間満了",$S30=""),1,0)+IF(AND($AG30="外国",$AH30=""),1,0)+IF(AND($AG30="外国",$AI30=""),1,0)+IF(AND($AC30="未回収",$AD30=""),1,0)+IF(AND($V30="あり",$X30=""),1,0)+IF(AND($X30="ある",$Y30=""),1,0)+IF(AND($V30="あり",$Q30=""),1,0)+IF(AND($V30="あり",$Z30=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3212,21 +3287,23 @@
       <c r="V31" s="18" t="n"/>
       <c r="W31" s="18" t="n"/>
       <c r="X31" s="18" t="n"/>
-      <c r="Y31" s="48" t="n"/>
-      <c r="Z31" s="48" t="n"/>
-      <c r="AA31" s="18" t="n"/>
-      <c r="AB31" s="18" t="n"/>
+      <c r="Y31" s="20" t="n"/>
+      <c r="Z31" s="18" t="n"/>
+      <c r="AA31" s="48" t="n"/>
+      <c r="AB31" s="48" t="n"/>
       <c r="AC31" s="18" t="n"/>
       <c r="AD31" s="18" t="n"/>
       <c r="AE31" s="18" t="n"/>
       <c r="AF31" s="18" t="n"/>
-      <c r="AG31" s="20" t="n"/>
-      <c r="AH31" s="12">
-        <f>IF($A31="","",IF(AI31&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI31">
-        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($T31="",1,0)+IF($U31="",1,0)+IF($V31="",1,0)+IF($AA31="",1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0)+IF(AND($N31="契約期間満了",$S31=""),1,0)+IF(AND($AE31="外国",$AF31=""),1,0)+IF(AND($AE31="外国",$AG31=""),1,0)+IF(AND($AA31="未回収",$AB31=""),1,0)+IF(AND($V31="あり",$Q31=""),1,0)+IF(AND($V31="あり",$X31=""),1,0))</f>
+      <c r="AG31" s="18" t="n"/>
+      <c r="AH31" s="18" t="n"/>
+      <c r="AI31" s="20" t="n"/>
+      <c r="AJ31" s="12">
+        <f>IF($A31="","",IF(AK31&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK31">
+        <f>IF($A31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($N31="",1,0)+IF($T31="",1,0)+IF($U31="",1,0)+IF($V31="",1,0)+IF($AC31="",1,0)+IF(AND($N31="契約期間満了",$R31=""),1,0)+IF(AND($N31="契約期間満了",$S31=""),1,0)+IF(AND($AG31="外国",$AH31=""),1,0)+IF(AND($AG31="外国",$AI31=""),1,0)+IF(AND($AC31="未回収",$AD31=""),1,0)+IF(AND($V31="あり",$X31=""),1,0)+IF(AND($X31="ある",$Y31=""),1,0)+IF(AND($V31="あり",$Q31=""),1,0)+IF(AND($V31="あり",$Z31=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3258,21 +3335,23 @@
       <c r="V32" s="18" t="n"/>
       <c r="W32" s="18" t="n"/>
       <c r="X32" s="18" t="n"/>
-      <c r="Y32" s="48" t="n"/>
-      <c r="Z32" s="48" t="n"/>
-      <c r="AA32" s="18" t="n"/>
-      <c r="AB32" s="18" t="n"/>
+      <c r="Y32" s="20" t="n"/>
+      <c r="Z32" s="18" t="n"/>
+      <c r="AA32" s="48" t="n"/>
+      <c r="AB32" s="48" t="n"/>
       <c r="AC32" s="18" t="n"/>
       <c r="AD32" s="18" t="n"/>
       <c r="AE32" s="18" t="n"/>
       <c r="AF32" s="18" t="n"/>
-      <c r="AG32" s="20" t="n"/>
-      <c r="AH32" s="12">
-        <f>IF($A32="","",IF(AI32&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI32">
-        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($T32="",1,0)+IF($U32="",1,0)+IF($V32="",1,0)+IF($AA32="",1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0)+IF(AND($N32="契約期間満了",$S32=""),1,0)+IF(AND($AE32="外国",$AF32=""),1,0)+IF(AND($AE32="外国",$AG32=""),1,0)+IF(AND($AA32="未回収",$AB32=""),1,0)+IF(AND($V32="あり",$Q32=""),1,0)+IF(AND($V32="あり",$X32=""),1,0))</f>
+      <c r="AG32" s="18" t="n"/>
+      <c r="AH32" s="18" t="n"/>
+      <c r="AI32" s="20" t="n"/>
+      <c r="AJ32" s="12">
+        <f>IF($A32="","",IF(AK32&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK32">
+        <f>IF($A32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($N32="",1,0)+IF($T32="",1,0)+IF($U32="",1,0)+IF($V32="",1,0)+IF($AC32="",1,0)+IF(AND($N32="契約期間満了",$R32=""),1,0)+IF(AND($N32="契約期間満了",$S32=""),1,0)+IF(AND($AG32="外国",$AH32=""),1,0)+IF(AND($AG32="外国",$AI32=""),1,0)+IF(AND($AC32="未回収",$AD32=""),1,0)+IF(AND($V32="あり",$X32=""),1,0)+IF(AND($X32="ある",$Y32=""),1,0)+IF(AND($V32="あり",$Q32=""),1,0)+IF(AND($V32="あり",$Z32=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3304,21 +3383,23 @@
       <c r="V33" s="18" t="n"/>
       <c r="W33" s="18" t="n"/>
       <c r="X33" s="18" t="n"/>
-      <c r="Y33" s="48" t="n"/>
-      <c r="Z33" s="48" t="n"/>
-      <c r="AA33" s="18" t="n"/>
-      <c r="AB33" s="18" t="n"/>
+      <c r="Y33" s="20" t="n"/>
+      <c r="Z33" s="18" t="n"/>
+      <c r="AA33" s="48" t="n"/>
+      <c r="AB33" s="48" t="n"/>
       <c r="AC33" s="18" t="n"/>
       <c r="AD33" s="18" t="n"/>
       <c r="AE33" s="18" t="n"/>
       <c r="AF33" s="18" t="n"/>
-      <c r="AG33" s="20" t="n"/>
-      <c r="AH33" s="12">
-        <f>IF($A33="","",IF(AI33&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI33">
-        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($T33="",1,0)+IF($U33="",1,0)+IF($V33="",1,0)+IF($AA33="",1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0)+IF(AND($N33="契約期間満了",$S33=""),1,0)+IF(AND($AE33="外国",$AF33=""),1,0)+IF(AND($AE33="外国",$AG33=""),1,0)+IF(AND($AA33="未回収",$AB33=""),1,0)+IF(AND($V33="あり",$Q33=""),1,0)+IF(AND($V33="あり",$X33=""),1,0))</f>
+      <c r="AG33" s="18" t="n"/>
+      <c r="AH33" s="18" t="n"/>
+      <c r="AI33" s="20" t="n"/>
+      <c r="AJ33" s="12">
+        <f>IF($A33="","",IF(AK33&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK33">
+        <f>IF($A33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($N33="",1,0)+IF($T33="",1,0)+IF($U33="",1,0)+IF($V33="",1,0)+IF($AC33="",1,0)+IF(AND($N33="契約期間満了",$R33=""),1,0)+IF(AND($N33="契約期間満了",$S33=""),1,0)+IF(AND($AG33="外国",$AH33=""),1,0)+IF(AND($AG33="外国",$AI33=""),1,0)+IF(AND($AC33="未回収",$AD33=""),1,0)+IF(AND($V33="あり",$X33=""),1,0)+IF(AND($X33="ある",$Y33=""),1,0)+IF(AND($V33="あり",$Q33=""),1,0)+IF(AND($V33="あり",$Z33=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3350,21 +3431,23 @@
       <c r="V34" s="18" t="n"/>
       <c r="W34" s="18" t="n"/>
       <c r="X34" s="18" t="n"/>
-      <c r="Y34" s="48" t="n"/>
-      <c r="Z34" s="48" t="n"/>
-      <c r="AA34" s="18" t="n"/>
-      <c r="AB34" s="18" t="n"/>
+      <c r="Y34" s="20" t="n"/>
+      <c r="Z34" s="18" t="n"/>
+      <c r="AA34" s="48" t="n"/>
+      <c r="AB34" s="48" t="n"/>
       <c r="AC34" s="18" t="n"/>
       <c r="AD34" s="18" t="n"/>
       <c r="AE34" s="18" t="n"/>
       <c r="AF34" s="18" t="n"/>
-      <c r="AG34" s="20" t="n"/>
-      <c r="AH34" s="12">
-        <f>IF($A34="","",IF(AI34&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI34">
-        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($T34="",1,0)+IF($U34="",1,0)+IF($V34="",1,0)+IF($AA34="",1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0)+IF(AND($N34="契約期間満了",$S34=""),1,0)+IF(AND($AE34="外国",$AF34=""),1,0)+IF(AND($AE34="外国",$AG34=""),1,0)+IF(AND($AA34="未回収",$AB34=""),1,0)+IF(AND($V34="あり",$Q34=""),1,0)+IF(AND($V34="あり",$X34=""),1,0))</f>
+      <c r="AG34" s="18" t="n"/>
+      <c r="AH34" s="18" t="n"/>
+      <c r="AI34" s="20" t="n"/>
+      <c r="AJ34" s="12">
+        <f>IF($A34="","",IF(AK34&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK34">
+        <f>IF($A34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($N34="",1,0)+IF($T34="",1,0)+IF($U34="",1,0)+IF($V34="",1,0)+IF($AC34="",1,0)+IF(AND($N34="契約期間満了",$R34=""),1,0)+IF(AND($N34="契約期間満了",$S34=""),1,0)+IF(AND($AG34="外国",$AH34=""),1,0)+IF(AND($AG34="外国",$AI34=""),1,0)+IF(AND($AC34="未回収",$AD34=""),1,0)+IF(AND($V34="あり",$X34=""),1,0)+IF(AND($X34="ある",$Y34=""),1,0)+IF(AND($V34="あり",$Q34=""),1,0)+IF(AND($V34="あり",$Z34=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3396,21 +3479,23 @@
       <c r="V35" s="18" t="n"/>
       <c r="W35" s="18" t="n"/>
       <c r="X35" s="18" t="n"/>
-      <c r="Y35" s="48" t="n"/>
-      <c r="Z35" s="48" t="n"/>
-      <c r="AA35" s="18" t="n"/>
-      <c r="AB35" s="18" t="n"/>
+      <c r="Y35" s="20" t="n"/>
+      <c r="Z35" s="18" t="n"/>
+      <c r="AA35" s="48" t="n"/>
+      <c r="AB35" s="48" t="n"/>
       <c r="AC35" s="18" t="n"/>
       <c r="AD35" s="18" t="n"/>
       <c r="AE35" s="18" t="n"/>
       <c r="AF35" s="18" t="n"/>
-      <c r="AG35" s="20" t="n"/>
-      <c r="AH35" s="12">
-        <f>IF($A35="","",IF(AI35&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI35">
-        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($T35="",1,0)+IF($U35="",1,0)+IF($V35="",1,0)+IF($AA35="",1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0)+IF(AND($N35="契約期間満了",$S35=""),1,0)+IF(AND($AE35="外国",$AF35=""),1,0)+IF(AND($AE35="外国",$AG35=""),1,0)+IF(AND($AA35="未回収",$AB35=""),1,0)+IF(AND($V35="あり",$Q35=""),1,0)+IF(AND($V35="あり",$X35=""),1,0))</f>
+      <c r="AG35" s="18" t="n"/>
+      <c r="AH35" s="18" t="n"/>
+      <c r="AI35" s="20" t="n"/>
+      <c r="AJ35" s="12">
+        <f>IF($A35="","",IF(AK35&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK35">
+        <f>IF($A35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($N35="",1,0)+IF($T35="",1,0)+IF($U35="",1,0)+IF($V35="",1,0)+IF($AC35="",1,0)+IF(AND($N35="契約期間満了",$R35=""),1,0)+IF(AND($N35="契約期間満了",$S35=""),1,0)+IF(AND($AG35="外国",$AH35=""),1,0)+IF(AND($AG35="外国",$AI35=""),1,0)+IF(AND($AC35="未回収",$AD35=""),1,0)+IF(AND($V35="あり",$X35=""),1,0)+IF(AND($X35="ある",$Y35=""),1,0)+IF(AND($V35="あり",$Q35=""),1,0)+IF(AND($V35="あり",$Z35=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3442,21 +3527,23 @@
       <c r="V36" s="18" t="n"/>
       <c r="W36" s="18" t="n"/>
       <c r="X36" s="18" t="n"/>
-      <c r="Y36" s="48" t="n"/>
-      <c r="Z36" s="48" t="n"/>
-      <c r="AA36" s="18" t="n"/>
-      <c r="AB36" s="18" t="n"/>
+      <c r="Y36" s="20" t="n"/>
+      <c r="Z36" s="18" t="n"/>
+      <c r="AA36" s="48" t="n"/>
+      <c r="AB36" s="48" t="n"/>
       <c r="AC36" s="18" t="n"/>
       <c r="AD36" s="18" t="n"/>
       <c r="AE36" s="18" t="n"/>
       <c r="AF36" s="18" t="n"/>
-      <c r="AG36" s="20" t="n"/>
-      <c r="AH36" s="12">
-        <f>IF($A36="","",IF(AI36&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI36">
-        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($T36="",1,0)+IF($U36="",1,0)+IF($V36="",1,0)+IF($AA36="",1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0)+IF(AND($N36="契約期間満了",$S36=""),1,0)+IF(AND($AE36="外国",$AF36=""),1,0)+IF(AND($AE36="外国",$AG36=""),1,0)+IF(AND($AA36="未回収",$AB36=""),1,0)+IF(AND($V36="あり",$Q36=""),1,0)+IF(AND($V36="あり",$X36=""),1,0))</f>
+      <c r="AG36" s="18" t="n"/>
+      <c r="AH36" s="18" t="n"/>
+      <c r="AI36" s="20" t="n"/>
+      <c r="AJ36" s="12">
+        <f>IF($A36="","",IF(AK36&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK36">
+        <f>IF($A36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($N36="",1,0)+IF($T36="",1,0)+IF($U36="",1,0)+IF($V36="",1,0)+IF($AC36="",1,0)+IF(AND($N36="契約期間満了",$R36=""),1,0)+IF(AND($N36="契約期間満了",$S36=""),1,0)+IF(AND($AG36="外国",$AH36=""),1,0)+IF(AND($AG36="外国",$AI36=""),1,0)+IF(AND($AC36="未回収",$AD36=""),1,0)+IF(AND($V36="あり",$X36=""),1,0)+IF(AND($X36="ある",$Y36=""),1,0)+IF(AND($V36="あり",$Q36=""),1,0)+IF(AND($V36="あり",$Z36=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3488,21 +3575,23 @@
       <c r="V37" s="18" t="n"/>
       <c r="W37" s="18" t="n"/>
       <c r="X37" s="18" t="n"/>
-      <c r="Y37" s="48" t="n"/>
-      <c r="Z37" s="48" t="n"/>
-      <c r="AA37" s="18" t="n"/>
-      <c r="AB37" s="18" t="n"/>
+      <c r="Y37" s="20" t="n"/>
+      <c r="Z37" s="18" t="n"/>
+      <c r="AA37" s="48" t="n"/>
+      <c r="AB37" s="48" t="n"/>
       <c r="AC37" s="18" t="n"/>
       <c r="AD37" s="18" t="n"/>
       <c r="AE37" s="18" t="n"/>
       <c r="AF37" s="18" t="n"/>
-      <c r="AG37" s="20" t="n"/>
-      <c r="AH37" s="12">
-        <f>IF($A37="","",IF(AI37&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI37">
-        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($T37="",1,0)+IF($U37="",1,0)+IF($V37="",1,0)+IF($AA37="",1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0)+IF(AND($N37="契約期間満了",$S37=""),1,0)+IF(AND($AE37="外国",$AF37=""),1,0)+IF(AND($AE37="外国",$AG37=""),1,0)+IF(AND($AA37="未回収",$AB37=""),1,0)+IF(AND($V37="あり",$Q37=""),1,0)+IF(AND($V37="あり",$X37=""),1,0))</f>
+      <c r="AG37" s="18" t="n"/>
+      <c r="AH37" s="18" t="n"/>
+      <c r="AI37" s="20" t="n"/>
+      <c r="AJ37" s="12">
+        <f>IF($A37="","",IF(AK37&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK37">
+        <f>IF($A37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($N37="",1,0)+IF($T37="",1,0)+IF($U37="",1,0)+IF($V37="",1,0)+IF($AC37="",1,0)+IF(AND($N37="契約期間満了",$R37=""),1,0)+IF(AND($N37="契約期間満了",$S37=""),1,0)+IF(AND($AG37="外国",$AH37=""),1,0)+IF(AND($AG37="外国",$AI37=""),1,0)+IF(AND($AC37="未回収",$AD37=""),1,0)+IF(AND($V37="あり",$X37=""),1,0)+IF(AND($X37="ある",$Y37=""),1,0)+IF(AND($V37="あり",$Q37=""),1,0)+IF(AND($V37="あり",$Z37=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3534,21 +3623,23 @@
       <c r="V38" s="18" t="n"/>
       <c r="W38" s="18" t="n"/>
       <c r="X38" s="18" t="n"/>
-      <c r="Y38" s="48" t="n"/>
-      <c r="Z38" s="48" t="n"/>
-      <c r="AA38" s="18" t="n"/>
-      <c r="AB38" s="18" t="n"/>
+      <c r="Y38" s="20" t="n"/>
+      <c r="Z38" s="18" t="n"/>
+      <c r="AA38" s="48" t="n"/>
+      <c r="AB38" s="48" t="n"/>
       <c r="AC38" s="18" t="n"/>
       <c r="AD38" s="18" t="n"/>
       <c r="AE38" s="18" t="n"/>
       <c r="AF38" s="18" t="n"/>
-      <c r="AG38" s="20" t="n"/>
-      <c r="AH38" s="12">
-        <f>IF($A38="","",IF(AI38&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI38">
-        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($T38="",1,0)+IF($U38="",1,0)+IF($V38="",1,0)+IF($AA38="",1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0)+IF(AND($N38="契約期間満了",$S38=""),1,0)+IF(AND($AE38="外国",$AF38=""),1,0)+IF(AND($AE38="外国",$AG38=""),1,0)+IF(AND($AA38="未回収",$AB38=""),1,0)+IF(AND($V38="あり",$Q38=""),1,0)+IF(AND($V38="あり",$X38=""),1,0))</f>
+      <c r="AG38" s="18" t="n"/>
+      <c r="AH38" s="18" t="n"/>
+      <c r="AI38" s="20" t="n"/>
+      <c r="AJ38" s="12">
+        <f>IF($A38="","",IF(AK38&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK38">
+        <f>IF($A38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($N38="",1,0)+IF($T38="",1,0)+IF($U38="",1,0)+IF($V38="",1,0)+IF($AC38="",1,0)+IF(AND($N38="契約期間満了",$R38=""),1,0)+IF(AND($N38="契約期間満了",$S38=""),1,0)+IF(AND($AG38="外国",$AH38=""),1,0)+IF(AND($AG38="外国",$AI38=""),1,0)+IF(AND($AC38="未回収",$AD38=""),1,0)+IF(AND($V38="あり",$X38=""),1,0)+IF(AND($X38="ある",$Y38=""),1,0)+IF(AND($V38="あり",$Q38=""),1,0)+IF(AND($V38="あり",$Z38=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3580,21 +3671,23 @@
       <c r="V39" s="18" t="n"/>
       <c r="W39" s="18" t="n"/>
       <c r="X39" s="18" t="n"/>
-      <c r="Y39" s="48" t="n"/>
-      <c r="Z39" s="48" t="n"/>
-      <c r="AA39" s="18" t="n"/>
-      <c r="AB39" s="18" t="n"/>
+      <c r="Y39" s="20" t="n"/>
+      <c r="Z39" s="18" t="n"/>
+      <c r="AA39" s="48" t="n"/>
+      <c r="AB39" s="48" t="n"/>
       <c r="AC39" s="18" t="n"/>
       <c r="AD39" s="18" t="n"/>
       <c r="AE39" s="18" t="n"/>
       <c r="AF39" s="18" t="n"/>
-      <c r="AG39" s="20" t="n"/>
-      <c r="AH39" s="12">
-        <f>IF($A39="","",IF(AI39&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI39">
-        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($T39="",1,0)+IF($U39="",1,0)+IF($V39="",1,0)+IF($AA39="",1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0)+IF(AND($N39="契約期間満了",$S39=""),1,0)+IF(AND($AE39="外国",$AF39=""),1,0)+IF(AND($AE39="外国",$AG39=""),1,0)+IF(AND($AA39="未回収",$AB39=""),1,0)+IF(AND($V39="あり",$Q39=""),1,0)+IF(AND($V39="あり",$X39=""),1,0))</f>
+      <c r="AG39" s="18" t="n"/>
+      <c r="AH39" s="18" t="n"/>
+      <c r="AI39" s="20" t="n"/>
+      <c r="AJ39" s="12">
+        <f>IF($A39="","",IF(AK39&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK39">
+        <f>IF($A39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($N39="",1,0)+IF($T39="",1,0)+IF($U39="",1,0)+IF($V39="",1,0)+IF($AC39="",1,0)+IF(AND($N39="契約期間満了",$R39=""),1,0)+IF(AND($N39="契約期間満了",$S39=""),1,0)+IF(AND($AG39="外国",$AH39=""),1,0)+IF(AND($AG39="外国",$AI39=""),1,0)+IF(AND($AC39="未回収",$AD39=""),1,0)+IF(AND($V39="あり",$X39=""),1,0)+IF(AND($X39="ある",$Y39=""),1,0)+IF(AND($V39="あり",$Q39=""),1,0)+IF(AND($V39="あり",$Z39=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3626,21 +3719,23 @@
       <c r="V40" s="18" t="n"/>
       <c r="W40" s="18" t="n"/>
       <c r="X40" s="18" t="n"/>
-      <c r="Y40" s="48" t="n"/>
-      <c r="Z40" s="48" t="n"/>
-      <c r="AA40" s="18" t="n"/>
-      <c r="AB40" s="18" t="n"/>
+      <c r="Y40" s="20" t="n"/>
+      <c r="Z40" s="18" t="n"/>
+      <c r="AA40" s="48" t="n"/>
+      <c r="AB40" s="48" t="n"/>
       <c r="AC40" s="18" t="n"/>
       <c r="AD40" s="18" t="n"/>
       <c r="AE40" s="18" t="n"/>
       <c r="AF40" s="18" t="n"/>
-      <c r="AG40" s="20" t="n"/>
-      <c r="AH40" s="12">
-        <f>IF($A40="","",IF(AI40&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI40">
-        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($T40="",1,0)+IF($U40="",1,0)+IF($V40="",1,0)+IF($AA40="",1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0)+IF(AND($N40="契約期間満了",$S40=""),1,0)+IF(AND($AE40="外国",$AF40=""),1,0)+IF(AND($AE40="外国",$AG40=""),1,0)+IF(AND($AA40="未回収",$AB40=""),1,0)+IF(AND($V40="あり",$Q40=""),1,0)+IF(AND($V40="あり",$X40=""),1,0))</f>
+      <c r="AG40" s="18" t="n"/>
+      <c r="AH40" s="18" t="n"/>
+      <c r="AI40" s="20" t="n"/>
+      <c r="AJ40" s="12">
+        <f>IF($A40="","",IF(AK40&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK40">
+        <f>IF($A40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($N40="",1,0)+IF($T40="",1,0)+IF($U40="",1,0)+IF($V40="",1,0)+IF($AC40="",1,0)+IF(AND($N40="契約期間満了",$R40=""),1,0)+IF(AND($N40="契約期間満了",$S40=""),1,0)+IF(AND($AG40="外国",$AH40=""),1,0)+IF(AND($AG40="外国",$AI40=""),1,0)+IF(AND($AC40="未回収",$AD40=""),1,0)+IF(AND($V40="あり",$X40=""),1,0)+IF(AND($X40="ある",$Y40=""),1,0)+IF(AND($V40="あり",$Q40=""),1,0)+IF(AND($V40="あり",$Z40=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3672,21 +3767,23 @@
       <c r="V41" s="18" t="n"/>
       <c r="W41" s="18" t="n"/>
       <c r="X41" s="18" t="n"/>
-      <c r="Y41" s="48" t="n"/>
-      <c r="Z41" s="48" t="n"/>
-      <c r="AA41" s="18" t="n"/>
-      <c r="AB41" s="18" t="n"/>
+      <c r="Y41" s="20" t="n"/>
+      <c r="Z41" s="18" t="n"/>
+      <c r="AA41" s="48" t="n"/>
+      <c r="AB41" s="48" t="n"/>
       <c r="AC41" s="18" t="n"/>
       <c r="AD41" s="18" t="n"/>
       <c r="AE41" s="18" t="n"/>
       <c r="AF41" s="18" t="n"/>
-      <c r="AG41" s="20" t="n"/>
-      <c r="AH41" s="12">
-        <f>IF($A41="","",IF(AI41&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI41">
-        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($T41="",1,0)+IF($U41="",1,0)+IF($V41="",1,0)+IF($AA41="",1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0)+IF(AND($N41="契約期間満了",$S41=""),1,0)+IF(AND($AE41="外国",$AF41=""),1,0)+IF(AND($AE41="外国",$AG41=""),1,0)+IF(AND($AA41="未回収",$AB41=""),1,0)+IF(AND($V41="あり",$Q41=""),1,0)+IF(AND($V41="あり",$X41=""),1,0))</f>
+      <c r="AG41" s="18" t="n"/>
+      <c r="AH41" s="18" t="n"/>
+      <c r="AI41" s="20" t="n"/>
+      <c r="AJ41" s="12">
+        <f>IF($A41="","",IF(AK41&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK41">
+        <f>IF($A41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($N41="",1,0)+IF($T41="",1,0)+IF($U41="",1,0)+IF($V41="",1,0)+IF($AC41="",1,0)+IF(AND($N41="契約期間満了",$R41=""),1,0)+IF(AND($N41="契約期間満了",$S41=""),1,0)+IF(AND($AG41="外国",$AH41=""),1,0)+IF(AND($AG41="外国",$AI41=""),1,0)+IF(AND($AC41="未回収",$AD41=""),1,0)+IF(AND($V41="あり",$X41=""),1,0)+IF(AND($X41="ある",$Y41=""),1,0)+IF(AND($V41="あり",$Q41=""),1,0)+IF(AND($V41="あり",$Z41=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3718,21 +3815,23 @@
       <c r="V42" s="18" t="n"/>
       <c r="W42" s="18" t="n"/>
       <c r="X42" s="18" t="n"/>
-      <c r="Y42" s="48" t="n"/>
-      <c r="Z42" s="48" t="n"/>
-      <c r="AA42" s="18" t="n"/>
-      <c r="AB42" s="18" t="n"/>
+      <c r="Y42" s="20" t="n"/>
+      <c r="Z42" s="18" t="n"/>
+      <c r="AA42" s="48" t="n"/>
+      <c r="AB42" s="48" t="n"/>
       <c r="AC42" s="18" t="n"/>
       <c r="AD42" s="18" t="n"/>
       <c r="AE42" s="18" t="n"/>
       <c r="AF42" s="18" t="n"/>
-      <c r="AG42" s="20" t="n"/>
-      <c r="AH42" s="12">
-        <f>IF($A42="","",IF(AI42&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI42">
-        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($T42="",1,0)+IF($U42="",1,0)+IF($V42="",1,0)+IF($AA42="",1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0)+IF(AND($N42="契約期間満了",$S42=""),1,0)+IF(AND($AE42="外国",$AF42=""),1,0)+IF(AND($AE42="外国",$AG42=""),1,0)+IF(AND($AA42="未回収",$AB42=""),1,0)+IF(AND($V42="あり",$Q42=""),1,0)+IF(AND($V42="あり",$X42=""),1,0))</f>
+      <c r="AG42" s="18" t="n"/>
+      <c r="AH42" s="18" t="n"/>
+      <c r="AI42" s="20" t="n"/>
+      <c r="AJ42" s="12">
+        <f>IF($A42="","",IF(AK42&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK42">
+        <f>IF($A42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($N42="",1,0)+IF($T42="",1,0)+IF($U42="",1,0)+IF($V42="",1,0)+IF($AC42="",1,0)+IF(AND($N42="契約期間満了",$R42=""),1,0)+IF(AND($N42="契約期間満了",$S42=""),1,0)+IF(AND($AG42="外国",$AH42=""),1,0)+IF(AND($AG42="外国",$AI42=""),1,0)+IF(AND($AC42="未回収",$AD42=""),1,0)+IF(AND($V42="あり",$X42=""),1,0)+IF(AND($X42="ある",$Y42=""),1,0)+IF(AND($V42="あり",$Q42=""),1,0)+IF(AND($V42="あり",$Z42=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3764,21 +3863,23 @@
       <c r="V43" s="18" t="n"/>
       <c r="W43" s="18" t="n"/>
       <c r="X43" s="18" t="n"/>
-      <c r="Y43" s="48" t="n"/>
-      <c r="Z43" s="48" t="n"/>
-      <c r="AA43" s="18" t="n"/>
-      <c r="AB43" s="18" t="n"/>
+      <c r="Y43" s="20" t="n"/>
+      <c r="Z43" s="18" t="n"/>
+      <c r="AA43" s="48" t="n"/>
+      <c r="AB43" s="48" t="n"/>
       <c r="AC43" s="18" t="n"/>
       <c r="AD43" s="18" t="n"/>
       <c r="AE43" s="18" t="n"/>
       <c r="AF43" s="18" t="n"/>
-      <c r="AG43" s="20" t="n"/>
-      <c r="AH43" s="12">
-        <f>IF($A43="","",IF(AI43&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI43">
-        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($T43="",1,0)+IF($U43="",1,0)+IF($V43="",1,0)+IF($AA43="",1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0)+IF(AND($N43="契約期間満了",$S43=""),1,0)+IF(AND($AE43="外国",$AF43=""),1,0)+IF(AND($AE43="外国",$AG43=""),1,0)+IF(AND($AA43="未回収",$AB43=""),1,0)+IF(AND($V43="あり",$Q43=""),1,0)+IF(AND($V43="あり",$X43=""),1,0))</f>
+      <c r="AG43" s="18" t="n"/>
+      <c r="AH43" s="18" t="n"/>
+      <c r="AI43" s="20" t="n"/>
+      <c r="AJ43" s="12">
+        <f>IF($A43="","",IF(AK43&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK43">
+        <f>IF($A43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($N43="",1,0)+IF($T43="",1,0)+IF($U43="",1,0)+IF($V43="",1,0)+IF($AC43="",1,0)+IF(AND($N43="契約期間満了",$R43=""),1,0)+IF(AND($N43="契約期間満了",$S43=""),1,0)+IF(AND($AG43="外国",$AH43=""),1,0)+IF(AND($AG43="外国",$AI43=""),1,0)+IF(AND($AC43="未回収",$AD43=""),1,0)+IF(AND($V43="あり",$X43=""),1,0)+IF(AND($X43="ある",$Y43=""),1,0)+IF(AND($V43="あり",$Q43=""),1,0)+IF(AND($V43="あり",$Z43=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3810,21 +3911,23 @@
       <c r="V44" s="18" t="n"/>
       <c r="W44" s="18" t="n"/>
       <c r="X44" s="18" t="n"/>
-      <c r="Y44" s="48" t="n"/>
-      <c r="Z44" s="48" t="n"/>
-      <c r="AA44" s="18" t="n"/>
-      <c r="AB44" s="18" t="n"/>
+      <c r="Y44" s="20" t="n"/>
+      <c r="Z44" s="18" t="n"/>
+      <c r="AA44" s="48" t="n"/>
+      <c r="AB44" s="48" t="n"/>
       <c r="AC44" s="18" t="n"/>
       <c r="AD44" s="18" t="n"/>
       <c r="AE44" s="18" t="n"/>
       <c r="AF44" s="18" t="n"/>
-      <c r="AG44" s="20" t="n"/>
-      <c r="AH44" s="12">
-        <f>IF($A44="","",IF(AI44&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI44">
-        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($T44="",1,0)+IF($U44="",1,0)+IF($V44="",1,0)+IF($AA44="",1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0)+IF(AND($N44="契約期間満了",$S44=""),1,0)+IF(AND($AE44="外国",$AF44=""),1,0)+IF(AND($AE44="外国",$AG44=""),1,0)+IF(AND($AA44="未回収",$AB44=""),1,0)+IF(AND($V44="あり",$Q44=""),1,0)+IF(AND($V44="あり",$X44=""),1,0))</f>
+      <c r="AG44" s="18" t="n"/>
+      <c r="AH44" s="18" t="n"/>
+      <c r="AI44" s="20" t="n"/>
+      <c r="AJ44" s="12">
+        <f>IF($A44="","",IF(AK44&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK44">
+        <f>IF($A44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($N44="",1,0)+IF($T44="",1,0)+IF($U44="",1,0)+IF($V44="",1,0)+IF($AC44="",1,0)+IF(AND($N44="契約期間満了",$R44=""),1,0)+IF(AND($N44="契約期間満了",$S44=""),1,0)+IF(AND($AG44="外国",$AH44=""),1,0)+IF(AND($AG44="外国",$AI44=""),1,0)+IF(AND($AC44="未回収",$AD44=""),1,0)+IF(AND($V44="あり",$X44=""),1,0)+IF(AND($X44="ある",$Y44=""),1,0)+IF(AND($V44="あり",$Q44=""),1,0)+IF(AND($V44="あり",$Z44=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3856,21 +3959,23 @@
       <c r="V45" s="18" t="n"/>
       <c r="W45" s="18" t="n"/>
       <c r="X45" s="18" t="n"/>
-      <c r="Y45" s="48" t="n"/>
-      <c r="Z45" s="48" t="n"/>
-      <c r="AA45" s="18" t="n"/>
-      <c r="AB45" s="18" t="n"/>
+      <c r="Y45" s="20" t="n"/>
+      <c r="Z45" s="18" t="n"/>
+      <c r="AA45" s="48" t="n"/>
+      <c r="AB45" s="48" t="n"/>
       <c r="AC45" s="18" t="n"/>
       <c r="AD45" s="18" t="n"/>
       <c r="AE45" s="18" t="n"/>
       <c r="AF45" s="18" t="n"/>
-      <c r="AG45" s="20" t="n"/>
-      <c r="AH45" s="12">
-        <f>IF($A45="","",IF(AI45&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI45">
-        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($T45="",1,0)+IF($U45="",1,0)+IF($V45="",1,0)+IF($AA45="",1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0)+IF(AND($N45="契約期間満了",$S45=""),1,0)+IF(AND($AE45="外国",$AF45=""),1,0)+IF(AND($AE45="外国",$AG45=""),1,0)+IF(AND($AA45="未回収",$AB45=""),1,0)+IF(AND($V45="あり",$Q45=""),1,0)+IF(AND($V45="あり",$X45=""),1,0))</f>
+      <c r="AG45" s="18" t="n"/>
+      <c r="AH45" s="18" t="n"/>
+      <c r="AI45" s="20" t="n"/>
+      <c r="AJ45" s="12">
+        <f>IF($A45="","",IF(AK45&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK45">
+        <f>IF($A45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($N45="",1,0)+IF($T45="",1,0)+IF($U45="",1,0)+IF($V45="",1,0)+IF($AC45="",1,0)+IF(AND($N45="契約期間満了",$R45=""),1,0)+IF(AND($N45="契約期間満了",$S45=""),1,0)+IF(AND($AG45="外国",$AH45=""),1,0)+IF(AND($AG45="外国",$AI45=""),1,0)+IF(AND($AC45="未回収",$AD45=""),1,0)+IF(AND($V45="あり",$X45=""),1,0)+IF(AND($X45="ある",$Y45=""),1,0)+IF(AND($V45="あり",$Q45=""),1,0)+IF(AND($V45="あり",$Z45=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3902,21 +4007,23 @@
       <c r="V46" s="18" t="n"/>
       <c r="W46" s="18" t="n"/>
       <c r="X46" s="18" t="n"/>
-      <c r="Y46" s="48" t="n"/>
-      <c r="Z46" s="48" t="n"/>
-      <c r="AA46" s="18" t="n"/>
-      <c r="AB46" s="18" t="n"/>
+      <c r="Y46" s="20" t="n"/>
+      <c r="Z46" s="18" t="n"/>
+      <c r="AA46" s="48" t="n"/>
+      <c r="AB46" s="48" t="n"/>
       <c r="AC46" s="18" t="n"/>
       <c r="AD46" s="18" t="n"/>
       <c r="AE46" s="18" t="n"/>
       <c r="AF46" s="18" t="n"/>
-      <c r="AG46" s="20" t="n"/>
-      <c r="AH46" s="12">
-        <f>IF($A46="","",IF(AI46&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI46">
-        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($T46="",1,0)+IF($U46="",1,0)+IF($V46="",1,0)+IF($AA46="",1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0)+IF(AND($N46="契約期間満了",$S46=""),1,0)+IF(AND($AE46="外国",$AF46=""),1,0)+IF(AND($AE46="外国",$AG46=""),1,0)+IF(AND($AA46="未回収",$AB46=""),1,0)+IF(AND($V46="あり",$Q46=""),1,0)+IF(AND($V46="あり",$X46=""),1,0))</f>
+      <c r="AG46" s="18" t="n"/>
+      <c r="AH46" s="18" t="n"/>
+      <c r="AI46" s="20" t="n"/>
+      <c r="AJ46" s="12">
+        <f>IF($A46="","",IF(AK46&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK46">
+        <f>IF($A46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($N46="",1,0)+IF($T46="",1,0)+IF($U46="",1,0)+IF($V46="",1,0)+IF($AC46="",1,0)+IF(AND($N46="契約期間満了",$R46=""),1,0)+IF(AND($N46="契約期間満了",$S46=""),1,0)+IF(AND($AG46="外国",$AH46=""),1,0)+IF(AND($AG46="外国",$AI46=""),1,0)+IF(AND($AC46="未回収",$AD46=""),1,0)+IF(AND($V46="あり",$X46=""),1,0)+IF(AND($X46="ある",$Y46=""),1,0)+IF(AND($V46="あり",$Q46=""),1,0)+IF(AND($V46="あり",$Z46=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3948,21 +4055,23 @@
       <c r="V47" s="18" t="n"/>
       <c r="W47" s="18" t="n"/>
       <c r="X47" s="18" t="n"/>
-      <c r="Y47" s="48" t="n"/>
-      <c r="Z47" s="48" t="n"/>
-      <c r="AA47" s="18" t="n"/>
-      <c r="AB47" s="18" t="n"/>
+      <c r="Y47" s="20" t="n"/>
+      <c r="Z47" s="18" t="n"/>
+      <c r="AA47" s="48" t="n"/>
+      <c r="AB47" s="48" t="n"/>
       <c r="AC47" s="18" t="n"/>
       <c r="AD47" s="18" t="n"/>
       <c r="AE47" s="18" t="n"/>
       <c r="AF47" s="18" t="n"/>
-      <c r="AG47" s="20" t="n"/>
-      <c r="AH47" s="12">
-        <f>IF($A47="","",IF(AI47&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI47">
-        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($T47="",1,0)+IF($U47="",1,0)+IF($V47="",1,0)+IF($AA47="",1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0)+IF(AND($N47="契約期間満了",$S47=""),1,0)+IF(AND($AE47="外国",$AF47=""),1,0)+IF(AND($AE47="外国",$AG47=""),1,0)+IF(AND($AA47="未回収",$AB47=""),1,0)+IF(AND($V47="あり",$Q47=""),1,0)+IF(AND($V47="あり",$X47=""),1,0))</f>
+      <c r="AG47" s="18" t="n"/>
+      <c r="AH47" s="18" t="n"/>
+      <c r="AI47" s="20" t="n"/>
+      <c r="AJ47" s="12">
+        <f>IF($A47="","",IF(AK47&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK47">
+        <f>IF($A47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($N47="",1,0)+IF($T47="",1,0)+IF($U47="",1,0)+IF($V47="",1,0)+IF($AC47="",1,0)+IF(AND($N47="契約期間満了",$R47=""),1,0)+IF(AND($N47="契約期間満了",$S47=""),1,0)+IF(AND($AG47="外国",$AH47=""),1,0)+IF(AND($AG47="外国",$AI47=""),1,0)+IF(AND($AC47="未回収",$AD47=""),1,0)+IF(AND($V47="あり",$X47=""),1,0)+IF(AND($X47="ある",$Y47=""),1,0)+IF(AND($V47="あり",$Q47=""),1,0)+IF(AND($V47="あり",$Z47=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3994,21 +4103,23 @@
       <c r="V48" s="18" t="n"/>
       <c r="W48" s="18" t="n"/>
       <c r="X48" s="18" t="n"/>
-      <c r="Y48" s="48" t="n"/>
-      <c r="Z48" s="48" t="n"/>
-      <c r="AA48" s="18" t="n"/>
-      <c r="AB48" s="18" t="n"/>
+      <c r="Y48" s="20" t="n"/>
+      <c r="Z48" s="18" t="n"/>
+      <c r="AA48" s="48" t="n"/>
+      <c r="AB48" s="48" t="n"/>
       <c r="AC48" s="18" t="n"/>
       <c r="AD48" s="18" t="n"/>
       <c r="AE48" s="18" t="n"/>
       <c r="AF48" s="18" t="n"/>
-      <c r="AG48" s="20" t="n"/>
-      <c r="AH48" s="12">
-        <f>IF($A48="","",IF(AI48&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI48">
-        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($T48="",1,0)+IF($U48="",1,0)+IF($V48="",1,0)+IF($AA48="",1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0)+IF(AND($N48="契約期間満了",$S48=""),1,0)+IF(AND($AE48="外国",$AF48=""),1,0)+IF(AND($AE48="外国",$AG48=""),1,0)+IF(AND($AA48="未回収",$AB48=""),1,0)+IF(AND($V48="あり",$Q48=""),1,0)+IF(AND($V48="あり",$X48=""),1,0))</f>
+      <c r="AG48" s="18" t="n"/>
+      <c r="AH48" s="18" t="n"/>
+      <c r="AI48" s="20" t="n"/>
+      <c r="AJ48" s="12">
+        <f>IF($A48="","",IF(AK48&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK48">
+        <f>IF($A48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($N48="",1,0)+IF($T48="",1,0)+IF($U48="",1,0)+IF($V48="",1,0)+IF($AC48="",1,0)+IF(AND($N48="契約期間満了",$R48=""),1,0)+IF(AND($N48="契約期間満了",$S48=""),1,0)+IF(AND($AG48="外国",$AH48=""),1,0)+IF(AND($AG48="外国",$AI48=""),1,0)+IF(AND($AC48="未回収",$AD48=""),1,0)+IF(AND($V48="あり",$X48=""),1,0)+IF(AND($X48="ある",$Y48=""),1,0)+IF(AND($V48="あり",$Q48=""),1,0)+IF(AND($V48="あり",$Z48=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4040,21 +4151,23 @@
       <c r="V49" s="18" t="n"/>
       <c r="W49" s="18" t="n"/>
       <c r="X49" s="18" t="n"/>
-      <c r="Y49" s="48" t="n"/>
-      <c r="Z49" s="48" t="n"/>
-      <c r="AA49" s="18" t="n"/>
-      <c r="AB49" s="18" t="n"/>
+      <c r="Y49" s="20" t="n"/>
+      <c r="Z49" s="18" t="n"/>
+      <c r="AA49" s="48" t="n"/>
+      <c r="AB49" s="48" t="n"/>
       <c r="AC49" s="18" t="n"/>
       <c r="AD49" s="18" t="n"/>
       <c r="AE49" s="18" t="n"/>
       <c r="AF49" s="18" t="n"/>
-      <c r="AG49" s="20" t="n"/>
-      <c r="AH49" s="12">
-        <f>IF($A49="","",IF(AI49&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI49">
-        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($T49="",1,0)+IF($U49="",1,0)+IF($V49="",1,0)+IF($AA49="",1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0)+IF(AND($N49="契約期間満了",$S49=""),1,0)+IF(AND($AE49="外国",$AF49=""),1,0)+IF(AND($AE49="外国",$AG49=""),1,0)+IF(AND($AA49="未回収",$AB49=""),1,0)+IF(AND($V49="あり",$Q49=""),1,0)+IF(AND($V49="あり",$X49=""),1,0))</f>
+      <c r="AG49" s="18" t="n"/>
+      <c r="AH49" s="18" t="n"/>
+      <c r="AI49" s="20" t="n"/>
+      <c r="AJ49" s="12">
+        <f>IF($A49="","",IF(AK49&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK49">
+        <f>IF($A49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($N49="",1,0)+IF($T49="",1,0)+IF($U49="",1,0)+IF($V49="",1,0)+IF($AC49="",1,0)+IF(AND($N49="契約期間満了",$R49=""),1,0)+IF(AND($N49="契約期間満了",$S49=""),1,0)+IF(AND($AG49="外国",$AH49=""),1,0)+IF(AND($AG49="外国",$AI49=""),1,0)+IF(AND($AC49="未回収",$AD49=""),1,0)+IF(AND($V49="あり",$X49=""),1,0)+IF(AND($X49="ある",$Y49=""),1,0)+IF(AND($V49="あり",$Q49=""),1,0)+IF(AND($V49="あり",$Z49=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4086,21 +4199,23 @@
       <c r="V50" s="18" t="n"/>
       <c r="W50" s="18" t="n"/>
       <c r="X50" s="18" t="n"/>
-      <c r="Y50" s="48" t="n"/>
-      <c r="Z50" s="48" t="n"/>
-      <c r="AA50" s="18" t="n"/>
-      <c r="AB50" s="18" t="n"/>
+      <c r="Y50" s="20" t="n"/>
+      <c r="Z50" s="18" t="n"/>
+      <c r="AA50" s="48" t="n"/>
+      <c r="AB50" s="48" t="n"/>
       <c r="AC50" s="18" t="n"/>
       <c r="AD50" s="18" t="n"/>
       <c r="AE50" s="18" t="n"/>
       <c r="AF50" s="18" t="n"/>
-      <c r="AG50" s="20" t="n"/>
-      <c r="AH50" s="12">
-        <f>IF($A50="","",IF(AI50&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI50">
-        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($T50="",1,0)+IF($U50="",1,0)+IF($V50="",1,0)+IF($AA50="",1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0)+IF(AND($N50="契約期間満了",$S50=""),1,0)+IF(AND($AE50="外国",$AF50=""),1,0)+IF(AND($AE50="外国",$AG50=""),1,0)+IF(AND($AA50="未回収",$AB50=""),1,0)+IF(AND($V50="あり",$Q50=""),1,0)+IF(AND($V50="あり",$X50=""),1,0))</f>
+      <c r="AG50" s="18" t="n"/>
+      <c r="AH50" s="18" t="n"/>
+      <c r="AI50" s="20" t="n"/>
+      <c r="AJ50" s="12">
+        <f>IF($A50="","",IF(AK50&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK50">
+        <f>IF($A50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($N50="",1,0)+IF($T50="",1,0)+IF($U50="",1,0)+IF($V50="",1,0)+IF($AC50="",1,0)+IF(AND($N50="契約期間満了",$R50=""),1,0)+IF(AND($N50="契約期間満了",$S50=""),1,0)+IF(AND($AG50="外国",$AH50=""),1,0)+IF(AND($AG50="外国",$AI50=""),1,0)+IF(AND($AC50="未回収",$AD50=""),1,0)+IF(AND($V50="あり",$X50=""),1,0)+IF(AND($X50="ある",$Y50=""),1,0)+IF(AND($V50="あり",$Q50=""),1,0)+IF(AND($V50="あり",$Z50=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4132,21 +4247,23 @@
       <c r="V51" s="18" t="n"/>
       <c r="W51" s="18" t="n"/>
       <c r="X51" s="18" t="n"/>
-      <c r="Y51" s="48" t="n"/>
-      <c r="Z51" s="48" t="n"/>
-      <c r="AA51" s="18" t="n"/>
-      <c r="AB51" s="18" t="n"/>
+      <c r="Y51" s="20" t="n"/>
+      <c r="Z51" s="18" t="n"/>
+      <c r="AA51" s="48" t="n"/>
+      <c r="AB51" s="48" t="n"/>
       <c r="AC51" s="18" t="n"/>
       <c r="AD51" s="18" t="n"/>
       <c r="AE51" s="18" t="n"/>
       <c r="AF51" s="18" t="n"/>
-      <c r="AG51" s="20" t="n"/>
-      <c r="AH51" s="12">
-        <f>IF($A51="","",IF(AI51&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI51">
-        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($T51="",1,0)+IF($U51="",1,0)+IF($V51="",1,0)+IF($AA51="",1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0)+IF(AND($N51="契約期間満了",$S51=""),1,0)+IF(AND($AE51="外国",$AF51=""),1,0)+IF(AND($AE51="外国",$AG51=""),1,0)+IF(AND($AA51="未回収",$AB51=""),1,0)+IF(AND($V51="あり",$Q51=""),1,0)+IF(AND($V51="あり",$X51=""),1,0))</f>
+      <c r="AG51" s="18" t="n"/>
+      <c r="AH51" s="18" t="n"/>
+      <c r="AI51" s="20" t="n"/>
+      <c r="AJ51" s="12">
+        <f>IF($A51="","",IF(AK51&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK51">
+        <f>IF($A51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($N51="",1,0)+IF($T51="",1,0)+IF($U51="",1,0)+IF($V51="",1,0)+IF($AC51="",1,0)+IF(AND($N51="契約期間満了",$R51=""),1,0)+IF(AND($N51="契約期間満了",$S51=""),1,0)+IF(AND($AG51="外国",$AH51=""),1,0)+IF(AND($AG51="外国",$AI51=""),1,0)+IF(AND($AC51="未回収",$AD51=""),1,0)+IF(AND($V51="あり",$X51=""),1,0)+IF(AND($X51="ある",$Y51=""),1,0)+IF(AND($V51="あり",$Q51=""),1,0)+IF(AND($V51="あり",$Z51=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4178,21 +4295,23 @@
       <c r="V52" s="18" t="n"/>
       <c r="W52" s="18" t="n"/>
       <c r="X52" s="18" t="n"/>
-      <c r="Y52" s="48" t="n"/>
-      <c r="Z52" s="48" t="n"/>
-      <c r="AA52" s="18" t="n"/>
-      <c r="AB52" s="18" t="n"/>
+      <c r="Y52" s="20" t="n"/>
+      <c r="Z52" s="18" t="n"/>
+      <c r="AA52" s="48" t="n"/>
+      <c r="AB52" s="48" t="n"/>
       <c r="AC52" s="18" t="n"/>
       <c r="AD52" s="18" t="n"/>
       <c r="AE52" s="18" t="n"/>
       <c r="AF52" s="18" t="n"/>
-      <c r="AG52" s="20" t="n"/>
-      <c r="AH52" s="12">
-        <f>IF($A52="","",IF(AI52&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI52">
-        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($T52="",1,0)+IF($U52="",1,0)+IF($V52="",1,0)+IF($AA52="",1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0)+IF(AND($N52="契約期間満了",$S52=""),1,0)+IF(AND($AE52="外国",$AF52=""),1,0)+IF(AND($AE52="外国",$AG52=""),1,0)+IF(AND($AA52="未回収",$AB52=""),1,0)+IF(AND($V52="あり",$Q52=""),1,0)+IF(AND($V52="あり",$X52=""),1,0))</f>
+      <c r="AG52" s="18" t="n"/>
+      <c r="AH52" s="18" t="n"/>
+      <c r="AI52" s="20" t="n"/>
+      <c r="AJ52" s="12">
+        <f>IF($A52="","",IF(AK52&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK52">
+        <f>IF($A52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($N52="",1,0)+IF($T52="",1,0)+IF($U52="",1,0)+IF($V52="",1,0)+IF($AC52="",1,0)+IF(AND($N52="契約期間満了",$R52=""),1,0)+IF(AND($N52="契約期間満了",$S52=""),1,0)+IF(AND($AG52="外国",$AH52=""),1,0)+IF(AND($AG52="外国",$AI52=""),1,0)+IF(AND($AC52="未回収",$AD52=""),1,0)+IF(AND($V52="あり",$X52=""),1,0)+IF(AND($X52="ある",$Y52=""),1,0)+IF(AND($V52="あり",$Q52=""),1,0)+IF(AND($V52="あり",$Z52=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4224,21 +4343,23 @@
       <c r="V53" s="18" t="n"/>
       <c r="W53" s="18" t="n"/>
       <c r="X53" s="18" t="n"/>
-      <c r="Y53" s="48" t="n"/>
-      <c r="Z53" s="48" t="n"/>
-      <c r="AA53" s="18" t="n"/>
-      <c r="AB53" s="18" t="n"/>
+      <c r="Y53" s="20" t="n"/>
+      <c r="Z53" s="18" t="n"/>
+      <c r="AA53" s="48" t="n"/>
+      <c r="AB53" s="48" t="n"/>
       <c r="AC53" s="18" t="n"/>
       <c r="AD53" s="18" t="n"/>
       <c r="AE53" s="18" t="n"/>
       <c r="AF53" s="18" t="n"/>
-      <c r="AG53" s="20" t="n"/>
-      <c r="AH53" s="12">
-        <f>IF($A53="","",IF(AI53&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI53">
-        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($T53="",1,0)+IF($U53="",1,0)+IF($V53="",1,0)+IF($AA53="",1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0)+IF(AND($N53="契約期間満了",$S53=""),1,0)+IF(AND($AE53="外国",$AF53=""),1,0)+IF(AND($AE53="外国",$AG53=""),1,0)+IF(AND($AA53="未回収",$AB53=""),1,0)+IF(AND($V53="あり",$Q53=""),1,0)+IF(AND($V53="あり",$X53=""),1,0))</f>
+      <c r="AG53" s="18" t="n"/>
+      <c r="AH53" s="18" t="n"/>
+      <c r="AI53" s="20" t="n"/>
+      <c r="AJ53" s="12">
+        <f>IF($A53="","",IF(AK53&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK53">
+        <f>IF($A53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($N53="",1,0)+IF($T53="",1,0)+IF($U53="",1,0)+IF($V53="",1,0)+IF($AC53="",1,0)+IF(AND($N53="契約期間満了",$R53=""),1,0)+IF(AND($N53="契約期間満了",$S53=""),1,0)+IF(AND($AG53="外国",$AH53=""),1,0)+IF(AND($AG53="外国",$AI53=""),1,0)+IF(AND($AC53="未回収",$AD53=""),1,0)+IF(AND($V53="あり",$X53=""),1,0)+IF(AND($X53="ある",$Y53=""),1,0)+IF(AND($V53="あり",$Q53=""),1,0)+IF(AND($V53="あり",$Z53=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4270,21 +4391,23 @@
       <c r="V54" s="18" t="n"/>
       <c r="W54" s="18" t="n"/>
       <c r="X54" s="18" t="n"/>
-      <c r="Y54" s="48" t="n"/>
-      <c r="Z54" s="48" t="n"/>
-      <c r="AA54" s="18" t="n"/>
-      <c r="AB54" s="18" t="n"/>
+      <c r="Y54" s="20" t="n"/>
+      <c r="Z54" s="18" t="n"/>
+      <c r="AA54" s="48" t="n"/>
+      <c r="AB54" s="48" t="n"/>
       <c r="AC54" s="18" t="n"/>
       <c r="AD54" s="18" t="n"/>
       <c r="AE54" s="18" t="n"/>
       <c r="AF54" s="18" t="n"/>
-      <c r="AG54" s="20" t="n"/>
-      <c r="AH54" s="12">
-        <f>IF($A54="","",IF(AI54&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI54">
-        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($T54="",1,0)+IF($U54="",1,0)+IF($V54="",1,0)+IF($AA54="",1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0)+IF(AND($N54="契約期間満了",$S54=""),1,0)+IF(AND($AE54="外国",$AF54=""),1,0)+IF(AND($AE54="外国",$AG54=""),1,0)+IF(AND($AA54="未回収",$AB54=""),1,0)+IF(AND($V54="あり",$Q54=""),1,0)+IF(AND($V54="あり",$X54=""),1,0))</f>
+      <c r="AG54" s="18" t="n"/>
+      <c r="AH54" s="18" t="n"/>
+      <c r="AI54" s="20" t="n"/>
+      <c r="AJ54" s="12">
+        <f>IF($A54="","",IF(AK54&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK54">
+        <f>IF($A54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($N54="",1,0)+IF($T54="",1,0)+IF($U54="",1,0)+IF($V54="",1,0)+IF($AC54="",1,0)+IF(AND($N54="契約期間満了",$R54=""),1,0)+IF(AND($N54="契約期間満了",$S54=""),1,0)+IF(AND($AG54="外国",$AH54=""),1,0)+IF(AND($AG54="外国",$AI54=""),1,0)+IF(AND($AC54="未回収",$AD54=""),1,0)+IF(AND($V54="あり",$X54=""),1,0)+IF(AND($X54="ある",$Y54=""),1,0)+IF(AND($V54="あり",$Q54=""),1,0)+IF(AND($V54="あり",$Z54=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4316,21 +4439,23 @@
       <c r="V55" s="18" t="n"/>
       <c r="W55" s="18" t="n"/>
       <c r="X55" s="18" t="n"/>
-      <c r="Y55" s="48" t="n"/>
-      <c r="Z55" s="48" t="n"/>
-      <c r="AA55" s="18" t="n"/>
-      <c r="AB55" s="18" t="n"/>
+      <c r="Y55" s="20" t="n"/>
+      <c r="Z55" s="18" t="n"/>
+      <c r="AA55" s="48" t="n"/>
+      <c r="AB55" s="48" t="n"/>
       <c r="AC55" s="18" t="n"/>
       <c r="AD55" s="18" t="n"/>
       <c r="AE55" s="18" t="n"/>
       <c r="AF55" s="18" t="n"/>
-      <c r="AG55" s="20" t="n"/>
-      <c r="AH55" s="12">
-        <f>IF($A55="","",IF(AI55&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI55">
-        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($T55="",1,0)+IF($U55="",1,0)+IF($V55="",1,0)+IF($AA55="",1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0)+IF(AND($N55="契約期間満了",$S55=""),1,0)+IF(AND($AE55="外国",$AF55=""),1,0)+IF(AND($AE55="外国",$AG55=""),1,0)+IF(AND($AA55="未回収",$AB55=""),1,0)+IF(AND($V55="あり",$Q55=""),1,0)+IF(AND($V55="あり",$X55=""),1,0))</f>
+      <c r="AG55" s="18" t="n"/>
+      <c r="AH55" s="18" t="n"/>
+      <c r="AI55" s="20" t="n"/>
+      <c r="AJ55" s="12">
+        <f>IF($A55="","",IF(AK55&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK55">
+        <f>IF($A55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($N55="",1,0)+IF($T55="",1,0)+IF($U55="",1,0)+IF($V55="",1,0)+IF($AC55="",1,0)+IF(AND($N55="契約期間満了",$R55=""),1,0)+IF(AND($N55="契約期間満了",$S55=""),1,0)+IF(AND($AG55="外国",$AH55=""),1,0)+IF(AND($AG55="外国",$AI55=""),1,0)+IF(AND($AC55="未回収",$AD55=""),1,0)+IF(AND($V55="あり",$X55=""),1,0)+IF(AND($X55="ある",$Y55=""),1,0)+IF(AND($V55="あり",$Q55=""),1,0)+IF(AND($V55="あり",$Z55=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4362,21 +4487,23 @@
       <c r="V56" s="18" t="n"/>
       <c r="W56" s="18" t="n"/>
       <c r="X56" s="18" t="n"/>
-      <c r="Y56" s="48" t="n"/>
-      <c r="Z56" s="48" t="n"/>
-      <c r="AA56" s="18" t="n"/>
-      <c r="AB56" s="18" t="n"/>
+      <c r="Y56" s="20" t="n"/>
+      <c r="Z56" s="18" t="n"/>
+      <c r="AA56" s="48" t="n"/>
+      <c r="AB56" s="48" t="n"/>
       <c r="AC56" s="18" t="n"/>
       <c r="AD56" s="18" t="n"/>
       <c r="AE56" s="18" t="n"/>
       <c r="AF56" s="18" t="n"/>
-      <c r="AG56" s="20" t="n"/>
-      <c r="AH56" s="12">
-        <f>IF($A56="","",IF(AI56&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI56">
-        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($T56="",1,0)+IF($U56="",1,0)+IF($V56="",1,0)+IF($AA56="",1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0)+IF(AND($N56="契約期間満了",$S56=""),1,0)+IF(AND($AE56="外国",$AF56=""),1,0)+IF(AND($AE56="外国",$AG56=""),1,0)+IF(AND($AA56="未回収",$AB56=""),1,0)+IF(AND($V56="あり",$Q56=""),1,0)+IF(AND($V56="あり",$X56=""),1,0))</f>
+      <c r="AG56" s="18" t="n"/>
+      <c r="AH56" s="18" t="n"/>
+      <c r="AI56" s="20" t="n"/>
+      <c r="AJ56" s="12">
+        <f>IF($A56="","",IF(AK56&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK56">
+        <f>IF($A56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($N56="",1,0)+IF($T56="",1,0)+IF($U56="",1,0)+IF($V56="",1,0)+IF($AC56="",1,0)+IF(AND($N56="契約期間満了",$R56=""),1,0)+IF(AND($N56="契約期間満了",$S56=""),1,0)+IF(AND($AG56="外国",$AH56=""),1,0)+IF(AND($AG56="外国",$AI56=""),1,0)+IF(AND($AC56="未回収",$AD56=""),1,0)+IF(AND($V56="あり",$X56=""),1,0)+IF(AND($X56="ある",$Y56=""),1,0)+IF(AND($V56="あり",$Q56=""),1,0)+IF(AND($V56="あり",$Z56=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4408,21 +4535,23 @@
       <c r="V57" s="18" t="n"/>
       <c r="W57" s="18" t="n"/>
       <c r="X57" s="18" t="n"/>
-      <c r="Y57" s="48" t="n"/>
-      <c r="Z57" s="48" t="n"/>
-      <c r="AA57" s="18" t="n"/>
-      <c r="AB57" s="18" t="n"/>
+      <c r="Y57" s="20" t="n"/>
+      <c r="Z57" s="18" t="n"/>
+      <c r="AA57" s="48" t="n"/>
+      <c r="AB57" s="48" t="n"/>
       <c r="AC57" s="18" t="n"/>
       <c r="AD57" s="18" t="n"/>
       <c r="AE57" s="18" t="n"/>
       <c r="AF57" s="18" t="n"/>
-      <c r="AG57" s="20" t="n"/>
-      <c r="AH57" s="12">
-        <f>IF($A57="","",IF(AI57&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI57">
-        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($T57="",1,0)+IF($U57="",1,0)+IF($V57="",1,0)+IF($AA57="",1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0)+IF(AND($N57="契約期間満了",$S57=""),1,0)+IF(AND($AE57="外国",$AF57=""),1,0)+IF(AND($AE57="外国",$AG57=""),1,0)+IF(AND($AA57="未回収",$AB57=""),1,0)+IF(AND($V57="あり",$Q57=""),1,0)+IF(AND($V57="あり",$X57=""),1,0))</f>
+      <c r="AG57" s="18" t="n"/>
+      <c r="AH57" s="18" t="n"/>
+      <c r="AI57" s="20" t="n"/>
+      <c r="AJ57" s="12">
+        <f>IF($A57="","",IF(AK57&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK57">
+        <f>IF($A57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($N57="",1,0)+IF($T57="",1,0)+IF($U57="",1,0)+IF($V57="",1,0)+IF($AC57="",1,0)+IF(AND($N57="契約期間満了",$R57=""),1,0)+IF(AND($N57="契約期間満了",$S57=""),1,0)+IF(AND($AG57="外国",$AH57=""),1,0)+IF(AND($AG57="外国",$AI57=""),1,0)+IF(AND($AC57="未回収",$AD57=""),1,0)+IF(AND($V57="あり",$X57=""),1,0)+IF(AND($X57="ある",$Y57=""),1,0)+IF(AND($V57="あり",$Q57=""),1,0)+IF(AND($V57="あり",$Z57=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4454,21 +4583,23 @@
       <c r="V58" s="18" t="n"/>
       <c r="W58" s="18" t="n"/>
       <c r="X58" s="18" t="n"/>
-      <c r="Y58" s="48" t="n"/>
-      <c r="Z58" s="48" t="n"/>
-      <c r="AA58" s="18" t="n"/>
-      <c r="AB58" s="18" t="n"/>
+      <c r="Y58" s="20" t="n"/>
+      <c r="Z58" s="18" t="n"/>
+      <c r="AA58" s="48" t="n"/>
+      <c r="AB58" s="48" t="n"/>
       <c r="AC58" s="18" t="n"/>
       <c r="AD58" s="18" t="n"/>
       <c r="AE58" s="18" t="n"/>
       <c r="AF58" s="18" t="n"/>
-      <c r="AG58" s="20" t="n"/>
-      <c r="AH58" s="12">
-        <f>IF($A58="","",IF(AI58&gt;0,"未入力","CSV可"))</f>
-        <v/>
-      </c>
-      <c r="AI58">
-        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($T58="",1,0)+IF($U58="",1,0)+IF($V58="",1,0)+IF($AA58="",1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0)+IF(AND($N58="契約期間満了",$S58=""),1,0)+IF(AND($AE58="外国",$AF58=""),1,0)+IF(AND($AE58="外国",$AG58=""),1,0)+IF(AND($AA58="未回収",$AB58=""),1,0)+IF(AND($V58="あり",$Q58=""),1,0)+IF(AND($V58="あり",$X58=""),1,0))</f>
+      <c r="AG58" s="18" t="n"/>
+      <c r="AH58" s="18" t="n"/>
+      <c r="AI58" s="20" t="n"/>
+      <c r="AJ58" s="12">
+        <f>IF($A58="","",IF(AK58&gt;0,"未入力","CSV可"))</f>
+        <v/>
+      </c>
+      <c r="AK58">
+        <f>IF($A58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($N58="",1,0)+IF($T58="",1,0)+IF($U58="",1,0)+IF($V58="",1,0)+IF($AC58="",1,0)+IF(AND($N58="契約期間満了",$R58=""),1,0)+IF(AND($N58="契約期間満了",$S58=""),1,0)+IF(AND($AG58="外国",$AH58=""),1,0)+IF(AND($AG58="外国",$AI58=""),1,0)+IF(AND($AC58="未回収",$AD58=""),1,0)+IF(AND($V58="あり",$X58=""),1,0)+IF(AND($X58="ある",$Y58=""),1,0)+IF(AND($V58="あり",$Q58=""),1,0)+IF(AND($V58="あり",$Z58=""),1,0))</f>
         <v/>
       </c>
     </row>
@@ -4477,18 +4608,18 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="R1:AI1"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="AE6:AG6"/>
-    <mergeCell ref="AD6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="T6:AB6"/>
+    <mergeCell ref="AF6"/>
     <mergeCell ref="L6:S6"/>
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="AG6:AI6"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="T6:Z6"/>
-    <mergeCell ref="AA6:AC6"/>
-    <mergeCell ref="Q1:AG1"/>
+    <mergeCell ref="AC6:AE6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
@@ -4516,10 +4647,10 @@
     <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",B9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",LENB(B9)&lt;&gt;LEN(B9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
       <formula>AND(B9&lt;&gt;"",ISERROR(FIND("　",B9)),ISERROR(FIND(" ",B9)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4527,7 +4658,7 @@
     <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",C9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(C9),C9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4535,10 +4666,10 @@
     <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",D9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LEN(D9)&lt;&gt;12)</formula>
     </cfRule>
-    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
       <formula>AND(D9&lt;&gt;"",D9&lt;&gt;"後日提出",D9&lt;&gt;"別経路提出",LENB(D9)&lt;&gt;LEN(D9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4546,10 +4677,10 @@
     <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",E9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LEN(E9)&lt;&gt;10)</formula>
     </cfRule>
-    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
       <formula>AND(E9&lt;&gt;"",E9&lt;&gt;"後日提出",LENB(E9)&lt;&gt;LEN(E9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4557,10 +4688,10 @@
     <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",F9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LEN(F9)&lt;&gt;11)</formula>
     </cfRule>
-    <cfRule type="expression" priority="45" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="49" dxfId="1" stopIfTrue="1">
       <formula>AND(F9&lt;&gt;"",F9&lt;&gt;"後日提出",F9&lt;&gt;"なし",LENB(F9)&lt;&gt;LEN(F9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4568,10 +4699,10 @@
     <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",G9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="37" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LEN(SUBSTITUTE(G9,"-",""))&lt;&gt;7)</formula>
     </cfRule>
-    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
       <formula>AND(G9&lt;&gt;"",LENB(G9)&lt;&gt;LEN(G9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4584,7 +4715,7 @@
     <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",I9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
       <formula>AND(I9&lt;&gt;"",LENB(I9)&lt;&gt;LEN(I9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4592,7 +4723,7 @@
     <cfRule type="expression" priority="13" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",L9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="54" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(L9),L9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4605,7 +4736,7 @@
     <cfRule type="expression" priority="15" dxfId="2" stopIfTrue="1">
       <formula>AND($A9&lt;&gt;"",T9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="56" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(T9),T9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4619,19 +4750,19 @@
       <formula>AND($A9&lt;&gt;"",V9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA9:AA58">
+  <conditionalFormatting sqref="AC9:AC58">
     <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
-      <formula>AND($A9&lt;&gt;"",AA9="")</formula>
+      <formula>AND($A9&lt;&gt;"",AC9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A58">
     <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
       <formula>AND($A9="",OR($L9&lt;&gt;"",$N9&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",LENB(A9)&lt;&gt;LEN(A9)*2)</formula>
     </cfRule>
-    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="43" dxfId="1" stopIfTrue="1">
       <formula>AND(A9&lt;&gt;"",ISERROR(FIND("　",A9)),ISERROR(FIND(" ",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4639,7 +4770,7 @@
     <cfRule type="expression" priority="20" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",R9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="27" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="29" dxfId="3" stopIfTrue="1">
       <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),R9="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4647,77 +4778,96 @@
     <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
       <formula>AND($N9="契約期間満了",S9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="30" dxfId="3" stopIfTrue="1">
       <formula>AND($N9&lt;&gt;"",NOT($N9="契約期間満了"),S9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF9:AF58">
+  <conditionalFormatting sqref="AH9:AH58">
     <cfRule type="expression" priority="22" dxfId="2" stopIfTrue="1">
-      <formula>AND($AE9="外国",AF9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="29" dxfId="3" stopIfTrue="1">
-      <formula>AND($AE9&lt;&gt;"",NOT($AE9="外国"),AF9="")</formula>
+      <formula>AND($AG9="外国",AH9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="31" dxfId="3" stopIfTrue="1">
+      <formula>AND($AG9&lt;&gt;"",NOT($AG9="外国"),AH9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG9:AG58">
+  <conditionalFormatting sqref="AI9:AI58">
     <cfRule type="expression" priority="23" dxfId="2" stopIfTrue="1">
-      <formula>AND($AE9="外国",AG9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="30" dxfId="3" stopIfTrue="1">
-      <formula>AND($AE9&lt;&gt;"",NOT($AE9="外国"),AG9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="53" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(AG9),AG9&gt;80000)</formula>
+      <formula>AND($AG9="外国",AI9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="3" stopIfTrue="1">
+      <formula>AND($AG9&lt;&gt;"",NOT($AG9="外国"),AI9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="58" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AI9),AI9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB9:AB58">
+  <conditionalFormatting sqref="AD9:AD58">
     <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
-      <formula>AND($AA9="未回収",AB9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="31" dxfId="3" stopIfTrue="1">
-      <formula>AND($AA9&lt;&gt;"",NOT($AA9="未回収"),AB9="")</formula>
+      <formula>AND($AC9="未回収",AD9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="33" dxfId="3" stopIfTrue="1">
+      <formula>AND($AC9&lt;&gt;"",NOT($AC9="未回収"),AD9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X9:X58">
+    <cfRule type="expression" priority="25" dxfId="2" stopIfTrue="1">
+      <formula>AND($V9="あり",X9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="34" dxfId="3" stopIfTrue="1">
+      <formula>AND($V9&lt;&gt;"",NOT($V9="あり"),X9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y9:Y58">
+    <cfRule type="expression" priority="26" dxfId="2" stopIfTrue="1">
+      <formula>AND($X9="ある",Y9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="3" stopIfTrue="1">
+      <formula>AND($X9&lt;&gt;"",NOT($X9="ある"),Y9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="57" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(Y9),Y9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q9:Q58">
-    <cfRule type="expression" priority="25" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="27" dxfId="2" stopIfTrue="1">
       <formula>AND($V9="あり",Q9="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="36" dxfId="3" stopIfTrue="1">
       <formula>AND($V9&lt;&gt;"",NOT($V9="あり"),Q9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X9:X58">
-    <cfRule type="expression" priority="26" dxfId="2" stopIfTrue="1">
-      <formula>AND($V9="あり",X9="")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="33" dxfId="3" stopIfTrue="1">
-      <formula>AND($V9&lt;&gt;"",NOT($V9="あり"),X9="")</formula>
+  <conditionalFormatting sqref="Z9:Z58">
+    <cfRule type="expression" priority="28" dxfId="2" stopIfTrue="1">
+      <formula>AND($V9="あり",Z9="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="37" dxfId="3" stopIfTrue="1">
+      <formula>AND($V9&lt;&gt;"",NOT($V9="あり"),Z9="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J58">
-    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
       <formula>AND(J9&lt;&gt;"",LENB(J9)&lt;&gt;LEN(J9)*2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K58">
-    <cfRule type="expression" priority="49" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="53" dxfId="1" stopIfTrue="1">
       <formula>AND(K9&lt;&gt;"",LENB(K9)&lt;&gt;LEN(K9))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P58">
-    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="55" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(P9),P9&gt;80000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH9:AH58">
-    <cfRule type="expression" priority="54" dxfId="0" stopIfTrue="1">
-      <formula>AH9="CSV可"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="55" dxfId="1" stopIfTrue="1">
-      <formula>AH9="未入力"</formula>
+  <conditionalFormatting sqref="AJ9:AJ58">
+    <cfRule type="expression" priority="59" dxfId="0" stopIfTrue="1">
+      <formula>AJ9="CSV可"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60" dxfId="1" stopIfTrue="1">
+      <formula>AJ9="未入力"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="21">
+  <dataValidations count="23">
     <dataValidation sqref="C8:C58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦の生年月日。例 1990/4/1。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
@@ -4769,24 +4919,31 @@
     <dataValidation sqref="V8:V58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人が離職票（基本手当の申請）を希望するか。" type="list" errorStyle="stop">
       <formula1>m_ありなし</formula1>
     </dataValidation>
-    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="X8:X58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="離職票の賃金欄と未計算欄の書き方が変わります。" type="list" errorStyle="stop">
+      <formula1>m_退職後給与</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y8:Y58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="『ある』のとき、その給与の支払日。" type="whole" errorStyle="warning" operator="between">
+      <formula1>1</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="直近1か月の賃金総額（参考）。詳細は台帳で。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="Z8:Z58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="AB8:AB58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="退職前直近の賞与額（参考）。" type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000000</formula2>
     </dataValidation>
-    <dataValidation sqref="AA8:AA58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
+    <dataValidation sqref="AC8:AC58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="本人・被扶養者分の資格確認書・高齢受給者証・限度額適用認定証などの回収状況。" type="list" errorStyle="stop">
       <formula1>m_回収状況</formula1>
     </dataValidation>
-    <dataValidation sqref="AC8:AC58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="分かれば。任意継続を希望される方には手続きのご案内をお送りします。空欄で構いません。" type="list" errorStyle="stop">
+    <dataValidation sqref="AE8:AE58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="分かれば。任意継続を希望される方には手続きのご案内をお送りします。空欄で構いません。" type="list" errorStyle="stop">
       <formula1>m_退職後</formula1>
     </dataValidation>
-    <dataValidation sqref="AE8:AE58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="日本国籍の方は『日本』。外国籍の方は『外国』を選び、右の2欄もご記入ください。" type="list" errorStyle="stop">
+    <dataValidation sqref="AG8:AG58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="日本国籍の方は『日本』。外国籍の方は『外国』を選び、右の2欄もご記入ください。" type="list" errorStyle="stop">
       <formula1>m_国籍</formula1>
     </dataValidation>
-    <dataValidation sqref="AG8:AG58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="在留カードの『在留期間（満了日）』。西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
+    <dataValidation sqref="AI8:AI58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="在留カードの『在留期間（満了日）』。西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
@@ -4804,7 +4961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4823,6 +4980,7 @@
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.5" customHeight="1">
@@ -4906,6 +5064,11 @@
           <t>国籍</t>
         </is>
       </c>
+      <c r="Q1" s="49" t="inlineStr">
+        <is>
+          <t>退職後給与</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="50" t="inlineStr">
@@ -4988,6 +5151,11 @@
           <t>日本</t>
         </is>
       </c>
+      <c r="Q2" s="50" t="inlineStr">
+        <is>
+          <t>ない</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
@@ -5063,6 +5231,11 @@
       <c r="P3" s="50" t="inlineStr">
         <is>
           <t>外国</t>
+        </is>
+      </c>
+      <c r="Q3" s="50" t="inlineStr">
+        <is>
+          <t>ある</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5798,7 +5971,7 @@
     <row r="18">
       <c r="A18" s="50" t="inlineStr">
         <is>
-          <t>AG</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B18" s="50" t="inlineStr">
@@ -5808,10 +5981,30 @@
       </c>
       <c r="C18" s="50" t="inlineStr">
         <is>
+          <t>その支払日</t>
+        </is>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="50" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
           <t>在留期間の満了日【外国籍のとき必須】</t>
         </is>
       </c>
-      <c r="D18" s="50" t="n">
+      <c r="D19" s="50" t="n">
         <v>0</v>
       </c>
     </row>
